--- a/Module 2/Week 8 - CAPM and investment styles/Homework 2 example.xlsx
+++ b/Module 2/Week 8 - CAPM and investment styles/Homework 2 example.xlsx
@@ -208,14 +208,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm"/>
-    <numFmt numFmtId="167" formatCode="General"/>
-    <numFmt numFmtId="168" formatCode="0.00000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,19 +267,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -349,12 +335,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -366,8 +352,12 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -386,23 +376,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -410,23 +400,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3519,9 +3493,9 @@
   <dimension ref="A1:N205"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="8.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="18.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="17.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3534,22 +3508,22 @@
       <c r="C1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="9" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3565,26 +3539,26 @@
         <f aca="false">Data!C2-Data!D2</f>
         <v>0.102204</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="5" t="n">
         <f aca="false">0.2*C2+0.8*B2</f>
         <v>-0.0293635063263042</v>
       </c>
       <c r="G2" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B2 + 'Optimal portfolio from homework'!$C$15*C2</f>
-        <v>-0.00192070391019506</v>
+        <v>-0.00192070391019516</v>
       </c>
       <c r="I2" s="9" t="n">
         <f aca="false">0.5*C2+0.5*B2</f>
         <v>0.0199743085460599</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="10" t="n">
+      <c r="M2" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B2</f>
         <v>0.00138621198753918</v>
       </c>
-      <c r="N2" s="10" t="n">
+      <c r="N2" s="8" t="n">
         <f aca="false">C2-M2</f>
         <v>0.100817788012461</v>
       </c>
@@ -3601,23 +3575,23 @@
         <f aca="false">Data!C3-Data!D3</f>
         <v>0.047685</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="5" t="n">
         <f aca="false">0.2*C3+0.8*B3</f>
         <v>-0.0175146517083923</v>
       </c>
       <c r="G3" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B3 + 'Optimal portfolio from homework'!$C$15*C3</f>
-        <v>-0.00391508438821414</v>
+        <v>-0.00391508438821417</v>
       </c>
       <c r="I3" s="9" t="n">
         <f aca="false">0.5*C3+0.5*B3</f>
         <v>0.00693521768225479</v>
       </c>
-      <c r="M3" s="10" t="n">
+      <c r="M3" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B3</f>
         <v>0.0031906115420036</v>
       </c>
-      <c r="N3" s="10" t="n">
+      <c r="N3" s="8" t="n">
         <f aca="false">C3-M3</f>
         <v>0.0444943884579964</v>
       </c>
@@ -3634,7 +3608,7 @@
         <f aca="false">Data!C4-Data!D4</f>
         <v>-0.034466</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="5" t="n">
         <f aca="false">0.2*C4+0.8*B4</f>
         <v>-0.0117771817801592</v>
       </c>
@@ -3646,11 +3620,11 @@
         <f aca="false">0.5*C4+0.5*B4</f>
         <v>-0.0202854886125995</v>
       </c>
-      <c r="M4" s="10" t="n">
+      <c r="M4" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B4</f>
         <v>0.00494861887845431</v>
       </c>
-      <c r="N4" s="10" t="n">
+      <c r="N4" s="8" t="n">
         <f aca="false">C4-M4</f>
         <v>-0.0394146188784543</v>
       </c>
@@ -3667,23 +3641,23 @@
         <f aca="false">Data!C5-Data!D5</f>
         <v>-0.075953</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="5" t="n">
         <f aca="false">0.2*C5+0.8*B5</f>
         <v>0.0222030755646817</v>
       </c>
       <c r="G5" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B5 + 'Optimal portfolio from homework'!$C$15*C5</f>
-        <v>0.00172934414819064</v>
+        <v>0.00172934414819069</v>
       </c>
       <c r="I5" s="9" t="n">
         <f aca="false">0.5*C5+0.5*B5</f>
         <v>-0.0146054527720739</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B5</f>
         <v>0.00830144901444975</v>
       </c>
-      <c r="N5" s="10" t="n">
+      <c r="N5" s="8" t="n">
         <f aca="false">C5-M5</f>
         <v>-0.0842544490144497</v>
       </c>
@@ -3700,7 +3674,7 @@
         <f aca="false">Data!C6-Data!D6</f>
         <v>0.011741</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="5" t="n">
         <f aca="false">0.2*C6+0.8*B6</f>
         <v>0.0112481655334483</v>
       </c>
@@ -3712,11 +3686,11 @@
         <f aca="false">0.5*C6+0.5*B6</f>
         <v>0.0114329784584052</v>
       </c>
-      <c r="M6" s="10" t="n">
+      <c r="M6" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B6</f>
         <v>0.00604175498978325</v>
       </c>
-      <c r="N6" s="10" t="n">
+      <c r="N6" s="8" t="n">
         <f aca="false">C6-M6</f>
         <v>0.00569924501021675</v>
       </c>
@@ -3733,23 +3707,23 @@
         <f aca="false">Data!C7-Data!D7</f>
         <v>0.058846</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="5" t="n">
         <f aca="false">0.2*C7+0.8*B7</f>
         <v>-0.0570961711194138</v>
       </c>
       <c r="G7" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B7 + 'Optimal portfolio from homework'!$C$15*C7</f>
-        <v>-0.0329125547952314</v>
+        <v>-0.0329125547952315</v>
       </c>
       <c r="I7" s="9" t="n">
         <f aca="false">0.5*C7+0.5*B7</f>
         <v>-0.0136178569496336</v>
       </c>
-      <c r="M7" s="10" t="n">
+      <c r="M7" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B7</f>
         <v>-0.000125425990441131</v>
       </c>
-      <c r="N7" s="10" t="n">
+      <c r="N7" s="8" t="n">
         <f aca="false">C7-M7</f>
         <v>0.0589714259904411</v>
       </c>
@@ -3766,23 +3740,23 @@
         <f aca="false">Data!C8-Data!D8</f>
         <v>-0.023746</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="5" t="n">
         <f aca="false">0.2*C8+0.8*B8</f>
         <v>-0.0126028535687007</v>
       </c>
       <c r="G8" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B8 + 'Optimal portfolio from homework'!$C$15*C8</f>
-        <v>-0.0149271293290811</v>
+        <v>-0.014927129329081</v>
       </c>
       <c r="I8" s="9" t="n">
         <f aca="false">0.5*C8+0.5*B8</f>
         <v>-0.0167815334804379</v>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="M8" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B8</f>
         <v>0.00471310902071968</v>
       </c>
-      <c r="N8" s="10" t="n">
+      <c r="N8" s="8" t="n">
         <f aca="false">C8-M8</f>
         <v>-0.0284591090207197</v>
       </c>
@@ -3799,7 +3773,7 @@
         <f aca="false">Data!C9-Data!D9</f>
         <v>-0.084085</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="5" t="n">
         <f aca="false">0.2*C9+0.8*B9</f>
         <v>-0.00628661061189545</v>
       </c>
@@ -3811,11 +3785,11 @@
         <f aca="false">0.5*C9+0.5*B9</f>
         <v>-0.0354610066324347</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B9</f>
         <v>0.00617105577364053</v>
       </c>
-      <c r="N9" s="10" t="n">
+      <c r="N9" s="8" t="n">
         <f aca="false">C9-M9</f>
         <v>-0.0902560557736405</v>
       </c>
@@ -3832,23 +3806,23 @@
         <f aca="false">Data!C10-Data!D10</f>
         <v>0.070825</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="5" t="n">
         <f aca="false">0.2*C10+0.8*B10</f>
         <v>-0.0582835687393802</v>
       </c>
       <c r="G10" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B10 + 'Optimal portfolio from homework'!$C$15*C10</f>
-        <v>-0.03135365997183</v>
+        <v>-0.0313536599718301</v>
       </c>
       <c r="I10" s="9" t="n">
         <f aca="false">0.5*C10+0.5*B10</f>
         <v>-0.00986785546211265</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B10</f>
         <v>-0.000409591521786886</v>
       </c>
-      <c r="N10" s="10" t="n">
+      <c r="N10" s="8" t="n">
         <f aca="false">C10-M10</f>
         <v>0.0712345915217869</v>
       </c>
@@ -3865,7 +3839,7 @@
         <f aca="false">Data!C11-Data!D11</f>
         <v>-0.188648</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="5" t="n">
         <f aca="false">0.2*C11+0.8*B11</f>
         <v>-0.172708800894104</v>
       </c>
@@ -3877,11 +3851,11 @@
         <f aca="false">0.5*C11+0.5*B11</f>
         <v>-0.178686000558815</v>
       </c>
-      <c r="M11" s="10" t="n">
+      <c r="M11" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B11</f>
         <v>-0.00536858407431034</v>
       </c>
-      <c r="N11" s="10" t="n">
+      <c r="N11" s="8" t="n">
         <f aca="false">C11-M11</f>
         <v>-0.18327941592569</v>
       </c>
@@ -3898,23 +3872,23 @@
         <f aca="false">Data!C12-Data!D12</f>
         <v>0.116378</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="5" t="n">
         <f aca="false">0.2*C12+0.8*B12</f>
         <v>-0.0343631015894336</v>
       </c>
       <c r="G12" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B12 + 'Optimal portfolio from homework'!$C$15*C12</f>
-        <v>-0.00292100481026557</v>
+        <v>-0.00292100481026564</v>
       </c>
       <c r="I12" s="9" t="n">
         <f aca="false">0.5*C12+0.5*B12</f>
         <v>0.022164811506604</v>
       </c>
-      <c r="M12" s="10" t="n">
+      <c r="M12" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B12</f>
         <v>0.000764905174787745</v>
       </c>
-      <c r="N12" s="10" t="n">
+      <c r="N12" s="8" t="n">
         <f aca="false">C12-M12</f>
         <v>0.115613094825212</v>
       </c>
@@ -3931,7 +3905,7 @@
         <f aca="false">Data!C13-Data!D13</f>
         <v>0.063307</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="5" t="n">
         <f aca="false">0.2*C13+0.8*B13</f>
         <v>0.0211982697395808</v>
       </c>
@@ -3943,11 +3917,11 @@
         <f aca="false">0.5*C13+0.5*B13</f>
         <v>0.036989043587238</v>
       </c>
-      <c r="M13" s="10" t="n">
+      <c r="M13" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B13</f>
         <v>0.00601295967338238</v>
       </c>
-      <c r="N13" s="10" t="n">
+      <c r="N13" s="8" t="n">
         <f aca="false">C13-M13</f>
         <v>0.0572940403266176</v>
       </c>
@@ -3964,7 +3938,7 @@
         <f aca="false">Data!C14-Data!D14</f>
         <v>0.06185</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="5" t="n">
         <f aca="false">0.2*C14+0.8*B14</f>
         <v>-0.0549305175111326</v>
       </c>
@@ -3976,11 +3950,11 @@
         <f aca="false">0.5*C14+0.5*B14</f>
         <v>-0.0111378234444579</v>
       </c>
-      <c r="M14" s="10" t="n">
+      <c r="M14" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B14</f>
         <v>-1.32525577952423E-006</v>
       </c>
-      <c r="N14" s="10" t="n">
+      <c r="N14" s="8" t="n">
         <f aca="false">C14-M14</f>
         <v>0.0618513252557795</v>
       </c>
@@ -3997,23 +3971,23 @@
         <f aca="false">Data!C15-Data!D15</f>
         <v>0.02739</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="5" t="n">
         <f aca="false">0.2*C15+0.8*B15</f>
         <v>-0.0798582417871222</v>
       </c>
       <c r="G15" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B15 + 'Optimal portfolio from homework'!$C$15*C15</f>
-        <v>-0.0574880351075215</v>
+        <v>-0.0574880351075217</v>
       </c>
       <c r="I15" s="9" t="n">
         <f aca="false">0.5*C15+0.5*B15</f>
         <v>-0.0396401511169514</v>
       </c>
-      <c r="M15" s="10" t="n">
+      <c r="M15" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B15</f>
         <v>-0.00143164859143193</v>
       </c>
-      <c r="N15" s="10" t="n">
+      <c r="N15" s="8" t="n">
         <f aca="false">C15-M15</f>
         <v>0.0288216485914319</v>
       </c>
@@ -4030,7 +4004,7 @@
         <f aca="false">Data!C16-Data!D16</f>
         <v>-0.026955</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="5" t="n">
         <f aca="false">0.2*C16+0.8*B16</f>
         <v>0.064529353828283</v>
       </c>
@@ -4042,11 +4016,11 @@
         <f aca="false">0.5*C16+0.5*B16</f>
         <v>0.0302227211426769</v>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="M16" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B16</f>
         <v>0.0108809776344133</v>
       </c>
-      <c r="N16" s="10" t="n">
+      <c r="N16" s="8" t="n">
         <f aca="false">C16-M16</f>
         <v>-0.0378359776344133</v>
       </c>
@@ -4063,7 +4037,7 @@
         <f aca="false">Data!C17-Data!D17</f>
         <v>-0.032218</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="5" t="n">
         <f aca="false">0.2*C17+0.8*B17</f>
         <v>0.069946988235294</v>
       </c>
@@ -4075,11 +4049,11 @@
         <f aca="false">0.5*C17+0.5*B17</f>
         <v>0.0316351176470588</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B17</f>
         <v>0.0113940996536831</v>
       </c>
-      <c r="N17" s="10" t="n">
+      <c r="N17" s="8" t="n">
         <f aca="false">C17-M17</f>
         <v>-0.0436120996536831</v>
       </c>
@@ -4096,7 +4070,7 @@
         <f aca="false">Data!C18-Data!D18</f>
         <v>0.093363</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18" s="5" t="n">
         <f aca="false">0.2*C18+0.8*B18</f>
         <v>0.0636141858811832</v>
       </c>
@@ -4108,11 +4082,11 @@
         <f aca="false">0.5*C18+0.5*B18</f>
         <v>0.0747699911757395</v>
       </c>
-      <c r="M18" s="10" t="n">
+      <c r="M18" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B18</f>
         <v>0.00890003613498342</v>
       </c>
-      <c r="N18" s="10" t="n">
+      <c r="N18" s="8" t="n">
         <f aca="false">C18-M18</f>
         <v>0.0844629638650166</v>
       </c>
@@ -4129,7 +4103,7 @@
         <f aca="false">Data!C19-Data!D19</f>
         <v>-0.031993</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19" s="5" t="n">
         <f aca="false">0.2*C19+0.8*B19</f>
         <v>-0.00471891871904122</v>
       </c>
@@ -4141,11 +4115,11 @@
         <f aca="false">0.5*C19+0.5*B19</f>
         <v>-0.0149466991994008</v>
       </c>
-      <c r="M19" s="10" t="n">
+      <c r="M19" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B19</f>
         <v>0.00546915025828778</v>
       </c>
-      <c r="N19" s="10" t="n">
+      <c r="N19" s="8" t="n">
         <f aca="false">C19-M19</f>
         <v>-0.0374621502582878</v>
       </c>
@@ -4162,23 +4136,23 @@
         <f aca="false">Data!C20-Data!D20</f>
         <v>-0.004882</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20" s="5" t="n">
         <f aca="false">0.2*C20+0.8*B20</f>
         <v>0.0595668294617564</v>
       </c>
       <c r="G20" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B20 + 'Optimal portfolio from homework'!$C$15*C20</f>
-        <v>0.0461238712249255</v>
+        <v>0.0461238712249256</v>
       </c>
       <c r="I20" s="9" t="n">
         <f aca="false">0.5*C20+0.5*B20</f>
         <v>0.0353985184135978</v>
       </c>
-      <c r="M20" s="10" t="n">
+      <c r="M20" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B20</f>
         <v>0.0101373246711324</v>
       </c>
-      <c r="N20" s="10" t="n">
+      <c r="N20" s="8" t="n">
         <f aca="false">C20-M20</f>
         <v>-0.0150193246711324</v>
       </c>
@@ -4195,7 +4169,7 @@
         <f aca="false">Data!C21-Data!D21</f>
         <v>0.015116</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="E21" s="5" t="n">
         <f aca="false">0.2*C21+0.8*B21</f>
         <v>0.0317340711871845</v>
       </c>
@@ -4207,11 +4181,11 @@
         <f aca="false">0.5*C21+0.5*B21</f>
         <v>0.0255022944919903</v>
       </c>
-      <c r="M21" s="10" t="n">
+      <c r="M21" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B21</f>
         <v>0.00761285910644298</v>
       </c>
-      <c r="N21" s="10" t="n">
+      <c r="N21" s="8" t="n">
         <f aca="false">C21-M21</f>
         <v>0.00750314089355702</v>
       </c>
@@ -4228,7 +4202,7 @@
         <f aca="false">Data!C22-Data!D22</f>
         <v>0.053016</v>
       </c>
-      <c r="E22" s="0" t="n">
+      <c r="E22" s="5" t="n">
         <f aca="false">0.2*C22+0.8*B22</f>
         <v>0.0402575167397658</v>
       </c>
@@ -4240,11 +4214,11 @@
         <f aca="false">0.5*C22+0.5*B22</f>
         <v>0.0450419479623536</v>
       </c>
-      <c r="M22" s="10" t="n">
+      <c r="M22" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B22</f>
         <v>0.00768767906760035</v>
       </c>
-      <c r="N22" s="10" t="n">
+      <c r="N22" s="8" t="n">
         <f aca="false">C22-M22</f>
         <v>0.0453283209323996</v>
       </c>
@@ -4261,23 +4235,23 @@
         <f aca="false">Data!C23-Data!D23</f>
         <v>0.043196</v>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="E23" s="5" t="n">
         <f aca="false">0.2*C23+0.8*B23</f>
         <v>-0.00630179538224738</v>
       </c>
       <c r="G23" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B23 + 'Optimal portfolio from homework'!$C$15*C23</f>
-        <v>0.00402262480809288</v>
+        <v>0.00402262480809286</v>
       </c>
       <c r="I23" s="9" t="n">
         <f aca="false">0.5*C23+0.5*B23</f>
         <v>0.0122598778860954</v>
       </c>
-      <c r="M23" s="10" t="n">
+      <c r="M23" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B23</f>
         <v>0.00415104729098054</v>
       </c>
-      <c r="N23" s="10" t="n">
+      <c r="N23" s="8" t="n">
         <f aca="false">C23-M23</f>
         <v>0.0390449527090195</v>
       </c>
@@ -4294,7 +4268,7 @@
         <f aca="false">Data!C24-Data!D24</f>
         <v>0.122068</v>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="E24" s="5" t="n">
         <f aca="false">0.2*C24+0.8*B24</f>
         <v>0.0722646927533201</v>
       </c>
@@ -4306,11 +4280,11 @@
         <f aca="false">0.5*C24+0.5*B24</f>
         <v>0.090940932970825</v>
       </c>
-      <c r="M24" s="10" t="n">
+      <c r="M24" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B24</f>
         <v>0.0091307746132822</v>
       </c>
-      <c r="N24" s="10" t="n">
+      <c r="N24" s="8" t="n">
         <f aca="false">C24-M24</f>
         <v>0.112937225386718</v>
       </c>
@@ -4327,23 +4301,23 @@
         <f aca="false">Data!C25-Data!D25</f>
         <v>-0.05812</v>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="E25" s="5" t="n">
         <f aca="false">0.2*C25+0.8*B25</f>
         <v>0.00385999111940632</v>
       </c>
       <c r="G25" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B25 + 'Optimal portfolio from homework'!$C$15*C25</f>
-        <v>-0.00906800833528887</v>
+        <v>-0.00906800833528884</v>
       </c>
       <c r="I25" s="9" t="n">
         <f aca="false">0.5*C25+0.5*B25</f>
         <v>-0.0193825055503711</v>
       </c>
-      <c r="M25" s="10" t="n">
+      <c r="M25" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B25</f>
         <v>0.00656390121989973</v>
       </c>
-      <c r="N25" s="10" t="n">
+      <c r="N25" s="8" t="n">
         <f aca="false">C25-M25</f>
         <v>-0.0646839012198997</v>
       </c>
@@ -4360,7 +4334,7 @@
         <f aca="false">Data!C26-Data!D26</f>
         <v>-0.019248</v>
       </c>
-      <c r="E26" s="0" t="n">
+      <c r="E26" s="5" t="n">
         <f aca="false">0.2*C26+0.8*B26</f>
         <v>-0.0326798327846499</v>
       </c>
@@ -4372,11 +4346,11 @@
         <f aca="false">0.5*C26+0.5*B26</f>
         <v>-0.0276428954904062</v>
       </c>
-      <c r="M26" s="10" t="n">
+      <c r="M26" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B26</f>
         <v>0.00304956114786403</v>
       </c>
-      <c r="N26" s="10" t="n">
+      <c r="N26" s="8" t="n">
         <f aca="false">C26-M26</f>
         <v>-0.022297561147864</v>
       </c>
@@ -4393,7 +4367,7 @@
         <f aca="false">Data!C27-Data!D27</f>
         <v>0.027476</v>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="E27" s="5" t="n">
         <f aca="false">0.2*C27+0.8*B27</f>
         <v>0.0302299681115489</v>
       </c>
@@ -4405,11 +4379,11 @@
         <f aca="false">0.5*C27+0.5*B27</f>
         <v>0.0291972300697181</v>
       </c>
-      <c r="M27" s="10" t="n">
+      <c r="M27" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B27</f>
         <v>0.00729753420310034</v>
       </c>
-      <c r="N27" s="10" t="n">
+      <c r="N27" s="8" t="n">
         <f aca="false">C27-M27</f>
         <v>0.0201784657968997</v>
       </c>
@@ -4426,7 +4400,7 @@
         <f aca="false">Data!C28-Data!D28</f>
         <v>-0.002797</v>
       </c>
-      <c r="E28" s="0" t="n">
+      <c r="E28" s="5" t="n">
         <f aca="false">0.2*C28+0.8*B28</f>
         <v>0.0474690006693365</v>
       </c>
@@ -4438,11 +4412,11 @@
         <f aca="false">0.5*C28+0.5*B28</f>
         <v>0.0286192504183353</v>
       </c>
-      <c r="M28" s="10" t="n">
+      <c r="M28" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B28</f>
         <v>0.00914483601974381</v>
       </c>
-      <c r="N28" s="10" t="n">
+      <c r="N28" s="8" t="n">
         <f aca="false">C28-M28</f>
         <v>-0.0119418360197438</v>
       </c>
@@ -4459,23 +4433,23 @@
         <f aca="false">Data!C29-Data!D29</f>
         <v>0.059161</v>
       </c>
-      <c r="E29" s="0" t="n">
+      <c r="E29" s="5" t="n">
         <f aca="false">0.2*C29+0.8*B29</f>
         <v>0.0243763529750303</v>
       </c>
       <c r="G29" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B29 + 'Optimal portfolio from homework'!$C$15*C29</f>
-        <v>0.0316318541399824</v>
+        <v>0.0316318541399823</v>
       </c>
       <c r="I29" s="9" t="n">
         <f aca="false">0.5*C29+0.5*B29</f>
         <v>0.0374205956093939</v>
       </c>
-      <c r="M29" s="10" t="n">
+      <c r="M29" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B29</f>
         <v>0.00633075731968276</v>
       </c>
-      <c r="N29" s="10" t="n">
+      <c r="N29" s="8" t="n">
         <f aca="false">C29-M29</f>
         <v>0.0528302426803172</v>
       </c>
@@ -4492,7 +4466,7 @@
         <f aca="false">Data!C30-Data!D30</f>
         <v>0.032872</v>
       </c>
-      <c r="E30" s="0" t="n">
+      <c r="E30" s="5" t="n">
         <f aca="false">0.2*C30+0.8*B30</f>
         <v>-0.0575465394133236</v>
       </c>
@@ -4504,11 +4478,11 @@
         <f aca="false">0.5*C30+0.5*B30</f>
         <v>-0.0236395871333273</v>
       </c>
-      <c r="M30" s="10" t="n">
+      <c r="M30" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B30</f>
         <v>0.000250831224394653</v>
       </c>
-      <c r="N30" s="10" t="n">
+      <c r="N30" s="8" t="n">
         <f aca="false">C30-M30</f>
         <v>0.0326211687756053</v>
       </c>
@@ -4525,23 +4499,23 @@
         <f aca="false">Data!C31-Data!D31</f>
         <v>0.021729</v>
       </c>
-      <c r="E31" s="0" t="n">
+      <c r="E31" s="5" t="n">
         <f aca="false">0.2*C31+0.8*B31</f>
         <v>-0.0376498547522984</v>
       </c>
       <c r="G31" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B31 + 'Optimal portfolio from homework'!$C$15*C31</f>
-        <v>-0.0252644092561989</v>
+        <v>-0.025264409256199</v>
       </c>
       <c r="I31" s="9" t="n">
         <f aca="false">0.5*C31+0.5*B31</f>
         <v>-0.0153827842201865</v>
       </c>
-      <c r="M31" s="10" t="n">
+      <c r="M31" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B31</f>
         <v>0.00200547719670786</v>
       </c>
-      <c r="N31" s="10" t="n">
+      <c r="N31" s="8" t="n">
         <f aca="false">C31-M31</f>
         <v>0.0197235228032921</v>
       </c>
@@ -4558,7 +4532,7 @@
         <f aca="false">Data!C32-Data!D32</f>
         <v>-0.058544</v>
       </c>
-      <c r="E32" s="0" t="n">
+      <c r="E32" s="5" t="n">
         <f aca="false">0.2*C32+0.8*B32</f>
         <v>0.0441800125592666</v>
       </c>
@@ -4570,11 +4544,11 @@
         <f aca="false">0.5*C32+0.5*B32</f>
         <v>0.00565850784954165</v>
       </c>
-      <c r="M32" s="10" t="n">
+      <c r="M32" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B32</f>
         <v>0.00976820608140383</v>
       </c>
-      <c r="N32" s="10" t="n">
+      <c r="N32" s="8" t="n">
         <f aca="false">C32-M32</f>
         <v>-0.0683122060814038</v>
       </c>
@@ -4591,23 +4565,23 @@
         <f aca="false">Data!C33-Data!D33</f>
         <v>0.055979</v>
       </c>
-      <c r="E33" s="0" t="n">
+      <c r="E33" s="5" t="n">
         <f aca="false">0.2*C33+0.8*B33</f>
         <v>-0.0251225062530773</v>
       </c>
       <c r="G33" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B33 + 'Optimal portfolio from homework'!$C$15*C33</f>
-        <v>-0.00820607548762569</v>
+        <v>-0.00820607548762573</v>
       </c>
       <c r="I33" s="9" t="n">
         <f aca="false">0.5*C33+0.5*B33</f>
         <v>0.00529055859182669</v>
       </c>
-      <c r="M33" s="10" t="n">
+      <c r="M33" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B33</f>
         <v>0.00245571938930323</v>
       </c>
-      <c r="N33" s="10" t="n">
+      <c r="N33" s="8" t="n">
         <f aca="false">C33-M33</f>
         <v>0.0535232806106968</v>
       </c>
@@ -4624,23 +4598,23 @@
         <f aca="false">Data!C34-Data!D34</f>
         <v>0.062729</v>
       </c>
-      <c r="E34" s="0" t="n">
+      <c r="E34" s="5" t="n">
         <f aca="false">0.2*C34+0.8*B34</f>
         <v>0.083816967326806</v>
       </c>
       <c r="G34" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B34 + 'Optimal portfolio from homework'!$C$15*C34</f>
-        <v>0.0794183666626601</v>
+        <v>0.0794183666626602</v>
       </c>
       <c r="I34" s="9" t="n">
         <f aca="false">0.5*C34+0.5*B34</f>
         <v>0.0759089795792538</v>
       </c>
-      <c r="M34" s="10" t="n">
+      <c r="M34" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B34</f>
         <v>0.0109881039155366</v>
       </c>
-      <c r="N34" s="10" t="n">
+      <c r="N34" s="8" t="n">
         <f aca="false">C34-M34</f>
         <v>0.0517408960844634</v>
       </c>
@@ -4657,7 +4631,7 @@
         <f aca="false">Data!C35-Data!D35</f>
         <v>0.019541</v>
       </c>
-      <c r="E35" s="0" t="n">
+      <c r="E35" s="5" t="n">
         <f aca="false">0.2*C35+0.8*B35</f>
         <v>0.0341346915286503</v>
       </c>
@@ -4669,11 +4643,11 @@
         <f aca="false">0.5*C35+0.5*B35</f>
         <v>0.0286620572054065</v>
       </c>
-      <c r="M35" s="10" t="n">
+      <c r="M35" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B35</f>
         <v>0.00773305539627394</v>
       </c>
-      <c r="N35" s="10" t="n">
+      <c r="N35" s="8" t="n">
         <f aca="false">C35-M35</f>
         <v>0.0118079446037261</v>
       </c>
@@ -4690,7 +4664,7 @@
         <f aca="false">Data!C36-Data!D36</f>
         <v>0.028514</v>
       </c>
-      <c r="E36" s="0" t="n">
+      <c r="E36" s="5" t="n">
         <f aca="false">0.2*C36+0.8*B36</f>
         <v>0.0056228</v>
       </c>
@@ -4702,11 +4676,11 @@
         <f aca="false">0.5*C36+0.5*B36</f>
         <v>0.014207</v>
       </c>
-      <c r="M36" s="10" t="n">
+      <c r="M36" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B36</f>
         <v>0.00532959871264696</v>
       </c>
-      <c r="N36" s="10" t="n">
+      <c r="N36" s="8" t="n">
         <f aca="false">C36-M36</f>
         <v>0.023184401287353</v>
       </c>
@@ -4723,7 +4697,7 @@
         <f aca="false">Data!C37-Data!D37</f>
         <v>0.025536</v>
       </c>
-      <c r="E37" s="0" t="n">
+      <c r="E37" s="5" t="n">
         <f aca="false">0.2*C37+0.8*B37</f>
         <v>0.0583979035399789</v>
       </c>
@@ -4735,11 +4709,11 @@
         <f aca="false">0.5*C37+0.5*B37</f>
         <v>0.0460746897124868</v>
       </c>
-      <c r="M37" s="10" t="n">
+      <c r="M37" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B37</f>
         <v>0.00956216301365726</v>
       </c>
-      <c r="N37" s="10" t="n">
+      <c r="N37" s="8" t="n">
         <f aca="false">C37-M37</f>
         <v>0.0159738369863427</v>
       </c>
@@ -4756,23 +4730,23 @@
         <f aca="false">Data!C38-Data!D38</f>
         <v>-0.054523</v>
       </c>
-      <c r="E38" s="0" t="n">
+      <c r="E38" s="5" t="n">
         <f aca="false">0.2*C38+0.8*B38</f>
         <v>0.00787224683128996</v>
       </c>
       <c r="G38" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B38 + 'Optimal portfolio from homework'!$C$15*C38</f>
-        <v>-0.00514236808623175</v>
+        <v>-0.00514236808623168</v>
       </c>
       <c r="I38" s="9" t="n">
         <f aca="false">0.5*C38+0.5*B38</f>
         <v>-0.0155259707304438</v>
       </c>
-      <c r="M38" s="10" t="n">
+      <c r="M38" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B38</f>
         <v>0.00682504118265208</v>
       </c>
-      <c r="N38" s="10" t="n">
+      <c r="N38" s="8" t="n">
         <f aca="false">C38-M38</f>
         <v>-0.0613480411826521</v>
       </c>
@@ -4789,7 +4763,7 @@
         <f aca="false">Data!C39-Data!D39</f>
         <v>0.05708</v>
       </c>
-      <c r="E39" s="0" t="n">
+      <c r="E39" s="5" t="n">
         <f aca="false">0.2*C39+0.8*B39</f>
         <v>0.0386662404048925</v>
       </c>
@@ -4801,11 +4775,11 @@
         <f aca="false">0.5*C39+0.5*B39</f>
         <v>0.0455714002530578</v>
       </c>
-      <c r="M39" s="10" t="n">
+      <c r="M39" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B39</f>
         <v>0.007497023764279</v>
       </c>
-      <c r="N39" s="10" t="n">
+      <c r="N39" s="8" t="n">
         <f aca="false">C39-M39</f>
         <v>0.049582976235721</v>
       </c>
@@ -4822,7 +4796,7 @@
         <f aca="false">Data!C40-Data!D40</f>
         <v>0.014974</v>
       </c>
-      <c r="E40" s="0" t="n">
+      <c r="E40" s="5" t="n">
         <f aca="false">0.2*C40+0.8*B40</f>
         <v>0.00311974125741468</v>
       </c>
@@ -4834,11 +4808,11 @@
         <f aca="false">0.5*C40+0.5*B40</f>
         <v>0.00756508828588418</v>
       </c>
-      <c r="M40" s="10" t="n">
+      <c r="M40" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B40</f>
         <v>0.00534585158158821</v>
       </c>
-      <c r="N40" s="10" t="n">
+      <c r="N40" s="8" t="n">
         <f aca="false">C40-M40</f>
         <v>0.00962814841841179</v>
       </c>
@@ -4855,7 +4829,7 @@
         <f aca="false">Data!C41-Data!D41</f>
         <v>0.069881</v>
       </c>
-      <c r="E41" s="0" t="n">
+      <c r="E41" s="5" t="n">
         <f aca="false">0.2*C41+0.8*B41</f>
         <v>0.0375595606288896</v>
       </c>
@@ -4867,11 +4841,11 @@
         <f aca="false">0.5*C41+0.5*B41</f>
         <v>0.049680100393056</v>
       </c>
-      <c r="M41" s="10" t="n">
+      <c r="M41" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B41</f>
         <v>0.00720622181851899</v>
       </c>
-      <c r="N41" s="10" t="n">
+      <c r="N41" s="8" t="n">
         <f aca="false">C41-M41</f>
         <v>0.062674778181481</v>
       </c>
@@ -4888,7 +4862,7 @@
         <f aca="false">Data!C42-Data!D42</f>
         <v>0.003919</v>
       </c>
-      <c r="E42" s="0" t="n">
+      <c r="E42" s="5" t="n">
         <f aca="false">0.2*C42+0.8*B42</f>
         <v>-0.00837941985364297</v>
       </c>
@@ -4900,11 +4874,11 @@
         <f aca="false">0.5*C42+0.5*B42</f>
         <v>-0.00376751240852686</v>
       </c>
-      <c r="M42" s="10" t="n">
+      <c r="M42" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B42</f>
         <v>0.00460925385037699</v>
       </c>
-      <c r="N42" s="10" t="n">
+      <c r="N42" s="8" t="n">
         <f aca="false">C42-M42</f>
         <v>-0.000690253850376994</v>
       </c>
@@ -4921,7 +4895,7 @@
         <f aca="false">Data!C43-Data!D43</f>
         <v>-0.018868</v>
       </c>
-      <c r="E43" s="0" t="n">
+      <c r="E43" s="5" t="n">
         <f aca="false">0.2*C43+0.8*B43</f>
         <v>-0.017151834023525</v>
       </c>
@@ -4933,11 +4907,11 @@
         <f aca="false">0.5*C43+0.5*B43</f>
         <v>-0.0177953962647031</v>
       </c>
-      <c r="M43" s="10" t="n">
+      <c r="M43" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B43</f>
         <v>0.00427498209976514</v>
       </c>
-      <c r="N43" s="10" t="n">
+      <c r="N43" s="8" t="n">
         <f aca="false">C43-M43</f>
         <v>-0.0231429820997651</v>
       </c>
@@ -4954,23 +4928,23 @@
         <f aca="false">Data!C44-Data!D44</f>
         <v>0.070126</v>
       </c>
-      <c r="E44" s="0" t="n">
+      <c r="E44" s="5" t="n">
         <f aca="false">0.2*C44+0.8*B44</f>
         <v>-0.00234964586929725</v>
       </c>
       <c r="G44" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B44 + 'Optimal portfolio from homework'!$C$15*C44</f>
-        <v>0.0127675733066763</v>
+        <v>0.0127675733066762</v>
       </c>
       <c r="I44" s="9" t="n">
         <f aca="false">0.5*C44+0.5*B44</f>
         <v>0.0248287213316892</v>
       </c>
-      <c r="M44" s="10" t="n">
+      <c r="M44" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B44</f>
         <v>0.00403733576046029</v>
       </c>
-      <c r="N44" s="10" t="n">
+      <c r="N44" s="8" t="n">
         <f aca="false">C44-M44</f>
         <v>0.0660886642395397</v>
       </c>
@@ -4987,23 +4961,23 @@
         <f aca="false">Data!C45-Data!D45</f>
         <v>0.131426</v>
       </c>
-      <c r="E45" s="0" t="n">
+      <c r="E45" s="5" t="n">
         <f aca="false">0.2*C45+0.8*B45</f>
         <v>-0.0173664683450822</v>
       </c>
       <c r="G45" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B45 + 'Optimal portfolio from homework'!$C$15*C45</f>
-        <v>0.0136691758182434</v>
+        <v>0.0136691758182433</v>
       </c>
       <c r="I45" s="9" t="n">
         <f aca="false">0.5*C45+0.5*B45</f>
         <v>0.0384307072843236</v>
       </c>
-      <c r="M45" s="10" t="n">
+      <c r="M45" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B45</f>
         <v>0.00187414701835347</v>
       </c>
-      <c r="N45" s="10" t="n">
+      <c r="N45" s="8" t="n">
         <f aca="false">C45-M45</f>
         <v>0.129551852981647</v>
       </c>
@@ -5020,7 +4994,7 @@
         <f aca="false">Data!C46-Data!D46</f>
         <v>-0.107886</v>
       </c>
-      <c r="E46" s="0" t="n">
+      <c r="E46" s="5" t="n">
         <f aca="false">0.2*C46+0.8*B46</f>
         <v>-0.0779178835776844</v>
       </c>
@@ -5032,11 +5006,11 @@
         <f aca="false">0.5*C46+0.5*B46</f>
         <v>-0.0891559272360527</v>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="M46" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B46</f>
         <v>0.000867844509182743</v>
       </c>
-      <c r="N46" s="10" t="n">
+      <c r="N46" s="8" t="n">
         <f aca="false">C46-M46</f>
         <v>-0.108753844509183</v>
       </c>
@@ -5053,23 +5027,23 @@
         <f aca="false">Data!C47-Data!D47</f>
         <v>0.054635</v>
       </c>
-      <c r="E47" s="0" t="n">
+      <c r="E47" s="5" t="n">
         <f aca="false">0.2*C47+0.8*B47</f>
         <v>0.0982374242656939</v>
       </c>
       <c r="G47" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B47 + 'Optimal portfolio from homework'!$C$15*C47</f>
-        <v>0.0891426808339901</v>
+        <v>0.0891426808339899</v>
       </c>
       <c r="I47" s="9" t="n">
         <f aca="false">0.5*C47+0.5*B47</f>
         <v>0.0818865151660587</v>
       </c>
-      <c r="M47" s="10" t="n">
+      <c r="M47" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B47</f>
         <v>0.0122600973844519</v>
       </c>
-      <c r="N47" s="10" t="n">
+      <c r="N47" s="8" t="n">
         <f aca="false">C47-M47</f>
         <v>0.0423749026155481</v>
       </c>
@@ -5086,7 +5060,7 @@
         <f aca="false">Data!C48-Data!D48</f>
         <v>-0.008149</v>
       </c>
-      <c r="E48" s="0" t="n">
+      <c r="E48" s="5" t="n">
         <f aca="false">0.2*C48+0.8*B48</f>
         <v>-0.00349912064041541</v>
       </c>
@@ -5098,11 +5072,11 @@
         <f aca="false">0.5*C48+0.5*B48</f>
         <v>-0.00524282540025963</v>
       </c>
-      <c r="M48" s="10" t="n">
+      <c r="M48" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B48</f>
         <v>0.00518769661723969</v>
       </c>
-      <c r="N48" s="10" t="n">
+      <c r="N48" s="8" t="n">
         <f aca="false">C48-M48</f>
         <v>-0.0133366966172397</v>
       </c>
@@ -5119,23 +5093,23 @@
         <f aca="false">Data!C49-Data!D49</f>
         <v>-0.075998</v>
       </c>
-      <c r="E49" s="0" t="n">
+      <c r="E49" s="5" t="n">
         <f aca="false">0.2*C49+0.8*B49</f>
         <v>-0.0070588177708275</v>
       </c>
       <c r="G49" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B49 + 'Optimal portfolio from homework'!$C$15*C49</f>
-        <v>-0.0214383892126637</v>
+        <v>-0.0214383892126636</v>
       </c>
       <c r="I49" s="9" t="n">
         <f aca="false">0.5*C49+0.5*B49</f>
         <v>-0.0329110111067672</v>
       </c>
-      <c r="M49" s="10" t="n">
+      <c r="M49" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B49</f>
         <v>0.00598154794849526</v>
       </c>
-      <c r="N49" s="10" t="n">
+      <c r="N49" s="8" t="n">
         <f aca="false">C49-M49</f>
         <v>-0.0819795479484953</v>
       </c>
@@ -5152,23 +5126,23 @@
         <f aca="false">Data!C50-Data!D50</f>
         <v>0.103842</v>
       </c>
-      <c r="E50" s="0" t="n">
+      <c r="E50" s="5" t="n">
         <f aca="false">0.2*C50+0.8*B50</f>
         <v>0.0564851530224524</v>
       </c>
       <c r="G50" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B50 + 'Optimal portfolio from homework'!$C$15*C50</f>
-        <v>0.0663630068401844</v>
+        <v>0.0663630068401843</v>
       </c>
       <c r="I50" s="9" t="n">
         <f aca="false">0.5*C50+0.5*B50</f>
         <v>0.0742439706390328</v>
       </c>
-      <c r="M50" s="10" t="n">
+      <c r="M50" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B50</f>
         <v>0.00816846065160229</v>
       </c>
-      <c r="N50" s="10" t="n">
+      <c r="N50" s="8" t="n">
         <f aca="false">C50-M50</f>
         <v>0.0956735393483977</v>
       </c>
@@ -5185,7 +5159,7 @@
         <f aca="false">Data!C51-Data!D51</f>
         <v>0.028769</v>
       </c>
-      <c r="E51" s="0" t="n">
+      <c r="E51" s="5" t="n">
         <f aca="false">0.2*C51+0.8*B51</f>
         <v>0.0402086235099612</v>
       </c>
@@ -5197,11 +5171,11 @@
         <f aca="false">0.5*C51+0.5*B51</f>
         <v>0.0359187646937258</v>
       </c>
-      <c r="M51" s="10" t="n">
+      <c r="M51" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B51</f>
         <v>0.00806838331608505</v>
       </c>
-      <c r="N51" s="10" t="n">
+      <c r="N51" s="8" t="n">
         <f aca="false">C51-M51</f>
         <v>0.020700616683915</v>
       </c>
@@ -5218,23 +5192,23 @@
         <f aca="false">Data!C52-Data!D52</f>
         <v>-0.071169</v>
       </c>
-      <c r="E52" s="0" t="n">
+      <c r="E52" s="5" t="n">
         <f aca="false">0.2*C52+0.8*B52</f>
         <v>0.01201783989279</v>
       </c>
       <c r="G52" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B52 + 'Optimal portfolio from homework'!$C$15*C52</f>
-        <v>-0.00533355692654703</v>
+        <v>-0.005333556926547</v>
       </c>
       <c r="I52" s="9" t="n">
         <f aca="false">0.5*C52+0.5*B52</f>
         <v>-0.0191772250670062</v>
       </c>
-      <c r="M52" s="10" t="n">
+      <c r="M52" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B52</f>
         <v>0.00741782973837808</v>
       </c>
-      <c r="N52" s="10" t="n">
+      <c r="N52" s="8" t="n">
         <f aca="false">C52-M52</f>
         <v>-0.0785868297383781</v>
       </c>
@@ -5251,7 +5225,7 @@
         <f aca="false">Data!C53-Data!D53</f>
         <v>0.001054</v>
       </c>
-      <c r="E53" s="0" t="n">
+      <c r="E53" s="5" t="n">
         <f aca="false">0.2*C53+0.8*B53</f>
         <v>-0.00490555074741879</v>
       </c>
@@ -5263,11 +5237,11 @@
         <f aca="false">0.5*C53+0.5*B53</f>
         <v>-0.00267071921713674</v>
       </c>
-      <c r="M53" s="10" t="n">
+      <c r="M53" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B53</f>
         <v>0.0049301908546463</v>
       </c>
-      <c r="N53" s="10" t="n">
+      <c r="N53" s="8" t="n">
         <f aca="false">C53-M53</f>
         <v>-0.0038761908546463</v>
       </c>
@@ -5284,7 +5258,7 @@
         <f aca="false">Data!C54-Data!D54</f>
         <v>-0.057243</v>
       </c>
-      <c r="E54" s="0" t="n">
+      <c r="E54" s="5" t="n">
         <f aca="false">0.2*C54+0.8*B54</f>
         <v>-0.0596712909654904</v>
       </c>
@@ -5296,11 +5270,11 @@
         <f aca="false">0.5*C54+0.5*B54</f>
         <v>-0.0587606818534315</v>
       </c>
-      <c r="M54" s="10" t="n">
+      <c r="M54" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B54</f>
         <v>0.00151164201319165</v>
       </c>
-      <c r="N54" s="10" t="n">
+      <c r="N54" s="8" t="n">
         <f aca="false">C54-M54</f>
         <v>-0.0587546420131916</v>
       </c>
@@ -5317,7 +5291,7 @@
         <f aca="false">Data!C55-Data!D55</f>
         <v>0.001276</v>
       </c>
-      <c r="E55" s="0" t="n">
+      <c r="E55" s="5" t="n">
         <f aca="false">0.2*C55+0.8*B55</f>
         <v>0.0331267869172832</v>
       </c>
@@ -5329,11 +5303,11 @@
         <f aca="false">0.5*C55+0.5*B55</f>
         <v>0.021182741823302</v>
       </c>
-      <c r="M55" s="10" t="n">
+      <c r="M55" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B55</f>
         <v>0.00794282471861964</v>
       </c>
-      <c r="N55" s="10" t="n">
+      <c r="N55" s="8" t="n">
         <f aca="false">C55-M55</f>
         <v>-0.00666682471861964</v>
       </c>
@@ -5350,23 +5324,23 @@
         <f aca="false">Data!C56-Data!D56</f>
         <v>0.033928</v>
       </c>
-      <c r="E56" s="0" t="n">
+      <c r="E56" s="5" t="n">
         <f aca="false">0.2*C56+0.8*B56</f>
         <v>0.0177453769812824</v>
       </c>
       <c r="G56" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B56 + 'Optimal portfolio from homework'!$C$15*C56</f>
-        <v>0.0211208040793353</v>
+        <v>0.0211208040793352</v>
       </c>
       <c r="I56" s="9" t="n">
         <f aca="false">0.5*C56+0.5*B56</f>
         <v>0.0238138606133015</v>
       </c>
-      <c r="M56" s="10" t="n">
+      <c r="M56" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B56</f>
         <v>0.00620510836200148</v>
       </c>
-      <c r="N56" s="10" t="n">
+      <c r="N56" s="8" t="n">
         <f aca="false">C56-M56</f>
         <v>0.0277228916379985</v>
       </c>
@@ -5383,23 +5357,23 @@
         <f aca="false">Data!C57-Data!D57</f>
         <v>0.021468</v>
       </c>
-      <c r="E57" s="0" t="n">
+      <c r="E57" s="5" t="n">
         <f aca="false">0.2*C57+0.8*B57</f>
         <v>0.0221282696000629</v>
       </c>
       <c r="G57" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B57 + 'Optimal portfolio from homework'!$C$15*C57</f>
-        <v>0.0219905482987946</v>
+        <v>0.0219905482987945</v>
       </c>
       <c r="I57" s="9" t="n">
         <f aca="false">0.5*C57+0.5*B57</f>
         <v>0.0218806685000393</v>
       </c>
-      <c r="M57" s="10" t="n">
+      <c r="M57" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B57</f>
         <v>0.00675032180573532</v>
       </c>
-      <c r="N57" s="10" t="n">
+      <c r="N57" s="8" t="n">
         <f aca="false">C57-M57</f>
         <v>0.0147176781942647</v>
       </c>
@@ -5416,7 +5390,7 @@
         <f aca="false">Data!C58-Data!D58</f>
         <v>0.074248</v>
       </c>
-      <c r="E58" s="0" t="n">
+      <c r="E58" s="5" t="n">
         <f aca="false">0.2*C58+0.8*B58</f>
         <v>0.0353818503664769</v>
       </c>
@@ -5428,11 +5402,11 @@
         <f aca="false">0.5*C58+0.5*B58</f>
         <v>0.0499566564790481</v>
       </c>
-      <c r="M58" s="10" t="n">
+      <c r="M58" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B58</f>
         <v>0.00696425348161183</v>
       </c>
-      <c r="N58" s="10" t="n">
+      <c r="N58" s="8" t="n">
         <f aca="false">C58-M58</f>
         <v>0.0672837465183882</v>
       </c>
@@ -5449,23 +5423,23 @@
         <f aca="false">Data!C59-Data!D59</f>
         <v>-0.035473</v>
       </c>
-      <c r="E59" s="0" t="n">
+      <c r="E59" s="5" t="n">
         <f aca="false">0.2*C59+0.8*B59</f>
         <v>-0.0220507574945419</v>
       </c>
       <c r="G59" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B59 + 'Optimal portfolio from homework'!$C$15*C59</f>
-        <v>-0.0248504149429764</v>
+        <v>-0.0248504149429763</v>
       </c>
       <c r="I59" s="9" t="n">
         <f aca="false">0.5*C59+0.5*B59</f>
         <v>-0.0270840984340887</v>
       </c>
-      <c r="M59" s="10" t="n">
+      <c r="M59" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B59</f>
         <v>0.00414984485947844</v>
       </c>
-      <c r="N59" s="10" t="n">
+      <c r="N59" s="8" t="n">
         <f aca="false">C59-M59</f>
         <v>-0.0396228448594784</v>
       </c>
@@ -5482,7 +5456,7 @@
         <f aca="false">Data!C60-Data!D60</f>
         <v>0.005866</v>
       </c>
-      <c r="E60" s="0" t="n">
+      <c r="E60" s="5" t="n">
         <f aca="false">0.2*C60+0.8*B60</f>
         <v>0.00557310181037117</v>
       </c>
@@ -5494,11 +5468,11 @@
         <f aca="false">0.5*C60+0.5*B60</f>
         <v>0.00568293863148198</v>
       </c>
-      <c r="M60" s="10" t="n">
+      <c r="M60" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B60</f>
         <v>0.00568487738084748</v>
       </c>
-      <c r="N60" s="10" t="n">
+      <c r="N60" s="8" t="n">
         <f aca="false">C60-M60</f>
         <v>0.000181122619152523</v>
       </c>
@@ -5515,23 +5489,23 @@
         <f aca="false">Data!C61-Data!D61</f>
         <v>-0.037276</v>
       </c>
-      <c r="E61" s="0" t="n">
+      <c r="E61" s="5" t="n">
         <f aca="false">0.2*C61+0.8*B61</f>
         <v>-0.000316947525860148</v>
       </c>
       <c r="G61" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B61 + 'Optimal portfolio from homework'!$C$15*C61</f>
-        <v>-0.00802599364868424</v>
+        <v>-0.00802599364868422</v>
       </c>
       <c r="I61" s="9" t="n">
         <f aca="false">0.5*C61+0.5*B61</f>
         <v>-0.0141765922036626</v>
       </c>
-      <c r="M61" s="10" t="n">
+      <c r="M61" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B61</f>
         <v>0.00590204231393541</v>
       </c>
-      <c r="N61" s="10" t="n">
+      <c r="N61" s="8" t="n">
         <f aca="false">C61-M61</f>
         <v>-0.0431780423139354</v>
       </c>
@@ -5548,23 +5522,23 @@
         <f aca="false">Data!C62-Data!D62</f>
         <v>0.00631</v>
       </c>
-      <c r="E62" s="0" t="n">
+      <c r="E62" s="5" t="n">
         <f aca="false">0.2*C62+0.8*B62</f>
         <v>0.0426717586968104</v>
       </c>
       <c r="G62" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B62 + 'Optimal portfolio from homework'!$C$15*C62</f>
-        <v>0.0350872981618212</v>
+        <v>0.0350872981618211</v>
       </c>
       <c r="I62" s="9" t="n">
         <f aca="false">0.5*C62+0.5*B62</f>
         <v>0.0290360991855065</v>
       </c>
-      <c r="M62" s="10" t="n">
+      <c r="M62" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B62</f>
         <v>0.00861994453666457</v>
       </c>
-      <c r="N62" s="10" t="n">
+      <c r="N62" s="8" t="n">
         <f aca="false">C62-M62</f>
         <v>-0.00230994453666457</v>
       </c>
@@ -5581,23 +5555,23 @@
         <f aca="false">Data!C63-Data!D63</f>
         <v>-0.049866</v>
       </c>
-      <c r="E63" s="0" t="n">
+      <c r="E63" s="5" t="n">
         <f aca="false">0.2*C63+0.8*B63</f>
         <v>0.00073824242599704</v>
       </c>
       <c r="G63" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B63 + 'Optimal portfolio from homework'!$C$15*C63</f>
-        <v>-0.00981696428947658</v>
+        <v>-0.00981696428947656</v>
       </c>
       <c r="I63" s="9" t="n">
         <f aca="false">0.5*C63+0.5*B63</f>
         <v>-0.0182383484837519</v>
       </c>
-      <c r="M63" s="10" t="n">
+      <c r="M63" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B63</f>
         <v>0.00618541418703861</v>
       </c>
-      <c r="N63" s="10" t="n">
+      <c r="N63" s="8" t="n">
         <f aca="false">C63-M63</f>
         <v>-0.0560514141870386</v>
       </c>
@@ -5614,7 +5588,7 @@
         <f aca="false">Data!C64-Data!D64</f>
         <v>0.007228</v>
       </c>
-      <c r="E64" s="0" t="n">
+      <c r="E64" s="5" t="n">
         <f aca="false">0.2*C64+0.8*B64</f>
         <v>0.0313547843219829</v>
       </c>
@@ -5626,11 +5600,11 @@
         <f aca="false">0.5*C64+0.5*B64</f>
         <v>0.0223072402012393</v>
       </c>
-      <c r="M64" s="10" t="n">
+      <c r="M64" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B64</f>
         <v>0.00770789134434444</v>
       </c>
-      <c r="N64" s="10" t="n">
+      <c r="N64" s="8" t="n">
         <f aca="false">C64-M64</f>
         <v>-0.00047989134434444</v>
       </c>
@@ -5647,7 +5621,7 @@
         <f aca="false">Data!C65-Data!D65</f>
         <v>-0.080967</v>
       </c>
-      <c r="E65" s="0" t="n">
+      <c r="E65" s="5" t="n">
         <f aca="false">0.2*C65+0.8*B65</f>
         <v>-0.000924746379918368</v>
       </c>
@@ -5659,11 +5633,11 @@
         <f aca="false">0.5*C65+0.5*B65</f>
         <v>-0.030940591487449</v>
       </c>
-      <c r="M65" s="10" t="n">
+      <c r="M65" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B65</f>
         <v>0.00654682387686588</v>
       </c>
-      <c r="N65" s="10" t="n">
+      <c r="N65" s="8" t="n">
         <f aca="false">C65-M65</f>
         <v>-0.0875138238768659</v>
       </c>
@@ -5680,23 +5654,23 @@
         <f aca="false">Data!C66-Data!D66</f>
         <v>-0.042438</v>
       </c>
-      <c r="E66" s="0" t="n">
+      <c r="E66" s="5" t="n">
         <f aca="false">0.2*C66+0.8*B66</f>
         <v>0.0101322005021374</v>
       </c>
       <c r="G66" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B66 + 'Optimal portfolio from homework'!$C$15*C66</f>
-        <v>-0.000833072502105596</v>
+        <v>-0.000833072502105575</v>
       </c>
       <c r="I66" s="9" t="n">
         <f aca="false">0.5*C66+0.5*B66</f>
         <v>-0.00958162468616409</v>
       </c>
-      <c r="M66" s="10" t="n">
+      <c r="M66" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B66</f>
         <v>0.00681258662158605</v>
       </c>
-      <c r="N66" s="10" t="n">
+      <c r="N66" s="8" t="n">
         <f aca="false">C66-M66</f>
         <v>-0.049250586621586</v>
       </c>
@@ -5713,7 +5687,7 @@
         <f aca="false">Data!C67-Data!D67</f>
         <v>-0.146782</v>
       </c>
-      <c r="E67" s="0" t="n">
+      <c r="E67" s="5" t="n">
         <f aca="false">0.2*C67+0.8*B67</f>
         <v>-0.0401608258321306</v>
       </c>
@@ -5725,11 +5699,11 @@
         <f aca="false">0.5*C67+0.5*B67</f>
         <v>-0.0801437661450816</v>
       </c>
-      <c r="M67" s="10" t="n">
+      <c r="M67" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B67</f>
         <v>0.00447909799005658</v>
       </c>
-      <c r="N67" s="10" t="n">
+      <c r="N67" s="8" t="n">
         <f aca="false">C67-M67</f>
         <v>-0.151261097990057</v>
       </c>
@@ -5746,7 +5720,7 @@
         <f aca="false">Data!C68-Data!D68</f>
         <v>0.106586</v>
       </c>
-      <c r="E68" s="0" t="n">
+      <c r="E68" s="5" t="n">
         <f aca="false">0.2*C68+0.8*B68</f>
         <v>0.0618953439956774</v>
       </c>
@@ -5758,11 +5732,11 @@
         <f aca="false">0.5*C68+0.5*B68</f>
         <v>0.0786543399972984</v>
       </c>
-      <c r="M68" s="10" t="n">
+      <c r="M68" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B68</f>
         <v>0.00855399332255748</v>
       </c>
-      <c r="N68" s="10" t="n">
+      <c r="N68" s="8" t="n">
         <f aca="false">C68-M68</f>
         <v>0.0980320066774425</v>
       </c>
@@ -5779,23 +5753,23 @@
         <f aca="false">Data!C69-Data!D69</f>
         <v>0.046001</v>
       </c>
-      <c r="E69" s="0" t="n">
+      <c r="E69" s="5" t="n">
         <f aca="false">0.2*C69+0.8*B69</f>
         <v>-0.0140947797518802</v>
       </c>
       <c r="G69" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B69 + 'Optimal portfolio from homework'!$C$15*C69</f>
-        <v>-0.00155979557666413</v>
+        <v>-0.00155979557666415</v>
       </c>
       <c r="I69" s="9" t="n">
         <f aca="false">0.5*C69+0.5*B69</f>
         <v>0.00844113765507489</v>
       </c>
-      <c r="M69" s="10" t="n">
+      <c r="M69" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B69</f>
         <v>0.00348853445774387</v>
       </c>
-      <c r="N69" s="10" t="n">
+      <c r="N69" s="8" t="n">
         <f aca="false">C69-M69</f>
         <v>0.0425124655422561</v>
       </c>
@@ -5812,23 +5786,23 @@
         <f aca="false">Data!C70-Data!D70</f>
         <v>-0.040926</v>
       </c>
-      <c r="E70" s="0" t="n">
+      <c r="E70" s="5" t="n">
         <f aca="false">0.2*C70+0.8*B70</f>
         <v>0.0167878460123722</v>
       </c>
       <c r="G70" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B70 + 'Optimal portfolio from homework'!$C$15*C70</f>
-        <v>0.0047496937587057</v>
+        <v>0.00474969375870571</v>
       </c>
       <c r="I70" s="9" t="n">
         <f aca="false">0.5*C70+0.5*B70</f>
         <v>-0.00485484624226739</v>
       </c>
-      <c r="M70" s="10" t="n">
+      <c r="M70" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B70</f>
         <v>0.00731643083495735</v>
       </c>
-      <c r="N70" s="10" t="n">
+      <c r="N70" s="8" t="n">
         <f aca="false">C70-M70</f>
         <v>-0.0482424308349573</v>
       </c>
@@ -5845,7 +5819,7 @@
         <f aca="false">Data!C71-Data!D71</f>
         <v>-0.001497</v>
       </c>
-      <c r="E71" s="0" t="n">
+      <c r="E71" s="5" t="n">
         <f aca="false">0.2*C71+0.8*B71</f>
         <v>0.036392639736808</v>
       </c>
@@ -5857,11 +5831,11 @@
         <f aca="false">0.5*C71+0.5*B71</f>
         <v>0.022184024835505</v>
       </c>
-      <c r="M71" s="10" t="n">
+      <c r="M71" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B71</f>
         <v>0.008245805776486</v>
       </c>
-      <c r="N71" s="10" t="n">
+      <c r="N71" s="8" t="n">
         <f aca="false">C71-M71</f>
         <v>-0.009742805776486</v>
       </c>
@@ -5878,23 +5852,23 @@
         <f aca="false">Data!C72-Data!D72</f>
         <v>-0.066354</v>
       </c>
-      <c r="E72" s="0" t="n">
+      <c r="E72" s="5" t="n">
         <f aca="false">0.2*C72+0.8*B72</f>
         <v>0.0109566717819035</v>
       </c>
       <c r="G72" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B72 + 'Optimal portfolio from homework'!$C$15*C72</f>
-        <v>-0.00516905370768323</v>
+        <v>-0.0051690537076832</v>
       </c>
       <c r="I72" s="9" t="n">
         <f aca="false">0.5*C72+0.5*B72</f>
         <v>-0.0180348301363103</v>
       </c>
-      <c r="M72" s="10" t="n">
+      <c r="M72" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B72</f>
         <v>0.0072573030614351</v>
       </c>
-      <c r="N72" s="10" t="n">
+      <c r="N72" s="8" t="n">
         <f aca="false">C72-M72</f>
         <v>-0.0736113030614351</v>
       </c>
@@ -5911,23 +5885,23 @@
         <f aca="false">Data!C73-Data!D73</f>
         <v>-0.035134</v>
       </c>
-      <c r="E73" s="0" t="n">
+      <c r="E73" s="5" t="n">
         <f aca="false">0.2*C73+0.8*B73</f>
         <v>0.0130834004612626</v>
       </c>
       <c r="G73" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B73 + 'Optimal portfolio from homework'!$C$15*C73</f>
-        <v>0.00302604944181644</v>
+        <v>0.00302604944181648</v>
       </c>
       <c r="I73" s="9" t="n">
         <f aca="false">0.5*C73+0.5*B73</f>
         <v>-0.00499812471171091</v>
       </c>
-      <c r="M73" s="10" t="n">
+      <c r="M73" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B73</f>
         <v>0.00693078280868511</v>
       </c>
-      <c r="N73" s="10" t="n">
+      <c r="N73" s="8" t="n">
         <f aca="false">C73-M73</f>
         <v>-0.0420647828086851</v>
       </c>
@@ -5944,23 +5918,23 @@
         <f aca="false">Data!C74-Data!D74</f>
         <v>0.037453</v>
       </c>
-      <c r="E74" s="0" t="n">
+      <c r="E74" s="5" t="n">
         <f aca="false">0.2*C74+0.8*B74</f>
         <v>-0.0202623936604838</v>
       </c>
       <c r="G74" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B74 + 'Optimal portfolio from homework'!$C$15*C74</f>
-        <v>-0.00822391859305785</v>
+        <v>-0.00822391859305788</v>
       </c>
       <c r="I74" s="9" t="n">
         <f aca="false">0.5*C74+0.5*B74</f>
         <v>0.00138087896219765</v>
       </c>
-      <c r="M74" s="10" t="n">
+      <c r="M74" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B74</f>
         <v>0.00313499160986238</v>
       </c>
-      <c r="N74" s="10" t="n">
+      <c r="N74" s="8" t="n">
         <f aca="false">C74-M74</f>
         <v>0.0343180083901376</v>
       </c>
@@ -5977,7 +5951,7 @@
         <f aca="false">Data!C75-Data!D75</f>
         <v>0.065183</v>
       </c>
-      <c r="E75" s="0" t="n">
+      <c r="E75" s="5" t="n">
         <f aca="false">0.2*C75+0.8*B75</f>
         <v>0.0495218538765582</v>
       </c>
@@ -5989,11 +5963,11 @@
         <f aca="false">0.5*C75+0.5*B75</f>
         <v>0.0553947836728489</v>
       </c>
-      <c r="M75" s="10" t="n">
+      <c r="M75" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B75</f>
         <v>0.00822940662129421</v>
       </c>
-      <c r="N75" s="10" t="n">
+      <c r="N75" s="8" t="n">
         <f aca="false">C75-M75</f>
         <v>0.0569535933787058</v>
       </c>
@@ -6010,23 +5984,23 @@
         <f aca="false">Data!C76-Data!D76</f>
         <v>-0.025419</v>
       </c>
-      <c r="E76" s="0" t="n">
+      <c r="E76" s="5" t="n">
         <f aca="false">0.2*C76+0.8*B76</f>
         <v>0.001506567922308</v>
       </c>
       <c r="G76" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B76 + 'Optimal portfolio from homework'!$C$15*C76</f>
-        <v>-0.00410965952674637</v>
+        <v>-0.00410965952674636</v>
       </c>
       <c r="I76" s="9" t="n">
         <f aca="false">0.5*C76+0.5*B76</f>
         <v>-0.0085905200485575</v>
       </c>
-      <c r="M76" s="10" t="n">
+      <c r="M76" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B76</f>
         <v>0.00585859232281019</v>
       </c>
-      <c r="N76" s="10" t="n">
+      <c r="N76" s="8" t="n">
         <f aca="false">C76-M76</f>
         <v>-0.0312775923228102</v>
       </c>
@@ -6043,23 +6017,23 @@
         <f aca="false">Data!C77-Data!D77</f>
         <v>-0.001546</v>
       </c>
-      <c r="E77" s="0" t="n">
+      <c r="E77" s="5" t="n">
         <f aca="false">0.2*C77+0.8*B77</f>
         <v>0.00548353590916998</v>
       </c>
       <c r="G77" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B77 + 'Optimal portfolio from homework'!$C$15*C77</f>
-        <v>0.00401729116212845</v>
+        <v>0.00401729116212846</v>
       </c>
       <c r="I77" s="9" t="n">
         <f aca="false">0.5*C77+0.5*B77</f>
         <v>0.00284745994323124</v>
       </c>
-      <c r="M77" s="10" t="n">
+      <c r="M77" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B77</f>
         <v>0.00579533610619273</v>
       </c>
-      <c r="N77" s="10" t="n">
+      <c r="N77" s="8" t="n">
         <f aca="false">C77-M77</f>
         <v>-0.00734133610619273</v>
       </c>
@@ -6076,23 +6050,23 @@
         <f aca="false">Data!C78-Data!D78</f>
         <v>-0.029412</v>
       </c>
-      <c r="E78" s="0" t="n">
+      <c r="E78" s="5" t="n">
         <f aca="false">0.2*C78+0.8*B78</f>
         <v>0.0127971491143318</v>
       </c>
       <c r="G78" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B78 + 'Optimal portfolio from homework'!$C$15*C78</f>
-        <v>0.00399301979972831</v>
+        <v>0.00399301979972836</v>
       </c>
       <c r="I78" s="9" t="n">
         <f aca="false">0.5*C78+0.5*B78</f>
         <v>-0.00303128180354262</v>
       </c>
-      <c r="M78" s="10" t="n">
+      <c r="M78" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B78</f>
         <v>0.00681732498601138</v>
       </c>
-      <c r="N78" s="10" t="n">
+      <c r="N78" s="8" t="n">
         <f aca="false">C78-M78</f>
         <v>-0.0362293249860114</v>
       </c>
@@ -6109,7 +6083,7 @@
         <f aca="false">Data!C79-Data!D79</f>
         <v>0.047049</v>
       </c>
-      <c r="E79" s="0" t="n">
+      <c r="E79" s="5" t="n">
         <f aca="false">0.2*C79+0.8*B79</f>
         <v>0.0258254108882064</v>
       </c>
@@ -6121,11 +6095,11 @@
         <f aca="false">0.5*C79+0.5*B79</f>
         <v>0.033784256805129</v>
       </c>
-      <c r="M79" s="10" t="n">
+      <c r="M79" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B79</f>
         <v>0.00663778333712881</v>
       </c>
-      <c r="N79" s="10" t="n">
+      <c r="N79" s="8" t="n">
         <f aca="false">C79-M79</f>
         <v>0.0404112166628712</v>
       </c>
@@ -6142,7 +6116,7 @@
         <f aca="false">Data!C80-Data!D80</f>
         <v>-0.013709</v>
       </c>
-      <c r="E80" s="0" t="n">
+      <c r="E80" s="5" t="n">
         <f aca="false">0.2*C80+0.8*B80</f>
         <v>-0.0138461521539568</v>
       </c>
@@ -6154,11 +6128,11 @@
         <f aca="false">0.5*C80+0.5*B80</f>
         <v>-0.013794720096223</v>
       </c>
-      <c r="M80" s="10" t="n">
+      <c r="M80" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B80</f>
         <v>0.0044553123294133</v>
       </c>
-      <c r="N80" s="10" t="n">
+      <c r="N80" s="8" t="n">
         <f aca="false">C80-M80</f>
         <v>-0.0181643123294133</v>
       </c>
@@ -6175,7 +6149,7 @@
         <f aca="false">Data!C81-Data!D81</f>
         <v>-0.007143</v>
       </c>
-      <c r="E81" s="0" t="n">
+      <c r="E81" s="5" t="n">
         <f aca="false">0.2*C81+0.8*B81</f>
         <v>0.0304691119784657</v>
       </c>
@@ -6187,11 +6161,11 @@
         <f aca="false">0.5*C81+0.5*B81</f>
         <v>0.0163645699865411</v>
       </c>
-      <c r="M81" s="10" t="n">
+      <c r="M81" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B81</f>
         <v>0.00786559155461235</v>
       </c>
-      <c r="N81" s="10" t="n">
+      <c r="N81" s="8" t="n">
         <f aca="false">C81-M81</f>
         <v>-0.0150085915546123</v>
       </c>
@@ -6208,7 +6182,7 @@
         <f aca="false">Data!C82-Data!D82</f>
         <v>-0.058915</v>
       </c>
-      <c r="E82" s="0" t="n">
+      <c r="E82" s="5" t="n">
         <f aca="false">0.2*C82+0.8*B82</f>
         <v>-0.0231266812524782</v>
       </c>
@@ -6220,11 +6194,11 @@
         <f aca="false">0.5*C82+0.5*B82</f>
         <v>-0.0365473007827989</v>
       </c>
-      <c r="M82" s="10" t="n">
+      <c r="M82" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B82</f>
         <v>0.00443633233230992</v>
       </c>
-      <c r="N82" s="10" t="n">
+      <c r="N82" s="8" t="n">
         <f aca="false">C82-M82</f>
         <v>-0.0633513323323099</v>
       </c>
@@ -6241,23 +6215,23 @@
         <f aca="false">Data!C83-Data!D83</f>
         <v>-0.030372</v>
       </c>
-      <c r="E83" s="0" t="n">
+      <c r="E83" s="5" t="n">
         <f aca="false">0.2*C83+0.8*B83</f>
         <v>0.0133112805318973</v>
       </c>
       <c r="G83" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B83 + 'Optimal portfolio from homework'!$C$15*C83</f>
-        <v>0.00419967182244003</v>
+        <v>0.00419967182244006</v>
       </c>
       <c r="I83" s="9" t="n">
         <f aca="false">0.5*C83+0.5*B83</f>
         <v>-0.00306994966756421</v>
       </c>
-      <c r="M83" s="10" t="n">
+      <c r="M83" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B83</f>
         <v>0.00687332474677096</v>
       </c>
-      <c r="N83" s="10" t="n">
+      <c r="N83" s="8" t="n">
         <f aca="false">C83-M83</f>
         <v>-0.037245324746771</v>
       </c>
@@ -6274,7 +6248,7 @@
         <f aca="false">Data!C84-Data!D84</f>
         <v>0.009589</v>
       </c>
-      <c r="E84" s="0" t="n">
+      <c r="E84" s="5" t="n">
         <f aca="false">0.2*C84+0.8*B84</f>
         <v>0.0233770274678111</v>
       </c>
@@ -6286,11 +6260,11 @@
         <f aca="false">0.5*C84+0.5*B84</f>
         <v>0.0182065171673819</v>
       </c>
-      <c r="M84" s="10" t="n">
+      <c r="M84" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B84</f>
         <v>0.00703776741204038</v>
       </c>
-      <c r="N84" s="10" t="n">
+      <c r="N84" s="8" t="n">
         <f aca="false">C84-M84</f>
         <v>0.00255123258795962</v>
       </c>
@@ -6307,23 +6281,23 @@
         <f aca="false">Data!C85-Data!D85</f>
         <v>0.012453</v>
       </c>
-      <c r="E85" s="0" t="n">
+      <c r="E85" s="5" t="n">
         <f aca="false">0.2*C85+0.8*B85</f>
         <v>0.000375882081253688</v>
       </c>
       <c r="G85" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B85 + 'Optimal portfolio from homework'!$C$15*C85</f>
-        <v>0.0028949688227643</v>
+        <v>0.00289496882276429</v>
       </c>
       <c r="I85" s="9" t="n">
         <f aca="false">0.5*C85+0.5*B85</f>
         <v>0.00490480130078356</v>
       </c>
-      <c r="M85" s="10" t="n">
+      <c r="M85" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B85</f>
         <v>0.00516823538306183</v>
       </c>
-      <c r="N85" s="10" t="n">
+      <c r="N85" s="8" t="n">
         <f aca="false">C85-M85</f>
         <v>0.00728476461693817</v>
       </c>
@@ -6340,23 +6314,23 @@
         <f aca="false">Data!C86-Data!D86</f>
         <v>0.053575</v>
       </c>
-      <c r="E86" s="0" t="n">
+      <c r="E86" s="5" t="n">
         <f aca="false">0.2*C86+0.8*B86</f>
         <v>-0.013425291747854</v>
       </c>
       <c r="G86" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B86 + 'Optimal portfolio from homework'!$C$15*C86</f>
-        <v>0.00054985925712038</v>
+        <v>0.000549859257120356</v>
       </c>
       <c r="I86" s="9" t="n">
         <f aca="false">0.5*C86+0.5*B86</f>
         <v>0.0116998176575912</v>
       </c>
-      <c r="M86" s="10" t="n">
+      <c r="M86" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B86</f>
         <v>0.00342149697950087</v>
       </c>
-      <c r="N86" s="10" t="n">
+      <c r="N86" s="8" t="n">
         <f aca="false">C86-M86</f>
         <v>0.0501535030204991</v>
       </c>
@@ -6373,23 +6347,23 @@
         <f aca="false">Data!C87-Data!D87</f>
         <v>-0.0463</v>
       </c>
-      <c r="E87" s="0" t="n">
+      <c r="E87" s="5" t="n">
         <f aca="false">0.2*C87+0.8*B87</f>
         <v>0.0366565942658558</v>
       </c>
       <c r="G87" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B87 + 'Optimal portfolio from homework'!$C$15*C87</f>
-        <v>0.0193532228702997</v>
+        <v>0.0193532228702998</v>
       </c>
       <c r="I87" s="9" t="n">
         <f aca="false">0.5*C87+0.5*B87</f>
         <v>0.00554787141615987</v>
       </c>
-      <c r="M87" s="10" t="n">
+      <c r="M87" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B87</f>
         <v>0.00897735918692819</v>
       </c>
-      <c r="N87" s="10" t="n">
+      <c r="N87" s="8" t="n">
         <f aca="false">C87-M87</f>
         <v>-0.0552773591869282</v>
       </c>
@@ -6406,7 +6380,7 @@
         <f aca="false">Data!C88-Data!D88</f>
         <v>-0.021369</v>
       </c>
-      <c r="E88" s="0" t="n">
+      <c r="E88" s="5" t="n">
         <f aca="false">0.2*C88+0.8*B88</f>
         <v>-0.0170231513360711</v>
       </c>
@@ -6418,11 +6392,11 @@
         <f aca="false">0.5*C88+0.5*B88</f>
         <v>-0.0186528445850444</v>
       </c>
-      <c r="M88" s="10" t="n">
+      <c r="M88" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B88</f>
         <v>0.00432485564903261</v>
       </c>
-      <c r="N88" s="10" t="n">
+      <c r="N88" s="8" t="n">
         <f aca="false">C88-M88</f>
         <v>-0.0256938556490326</v>
       </c>
@@ -6439,7 +6413,7 @@
         <f aca="false">Data!C89-Data!D89</f>
         <v>0.021242</v>
       </c>
-      <c r="E89" s="0" t="n">
+      <c r="E89" s="5" t="n">
         <f aca="false">0.2*C89+0.8*B89</f>
         <v>0.011841079985318</v>
       </c>
@@ -6451,11 +6425,11 @@
         <f aca="false">0.5*C89+0.5*B89</f>
         <v>0.0153664249908238</v>
       </c>
-      <c r="M89" s="10" t="n">
+      <c r="M89" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B89</f>
         <v>0.00593808069330151</v>
       </c>
-      <c r="N89" s="10" t="n">
+      <c r="N89" s="8" t="n">
         <f aca="false">C89-M89</f>
         <v>0.0153039193066985</v>
       </c>
@@ -6472,23 +6446,23 @@
         <f aca="false">Data!C90-Data!D90</f>
         <v>-0.011542</v>
       </c>
-      <c r="E90" s="0" t="n">
+      <c r="E90" s="5" t="n">
         <f aca="false">0.2*C90+0.8*B90</f>
         <v>0.00787236044047369</v>
       </c>
       <c r="G90" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B90 + 'Optimal portfolio from homework'!$C$15*C90</f>
-        <v>0.00382284644967362</v>
+        <v>0.00382284644967363</v>
       </c>
       <c r="I90" s="9" t="n">
         <f aca="false">0.5*C90+0.5*B90</f>
         <v>0.000591975275296055</v>
       </c>
-      <c r="M90" s="10" t="n">
+      <c r="M90" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B90</f>
         <v>0.00614332844564618</v>
       </c>
-      <c r="N90" s="10" t="n">
+      <c r="N90" s="8" t="n">
         <f aca="false">C90-M90</f>
         <v>-0.0176853284456462</v>
       </c>
@@ -6505,23 +6479,23 @@
         <f aca="false">Data!C91-Data!D91</f>
         <v>-0.012937</v>
       </c>
-      <c r="E91" s="0" t="n">
+      <c r="E91" s="5" t="n">
         <f aca="false">0.2*C91+0.8*B91</f>
         <v>-0.0180507357459402</v>
       </c>
       <c r="G91" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B91 + 'Optimal portfolio from homework'!$C$15*C91</f>
-        <v>-0.0169840951778961</v>
+        <v>-0.0169840951778962</v>
       </c>
       <c r="I91" s="9" t="n">
         <f aca="false">0.5*C91+0.5*B91</f>
         <v>-0.0161330848412126</v>
       </c>
-      <c r="M91" s="10" t="n">
+      <c r="M91" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B91</f>
         <v>0.00410962308201003</v>
       </c>
-      <c r="N91" s="10" t="n">
+      <c r="N91" s="8" t="n">
         <f aca="false">C91-M91</f>
         <v>-0.01704662308201</v>
       </c>
@@ -6538,7 +6512,7 @@
         <f aca="false">Data!C92-Data!D92</f>
         <v>-0.080809</v>
       </c>
-      <c r="E92" s="0" t="n">
+      <c r="E92" s="5" t="n">
         <f aca="false">0.2*C92+0.8*B92</f>
         <v>0.000480351712544617</v>
       </c>
@@ -6550,11 +6524,11 @@
         <f aca="false">0.5*C92+0.5*B92</f>
         <v>-0.0300031551796596</v>
       </c>
-      <c r="M92" s="10" t="n">
+      <c r="M92" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B92</f>
         <v>0.00665574915999072</v>
       </c>
-      <c r="N92" s="10" t="n">
+      <c r="N92" s="8" t="n">
         <f aca="false">C92-M92</f>
         <v>-0.0874647491599907</v>
       </c>
@@ -6571,7 +6545,7 @@
         <f aca="false">Data!C93-Data!D93</f>
         <v>0.042081</v>
       </c>
-      <c r="E93" s="0" t="n">
+      <c r="E93" s="5" t="n">
         <f aca="false">0.2*C93+0.8*B93</f>
         <v>-0.0399164471799094</v>
       </c>
@@ -6583,11 +6557,11 @@
         <f aca="false">0.5*C93+0.5*B93</f>
         <v>-0.00916740448744337</v>
       </c>
-      <c r="M93" s="10" t="n">
+      <c r="M93" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B93</f>
         <v>0.00150292193425404</v>
       </c>
-      <c r="N93" s="10" t="n">
+      <c r="N93" s="8" t="n">
         <f aca="false">C93-M93</f>
         <v>0.040578078065746</v>
       </c>
@@ -6604,7 +6578,7 @@
         <f aca="false">Data!C94-Data!D94</f>
         <v>-0.002665</v>
       </c>
-      <c r="E94" s="0" t="n">
+      <c r="E94" s="5" t="n">
         <f aca="false">0.2*C94+0.8*B94</f>
         <v>-0.0204532752219876</v>
       </c>
@@ -6616,11 +6590,11 @@
         <f aca="false">0.5*C94+0.5*B94</f>
         <v>-0.0137826720137423</v>
       </c>
-      <c r="M94" s="10" t="n">
+      <c r="M94" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B94</f>
         <v>0.00375616544201563</v>
       </c>
-      <c r="N94" s="10" t="n">
+      <c r="N94" s="8" t="n">
         <f aca="false">C94-M94</f>
         <v>-0.00642116544201563</v>
       </c>
@@ -6637,23 +6611,23 @@
         <f aca="false">Data!C95-Data!D95</f>
         <v>0.022494</v>
       </c>
-      <c r="E95" s="0" t="n">
+      <c r="E95" s="5" t="n">
         <f aca="false">0.2*C95+0.8*B95</f>
         <v>0.0718805319634189</v>
       </c>
       <c r="G95" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B95 + 'Optimal portfolio from homework'!$C$15*C95</f>
-        <v>0.061579319479178</v>
+        <v>0.0615793194791781</v>
       </c>
       <c r="I95" s="9" t="n">
         <f aca="false">0.5*C95+0.5*B95</f>
         <v>0.0533605824771368</v>
       </c>
-      <c r="M95" s="10" t="n">
+      <c r="M95" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B95</f>
         <v>0.0106796521961804</v>
       </c>
-      <c r="N95" s="10" t="n">
+      <c r="N95" s="8" t="n">
         <f aca="false">C95-M95</f>
         <v>0.0118143478038196</v>
       </c>
@@ -6670,23 +6644,23 @@
         <f aca="false">Data!C96-Data!D96</f>
         <v>-0.080244</v>
       </c>
-      <c r="E96" s="0" t="n">
+      <c r="E96" s="5" t="n">
         <f aca="false">0.2*C96+0.8*B96</f>
         <v>-0.013757849255441</v>
       </c>
       <c r="G96" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B96 + 'Optimal portfolio from homework'!$C$15*C96</f>
-        <v>-0.0276257589638262</v>
+        <v>-0.0276257589638261</v>
       </c>
       <c r="I96" s="9" t="n">
         <f aca="false">0.5*C96+0.5*B96</f>
         <v>-0.0386901557846506</v>
       </c>
-      <c r="M96" s="10" t="n">
+      <c r="M96" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B96</f>
         <v>0.00551762699062079</v>
       </c>
-      <c r="N96" s="10" t="n">
+      <c r="N96" s="8" t="n">
         <f aca="false">C96-M96</f>
         <v>-0.0857616269906208</v>
       </c>
@@ -6703,23 +6677,23 @@
         <f aca="false">Data!C97-Data!D97</f>
         <v>0.006152</v>
       </c>
-      <c r="E97" s="0" t="n">
+      <c r="E97" s="5" t="n">
         <f aca="false">0.2*C97+0.8*B97</f>
         <v>-0.011590289264695</v>
       </c>
       <c r="G97" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B97 + 'Optimal portfolio from homework'!$C$15*C97</f>
-        <v>-0.00788954162345818</v>
+        <v>-0.00788954162345817</v>
       </c>
       <c r="I97" s="9" t="n">
         <f aca="false">0.5*C97+0.5*B97</f>
         <v>-0.00493693079043437</v>
       </c>
-      <c r="M97" s="10" t="n">
+      <c r="M97" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B97</f>
         <v>0.00431919819372522</v>
       </c>
-      <c r="N97" s="10" t="n">
+      <c r="N97" s="8" t="n">
         <f aca="false">C97-M97</f>
         <v>0.00183280180627478</v>
       </c>
@@ -6736,23 +6710,23 @@
         <f aca="false">Data!C98-Data!D98</f>
         <v>0.047582</v>
       </c>
-      <c r="E98" s="0" t="n">
+      <c r="E98" s="5" t="n">
         <f aca="false">0.2*C98+0.8*B98</f>
         <v>-0.0303768427843803</v>
       </c>
       <c r="G98" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B98 + 'Optimal portfolio from homework'!$C$15*C98</f>
-        <v>-0.0141159195605695</v>
+        <v>-0.0141159195605696</v>
       </c>
       <c r="I98" s="9" t="n">
         <f aca="false">0.5*C98+0.5*B98</f>
         <v>-0.00114227674023766</v>
       </c>
-      <c r="M98" s="10" t="n">
+      <c r="M98" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B98</f>
         <v>0.00217220900369559</v>
       </c>
-      <c r="N98" s="10" t="n">
+      <c r="N98" s="8" t="n">
         <f aca="false">C98-M98</f>
         <v>0.0454097909963044</v>
       </c>
@@ -6769,23 +6743,23 @@
         <f aca="false">Data!C99-Data!D99</f>
         <v>0.10875</v>
       </c>
-      <c r="E99" s="0" t="n">
+      <c r="E99" s="5" t="n">
         <f aca="false">0.2*C99+0.8*B99</f>
         <v>0.0204286376326075</v>
       </c>
       <c r="G99" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B99 + 'Optimal portfolio from homework'!$C$15*C99</f>
-        <v>0.0388510107872574</v>
+        <v>0.0388510107872573</v>
       </c>
       <c r="I99" s="9" t="n">
         <f aca="false">0.5*C99+0.5*B99</f>
         <v>0.0535491485203797</v>
       </c>
-      <c r="M99" s="10" t="n">
+      <c r="M99" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B99</f>
         <v>0.00523115245482487</v>
       </c>
-      <c r="N99" s="10" t="n">
+      <c r="N99" s="8" t="n">
         <f aca="false">C99-M99</f>
         <v>0.103518847545175</v>
       </c>
@@ -6802,23 +6776,23 @@
         <f aca="false">Data!C100-Data!D100</f>
         <v>-0.000646</v>
       </c>
-      <c r="E100" s="0" t="n">
+      <c r="E100" s="5" t="n">
         <f aca="false">0.2*C100+0.8*B100</f>
         <v>0.0539143006497395</v>
       </c>
       <c r="G100" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B100 + 'Optimal portfolio from homework'!$C$15*C100</f>
-        <v>0.0425339257205313</v>
+        <v>0.0425339257205314</v>
       </c>
       <c r="I100" s="9" t="n">
         <f aca="false">0.5*C100+0.5*B100</f>
         <v>0.0334541879060872</v>
       </c>
-      <c r="M100" s="10" t="n">
+      <c r="M100" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B100</f>
         <v>0.00962186359771063</v>
       </c>
-      <c r="N100" s="10" t="n">
+      <c r="N100" s="8" t="n">
         <f aca="false">C100-M100</f>
         <v>-0.0102678635977106</v>
       </c>
@@ -6835,7 +6809,7 @@
         <f aca="false">Data!C101-Data!D101</f>
         <v>0.033055</v>
       </c>
-      <c r="E101" s="0" t="n">
+      <c r="E101" s="5" t="n">
         <f aca="false">0.2*C101+0.8*B101</f>
         <v>0.00952063103321217</v>
       </c>
@@ -6847,11 +6821,11 @@
         <f aca="false">0.5*C101+0.5*B101</f>
         <v>0.0183460193957576</v>
       </c>
-      <c r="M101" s="10" t="n">
+      <c r="M101" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B101</f>
         <v>0.00556669143852582</v>
       </c>
-      <c r="N101" s="10" t="n">
+      <c r="N101" s="8" t="n">
         <f aca="false">C101-M101</f>
         <v>0.0274883085614742</v>
       </c>
@@ -6868,23 +6842,23 @@
         <f aca="false">Data!C102-Data!D102</f>
         <v>-0.050316</v>
       </c>
-      <c r="E102" s="0" t="n">
+      <c r="E102" s="5" t="n">
         <f aca="false">0.2*C102+0.8*B102</f>
         <v>0.00412004069218676</v>
       </c>
       <c r="G102" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B102 + 'Optimal portfolio from homework'!$C$15*C102</f>
-        <v>-0.00723441566823062</v>
+        <v>-0.00723441566823056</v>
       </c>
       <c r="I102" s="9" t="n">
         <f aca="false">0.5*C102+0.5*B102</f>
         <v>-0.0162934745673833</v>
       </c>
-      <c r="M102" s="10" t="n">
+      <c r="M102" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B102</f>
         <v>0.00646074519126224</v>
       </c>
-      <c r="N102" s="10" t="n">
+      <c r="N102" s="8" t="n">
         <f aca="false">C102-M102</f>
         <v>-0.0567767451912622</v>
       </c>
@@ -6901,23 +6875,23 @@
         <f aca="false">Data!C103-Data!D103</f>
         <v>0.08778</v>
       </c>
-      <c r="E103" s="0" t="n">
+      <c r="E103" s="5" t="n">
         <f aca="false">0.2*C103+0.8*B103</f>
         <v>0.0193957227071896</v>
       </c>
       <c r="G103" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B103 + 'Optimal portfolio from homework'!$C$15*C103</f>
-        <v>0.0336595501712495</v>
+        <v>0.0336595501712494</v>
       </c>
       <c r="I103" s="9" t="n">
         <f aca="false">0.5*C103+0.5*B103</f>
         <v>0.0450398266919935</v>
       </c>
-      <c r="M103" s="10" t="n">
+      <c r="M103" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B103</f>
         <v>0.00548184234556446</v>
       </c>
-      <c r="N103" s="10" t="n">
+      <c r="N103" s="8" t="n">
         <f aca="false">C103-M103</f>
         <v>0.0822981576544355</v>
       </c>
@@ -6934,7 +6908,7 @@
         <f aca="false">Data!C104-Data!D104</f>
         <v>0.011569</v>
       </c>
-      <c r="E104" s="0" t="n">
+      <c r="E104" s="5" t="n">
         <f aca="false">0.2*C104+0.8*B104</f>
         <v>0.031564653513709</v>
       </c>
@@ -6946,11 +6920,11 @@
         <f aca="false">0.5*C104+0.5*B104</f>
         <v>0.0240662834460681</v>
       </c>
-      <c r="M104" s="10" t="n">
+      <c r="M104" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B104</f>
         <v>0.00765568241149295</v>
       </c>
-      <c r="N104" s="10" t="n">
+      <c r="N104" s="8" t="n">
         <f aca="false">C104-M104</f>
         <v>0.00391331758850705</v>
       </c>
@@ -6967,23 +6941,23 @@
         <f aca="false">Data!C105-Data!D105</f>
         <v>-0.013746</v>
       </c>
-      <c r="E105" s="0" t="n">
+      <c r="E105" s="5" t="n">
         <f aca="false">0.2*C105+0.8*B105</f>
         <v>-0.00187329183724284</v>
       </c>
       <c r="G105" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B105 + 'Optimal portfolio from homework'!$C$15*C105</f>
-        <v>-0.00434974208968279</v>
+        <v>-0.00434974208968278</v>
       </c>
       <c r="I105" s="9" t="n">
         <f aca="false">0.5*C105+0.5*B105</f>
         <v>-0.00632555739827678</v>
       </c>
-      <c r="M105" s="10" t="n">
+      <c r="M105" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B105</f>
         <v>0.00540540702125768</v>
       </c>
-      <c r="N105" s="10" t="n">
+      <c r="N105" s="8" t="n">
         <f aca="false">C105-M105</f>
         <v>-0.0191514070212577</v>
       </c>
@@ -7000,23 +6974,23 @@
         <f aca="false">Data!C106-Data!D106</f>
         <v>0.010032</v>
       </c>
-      <c r="E106" s="0" t="n">
+      <c r="E106" s="5" t="n">
         <f aca="false">0.2*C106+0.8*B106</f>
         <v>0.00191185182901974</v>
       </c>
       <c r="G106" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B106 + 'Optimal portfolio from homework'!$C$15*C106</f>
-        <v>0.00360558022798377</v>
+        <v>0.00360558022798376</v>
       </c>
       <c r="I106" s="9" t="n">
         <f aca="false">0.5*C106+0.5*B106</f>
         <v>0.00495690739313733</v>
       </c>
-      <c r="M106" s="10" t="n">
+      <c r="M106" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B106</f>
         <v>0.00532844496976834</v>
       </c>
-      <c r="N106" s="10" t="n">
+      <c r="N106" s="8" t="n">
         <f aca="false">C106-M106</f>
         <v>0.00470355503023166</v>
       </c>
@@ -7033,7 +7007,7 @@
         <f aca="false">Data!C107-Data!D107</f>
         <v>-0.04064</v>
       </c>
-      <c r="E107" s="0" t="n">
+      <c r="E107" s="5" t="n">
         <f aca="false">0.2*C107+0.8*B107</f>
         <v>-0.0229526021677239</v>
       </c>
@@ -7045,11 +7019,11 @@
         <f aca="false">0.5*C107+0.5*B107</f>
         <v>-0.0295853763548275</v>
       </c>
-      <c r="M107" s="10" t="n">
+      <c r="M107" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B107</f>
         <v>0.00416027785629064</v>
       </c>
-      <c r="N107" s="10" t="n">
+      <c r="N107" s="8" t="n">
         <f aca="false">C107-M107</f>
         <v>-0.0448002778562906</v>
       </c>
@@ -7066,23 +7040,23 @@
         <f aca="false">Data!C108-Data!D108</f>
         <v>-0.068221</v>
       </c>
-      <c r="E108" s="0" t="n">
+      <c r="E108" s="5" t="n">
         <f aca="false">0.2*C108+0.8*B108</f>
         <v>0.0158677405718939</v>
       </c>
       <c r="G108" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B108 + 'Optimal portfolio from homework'!$C$15*C108</f>
-        <v>-0.00167177778920301</v>
+        <v>-0.00167177778920294</v>
       </c>
       <c r="I108" s="9" t="n">
         <f aca="false">0.5*C108+0.5*B108</f>
         <v>-0.0156655371425663</v>
       </c>
-      <c r="M108" s="10" t="n">
+      <c r="M108" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B108</f>
         <v>0.00767638792385521</v>
       </c>
-      <c r="N108" s="10" t="n">
+      <c r="N108" s="8" t="n">
         <f aca="false">C108-M108</f>
         <v>-0.0758973879238552</v>
       </c>
@@ -7099,23 +7073,23 @@
         <f aca="false">Data!C109-Data!D109</f>
         <v>-0.024134</v>
       </c>
-      <c r="E109" s="0" t="n">
+      <c r="E109" s="5" t="n">
         <f aca="false">0.2*C109+0.8*B109</f>
         <v>0.0106341501312114</v>
       </c>
       <c r="G109" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B109 + 'Optimal portfolio from homework'!$C$15*C109</f>
-        <v>0.00338208994502777</v>
+        <v>0.00338208994502776</v>
       </c>
       <c r="I109" s="9" t="n">
         <f aca="false">0.5*C109+0.5*B109</f>
         <v>-0.00240390616799288</v>
       </c>
-      <c r="M109" s="10" t="n">
+      <c r="M109" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B109</f>
         <v>0.0065620739540474</v>
       </c>
-      <c r="N109" s="10" t="n">
+      <c r="N109" s="8" t="n">
         <f aca="false">C109-M109</f>
         <v>-0.0306960739540474</v>
       </c>
@@ -7132,7 +7106,7 @@
         <f aca="false">Data!C110-Data!D110</f>
         <v>0.033851</v>
       </c>
-      <c r="E110" s="0" t="n">
+      <c r="E110" s="5" t="n">
         <f aca="false">0.2*C110+0.8*B110</f>
         <v>0.0215153111003535</v>
       </c>
@@ -7144,11 +7118,11 @@
         <f aca="false">0.5*C110+0.5*B110</f>
         <v>0.0261411944377209</v>
       </c>
-      <c r="M110" s="10" t="n">
+      <c r="M110" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B110</f>
         <v>0.0065053043308962</v>
       </c>
-      <c r="N110" s="10" t="n">
+      <c r="N110" s="8" t="n">
         <f aca="false">C110-M110</f>
         <v>0.0273456956691038</v>
       </c>
@@ -7165,7 +7139,7 @@
         <f aca="false">Data!C111-Data!D111</f>
         <v>0.043894</v>
       </c>
-      <c r="E111" s="0" t="n">
+      <c r="E111" s="5" t="n">
         <f aca="false">0.2*C111+0.8*B111</f>
         <v>0.0401607861256297</v>
       </c>
@@ -7177,11 +7151,11 @@
         <f aca="false">0.5*C111+0.5*B111</f>
         <v>0.0415607413285185</v>
       </c>
-      <c r="M111" s="10" t="n">
+      <c r="M111" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B111</f>
         <v>0.00782469190950674</v>
       </c>
-      <c r="N111" s="10" t="n">
+      <c r="N111" s="8" t="n">
         <f aca="false">C111-M111</f>
         <v>0.0360693080904933</v>
       </c>
@@ -7198,23 +7172,23 @@
         <f aca="false">Data!C112-Data!D112</f>
         <v>-0.008448</v>
       </c>
-      <c r="E112" s="0" t="n">
+      <c r="E112" s="5" t="n">
         <f aca="false">0.2*C112+0.8*B112</f>
         <v>-0.00112919976226487</v>
       </c>
       <c r="G112" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B112 + 'Optimal portfolio from homework'!$C$15*C112</f>
-        <v>-0.00265578025660827</v>
+        <v>-0.00265578025660826</v>
       </c>
       <c r="I112" s="9" t="n">
         <f aca="false">0.5*C112+0.5*B112</f>
         <v>-0.00387374985141554</v>
       </c>
-      <c r="M112" s="10" t="n">
+      <c r="M112" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B112</f>
         <v>0.00538038566138122</v>
       </c>
-      <c r="N112" s="10" t="n">
+      <c r="N112" s="8" t="n">
         <f aca="false">C112-M112</f>
         <v>-0.0138283856613812</v>
       </c>
@@ -7231,7 +7205,7 @@
         <f aca="false">Data!C113-Data!D113</f>
         <v>0.018707</v>
       </c>
-      <c r="E113" s="0" t="n">
+      <c r="E113" s="5" t="n">
         <f aca="false">0.2*C113+0.8*B113</f>
         <v>0.0114863208897041</v>
       </c>
@@ -7243,11 +7217,11 @@
         <f aca="false">0.5*C113+0.5*B113</f>
         <v>0.0141940755560651</v>
       </c>
-      <c r="M113" s="10" t="n">
+      <c r="M113" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B113</f>
         <v>0.0059501541600973</v>
       </c>
-      <c r="N113" s="10" t="n">
+      <c r="N113" s="8" t="n">
         <f aca="false">C113-M113</f>
         <v>0.0127568458399027</v>
       </c>
@@ -7264,23 +7238,23 @@
         <f aca="false">Data!C114-Data!D114</f>
         <v>-0.001983</v>
       </c>
-      <c r="E114" s="0" t="n">
+      <c r="E114" s="5" t="n">
         <f aca="false">0.2*C114+0.8*B114</f>
         <v>0.0102733523312299</v>
       </c>
       <c r="G114" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B114 + 'Optimal portfolio from homework'!$C$15*C114</f>
-        <v>0.00771688026027663</v>
+        <v>0.00771688026027662</v>
       </c>
       <c r="I114" s="9" t="n">
         <f aca="false">0.5*C114+0.5*B114</f>
         <v>0.00567722020701866</v>
       </c>
-      <c r="M114" s="10" t="n">
+      <c r="M114" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B114</f>
         <v>0.00618212381456252</v>
       </c>
-      <c r="N114" s="10" t="n">
+      <c r="N114" s="8" t="n">
         <f aca="false">C114-M114</f>
         <v>-0.00816512381456252</v>
       </c>
@@ -7297,23 +7271,23 @@
         <f aca="false">Data!C115-Data!D115</f>
         <v>-0.01686</v>
       </c>
-      <c r="E115" s="0" t="n">
+      <c r="E115" s="5" t="n">
         <f aca="false">0.2*C115+0.8*B115</f>
         <v>0.00104062546394897</v>
       </c>
       <c r="G115" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B115 + 'Optimal portfolio from homework'!$C$15*C115</f>
-        <v>-0.00269314848562774</v>
+        <v>-0.00269314848562773</v>
       </c>
       <c r="I115" s="9" t="n">
         <f aca="false">0.5*C115+0.5*B115</f>
         <v>-0.00567210908503189</v>
       </c>
-      <c r="M115" s="10" t="n">
+      <c r="M115" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B115</f>
         <v>0.00568588643035104</v>
       </c>
-      <c r="N115" s="10" t="n">
+      <c r="N115" s="8" t="n">
         <f aca="false">C115-M115</f>
         <v>-0.022545886430351</v>
       </c>
@@ -7330,7 +7304,7 @@
         <f aca="false">Data!C116-Data!D116</f>
         <v>0.01788</v>
       </c>
-      <c r="E116" s="0" t="n">
+      <c r="E116" s="5" t="n">
         <f aca="false">0.2*C116+0.8*B116</f>
         <v>0.0193556648044692</v>
       </c>
@@ -7342,11 +7316,11 @@
         <f aca="false">0.5*C116+0.5*B116</f>
         <v>0.0188022905027933</v>
       </c>
-      <c r="M116" s="10" t="n">
+      <c r="M116" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B116</f>
         <v>0.00658734962513217</v>
       </c>
-      <c r="N116" s="10" t="n">
+      <c r="N116" s="8" t="n">
         <f aca="false">C116-M116</f>
         <v>0.0112926503748678</v>
       </c>
@@ -7363,7 +7337,7 @@
         <f aca="false">Data!C117-Data!D117</f>
         <v>0.030253</v>
       </c>
-      <c r="E117" s="0" t="n">
+      <c r="E117" s="5" t="n">
         <f aca="false">0.2*C117+0.8*B117</f>
         <v>0.00767818234057466</v>
       </c>
@@ -7375,11 +7349,11 @@
         <f aca="false">0.5*C117+0.5*B117</f>
         <v>0.0161437389628592</v>
       </c>
-      <c r="M117" s="10" t="n">
+      <c r="M117" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B117</f>
         <v>0.0054650185511795</v>
       </c>
-      <c r="N117" s="10" t="n">
+      <c r="N117" s="8" t="n">
         <f aca="false">C117-M117</f>
         <v>0.0247879814488205</v>
       </c>
@@ -7396,23 +7370,23 @@
         <f aca="false">Data!C118-Data!D118</f>
         <v>-0.015336</v>
       </c>
-      <c r="E118" s="0" t="n">
+      <c r="E118" s="5" t="n">
         <f aca="false">0.2*C118+0.8*B118</f>
         <v>0.0126854873870723</v>
       </c>
       <c r="G118" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B118 + 'Optimal portfolio from homework'!$C$15*C118</f>
-        <v>0.00684066929147255</v>
+        <v>0.00684066929147257</v>
       </c>
       <c r="I118" s="9" t="n">
         <f aca="false">0.5*C118+0.5*B118</f>
         <v>0.0021774296169202</v>
       </c>
-      <c r="M118" s="10" t="n">
+      <c r="M118" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B118</f>
         <v>0.00658521018071352</v>
       </c>
-      <c r="N118" s="10" t="n">
+      <c r="N118" s="8" t="n">
         <f aca="false">C118-M118</f>
         <v>-0.0219212101807135</v>
       </c>
@@ -7429,7 +7403,7 @@
         <f aca="false">Data!C119-Data!D119</f>
         <v>-0.010652</v>
       </c>
-      <c r="E119" s="0" t="n">
+      <c r="E119" s="5" t="n">
         <f aca="false">0.2*C119+0.8*B119</f>
         <v>0.0156902544266243</v>
       </c>
@@ -7441,11 +7415,11 @@
         <f aca="false">0.5*C119+0.5*B119</f>
         <v>0.00581190901664019</v>
       </c>
-      <c r="M119" s="10" t="n">
+      <c r="M119" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B119</f>
         <v>0.0067492103322333</v>
       </c>
-      <c r="N119" s="10" t="n">
+      <c r="N119" s="8" t="n">
         <f aca="false">C119-M119</f>
         <v>-0.0174012103322333</v>
       </c>
@@ -7462,23 +7436,23 @@
         <f aca="false">Data!C120-Data!D120</f>
         <v>0.005281</v>
       </c>
-      <c r="E120" s="0" t="n">
+      <c r="E120" s="5" t="n">
         <f aca="false">0.2*C120+0.8*B120</f>
         <v>0.0248909016305261</v>
       </c>
       <c r="G120" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B120 + 'Optimal portfolio from homework'!$C$15*C120</f>
-        <v>0.0208006009866028</v>
+        <v>0.0208006009866029</v>
       </c>
       <c r="I120" s="9" t="n">
         <f aca="false">0.5*C120+0.5*B120</f>
         <v>0.0175371885190788</v>
       </c>
-      <c r="M120" s="10" t="n">
+      <c r="M120" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B120</f>
         <v>0.00722615441974674</v>
       </c>
-      <c r="N120" s="10" t="n">
+      <c r="N120" s="8" t="n">
         <f aca="false">C120-M120</f>
         <v>-0.00194515441974675</v>
       </c>
@@ -7495,7 +7469,7 @@
         <f aca="false">Data!C121-Data!D121</f>
         <v>0.010292</v>
       </c>
-      <c r="E121" s="0" t="n">
+      <c r="E121" s="5" t="n">
         <f aca="false">0.2*C121+0.8*B121</f>
         <v>0.0101543066693075</v>
       </c>
@@ -7507,11 +7481,11 @@
         <f aca="false">0.5*C121+0.5*B121</f>
         <v>0.0102059416683172</v>
       </c>
-      <c r="M121" s="10" t="n">
+      <c r="M121" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B121</f>
         <v>0.00597798909166793</v>
       </c>
-      <c r="N121" s="10" t="n">
+      <c r="N121" s="8" t="n">
         <f aca="false">C121-M121</f>
         <v>0.00431401090833207</v>
       </c>
@@ -7528,7 +7502,7 @@
         <f aca="false">Data!C122-Data!D122</f>
         <v>0.035036</v>
       </c>
-      <c r="E122" s="0" t="n">
+      <c r="E122" s="5" t="n">
         <f aca="false">0.2*C122+0.8*B122</f>
         <v>0.0518285208005835</v>
       </c>
@@ -7540,11 +7514,11 @@
         <f aca="false">0.5*C122+0.5*B122</f>
         <v>0.0455313255003647</v>
       </c>
-      <c r="M122" s="10" t="n">
+      <c r="M122" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B122</f>
         <v>0.00889049851128649</v>
       </c>
-      <c r="N122" s="10" t="n">
+      <c r="N122" s="8" t="n">
         <f aca="false">C122-M122</f>
         <v>0.0261455014887135</v>
       </c>
@@ -7561,7 +7535,7 @@
         <f aca="false">Data!C123-Data!D123</f>
         <v>-0.018259</v>
       </c>
-      <c r="E123" s="0" t="n">
+      <c r="E123" s="5" t="n">
         <f aca="false">0.2*C123+0.8*B123</f>
         <v>-0.0341194130614748</v>
       </c>
@@ -7573,11 +7547,11 @@
         <f aca="false">0.5*C123+0.5*B123</f>
         <v>-0.0281717581634218</v>
       </c>
-      <c r="M123" s="10" t="n">
+      <c r="M123" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B123</f>
         <v>0.00291970868486106</v>
       </c>
-      <c r="N123" s="10" t="n">
+      <c r="N123" s="8" t="n">
         <f aca="false">C123-M123</f>
         <v>-0.0211787086848611</v>
       </c>
@@ -7594,23 +7568,23 @@
         <f aca="false">Data!C124-Data!D124</f>
         <v>0.001527</v>
       </c>
-      <c r="E124" s="0" t="n">
+      <c r="E124" s="5" t="n">
         <f aca="false">0.2*C124+0.8*B124</f>
         <v>-0.0210668165406182</v>
       </c>
       <c r="G124" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B124 + 'Optimal portfolio from homework'!$C$15*C124</f>
-        <v>-0.0163541206747238</v>
+        <v>-0.0163541206747239</v>
       </c>
       <c r="I124" s="9" t="n">
         <f aca="false">0.5*C124+0.5*B124</f>
         <v>-0.0125941353378864</v>
       </c>
-      <c r="M124" s="10" t="n">
+      <c r="M124" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B124</f>
         <v>0.00364101921787425</v>
       </c>
-      <c r="N124" s="10" t="n">
+      <c r="N124" s="8" t="n">
         <f aca="false">C124-M124</f>
         <v>-0.00211401921787425</v>
       </c>
@@ -7627,23 +7601,23 @@
         <f aca="false">Data!C125-Data!D125</f>
         <v>-0.007178</v>
       </c>
-      <c r="E125" s="0" t="n">
+      <c r="E125" s="5" t="n">
         <f aca="false">0.2*C125+0.8*B125</f>
         <v>0.000430331668102282</v>
       </c>
       <c r="G125" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B125 + 'Optimal portfolio from homework'!$C$15*C125</f>
-        <v>-0.00115664028655438</v>
+        <v>-0.00115664028655437</v>
       </c>
       <c r="I125" s="9" t="n">
         <f aca="false">0.5*C125+0.5*B125</f>
         <v>-0.00242279270743607</v>
       </c>
-      <c r="M125" s="10" t="n">
+      <c r="M125" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B125</f>
         <v>0.00548392084753217</v>
       </c>
-      <c r="N125" s="10" t="n">
+      <c r="N125" s="8" t="n">
         <f aca="false">C125-M125</f>
         <v>-0.0126619208475322</v>
       </c>
@@ -7660,23 +7634,23 @@
         <f aca="false">Data!C126-Data!D126</f>
         <v>-0.011087</v>
       </c>
-      <c r="E126" s="0" t="n">
+      <c r="E126" s="5" t="n">
         <f aca="false">0.2*C126+0.8*B126</f>
         <v>0.0158191871199739</v>
       </c>
       <c r="G126" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B126 + 'Optimal portfolio from homework'!$C$15*C126</f>
-        <v>0.0102070021852452</v>
+        <v>0.0102070021852453</v>
       </c>
       <c r="I126" s="9" t="n">
         <f aca="false">0.5*C126+0.5*B126</f>
         <v>0.00572936694998368</v>
       </c>
-      <c r="M126" s="10" t="n">
+      <c r="M126" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B126</f>
         <v>0.00676633487713663</v>
       </c>
-      <c r="N126" s="10" t="n">
+      <c r="N126" s="8" t="n">
         <f aca="false">C126-M126</f>
         <v>-0.0178533348771366</v>
       </c>
@@ -7693,7 +7667,7 @@
         <f aca="false">Data!C127-Data!D127</f>
         <v>-0.042021</v>
       </c>
-      <c r="E127" s="0" t="n">
+      <c r="E127" s="5" t="n">
         <f aca="false">0.2*C127+0.8*B127</f>
         <v>-0.00468376681233853</v>
       </c>
@@ -7705,11 +7679,11 @@
         <f aca="false">0.5*C127+0.5*B127</f>
         <v>-0.0186852292577116</v>
       </c>
-      <c r="M127" s="10" t="n">
+      <c r="M127" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B127</f>
         <v>0.00563099211336204</v>
       </c>
-      <c r="N127" s="10" t="n">
+      <c r="N127" s="8" t="n">
         <f aca="false">C127-M127</f>
         <v>-0.047651992113362</v>
       </c>
@@ -7726,7 +7700,7 @@
         <f aca="false">Data!C128-Data!D128</f>
         <v>-0.026669</v>
       </c>
-      <c r="E128" s="0" t="n">
+      <c r="E128" s="5" t="n">
         <f aca="false">0.2*C128+0.8*B128</f>
         <v>0.023060689023467</v>
       </c>
@@ -7738,11 +7712,11 @@
         <f aca="false">0.5*C128+0.5*B128</f>
         <v>0.0044120556396669</v>
       </c>
-      <c r="M128" s="10" t="n">
+      <c r="M128" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B128</f>
         <v>0.00758776841505602</v>
       </c>
-      <c r="N128" s="10" t="n">
+      <c r="N128" s="8" t="n">
         <f aca="false">C128-M128</f>
         <v>-0.034256768415056</v>
       </c>
@@ -7759,23 +7733,23 @@
         <f aca="false">Data!C129-Data!D129</f>
         <v>-0.01173</v>
       </c>
-      <c r="E129" s="0" t="n">
+      <c r="E129" s="5" t="n">
         <f aca="false">0.2*C129+0.8*B129</f>
         <v>0.0223440345754897</v>
       </c>
       <c r="G129" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B129 + 'Optimal portfolio from homework'!$C$15*C129</f>
-        <v>0.0152367553962697</v>
+        <v>0.0152367553962698</v>
       </c>
       <c r="I129" s="9" t="n">
         <f aca="false">0.5*C129+0.5*B129</f>
         <v>0.00956627160968107</v>
       </c>
-      <c r="M129" s="10" t="n">
+      <c r="M129" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B129</f>
         <v>0.00729398660947269</v>
       </c>
-      <c r="N129" s="10" t="n">
+      <c r="N129" s="8" t="n">
         <f aca="false">C129-M129</f>
         <v>-0.0190239866094727</v>
       </c>
@@ -7792,23 +7766,23 @@
         <f aca="false">Data!C130-Data!D130</f>
         <v>-0.020848</v>
       </c>
-      <c r="E130" s="0" t="n">
+      <c r="E130" s="5" t="n">
         <f aca="false">0.2*C130+0.8*B130</f>
         <v>-0.000934800574354315</v>
       </c>
       <c r="G130" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B130 + 'Optimal portfolio from homework'!$C$15*C130</f>
-        <v>-0.00508836411423967</v>
+        <v>-0.00508836411423965</v>
       </c>
       <c r="I130" s="9" t="n">
         <f aca="false">0.5*C130+0.5*B130</f>
         <v>-0.00840225035897145</v>
       </c>
-      <c r="M130" s="10" t="n">
+      <c r="M130" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B130</f>
         <v>0.00559247892188924</v>
       </c>
-      <c r="N130" s="10" t="n">
+      <c r="N130" s="8" t="n">
         <f aca="false">C130-M130</f>
         <v>-0.0264404789218892</v>
       </c>
@@ -7825,7 +7799,7 @@
         <f aca="false">Data!C131-Data!D131</f>
         <v>0.026997</v>
       </c>
-      <c r="E131" s="0" t="n">
+      <c r="E131" s="5" t="n">
         <f aca="false">0.2*C131+0.8*B131</f>
         <v>-0.0509126770002601</v>
       </c>
@@ -7837,11 +7811,11 @@
         <f aca="false">0.5*C131+0.5*B131</f>
         <v>-0.0216965481251625</v>
       </c>
-      <c r="M131" s="10" t="n">
+      <c r="M131" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B131</f>
         <v>0.000870113154157406</v>
       </c>
-      <c r="N131" s="10" t="n">
+      <c r="N131" s="8" t="n">
         <f aca="false">C131-M131</f>
         <v>0.0261268868458426</v>
       </c>
@@ -7858,7 +7832,7 @@
         <f aca="false">Data!C132-Data!D132</f>
         <v>0.000458</v>
       </c>
-      <c r="E132" s="0" t="n">
+      <c r="E132" s="5" t="n">
         <f aca="false">0.2*C132+0.8*B132</f>
         <v>0.014864797159499</v>
       </c>
@@ -7870,11 +7844,11 @@
         <f aca="false">0.5*C132+0.5*B132</f>
         <v>0.00946224822468687</v>
       </c>
-      <c r="M132" s="10" t="n">
+      <c r="M132" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B132</f>
         <v>0.00650753169616235</v>
       </c>
-      <c r="N132" s="10" t="n">
+      <c r="N132" s="8" t="n">
         <f aca="false">C132-M132</f>
         <v>-0.00604953169616235</v>
       </c>
@@ -7891,23 +7865,23 @@
         <f aca="false">Data!C133-Data!D133</f>
         <v>0.048245</v>
       </c>
-      <c r="E133" s="0" t="n">
+      <c r="E133" s="5" t="n">
         <f aca="false">0.2*C133+0.8*B133</f>
         <v>-0.0641921339514028</v>
       </c>
       <c r="G133" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B133 + 'Optimal portfolio from homework'!$C$15*C133</f>
-        <v>-0.0407396103198513</v>
+        <v>-0.0407396103198514</v>
       </c>
       <c r="I133" s="9" t="n">
         <f aca="false">0.5*C133+0.5*B133</f>
         <v>-0.0220282087196267</v>
       </c>
-      <c r="M133" s="10" t="n">
+      <c r="M133" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B133</f>
         <v>-0.000520028923063041</v>
       </c>
-      <c r="N133" s="10" t="n">
+      <c r="N133" s="8" t="n">
         <f aca="false">C133-M133</f>
         <v>0.048765028923063</v>
       </c>
@@ -7924,7 +7898,7 @@
         <f aca="false">Data!C134-Data!D134</f>
         <v>0.029773</v>
       </c>
-      <c r="E134" s="0" t="n">
+      <c r="E134" s="5" t="n">
         <f aca="false">0.2*C134+0.8*B134</f>
         <v>0.0682911917732459</v>
       </c>
@@ -7936,11 +7910,11 @@
         <f aca="false">0.5*C134+0.5*B134</f>
         <v>0.0538468698582787</v>
       </c>
-      <c r="M134" s="10" t="n">
+      <c r="M134" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B134</f>
         <v>0.0102795472913139</v>
       </c>
-      <c r="N134" s="10" t="n">
+      <c r="N134" s="8" t="n">
         <f aca="false">C134-M134</f>
         <v>0.0194934527086861</v>
       </c>
@@ -7957,7 +7931,7 @@
         <f aca="false">Data!C135-Data!D135</f>
         <v>0.000431</v>
       </c>
-      <c r="E135" s="0" t="n">
+      <c r="E135" s="5" t="n">
         <f aca="false">0.2*C135+0.8*B135</f>
         <v>0.0242502966554648</v>
       </c>
@@ -7969,11 +7943,11 @@
         <f aca="false">0.5*C135+0.5*B135</f>
         <v>0.0153180604096655</v>
       </c>
-      <c r="M135" s="10" t="n">
+      <c r="M135" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B135</f>
         <v>0.007252277096253</v>
       </c>
-      <c r="N135" s="10" t="n">
+      <c r="N135" s="8" t="n">
         <f aca="false">C135-M135</f>
         <v>-0.006821277096253</v>
       </c>
@@ -7990,23 +7964,23 @@
         <f aca="false">Data!C136-Data!D136</f>
         <v>-0.027778</v>
       </c>
-      <c r="E136" s="0" t="n">
+      <c r="E136" s="5" t="n">
         <f aca="false">0.2*C136+0.8*B136</f>
         <v>0.00841749877686103</v>
       </c>
       <c r="G136" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B136 + 'Optimal portfolio from homework'!$C$15*C136</f>
-        <v>0.000867717307093013</v>
+        <v>0.000867717307093044</v>
       </c>
       <c r="I136" s="9" t="n">
         <f aca="false">0.5*C136+0.5*B136</f>
         <v>-0.00515581326446186</v>
       </c>
-      <c r="M136" s="10" t="n">
+      <c r="M136" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B136</f>
         <v>0.00644407988408135</v>
       </c>
-      <c r="N136" s="10" t="n">
+      <c r="N136" s="8" t="n">
         <f aca="false">C136-M136</f>
         <v>-0.0342220798840814</v>
       </c>
@@ -8023,7 +7997,7 @@
         <f aca="false">Data!C137-Data!D137</f>
         <v>-0.006747</v>
       </c>
-      <c r="E137" s="0" t="n">
+      <c r="E137" s="5" t="n">
         <f aca="false">0.2*C137+0.8*B137</f>
         <v>0.0292997023092215</v>
       </c>
@@ -8035,11 +8009,11 @@
         <f aca="false">0.5*C137+0.5*B137</f>
         <v>0.0157821889432635</v>
       </c>
-      <c r="M137" s="10" t="n">
+      <c r="M137" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B137</f>
         <v>0.00776657054942773</v>
       </c>
-      <c r="N137" s="10" t="n">
+      <c r="N137" s="8" t="n">
         <f aca="false">C137-M137</f>
         <v>-0.0145135705494277</v>
       </c>
@@ -8056,7 +8030,7 @@
         <f aca="false">Data!C138-Data!D138</f>
         <v>0.006343</v>
       </c>
-      <c r="E138" s="0" t="n">
+      <c r="E138" s="5" t="n">
         <f aca="false">0.2*C138+0.8*B138</f>
         <v>-0.0513282412155955</v>
       </c>
@@ -8068,11 +8042,11 @@
         <f aca="false">0.5*C138+0.5*B138</f>
         <v>-0.0297015257597472</v>
       </c>
-      <c r="M138" s="10" t="n">
+      <c r="M138" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B138</f>
         <v>0.0011647499737794</v>
       </c>
-      <c r="N138" s="10" t="n">
+      <c r="N138" s="8" t="n">
         <f aca="false">C138-M138</f>
         <v>0.00517825002622061</v>
       </c>
@@ -8089,7 +8063,7 @@
         <f aca="false">Data!C139-Data!D139</f>
         <v>0.088632</v>
       </c>
-      <c r="E139" s="0" t="n">
+      <c r="E139" s="5" t="n">
         <f aca="false">0.2*C139+0.8*B139</f>
         <v>0.0725498017916159</v>
       </c>
@@ -8101,11 +8075,11 @@
         <f aca="false">0.5*C139+0.5*B139</f>
         <v>0.0785806261197599</v>
       </c>
-      <c r="M139" s="10" t="n">
+      <c r="M139" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B139</f>
         <v>0.00968371366736449</v>
       </c>
-      <c r="N139" s="10" t="n">
+      <c r="N139" s="8" t="n">
         <f aca="false">C139-M139</f>
         <v>0.0789482863326355</v>
       </c>
@@ -8122,7 +8096,7 @@
         <f aca="false">Data!C140-Data!D140</f>
         <v>0.010377</v>
       </c>
-      <c r="E140" s="0" t="n">
+      <c r="E140" s="5" t="n">
         <f aca="false">0.2*C140+0.8*B140</f>
         <v>0.0119624962750082</v>
       </c>
@@ -8134,11 +8108,11 @@
         <f aca="false">0.5*C140+0.5*B140</f>
         <v>0.0113679351718801</v>
       </c>
-      <c r="M140" s="10" t="n">
+      <c r="M140" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B140</f>
         <v>0.00612003940539015</v>
       </c>
-      <c r="N140" s="10" t="n">
+      <c r="N140" s="8" t="n">
         <f aca="false">C140-M140</f>
         <v>0.00425696059460985</v>
       </c>
@@ -8155,7 +8129,7 @@
         <f aca="false">Data!C141-Data!D141</f>
         <v>0.065507</v>
       </c>
-      <c r="E141" s="0" t="n">
+      <c r="E141" s="5" t="n">
         <f aca="false">0.2*C141+0.8*B141</f>
         <v>-0.000907457890148242</v>
       </c>
@@ -8167,11 +8141,11 @@
         <f aca="false">0.5*C141+0.5*B141</f>
         <v>0.0239979638186573</v>
       </c>
-      <c r="M141" s="10" t="n">
+      <c r="M141" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B141</f>
         <v>0.00422497046626221</v>
       </c>
-      <c r="N141" s="10" t="n">
+      <c r="N141" s="8" t="n">
         <f aca="false">C141-M141</f>
         <v>0.0612820295337378</v>
       </c>
@@ -8188,23 +8162,23 @@
         <f aca="false">Data!C142-Data!D142</f>
         <v>-0.027315</v>
       </c>
-      <c r="E142" s="0" t="n">
+      <c r="E142" s="5" t="n">
         <f aca="false">0.2*C142+0.8*B142</f>
         <v>0.0079677908681704</v>
       </c>
       <c r="G142" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B142 + 'Optimal portfolio from homework'!$C$15*C142</f>
-        <v>0.000608385149233271</v>
+        <v>0.00060838514923329</v>
       </c>
       <c r="I142" s="9" t="n">
         <f aca="false">0.5*C142+0.5*B142</f>
         <v>-0.0052632557073935</v>
       </c>
-      <c r="M142" s="10" t="n">
+      <c r="M142" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B142</f>
         <v>0.00640107214870908</v>
       </c>
-      <c r="N142" s="10" t="n">
+      <c r="N142" s="8" t="n">
         <f aca="false">C142-M142</f>
         <v>-0.0337160721487091</v>
       </c>
@@ -8221,7 +8195,7 @@
         <f aca="false">Data!C143-Data!D143</f>
         <v>0.011138</v>
       </c>
-      <c r="E143" s="0" t="n">
+      <c r="E143" s="5" t="n">
         <f aca="false">0.2*C143+0.8*B143</f>
         <v>0.018267598543919</v>
       </c>
@@ -8233,11 +8207,11 @@
         <f aca="false">0.5*C143+0.5*B143</f>
         <v>0.0155939990899494</v>
       </c>
-      <c r="M143" s="10" t="n">
+      <c r="M143" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B143</f>
         <v>0.00660799539554286</v>
       </c>
-      <c r="N143" s="10" t="n">
+      <c r="N143" s="8" t="n">
         <f aca="false">C143-M143</f>
         <v>0.00453000460445714</v>
       </c>
@@ -8254,23 +8228,23 @@
         <f aca="false">Data!C144-Data!D144</f>
         <v>-0.034425</v>
       </c>
-      <c r="E144" s="0" t="n">
+      <c r="E144" s="5" t="n">
         <f aca="false">0.2*C144+0.8*B144</f>
         <v>0.0211184037700887</v>
       </c>
       <c r="G144" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B144 + 'Optimal portfolio from homework'!$C$15*C144</f>
-        <v>0.00953296981498784</v>
+        <v>0.00953296981498786</v>
       </c>
       <c r="I144" s="9" t="n">
         <f aca="false">0.5*C144+0.5*B144</f>
         <v>0.000289627356305458</v>
       </c>
-      <c r="M144" s="10" t="n">
+      <c r="M144" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B144</f>
         <v>0.00755675339422421</v>
       </c>
-      <c r="N144" s="10" t="n">
+      <c r="N144" s="8" t="n">
         <f aca="false">C144-M144</f>
         <v>-0.0419817533942242</v>
       </c>
@@ -8287,7 +8261,7 @@
         <f aca="false">Data!C145-Data!D145</f>
         <v>0.044365</v>
       </c>
-      <c r="E145" s="0" t="n">
+      <c r="E145" s="5" t="n">
         <f aca="false">0.2*C145+0.8*B145</f>
         <v>0.0317967474248838</v>
       </c>
@@ -8299,11 +8273,11 @@
         <f aca="false">0.5*C145+0.5*B145</f>
         <v>0.0365098421405524</v>
       </c>
-      <c r="M145" s="10" t="n">
+      <c r="M145" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B145</f>
         <v>0.0071539111852582</v>
       </c>
-      <c r="N145" s="10" t="n">
+      <c r="N145" s="8" t="n">
         <f aca="false">C145-M145</f>
         <v>0.0372110888147418</v>
       </c>
@@ -8320,7 +8294,7 @@
         <f aca="false">Data!C146-Data!D146</f>
         <v>0.036684</v>
       </c>
-      <c r="E146" s="0" t="n">
+      <c r="E146" s="5" t="n">
         <f aca="false">0.2*C146+0.8*B146</f>
         <v>0.00589433152669695</v>
       </c>
@@ -8332,11 +8306,11 @@
         <f aca="false">0.5*C146+0.5*B146</f>
         <v>0.0174404572041856</v>
       </c>
-      <c r="M146" s="10" t="n">
+      <c r="M146" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B146</f>
         <v>0.00522154813360532</v>
       </c>
-      <c r="N146" s="10" t="n">
+      <c r="N146" s="8" t="n">
         <f aca="false">C146-M146</f>
         <v>0.0314624518663947</v>
       </c>
@@ -8353,7 +8327,7 @@
         <f aca="false">Data!C147-Data!D147</f>
         <v>0.027582</v>
       </c>
-      <c r="E147" s="0" t="n">
+      <c r="E147" s="5" t="n">
         <f aca="false">0.2*C147+0.8*B147</f>
         <v>-0.0613742734673333</v>
       </c>
@@ -8365,11 +8339,11 @@
         <f aca="false">0.5*C147+0.5*B147</f>
         <v>-0.0280156709170833</v>
       </c>
-      <c r="M147" s="10" t="n">
+      <c r="M147" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B147</f>
         <v>3.11774311574651E-005</v>
       </c>
-      <c r="N147" s="10" t="n">
+      <c r="N147" s="8" t="n">
         <f aca="false">C147-M147</f>
         <v>0.0275508225688425</v>
       </c>
@@ -8386,23 +8360,23 @@
         <f aca="false">Data!C148-Data!D148</f>
         <v>-0.014543</v>
       </c>
-      <c r="E148" s="0" t="n">
+      <c r="E148" s="5" t="n">
         <f aca="false">0.2*C148+0.8*B148</f>
         <v>-0.102845339118891</v>
       </c>
       <c r="G148" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B148 + 'Optimal portfolio from homework'!$C$15*C148</f>
-        <v>-0.08442693389876</v>
+        <v>-0.0844269338987598</v>
       </c>
       <c r="I148" s="9" t="n">
         <f aca="false">0.5*C148+0.5*B148</f>
         <v>-0.0697319619493067</v>
       </c>
-      <c r="M148" s="10" t="n">
+      <c r="M148" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B148</f>
         <v>-0.00258954121199947</v>
       </c>
-      <c r="N148" s="10" t="n">
+      <c r="N148" s="8" t="n">
         <f aca="false">C148-M148</f>
         <v>-0.0119534587880005</v>
       </c>
@@ -8419,23 +8393,23 @@
         <f aca="false">Data!C149-Data!D149</f>
         <v>0.069859</v>
       </c>
-      <c r="E149" s="0" t="n">
+      <c r="E149" s="5" t="n">
         <f aca="false">0.2*C149+0.8*B149</f>
         <v>0.116482593477805</v>
       </c>
       <c r="G149" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B149 + 'Optimal portfolio from homework'!$C$15*C149</f>
-        <v>0.106757684193843</v>
+        <v>0.106757684193844</v>
       </c>
       <c r="I149" s="9" t="n">
         <f aca="false">0.5*C149+0.5*B149</f>
         <v>0.0989987459236283</v>
       </c>
-      <c r="M149" s="10" t="n">
+      <c r="M149" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B149</f>
         <v>0.013465562851872</v>
       </c>
-      <c r="N149" s="10" t="n">
+      <c r="N149" s="8" t="n">
         <f aca="false">C149-M149</f>
         <v>0.056393437148128</v>
       </c>
@@ -8452,7 +8426,7 @@
         <f aca="false">Data!C150-Data!D150</f>
         <v>0.005084</v>
       </c>
-      <c r="E150" s="0" t="n">
+      <c r="E150" s="5" t="n">
         <f aca="false">0.2*C150+0.8*B150</f>
         <v>0.0389541887196255</v>
       </c>
@@ -8464,11 +8438,11 @@
         <f aca="false">0.5*C150+0.5*B150</f>
         <v>0.026252867949766</v>
       </c>
-      <c r="M150" s="10" t="n">
+      <c r="M150" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B150</f>
         <v>0.00834456819289343</v>
       </c>
-      <c r="N150" s="10" t="n">
+      <c r="N150" s="8" t="n">
         <f aca="false">C150-M150</f>
         <v>-0.00326056819289343</v>
       </c>
@@ -8485,7 +8459,7 @@
         <f aca="false">Data!C151-Data!D151</f>
         <v>0.026006</v>
       </c>
-      <c r="E151" s="0" t="n">
+      <c r="E151" s="5" t="n">
         <f aca="false">0.2*C151+0.8*B151</f>
         <v>0.020971725937636</v>
       </c>
@@ -8497,11 +8471,11 @@
         <f aca="false">0.5*C151+0.5*B151</f>
         <v>0.0228595787110225</v>
       </c>
-      <c r="M151" s="10" t="n">
+      <c r="M151" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B151</f>
         <v>0.0065866248671855</v>
       </c>
-      <c r="N151" s="10" t="n">
+      <c r="N151" s="8" t="n">
         <f aca="false">C151-M151</f>
         <v>0.0194193751328145</v>
       </c>
@@ -8518,23 +8492,23 @@
         <f aca="false">Data!C152-Data!D152</f>
         <v>0.115109</v>
       </c>
-      <c r="E152" s="0" t="n">
+      <c r="E152" s="5" t="n">
         <f aca="false">0.2*C152+0.8*B152</f>
         <v>0.067957877170418</v>
       </c>
       <c r="G152" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B152 + 'Optimal portfolio from homework'!$C$15*C152</f>
-        <v>0.0777928203386858</v>
+        <v>0.0777928203386857</v>
       </c>
       <c r="I152" s="9" t="n">
         <f aca="false">0.5*C152+0.5*B152</f>
         <v>0.0856395482315113</v>
       </c>
-      <c r="M152" s="10" t="n">
+      <c r="M152" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B152</f>
         <v>0.00889959926660839</v>
       </c>
-      <c r="N152" s="10" t="n">
+      <c r="N152" s="8" t="n">
         <f aca="false">C152-M152</f>
         <v>0.106209400733392</v>
       </c>
@@ -8551,7 +8525,7 @@
         <f aca="false">Data!C153-Data!D153</f>
         <v>-0.009646</v>
       </c>
-      <c r="E153" s="0" t="n">
+      <c r="E153" s="5" t="n">
         <f aca="false">0.2*C153+0.8*B153</f>
         <v>0.0554059280524122</v>
       </c>
@@ -8563,11 +8537,11 @@
         <f aca="false">0.5*C153+0.5*B153</f>
         <v>0.0310114550327576</v>
       </c>
-      <c r="M153" s="10" t="n">
+      <c r="M153" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B153</f>
         <v>0.00988290614938589</v>
       </c>
-      <c r="N153" s="10" t="n">
+      <c r="N153" s="8" t="n">
         <f aca="false">C153-M153</f>
         <v>-0.0195289061493859</v>
       </c>
@@ -8584,23 +8558,23 @@
         <f aca="false">Data!C154-Data!D154</f>
         <v>-0.037143</v>
       </c>
-      <c r="E154" s="0" t="n">
+      <c r="E154" s="5" t="n">
         <f aca="false">0.2*C154+0.8*B154</f>
         <v>-0.0379931535013007</v>
       </c>
       <c r="G154" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B154 + 'Optimal portfolio from homework'!$C$15*C154</f>
-        <v>-0.0378158255636434</v>
+        <v>-0.0378158255636433</v>
       </c>
       <c r="I154" s="9" t="n">
         <f aca="false">0.5*C154+0.5*B154</f>
         <v>-0.0376743459383129</v>
       </c>
-      <c r="M154" s="10" t="n">
+      <c r="M154" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B154</f>
         <v>0.00291202082208774</v>
       </c>
-      <c r="N154" s="10" t="n">
+      <c r="N154" s="8" t="n">
         <f aca="false">C154-M154</f>
         <v>-0.0400550208220877</v>
       </c>
@@ -8617,7 +8591,7 @@
         <f aca="false">Data!C155-Data!D155</f>
         <v>-0.004135</v>
       </c>
-      <c r="E155" s="0" t="n">
+      <c r="E155" s="5" t="n">
         <f aca="false">0.2*C155+0.8*B155</f>
         <v>-0.022277798827055</v>
       </c>
@@ -8629,11 +8603,11 @@
         <f aca="false">0.5*C155+0.5*B155</f>
         <v>-0.0154742492669094</v>
       </c>
-      <c r="M155" s="10" t="n">
+      <c r="M155" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B155</f>
         <v>0.00363478724868136</v>
       </c>
-      <c r="N155" s="10" t="n">
+      <c r="N155" s="8" t="n">
         <f aca="false">C155-M155</f>
         <v>-0.00776978724868136</v>
       </c>
@@ -8650,23 +8624,23 @@
         <f aca="false">Data!C156-Data!D156</f>
         <v>-0.055463</v>
       </c>
-      <c r="E156" s="0" t="n">
+      <c r="E156" s="5" t="n">
         <f aca="false">0.2*C156+0.8*B156</f>
         <v>0.0763125013110846</v>
       </c>
       <c r="G156" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B156 + 'Optimal portfolio from homework'!$C$15*C156</f>
-        <v>0.0488263145865679</v>
+        <v>0.0488263145865682</v>
       </c>
       <c r="I156" s="9" t="n">
         <f aca="false">0.5*C156+0.5*B156</f>
         <v>0.0268966883194278</v>
       </c>
-      <c r="M156" s="10" t="n">
+      <c r="M156" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B156</f>
         <v>0.0122676057487017</v>
       </c>
-      <c r="N156" s="10" t="n">
+      <c r="N156" s="8" t="n">
         <f aca="false">C156-M156</f>
         <v>-0.0677306057487017</v>
       </c>
@@ -8683,7 +8657,7 @@
         <f aca="false">Data!C157-Data!D157</f>
         <v>0.067142</v>
       </c>
-      <c r="E157" s="0" t="n">
+      <c r="E157" s="5" t="n">
         <f aca="false">0.2*C157+0.8*B157</f>
         <v>0.0440599650965104</v>
       </c>
@@ -8695,11 +8669,11 @@
         <f aca="false">0.5*C157+0.5*B157</f>
         <v>0.052715728185319</v>
       </c>
-      <c r="M157" s="10" t="n">
+      <c r="M157" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B157</f>
         <v>0.00776517976055786</v>
       </c>
-      <c r="N157" s="10" t="n">
+      <c r="N157" s="8" t="n">
         <f aca="false">C157-M157</f>
         <v>0.0593768202394421</v>
       </c>
@@ -8716,7 +8690,7 @@
         <f aca="false">Data!C158-Data!D158</f>
         <v>-0.020306</v>
       </c>
-      <c r="E158" s="0" t="n">
+      <c r="E158" s="5" t="n">
         <f aca="false">0.2*C158+0.8*B158</f>
         <v>-0.0122320020773226</v>
       </c>
@@ -8728,11 +8702,11 @@
         <f aca="false">0.5*C158+0.5*B158</f>
         <v>-0.0152597512983266</v>
       </c>
-      <c r="M158" s="10" t="n">
+      <c r="M158" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B158</f>
         <v>0.00468795755434063</v>
       </c>
-      <c r="N158" s="10" t="n">
+      <c r="N158" s="8" t="n">
         <f aca="false">C158-M158</f>
         <v>-0.0249939575543406</v>
       </c>
@@ -8749,23 +8723,23 @@
         <f aca="false">Data!C159-Data!D159</f>
         <v>-0.047282</v>
       </c>
-      <c r="E159" s="0" t="n">
+      <c r="E159" s="5" t="n">
         <f aca="false">0.2*C159+0.8*B159</f>
         <v>0.0125805614644667</v>
       </c>
       <c r="G159" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B159 + 'Optimal portfolio from homework'!$C$15*C159</f>
-        <v>9.42227607658094E-005</v>
+        <v>9.42227607658233E-005</v>
       </c>
       <c r="I159" s="9" t="n">
         <f aca="false">0.5*C159+0.5*B159</f>
         <v>-0.00986789908470828</v>
       </c>
-      <c r="M159" s="10" t="n">
+      <c r="M159" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B159</f>
         <v>0.00708358461375467</v>
       </c>
-      <c r="N159" s="10" t="n">
+      <c r="N159" s="8" t="n">
         <f aca="false">C159-M159</f>
         <v>-0.0543655846137547</v>
       </c>
@@ -8782,7 +8756,7 @@
         <f aca="false">Data!C160-Data!D160</f>
         <v>-0.045182</v>
       </c>
-      <c r="E160" s="0" t="n">
+      <c r="E160" s="5" t="n">
         <f aca="false">0.2*C160+0.8*B160</f>
         <v>0.0259255307028677</v>
       </c>
@@ -8794,11 +8768,11 @@
         <f aca="false">0.5*C160+0.5*B160</f>
         <v>-0.000739793310707702</v>
       </c>
-      <c r="M160" s="10" t="n">
+      <c r="M160" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B160</f>
         <v>0.00810859945825889</v>
       </c>
-      <c r="N160" s="10" t="n">
+      <c r="N160" s="8" t="n">
         <f aca="false">C160-M160</f>
         <v>-0.0532905994582589</v>
       </c>
@@ -8815,7 +8789,7 @@
         <f aca="false">Data!C161-Data!D161</f>
         <v>0.049515</v>
       </c>
-      <c r="E161" s="0" t="n">
+      <c r="E161" s="5" t="n">
         <f aca="false">0.2*C161+0.8*B161</f>
         <v>0.052484735881984</v>
       </c>
@@ -8827,11 +8801,11 @@
         <f aca="false">0.5*C161+0.5*B161</f>
         <v>0.05137108492624</v>
       </c>
-      <c r="M161" s="10" t="n">
+      <c r="M161" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B161</f>
         <v>0.00871288820175694</v>
       </c>
-      <c r="N161" s="10" t="n">
+      <c r="N161" s="8" t="n">
         <f aca="false">C161-M161</f>
         <v>0.0408021117982431</v>
       </c>
@@ -8848,23 +8822,23 @@
         <f aca="false">Data!C162-Data!D162</f>
         <v>0.069906</v>
       </c>
-      <c r="E162" s="0" t="n">
+      <c r="E162" s="5" t="n">
         <f aca="false">0.2*C162+0.8*B162</f>
         <v>0.0194698731391585</v>
       </c>
       <c r="G162" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B162 + 'Optimal portfolio from homework'!$C$15*C162</f>
-        <v>0.0299900137325595</v>
+        <v>0.0299900137325594</v>
       </c>
       <c r="I162" s="9" t="n">
         <f aca="false">0.5*C162+0.5*B162</f>
         <v>0.0383834207119741</v>
       </c>
-      <c r="M162" s="10" t="n">
+      <c r="M162" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B162</f>
         <v>0.00577122240447522</v>
       </c>
-      <c r="N162" s="10" t="n">
+      <c r="N162" s="8" t="n">
         <f aca="false">C162-M162</f>
         <v>0.0641347775955248</v>
       </c>
@@ -8881,7 +8855,7 @@
         <f aca="false">Data!C163-Data!D163</f>
         <v>-0.071151</v>
       </c>
-      <c r="E163" s="0" t="n">
+      <c r="E163" s="5" t="n">
         <f aca="false">0.2*C163+0.8*B163</f>
         <v>0.00435600177425187</v>
       </c>
@@ -8893,11 +8867,11 @@
         <f aca="false">0.5*C163+0.5*B163</f>
         <v>-0.0239591238910926</v>
       </c>
-      <c r="M163" s="10" t="n">
+      <c r="M163" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B163</f>
         <v>0.00680992207405762</v>
       </c>
-      <c r="N163" s="10" t="n">
+      <c r="N163" s="8" t="n">
         <f aca="false">C163-M163</f>
         <v>-0.0779609220740576</v>
       </c>
@@ -8914,23 +8888,23 @@
         <f aca="false">Data!C164-Data!D164</f>
         <v>0.040078</v>
       </c>
-      <c r="E164" s="0" t="n">
+      <c r="E164" s="5" t="n">
         <f aca="false">0.2*C164+0.8*B164</f>
         <v>0.0269114911015881</v>
       </c>
       <c r="G164" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B164 + 'Optimal portfolio from homework'!$C$15*C164</f>
-        <v>0.0296578067557963</v>
+        <v>0.0296578067557962</v>
       </c>
       <c r="I164" s="9" t="n">
         <f aca="false">0.5*C164+0.5*B164</f>
         <v>0.0318489319384926</v>
       </c>
-      <c r="M164" s="10" t="n">
+      <c r="M164" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B164</f>
         <v>0.00683448198997301</v>
       </c>
-      <c r="N164" s="10" t="n">
+      <c r="N164" s="8" t="n">
         <f aca="false">C164-M164</f>
         <v>0.033243518010027</v>
       </c>
@@ -8947,7 +8921,7 @@
         <f aca="false">Data!C165-Data!D165</f>
         <v>-0.00763</v>
       </c>
-      <c r="E165" s="0" t="n">
+      <c r="E165" s="5" t="n">
         <f aca="false">0.2*C165+0.8*B165</f>
         <v>0.0227062752234836</v>
       </c>
@@ -8959,11 +8933,11 @@
         <f aca="false">0.5*C165+0.5*B165</f>
         <v>0.0113301720146772</v>
       </c>
-      <c r="M165" s="10" t="n">
+      <c r="M165" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B165</f>
         <v>0.00725768399842872</v>
       </c>
-      <c r="N165" s="10" t="n">
+      <c r="N165" s="8" t="n">
         <f aca="false">C165-M165</f>
         <v>-0.0148876839984287</v>
       </c>
@@ -8980,7 +8954,7 @@
         <f aca="false">Data!C166-Data!D166</f>
         <v>-0.045941</v>
       </c>
-      <c r="E166" s="0" t="n">
+      <c r="E166" s="5" t="n">
         <f aca="false">0.2*C166+0.8*B166</f>
         <v>-0.046492938845069</v>
       </c>
@@ -8992,11 +8966,11 @@
         <f aca="false">0.5*C166+0.5*B166</f>
         <v>-0.0462859617781681</v>
       </c>
-      <c r="M166" s="10" t="n">
+      <c r="M166" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B166</f>
         <v>0.00237749034045643</v>
       </c>
-      <c r="N166" s="10" t="n">
+      <c r="N166" s="8" t="n">
         <f aca="false">C166-M166</f>
         <v>-0.0483184903404564</v>
       </c>
@@ -9013,7 +8987,7 @@
         <f aca="false">Data!C167-Data!D167</f>
         <v>0.037754</v>
       </c>
-      <c r="E167" s="0" t="n">
+      <c r="E167" s="5" t="n">
         <f aca="false">0.2*C167+0.8*B167</f>
         <v>0.0634966847788367</v>
       </c>
@@ -9025,11 +8999,11 @@
         <f aca="false">0.5*C167+0.5*B167</f>
         <v>0.0538431779867729</v>
       </c>
-      <c r="M167" s="10" t="n">
+      <c r="M167" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B167</f>
         <v>0.00977273219447915</v>
       </c>
-      <c r="N167" s="10" t="n">
+      <c r="N167" s="8" t="n">
         <f aca="false">C167-M167</f>
         <v>0.0279812678055209</v>
       </c>
@@ -9046,7 +9020,7 @@
         <f aca="false">Data!C168-Data!D168</f>
         <v>0.000724</v>
       </c>
-      <c r="E168" s="0" t="n">
+      <c r="E168" s="5" t="n">
         <f aca="false">0.2*C168+0.8*B168</f>
         <v>-0.00549588816395604</v>
       </c>
@@ -9058,11 +9032,11 @@
         <f aca="false">0.5*C168+0.5*B168</f>
         <v>-0.00316343010247253</v>
       </c>
-      <c r="M168" s="10" t="n">
+      <c r="M168" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B168</f>
         <v>0.00488860826937539</v>
       </c>
-      <c r="N168" s="10" t="n">
+      <c r="N168" s="8" t="n">
         <f aca="false">C168-M168</f>
         <v>-0.00416460826937539</v>
       </c>
@@ -9079,7 +9053,7 @@
         <f aca="false">Data!C169-Data!D169</f>
         <v>0.012417</v>
       </c>
-      <c r="E169" s="0" t="n">
+      <c r="E169" s="5" t="n">
         <f aca="false">0.2*C169+0.8*B169</f>
         <v>0.0381520613106511</v>
       </c>
@@ -9091,11 +9065,11 @@
         <f aca="false">0.5*C169+0.5*B169</f>
         <v>0.0285014133191569</v>
       </c>
-      <c r="M169" s="10" t="n">
+      <c r="M169" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B169</f>
         <v>0.00816464673780608</v>
       </c>
-      <c r="N169" s="10" t="n">
+      <c r="N169" s="8" t="n">
         <f aca="false">C169-M169</f>
         <v>0.00425235326219393</v>
       </c>
@@ -9112,7 +9086,7 @@
         <f aca="false">Data!C170-Data!D170</f>
         <v>-0.016208</v>
       </c>
-      <c r="E170" s="0" t="n">
+      <c r="E170" s="5" t="n">
         <f aca="false">0.2*C170+0.8*B170</f>
         <v>-0.0447275273405175</v>
       </c>
@@ -9124,11 +9098,11 @@
         <f aca="false">0.5*C170+0.5*B170</f>
         <v>-0.0340327045878234</v>
       </c>
-      <c r="M170" s="10" t="n">
+      <c r="M170" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B170</f>
         <v>0.00204590113537178</v>
       </c>
-      <c r="N170" s="10" t="n">
+      <c r="N170" s="8" t="n">
         <f aca="false">C170-M170</f>
         <v>-0.0182539011353718</v>
       </c>
@@ -9145,23 +9119,23 @@
         <f aca="false">Data!C171-Data!D171</f>
         <v>0.06294</v>
       </c>
-      <c r="E171" s="0" t="n">
+      <c r="E171" s="5" t="n">
         <f aca="false">0.2*C171+0.8*B171</f>
         <v>-0.0114091226471646</v>
       </c>
       <c r="G171" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B171 + 'Optimal portfolio from homework'!$C$15*C171</f>
-        <v>0.00409887275070274</v>
+        <v>0.0040988727507027</v>
       </c>
       <c r="I171" s="9" t="n">
         <f aca="false">0.5*C171+0.5*B171</f>
         <v>0.0164717983455222</v>
       </c>
-      <c r="M171" s="10" t="n">
+      <c r="M171" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B171</f>
         <v>0.00343285100679287</v>
       </c>
-      <c r="N171" s="10" t="n">
+      <c r="N171" s="8" t="n">
         <f aca="false">C171-M171</f>
         <v>0.0595071489932071</v>
       </c>
@@ -9178,7 +9152,7 @@
         <f aca="false">Data!C172-Data!D172</f>
         <v>0.010928</v>
       </c>
-      <c r="E172" s="0" t="n">
+      <c r="E172" s="5" t="n">
         <f aca="false">0.2*C172+0.8*B172</f>
         <v>0.0317320218265542</v>
       </c>
@@ -9190,11 +9164,11 @@
         <f aca="false">0.5*C172+0.5*B172</f>
         <v>0.0239305136415964</v>
       </c>
-      <c r="M172" s="10" t="n">
+      <c r="M172" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B172</f>
         <v>0.00767912246018036</v>
       </c>
-      <c r="N172" s="10" t="n">
+      <c r="N172" s="8" t="n">
         <f aca="false">C172-M172</f>
         <v>0.00324887753981964</v>
       </c>
@@ -9211,7 +9185,7 @@
         <f aca="false">Data!C173-Data!D173</f>
         <v>-0.004496</v>
       </c>
-      <c r="E173" s="0" t="n">
+      <c r="E173" s="5" t="n">
         <f aca="false">0.2*C173+0.8*B173</f>
         <v>-0.0707413807747489</v>
       </c>
@@ -9223,11 +9197,11 @@
         <f aca="false">0.5*C173+0.5*B173</f>
         <v>-0.0458993629842181</v>
       </c>
-      <c r="M173" s="10" t="n">
+      <c r="M173" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B173</f>
         <v>-0.000202891892177959</v>
       </c>
-      <c r="N173" s="10" t="n">
+      <c r="N173" s="8" t="n">
         <f aca="false">C173-M173</f>
         <v>-0.00429310810782204</v>
       </c>
@@ -9244,7 +9218,7 @@
         <f aca="false">Data!C174-Data!D174</f>
         <v>-0.032172</v>
       </c>
-      <c r="E174" s="0" t="n">
+      <c r="E174" s="5" t="n">
         <f aca="false">0.2*C174+0.8*B174</f>
         <v>-0.00531203787366722</v>
       </c>
@@ -9256,11 +9230,11 @@
         <f aca="false">0.5*C174+0.5*B174</f>
         <v>-0.015384523671042</v>
       </c>
-      <c r="M174" s="10" t="n">
+      <c r="M174" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B174</f>
         <v>0.00542495205587188</v>
       </c>
-      <c r="N174" s="10" t="n">
+      <c r="N174" s="8" t="n">
         <f aca="false">C174-M174</f>
         <v>-0.0375969520558719</v>
       </c>
@@ -9277,7 +9251,7 @@
         <f aca="false">Data!C175-Data!D175</f>
         <v>-0.022602</v>
       </c>
-      <c r="E175" s="0" t="n">
+      <c r="E175" s="5" t="n">
         <f aca="false">0.2*C175+0.8*B175</f>
         <v>-0.0711236604802747</v>
       </c>
@@ -9289,11 +9263,11 @@
         <f aca="false">0.5*C175+0.5*B175</f>
         <v>-0.0529280378001717</v>
       </c>
-      <c r="M175" s="10" t="n">
+      <c r="M175" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B175</f>
         <v>5.39707216330046E-005</v>
       </c>
-      <c r="N175" s="10" t="n">
+      <c r="N175" s="8" t="n">
         <f aca="false">C175-M175</f>
         <v>-0.022655970721633</v>
       </c>
@@ -9310,7 +9284,7 @@
         <f aca="false">Data!C176-Data!D176</f>
         <v>-0.030961</v>
       </c>
-      <c r="E176" s="0" t="n">
+      <c r="E176" s="5" t="n">
         <f aca="false">0.2*C176+0.8*B176</f>
         <v>0.0668441779978249</v>
       </c>
@@ -9322,11 +9296,11 @@
         <f aca="false">0.5*C176+0.5*B176</f>
         <v>0.0301672362486406</v>
       </c>
-      <c r="M176" s="10" t="n">
+      <c r="M176" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B176</f>
         <v>0.0111280939695242</v>
       </c>
-      <c r="N176" s="10" t="n">
+      <c r="N176" s="8" t="n">
         <f aca="false">C176-M176</f>
         <v>-0.0420890939695242</v>
       </c>
@@ -9343,7 +9317,7 @@
         <f aca="false">Data!C177-Data!D177</f>
         <v>-0.028337</v>
       </c>
-      <c r="E177" s="0" t="n">
+      <c r="E177" s="5" t="n">
         <f aca="false">0.2*C177+0.8*B177</f>
         <v>-0.0399127668763103</v>
       </c>
@@ -9355,11 +9329,11 @@
         <f aca="false">0.5*C177+0.5*B177</f>
         <v>-0.035571854297694</v>
       </c>
-      <c r="M177" s="10" t="n">
+      <c r="M177" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B177</f>
         <v>0.00262011387208703</v>
       </c>
-      <c r="N177" s="10" t="n">
+      <c r="N177" s="8" t="n">
         <f aca="false">C177-M177</f>
         <v>-0.030957113872087</v>
       </c>
@@ -9376,7 +9350,7 @@
         <f aca="false">Data!C178-Data!D178</f>
         <v>-0.025055</v>
       </c>
-      <c r="E178" s="0" t="n">
+      <c r="E178" s="5" t="n">
         <f aca="false">0.2*C178+0.8*B178</f>
         <v>-0.0802920903601772</v>
       </c>
@@ -9388,11 +9362,11 @@
         <f aca="false">0.5*C178+0.5*B178</f>
         <v>-0.0595781814751108</v>
       </c>
-      <c r="M178" s="10" t="n">
+      <c r="M178" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B178</f>
         <v>-0.000634224683780798</v>
       </c>
-      <c r="N178" s="10" t="n">
+      <c r="N178" s="8" t="n">
         <f aca="false">C178-M178</f>
         <v>-0.0244207753162192</v>
       </c>
@@ -9409,23 +9383,23 @@
         <f aca="false">Data!C179-Data!D179</f>
         <v>-0.022566</v>
       </c>
-      <c r="E179" s="0" t="n">
+      <c r="E179" s="5" t="n">
         <f aca="false">0.2*C179+0.8*B179</f>
         <v>0.0582966836471336</v>
       </c>
       <c r="G179" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B179 + 'Optimal portfolio from homework'!$C$15*C179</f>
-        <v>0.0414300673212075</v>
+        <v>0.0414300673212076</v>
       </c>
       <c r="I179" s="9" t="n">
         <f aca="false">0.5*C179+0.5*B179</f>
         <v>0.0279731772794585</v>
       </c>
-      <c r="M179" s="10" t="n">
+      <c r="M179" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B179</f>
         <v>0.0103170817091968</v>
       </c>
-      <c r="N179" s="10" t="n">
+      <c r="N179" s="8" t="n">
         <f aca="false">C179-M179</f>
         <v>-0.0328830817091968</v>
       </c>
@@ -9442,7 +9416,7 @@
         <f aca="false">Data!C180-Data!D180</f>
         <v>0.07081</v>
       </c>
-      <c r="E180" s="0" t="n">
+      <c r="E180" s="5" t="n">
         <f aca="false">0.2*C180+0.8*B180</f>
         <v>0.0564467591085758</v>
       </c>
@@ -9454,11 +9428,11 @@
         <f aca="false">0.5*C180+0.5*B180</f>
         <v>0.0618329744428599</v>
       </c>
-      <c r="M180" s="10" t="n">
+      <c r="M180" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B180</f>
         <v>0.00868933645508725</v>
       </c>
-      <c r="N180" s="10" t="n">
+      <c r="N180" s="8" t="n">
         <f aca="false">C180-M180</f>
         <v>0.0621206635449127</v>
       </c>
@@ -9475,7 +9449,7 @@
         <f aca="false">Data!C181-Data!D181</f>
         <v>0.026649</v>
       </c>
-      <c r="E181" s="0" t="n">
+      <c r="E181" s="5" t="n">
         <f aca="false">0.2*C181+0.8*B181</f>
         <v>-0.0434915629320993</v>
       </c>
@@ -9487,11 +9461,11 @@
         <f aca="false">0.5*C181+0.5*B181</f>
         <v>-0.0171888518325621</v>
       </c>
-      <c r="M181" s="10" t="n">
+      <c r="M181" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B181</f>
         <v>0.00146416432551256</v>
       </c>
-      <c r="N181" s="10" t="n">
+      <c r="N181" s="8" t="n">
         <f aca="false">C181-M181</f>
         <v>0.0251848356744874</v>
       </c>
@@ -9508,7 +9482,7 @@
         <f aca="false">Data!C182-Data!D182</f>
         <v>0.047732</v>
       </c>
-      <c r="E182" s="0" t="n">
+      <c r="E182" s="5" t="n">
         <f aca="false">0.2*C182+0.8*B182</f>
         <v>0.0568918103961374</v>
       </c>
@@ -9520,11 +9494,11 @@
         <f aca="false">0.5*C182+0.5*B182</f>
         <v>0.0534568814975858</v>
       </c>
-      <c r="M182" s="10" t="n">
+      <c r="M182" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B182</f>
         <v>0.00909067146772297</v>
       </c>
-      <c r="N182" s="10" t="n">
+      <c r="N182" s="8" t="n">
         <f aca="false">C182-M182</f>
         <v>0.038641328532277</v>
       </c>
@@ -9541,7 +9515,7 @@
         <f aca="false">Data!C183-Data!D183</f>
         <v>-0.053264</v>
       </c>
-      <c r="E183" s="0" t="n">
+      <c r="E183" s="5" t="n">
         <f aca="false">0.2*C183+0.8*B183</f>
         <v>-0.0329705362701598</v>
       </c>
@@ -9553,11 +9527,11 @@
         <f aca="false">0.5*C183+0.5*B183</f>
         <v>-0.0405805851688499</v>
       </c>
-      <c r="M183" s="10" t="n">
+      <c r="M183" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B183</f>
         <v>0.00356603476408752</v>
       </c>
-      <c r="N183" s="10" t="n">
+      <c r="N183" s="8" t="n">
         <f aca="false">C183-M183</f>
         <v>-0.0568300347640875</v>
       </c>
@@ -9574,23 +9548,23 @@
         <f aca="false">Data!C184-Data!D184</f>
         <v>0.089539</v>
       </c>
-      <c r="E184" s="0" t="n">
+      <c r="E184" s="5" t="n">
         <f aca="false">0.2*C184+0.8*B184</f>
         <v>0.0442863021485218</v>
       </c>
       <c r="G184" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B184 + 'Optimal portfolio from homework'!$C$15*C184</f>
-        <v>0.0537252653135911</v>
+        <v>0.053725265313591</v>
       </c>
       <c r="I184" s="9" t="n">
         <f aca="false">0.5*C184+0.5*B184</f>
         <v>0.0612560638428261</v>
       </c>
-      <c r="M184" s="10" t="n">
+      <c r="M184" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B184</f>
         <v>0.00742789055113004</v>
       </c>
-      <c r="N184" s="10" t="n">
+      <c r="N184" s="8" t="n">
         <f aca="false">C184-M184</f>
         <v>0.08211110944887</v>
       </c>
@@ -9607,23 +9581,23 @@
         <f aca="false">Data!C185-Data!D185</f>
         <v>-0.001529</v>
       </c>
-      <c r="E185" s="0" t="n">
+      <c r="E185" s="5" t="n">
         <f aca="false">0.2*C185+0.8*B185</f>
         <v>0.00930155367815784</v>
       </c>
       <c r="G185" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B185 + 'Optimal portfolio from homework'!$C$15*C185</f>
-        <v>0.00704247958801278</v>
+        <v>0.00704247958801279</v>
       </c>
       <c r="I185" s="9" t="n">
         <f aca="false">0.5*C185+0.5*B185</f>
         <v>0.00524009604884865</v>
       </c>
-      <c r="M185" s="10" t="n">
+      <c r="M185" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B185</f>
         <v>0.00609785441530446</v>
       </c>
-      <c r="N185" s="10" t="n">
+      <c r="N185" s="8" t="n">
         <f aca="false">C185-M185</f>
         <v>-0.00762685441530446</v>
       </c>
@@ -9640,23 +9614,23 @@
         <f aca="false">Data!C186-Data!D186</f>
         <v>-0.015553</v>
       </c>
-      <c r="E186" s="0" t="n">
+      <c r="E186" s="5" t="n">
         <f aca="false">0.2*C186+0.8*B186</f>
         <v>-0.00262445366613859</v>
       </c>
       <c r="G186" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B186 + 'Optimal portfolio from homework'!$C$15*C186</f>
-        <v>-0.00532113427120937</v>
+        <v>-0.00532113427120936</v>
       </c>
       <c r="I186" s="9" t="n">
         <f aca="false">0.5*C186+0.5*B186</f>
         <v>-0.00747265854133662</v>
       </c>
-      <c r="M186" s="10" t="n">
+      <c r="M186" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B186</f>
         <v>0.00537449695462075</v>
       </c>
-      <c r="N186" s="10" t="n">
+      <c r="N186" s="8" t="n">
         <f aca="false">C186-M186</f>
         <v>-0.0209274969546208</v>
       </c>
@@ -9673,23 +9647,23 @@
         <f aca="false">Data!C187-Data!D187</f>
         <v>-0.032305</v>
       </c>
-      <c r="E187" s="0" t="n">
+      <c r="E187" s="5" t="n">
         <f aca="false">0.2*C187+0.8*B187</f>
         <v>0.043100911301919</v>
       </c>
       <c r="G187" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B187 + 'Optimal portfolio from homework'!$C$15*C187</f>
-        <v>0.0273724872962761</v>
+        <v>0.0273724872962762</v>
       </c>
       <c r="I187" s="9" t="n">
         <f aca="false">0.5*C187+0.5*B187</f>
         <v>0.0148236945636994</v>
       </c>
-      <c r="M187" s="10" t="n">
+      <c r="M187" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B187</f>
         <v>0.00926645109933193</v>
       </c>
-      <c r="N187" s="10" t="n">
+      <c r="N187" s="8" t="n">
         <f aca="false">C187-M187</f>
         <v>-0.0415714510993319</v>
       </c>
@@ -9706,7 +9680,7 @@
         <f aca="false">Data!C188-Data!D188</f>
         <v>0.022817</v>
       </c>
-      <c r="E188" s="0" t="n">
+      <c r="E188" s="5" t="n">
         <f aca="false">0.2*C188+0.8*B188</f>
         <v>0.0265825705428243</v>
       </c>
@@ -9718,11 +9692,11 @@
         <f aca="false">0.5*C188+0.5*B188</f>
         <v>0.0251704815892652</v>
       </c>
-      <c r="M188" s="10" t="n">
+      <c r="M188" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B188</f>
         <v>0.00708217370449488</v>
       </c>
-      <c r="N188" s="10" t="n">
+      <c r="N188" s="8" t="n">
         <f aca="false">C188-M188</f>
         <v>0.0157348262955051</v>
       </c>
@@ -9739,7 +9713,7 @@
         <f aca="false">Data!C189-Data!D189</f>
         <v>-0.010304</v>
       </c>
-      <c r="E189" s="0" t="n">
+      <c r="E189" s="5" t="n">
         <f aca="false">0.2*C189+0.8*B189</f>
         <v>-0.018478771589032</v>
       </c>
@@ -9751,11 +9725,11 @@
         <f aca="false">0.5*C189+0.5*B189</f>
         <v>-0.015413232243145</v>
       </c>
-      <c r="M189" s="10" t="n">
+      <c r="M189" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B189</f>
         <v>0.00403391567472603</v>
       </c>
-      <c r="N189" s="10" t="n">
+      <c r="N189" s="8" t="n">
         <f aca="false">C189-M189</f>
         <v>-0.014337915674726</v>
       </c>
@@ -9772,7 +9746,7 @@
         <f aca="false">Data!C190-Data!D190</f>
         <v>-0.041642</v>
       </c>
-      <c r="E190" s="0" t="n">
+      <c r="E190" s="5" t="n">
         <f aca="false">0.2*C190+0.8*B190</f>
         <v>-0.0499948930070214</v>
       </c>
@@ -9784,11 +9758,11 @@
         <f aca="false">0.5*C190+0.5*B190</f>
         <v>-0.0468625581293884</v>
       </c>
-      <c r="M190" s="10" t="n">
+      <c r="M190" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B190</f>
         <v>0.00203158137296767</v>
       </c>
-      <c r="N190" s="10" t="n">
+      <c r="N190" s="8" t="n">
         <f aca="false">C190-M190</f>
         <v>-0.0436735813729677</v>
       </c>
@@ -9805,23 +9779,23 @@
         <f aca="false">Data!C191-Data!D191</f>
         <v>0.062622</v>
       </c>
-      <c r="E191" s="0" t="n">
+      <c r="E191" s="5" t="n">
         <f aca="false">0.2*C191+0.8*B191</f>
         <v>-0.0081587935703996</v>
       </c>
       <c r="G191" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B191 + 'Optimal portfolio from homework'!$C$15*C191</f>
-        <v>0.00660490749109523</v>
+        <v>0.00660490749109519</v>
       </c>
       <c r="I191" s="9" t="n">
         <f aca="false">0.5*C191+0.5*B191</f>
         <v>0.0183840040185003</v>
       </c>
-      <c r="M191" s="10" t="n">
+      <c r="M191" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B191</f>
         <v>0.00369566219300645</v>
       </c>
-      <c r="N191" s="10" t="n">
+      <c r="N191" s="8" t="n">
         <f aca="false">C191-M191</f>
         <v>0.0589263378069936</v>
       </c>
@@ -9838,7 +9812,7 @@
         <f aca="false">Data!C192-Data!D192</f>
         <v>0.015749</v>
       </c>
-      <c r="E192" s="0" t="n">
+      <c r="E192" s="5" t="n">
         <f aca="false">0.2*C192+0.8*B192</f>
         <v>0.0725861645752647</v>
       </c>
@@ -9850,11 +9824,11 @@
         <f aca="false">0.5*C192+0.5*B192</f>
         <v>0.0512722278595404</v>
       </c>
-      <c r="M192" s="10" t="n">
+      <c r="M192" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B192</f>
         <v>0.0108425948607468</v>
       </c>
-      <c r="N192" s="10" t="n">
+      <c r="N192" s="8" t="n">
         <f aca="false">C192-M192</f>
         <v>0.0049064051392532</v>
       </c>
@@ -9871,7 +9845,7 @@
         <f aca="false">Data!C193-Data!D193</f>
         <v>0.007747</v>
       </c>
-      <c r="E193" s="0" t="n">
+      <c r="E193" s="5" t="n">
         <f aca="false">0.2*C193+0.8*B193</f>
         <v>0.0343514931208391</v>
       </c>
@@ -9883,11 +9857,11 @@
         <f aca="false">0.5*C193+0.5*B193</f>
         <v>0.0243748082005244</v>
       </c>
-      <c r="M193" s="10" t="n">
+      <c r="M193" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B193</f>
         <v>0.00793731351223745</v>
       </c>
-      <c r="N193" s="10" t="n">
+      <c r="N193" s="8" t="n">
         <f aca="false">C193-M193</f>
         <v>-0.000190313512237451</v>
       </c>
@@ -9904,23 +9878,23 @@
         <f aca="false">Data!C194-Data!D194</f>
         <v>-0.016579</v>
       </c>
-      <c r="E194" s="0" t="n">
+      <c r="E194" s="5" t="n">
         <f aca="false">0.2*C194+0.8*B194</f>
         <v>0.00626813818884206</v>
       </c>
       <c r="G194" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B194 + 'Optimal portfolio from homework'!$C$15*C194</f>
-        <v>0.00150260362337784</v>
+        <v>0.00150260362337787</v>
       </c>
       <c r="I194" s="9" t="n">
         <f aca="false">0.5*C194+0.5*B194</f>
         <v>-0.00229953863197372</v>
       </c>
-      <c r="M194" s="10" t="n">
+      <c r="M194" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B194</f>
         <v>0.00609599744963612</v>
       </c>
-      <c r="N194" s="10" t="n">
+      <c r="N194" s="8" t="n">
         <f aca="false">C194-M194</f>
         <v>-0.0226749974496361</v>
       </c>
@@ -9937,7 +9911,7 @@
         <f aca="false">Data!C195-Data!D195</f>
         <v>-0.006703</v>
       </c>
-      <c r="E195" s="0" t="n">
+      <c r="E195" s="5" t="n">
         <f aca="false">0.2*C195+0.8*B195</f>
         <v>0.0379288731665886</v>
       </c>
@@ -9949,11 +9923,11 @@
         <f aca="false">0.5*C195+0.5*B195</f>
         <v>0.0211919207291179</v>
       </c>
-      <c r="M195" s="10" t="n">
+      <c r="M195" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B195</f>
         <v>0.00845020916635227</v>
       </c>
-      <c r="N195" s="10" t="n">
+      <c r="N195" s="8" t="n">
         <f aca="false">C195-M195</f>
         <v>-0.0151532091663523</v>
       </c>
@@ -9970,7 +9944,7 @@
         <f aca="false">Data!C196-Data!D196</f>
         <v>0.081395</v>
       </c>
-      <c r="E196" s="0" t="n">
+      <c r="E196" s="5" t="n">
         <f aca="false">0.2*C196+0.8*B196</f>
         <v>0.0384814076048781</v>
       </c>
@@ -9982,11 +9956,11 @@
         <f aca="false">0.5*C196+0.5*B196</f>
         <v>0.0545740047530488</v>
       </c>
-      <c r="M196" s="10" t="n">
+      <c r="M196" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B196</f>
         <v>0.00709670532195595</v>
       </c>
-      <c r="N196" s="10" t="n">
+      <c r="N196" s="8" t="n">
         <f aca="false">C196-M196</f>
         <v>0.0742982946780441</v>
       </c>
@@ -10003,23 +9977,23 @@
         <f aca="false">Data!C197-Data!D197</f>
         <v>0.044145</v>
       </c>
-      <c r="E197" s="0" t="n">
+      <c r="E197" s="5" t="n">
         <f aca="false">0.2*C197+0.8*B197</f>
         <v>-0.0276958429605494</v>
       </c>
       <c r="G197" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B197 + 'Optimal portfolio from homework'!$C$15*C197</f>
-        <v>-0.0127110331558893</v>
+        <v>-0.0127110331558894</v>
       </c>
       <c r="I197" s="9" t="n">
         <f aca="false">0.5*C197+0.5*B197</f>
         <v>-0.000755526850343392</v>
       </c>
-      <c r="M197" s="10" t="n">
+      <c r="M197" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B197</f>
         <v>0.00243933999317554</v>
       </c>
-      <c r="N197" s="10" t="n">
+      <c r="N197" s="8" t="n">
         <f aca="false">C197-M197</f>
         <v>0.0417056600068245</v>
       </c>
@@ -10036,23 +10010,23 @@
         <f aca="false">Data!C198-Data!D198</f>
         <v>0.007739</v>
       </c>
-      <c r="E198" s="0" t="n">
+      <c r="E198" s="5" t="n">
         <f aca="false">0.2*C198+0.8*B198</f>
         <v>0.0375934381034298</v>
       </c>
       <c r="G198" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B198 + 'Optimal portfolio from homework'!$C$15*C198</f>
-        <v>0.0313662968510567</v>
+        <v>0.0313662968510568</v>
       </c>
       <c r="I198" s="9" t="n">
         <f aca="false">0.5*C198+0.5*B198</f>
         <v>0.0263980238146436</v>
       </c>
-      <c r="M198" s="10" t="n">
+      <c r="M198" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B198</f>
         <v>0.00819454288699641</v>
       </c>
-      <c r="N198" s="10" t="n">
+      <c r="N198" s="8" t="n">
         <f aca="false">C198-M198</f>
         <v>-0.000455542886996413</v>
       </c>
@@ -10069,7 +10043,7 @@
         <f aca="false">Data!C199-Data!D199</f>
         <v>-0.01063</v>
       </c>
-      <c r="E199" s="0" t="n">
+      <c r="E199" s="5" t="n">
         <f aca="false">0.2*C199+0.8*B199</f>
         <v>0.023199921524434</v>
       </c>
@@ -10081,11 +10055,11 @@
         <f aca="false">0.5*C199+0.5*B199</f>
         <v>0.0105137009527712</v>
       </c>
-      <c r="M199" s="10" t="n">
+      <c r="M199" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B199</f>
         <v>0.00734441563178384</v>
       </c>
-      <c r="N199" s="10" t="n">
+      <c r="N199" s="8" t="n">
         <f aca="false">C199-M199</f>
         <v>-0.0179744156317838</v>
       </c>
@@ -10102,7 +10076,7 @@
         <f aca="false">Data!C200-Data!D200</f>
         <v>0.035026</v>
       </c>
-      <c r="E200" s="0" t="n">
+      <c r="E200" s="5" t="n">
         <f aca="false">0.2*C200+0.8*B200</f>
         <v>0.0130429890245112</v>
       </c>
@@ -10114,11 +10088,11 @@
         <f aca="false">0.5*C200+0.5*B200</f>
         <v>0.0212866181403195</v>
       </c>
-      <c r="M200" s="10" t="n">
+      <c r="M200" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B200</f>
         <v>0.00581477004652046</v>
       </c>
-      <c r="N200" s="10" t="n">
+      <c r="N200" s="8" t="n">
         <f aca="false">C200-M200</f>
         <v>0.0292112299534795</v>
       </c>
@@ -10135,7 +10109,7 @@
         <f aca="false">Data!C201-Data!D201</f>
         <v>0.03841</v>
       </c>
-      <c r="E201" s="0" t="n">
+      <c r="E201" s="5" t="n">
         <f aca="false">0.2*C201+0.8*B201</f>
         <v>0.0231548333856292</v>
       </c>
@@ -10147,11 +10121,11 @@
         <f aca="false">0.5*C201+0.5*B201</f>
         <v>0.0288755208660182</v>
       </c>
-      <c r="M201" s="10" t="n">
+      <c r="M201" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B201</f>
         <v>0.00656301635568523</v>
       </c>
-      <c r="N201" s="10" t="n">
+      <c r="N201" s="8" t="n">
         <f aca="false">C201-M201</f>
         <v>0.0318469836443148</v>
       </c>
@@ -10168,7 +10142,7 @@
         <f aca="false">Data!C202-Data!D202</f>
         <v>0.045918</v>
       </c>
-      <c r="E202" s="0" t="n">
+      <c r="E202" s="5" t="n">
         <f aca="false">0.2*C202+0.8*B202</f>
         <v>0.0229646164544249</v>
       </c>
@@ -10180,11 +10154,11 @@
         <f aca="false">0.5*C202+0.5*B202</f>
         <v>0.0315721352840155</v>
       </c>
-      <c r="M202" s="10" t="n">
+      <c r="M202" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B202</f>
         <v>0.00642884679313681</v>
       </c>
-      <c r="N202" s="10" t="n">
+      <c r="N202" s="8" t="n">
         <f aca="false">C202-M202</f>
         <v>0.0394891532068632</v>
       </c>
@@ -10201,23 +10175,23 @@
         <f aca="false">Data!C203-Data!D203</f>
         <v>0.044871</v>
       </c>
-      <c r="E203" s="0" t="n">
+      <c r="E203" s="5" t="n">
         <f aca="false">0.2*C203+0.8*B203</f>
         <v>-0.00147186242948482</v>
       </c>
       <c r="G203" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!$B$15*B203 + 'Optimal portfolio from homework'!$C$15*C203</f>
-        <v>0.00819449100808136</v>
+        <v>0.00819449100808135</v>
       </c>
       <c r="I203" s="9" t="n">
         <f aca="false">0.5*C203+0.5*B203</f>
         <v>0.015906710981572</v>
       </c>
-      <c r="M203" s="10" t="n">
+      <c r="M203" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B203</f>
         <v>0.00450751800411338</v>
       </c>
-      <c r="N203" s="10" t="n">
+      <c r="N203" s="8" t="n">
         <f aca="false">C203-M203</f>
         <v>0.0403634819958866</v>
       </c>
@@ -10234,7 +10208,7 @@
         <f aca="false">Data!C204-Data!D204</f>
         <v>-0.045412</v>
       </c>
-      <c r="E204" s="0" t="n">
+      <c r="E204" s="5" t="n">
         <f aca="false">0.2*C204+0.8*B204</f>
         <v>0.0345701231055359</v>
       </c>
@@ -10246,11 +10220,11 @@
         <f aca="false">0.5*C204+0.5*B204</f>
         <v>0.00457682694095996</v>
       </c>
-      <c r="M204" s="10" t="n">
+      <c r="M204" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B204</f>
         <v>0.00879780699569768</v>
       </c>
-      <c r="N204" s="10" t="n">
+      <c r="N204" s="8" t="n">
         <f aca="false">C204-M204</f>
         <v>-0.0542098069956977</v>
       </c>
@@ -10267,7 +10241,7 @@
         <f aca="false">Data!C205-Data!D205</f>
         <v>-0.023762</v>
       </c>
-      <c r="E205" s="0" t="n">
+      <c r="E205" s="5" t="n">
         <f aca="false">0.2*C205+0.8*B205</f>
         <v>-0.0268774108537389</v>
       </c>
@@ -10279,11 +10253,11 @@
         <f aca="false">0.5*C205+0.5*B205</f>
         <v>-0.0257091317835868</v>
       </c>
-      <c r="M205" s="10" t="n">
+      <c r="M205" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B205</f>
         <v>0.00358131885560843</v>
       </c>
-      <c r="N205" s="10" t="n">
+      <c r="N205" s="8" t="n">
         <f aca="false">C205-M205</f>
         <v>-0.0273433188556084</v>
       </c>
@@ -10307,24 +10281,24 @@
   <dimension ref="A1:J1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="29.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="29.03"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="1" t="n">
@@ -10337,7 +10311,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="1" t="n">
@@ -10350,86 +10324,86 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="11" t="n">
         <f aca="false">B3/B4</f>
         <v>0.18518066825192</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="11" t="n">
         <f aca="false">C3/C4</f>
         <v>0.120382598896978</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="11" t="n">
         <f aca="false">CORREL('Excess returns'!B2:B205,'Excess returns'!C2:C205)</f>
         <v>0.0598620726348209</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11"/>
+      <c r="A9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="11" t="n">
         <f aca="false">B4^2</f>
         <v>0.00212190415816005</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="11" t="n">
         <f aca="false">B6*B4*C4</f>
         <v>0.000134622108299787</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="12" t="n">
         <f aca="false">B6*B4*C4</f>
         <v>0.000134622108299787</v>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="11" t="n">
         <f aca="false">C4^2</f>
         <v>0.0023834360970021</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="11" t="n">
         <f aca="false" t="array" ref="B14:C14">TRANSPOSE( MMULT( MINVERSE( B11:C12 ), TRANSPOSE( B3:C3 ) ))</f>
-        <v>3.87751536012174</v>
-      </c>
-      <c r="C14" s="12" t="n">
+        <v>3.87751536012175</v>
+      </c>
+      <c r="C14" s="11" t="n">
         <v>2.24681209910872</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="1" t="n">
@@ -10438,394 +10412,394 @@
       </c>
       <c r="C15" s="1" t="n">
         <f aca="false">C14/(B14+C14)</f>
-        <v>0.366866748074088</v>
+        <v>0.366866748074087</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="12" t="n">
         <f aca="false" t="array" ref="B17:B17">MMULT(B15:C15,TRANSPOSE(B3:C3)) / SQRT( MMULT( B15:C15, MMULT( B11:C12, TRANSPOSE(B15:C15) ) ) )</f>
         <v>0.215129592204537</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="7" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6"/>
+      <c r="A23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="J24" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="9" t="s">
         <v>16</v>
       </c>
       <c r="D25" s="1" t="n">
         <f aca="false">B3</f>
         <v>0.0085301865477073</v>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="F25" s="8" t="n">
         <f aca="false">AVERAGE('Excess returns'!E2:E205)</f>
         <v>0.00799957570875407</v>
       </c>
-      <c r="H25" s="10" t="n">
+      <c r="H25" s="8" t="n">
         <f aca="false">AVERAGE('Excess returns'!G2:G205)</f>
         <v>0.00755686918280913</v>
       </c>
-      <c r="J25" s="10" t="n">
+      <c r="J25" s="8" t="n">
         <f aca="false">AVERAGE('Excess returns'!I2:I205)</f>
         <v>0.00720365945032424</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D26" s="1" t="n">
         <f aca="false">B4</f>
         <v>0.0460641309280882</v>
       </c>
-      <c r="F26" s="10" t="n">
+      <c r="F26" s="8" t="n">
         <f aca="false">STDEV('Excess returns'!E2:E205)</f>
         <v>0.0386837844549684</v>
       </c>
-      <c r="H26" s="10" t="n">
+      <c r="H26" s="8" t="n">
         <f aca="false">STDEV('Excess returns'!G2:G205)</f>
         <v>0.0351270557684335</v>
       </c>
-      <c r="J26" s="10" t="n">
+      <c r="J26" s="8" t="n">
         <f aca="false">STDEV('Excess returns'!I2:I205)</f>
         <v>0.0345491840416012</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="15" t="n">
+      <c r="B27" s="13" t="n">
         <f aca="false">C5</f>
         <v>0.120382598896978</v>
       </c>
-      <c r="D27" s="12" t="n">
-        <f aca="false">B5</f>
+      <c r="D27" s="11" t="n">
+        <f aca="false">D25/D26</f>
         <v>0.18518066825192</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="F27" s="11" t="n">
         <f aca="false">F25/F26</f>
         <v>0.206794030663322</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="H27" s="11" t="n">
         <f aca="false">H25/H26</f>
         <v>0.215129592204537</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="J27" s="11" t="n">
         <f aca="false">J25/J26</f>
         <v>0.208504474133172</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="D28" s="11" t="n">
         <f aca="false">B6</f>
         <v>0.0598620726348209</v>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="F28" s="12" t="n">
         <f aca="false">CORREL('Excess returns'!E2:E205,'Excess returns'!C2:C205)</f>
         <v>0.309434176510314</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="H28" s="12" t="n">
         <f aca="false">CORREL('Excess returns'!G2:G205,'Excess returns'!$C2:$C205)</f>
         <v>0.559581774238304</v>
       </c>
-      <c r="J28" s="13" t="n">
+      <c r="J28" s="12" t="n">
         <f aca="false">CORREL('Excess returns'!I2:I205,'Excess returns'!$C2:$C205)</f>
         <v>0.746442257783727</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="D29" s="11" t="n">
         <f aca="false">D27*D28</f>
         <v>0.0110852986134611</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="F29" s="11" t="n">
         <f aca="false">F27*F28</f>
         <v>0.0639891405855537</v>
       </c>
-      <c r="H29" s="15" t="n">
+      <c r="H29" s="13" t="n">
         <f aca="false">H27*H28</f>
         <v>0.120382598896978</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="J29" s="11" t="n">
         <f aca="false">J27*J28</f>
         <v>0.155636550429974</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6" t="s">
+      <c r="E30" s="7"/>
+      <c r="F30" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G30" s="6"/>
-      <c r="H30" s="16" t="s">
+      <c r="G30" s="7"/>
+      <c r="H30" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="J30" s="6" t="s">
+      <c r="J30" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="10" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="15" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="15" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="15" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17"/>
+      <c r="A37" s="15"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="F38" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H38" s="8" t="s">
+      <c r="H38" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J38" s="8" t="s">
+      <c r="J38" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="13" t="n">
+      <c r="D39" s="12" t="n">
         <f aca="false">D28*$C$4/D26</f>
         <v>0.063444009844686</v>
       </c>
-      <c r="F39" s="13" t="n">
+      <c r="F39" s="12" t="n">
         <f aca="false">F28*$C$4/F26</f>
         <v>0.390518021725858</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="H39" s="12" t="n">
         <f aca="false">H28*$C$4/H26</f>
         <v>0.777720536212386</v>
       </c>
-      <c r="J39" s="13" t="n">
+      <c r="J39" s="12" t="n">
         <f aca="false">J28*$C$4/J26</f>
         <v>1.05477585335202</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D40" s="12" t="n">
+      <c r="D40" s="11" t="n">
         <f aca="false">SLOPE('Excess returns'!C2:C205,'Excess returns'!B2:B205)</f>
         <v>0.063444009844686</v>
       </c>
-      <c r="F40" s="13" t="n">
+      <c r="F40" s="12" t="n">
         <f aca="false">SLOPE('Excess returns'!$C2:$C205,'Excess returns'!E2:E205)</f>
         <v>0.390518021725858</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="H40" s="12" t="n">
         <f aca="false">SLOPE('Excess returns'!$C2:$C205,'Excess returns'!G2:G205)</f>
-        <v>0.777720536212386</v>
-      </c>
-      <c r="J40" s="13" t="n">
+        <v>0.777720536212385</v>
+      </c>
+      <c r="J40" s="12" t="n">
         <f aca="false">SLOPE('Excess returns'!$C2:$C205,'Excess returns'!I2:I205)</f>
         <v>1.05477585335202</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="10" t="n">
+      <c r="D41" s="8" t="n">
         <f aca="false">$C$3-D39*D25</f>
         <v>0.00533594311363143</v>
       </c>
-      <c r="F41" s="10" t="n">
+      <c r="F41" s="8" t="n">
         <f aca="false">$C$3-F39*F25</f>
         <v>0.00275315387251231</v>
       </c>
-      <c r="H41" s="10" t="n">
+      <c r="H41" s="8" t="n">
         <f aca="false">$C$3-H39*H25</f>
         <v>0</v>
       </c>
-      <c r="J41" s="10" t="n">
+      <c r="J41" s="8" t="n">
         <f aca="false">$C$3-J39*J25</f>
         <v>-0.0017211136910319</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D42" s="10" t="n">
+      <c r="D42" s="8" t="n">
         <f aca="false">INTERCEPT('Excess returns'!C2:C205,'Excess returns'!B2:B205)</f>
         <v>0.00533594311363143</v>
       </c>
-      <c r="F42" s="10" t="n">
+      <c r="F42" s="8" t="n">
         <f aca="false">INTERCEPT('Excess returns'!$C2:$C205,'Excess returns'!E2:E205)</f>
         <v>0.00275315387251231</v>
       </c>
-      <c r="H42" s="10" t="n">
+      <c r="H42" s="8" t="n">
         <f aca="false">INTERCEPT('Excess returns'!$C2:$C205,'Excess returns'!G2:G205)</f>
-        <v>8.67361737988404E-019</v>
-      </c>
-      <c r="J42" s="10" t="n">
+        <v>6.93889390390723E-018</v>
+      </c>
+      <c r="J42" s="8" t="n">
         <f aca="false">INTERCEPT('Excess returns'!$C2:$C205,'Excess returns'!I2:I205)</f>
         <v>-0.0017211136910319</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6" t="s">
+      <c r="E43" s="7"/>
+      <c r="F43" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="6"/>
-      <c r="H43" s="16" t="s">
+      <c r="G43" s="7"/>
+      <c r="H43" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="J43" s="6" t="s">
+      <c r="J43" s="7" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="7" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6"/>
+      <c r="A47" s="7"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D48" s="13" t="n">
+      <c r="D48" s="12" t="n">
         <f aca="false">SQRT(C4^2 - D39^2*B4^2)</f>
         <v>0.0487328957752134</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D49" s="13" t="n">
+      <c r="D49" s="12" t="n">
         <f aca="false">STDEV('Excess returns'!N2:N205)</f>
         <v>0.0487328957752135</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D50" s="12" t="n">
+      <c r="D50" s="11" t="n">
         <f aca="false">D42/D49</f>
         <v>0.109493659852354</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D51" s="12" t="n">
+      <c r="D51" s="11" t="n">
         <f aca="false">SQRT(D27^2 + D50^2)</f>
         <v>0.215129592204537</v>
       </c>
-      <c r="E51" s="19" t="s">
+      <c r="E51" s="15" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="7" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="17"/>
+      <c r="A56" s="15"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/Module 2/Week 8 - CAPM and investment styles/Homework 2 example.xlsx
+++ b/Module 2/Week 8 - CAPM and investment styles/Homework 2 example.xlsx
@@ -214,7 +214,7 @@
     <numFmt numFmtId="166" formatCode="yyyy\-mm"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,6 +267,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -335,7 +341,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -388,15 +394,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3556,7 +3570,7 @@
       </c>
       <c r="M2" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B2</f>
-        <v>0.00138621198753918</v>
+        <v>0.00138621198753916</v>
       </c>
       <c r="N2" s="8" t="n">
         <f aca="false">C2-M2</f>
@@ -3655,11 +3669,11 @@
       </c>
       <c r="M5" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B5</f>
-        <v>0.00830144901444975</v>
+        <v>0.00830144901444976</v>
       </c>
       <c r="N5" s="8" t="n">
         <f aca="false">C5-M5</f>
-        <v>-0.0842544490144497</v>
+        <v>-0.0842544490144498</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3688,11 +3702,11 @@
       </c>
       <c r="M6" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B6</f>
-        <v>0.00604175498978325</v>
+        <v>0.00604175498978326</v>
       </c>
       <c r="N6" s="8" t="n">
         <f aca="false">C6-M6</f>
-        <v>0.00569924501021675</v>
+        <v>0.00569924501021674</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3721,11 +3735,11 @@
       </c>
       <c r="M7" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B7</f>
-        <v>-0.000125425990441131</v>
+        <v>-0.000125425990441149</v>
       </c>
       <c r="N7" s="8" t="n">
         <f aca="false">C7-M7</f>
-        <v>0.0589714259904411</v>
+        <v>0.0589714259904412</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3820,7 +3834,7 @@
       </c>
       <c r="M10" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B10</f>
-        <v>-0.000409591521786886</v>
+        <v>-0.000409591521786904</v>
       </c>
       <c r="N10" s="8" t="n">
         <f aca="false">C10-M10</f>
@@ -3853,7 +3867,7 @@
       </c>
       <c r="M11" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B11</f>
-        <v>-0.00536858407431034</v>
+        <v>-0.0053685840743104</v>
       </c>
       <c r="N11" s="8" t="n">
         <f aca="false">C11-M11</f>
@@ -3886,7 +3900,7 @@
       </c>
       <c r="M12" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B12</f>
-        <v>0.000764905174787745</v>
+        <v>0.000764905174787732</v>
       </c>
       <c r="N12" s="8" t="n">
         <f aca="false">C12-M12</f>
@@ -3919,7 +3933,7 @@
       </c>
       <c r="M13" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B13</f>
-        <v>0.00601295967338238</v>
+        <v>0.00601295967338239</v>
       </c>
       <c r="N13" s="8" t="n">
         <f aca="false">C13-M13</f>
@@ -3952,7 +3966,7 @@
       </c>
       <c r="M14" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B14</f>
-        <v>-1.32525577952423E-006</v>
+        <v>-1.32525577954245E-006</v>
       </c>
       <c r="N14" s="8" t="n">
         <f aca="false">C14-M14</f>
@@ -3985,11 +3999,11 @@
       </c>
       <c r="M15" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B15</f>
-        <v>-0.00143164859143193</v>
+        <v>-0.00143164859143197</v>
       </c>
       <c r="N15" s="8" t="n">
         <f aca="false">C15-M15</f>
-        <v>0.0288216485914319</v>
+        <v>0.028821648591432</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4022,7 +4036,7 @@
       </c>
       <c r="N16" s="8" t="n">
         <f aca="false">C16-M16</f>
-        <v>-0.0378359776344133</v>
+        <v>-0.0378359776344134</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4084,7 +4098,7 @@
       </c>
       <c r="M18" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B18</f>
-        <v>0.00890003613498342</v>
+        <v>0.00890003613498343</v>
       </c>
       <c r="N18" s="8" t="n">
         <f aca="false">C18-M18</f>
@@ -4183,11 +4197,11 @@
       </c>
       <c r="M21" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B21</f>
-        <v>0.00761285910644298</v>
+        <v>0.00761285910644299</v>
       </c>
       <c r="N21" s="8" t="n">
         <f aca="false">C21-M21</f>
-        <v>0.00750314089355702</v>
+        <v>0.00750314089355701</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4216,7 +4230,7 @@
       </c>
       <c r="M22" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B22</f>
-        <v>0.00768767906760035</v>
+        <v>0.00768767906760036</v>
       </c>
       <c r="N22" s="8" t="n">
         <f aca="false">C22-M22</f>
@@ -4282,7 +4296,7 @@
       </c>
       <c r="M24" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B24</f>
-        <v>0.0091307746132822</v>
+        <v>0.00913077461328222</v>
       </c>
       <c r="N24" s="8" t="n">
         <f aca="false">C24-M24</f>
@@ -4315,7 +4329,7 @@
       </c>
       <c r="M25" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B25</f>
-        <v>0.00656390121989973</v>
+        <v>0.00656390121989974</v>
       </c>
       <c r="N25" s="8" t="n">
         <f aca="false">C25-M25</f>
@@ -4348,7 +4362,7 @@
       </c>
       <c r="M26" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B26</f>
-        <v>0.00304956114786403</v>
+        <v>0.00304956114786402</v>
       </c>
       <c r="N26" s="8" t="n">
         <f aca="false">C26-M26</f>
@@ -4381,7 +4395,7 @@
       </c>
       <c r="M27" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B27</f>
-        <v>0.00729753420310034</v>
+        <v>0.00729753420310035</v>
       </c>
       <c r="N27" s="8" t="n">
         <f aca="false">C27-M27</f>
@@ -4414,7 +4428,7 @@
       </c>
       <c r="M28" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B28</f>
-        <v>0.00914483601974381</v>
+        <v>0.00914483601974383</v>
       </c>
       <c r="N28" s="8" t="n">
         <f aca="false">C28-M28</f>
@@ -4480,11 +4494,11 @@
       </c>
       <c r="M30" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B30</f>
-        <v>0.000250831224394653</v>
+        <v>0.00025083122439464</v>
       </c>
       <c r="N30" s="8" t="n">
         <f aca="false">C30-M30</f>
-        <v>0.0326211687756053</v>
+        <v>0.0326211687756054</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4513,11 +4527,11 @@
       </c>
       <c r="M31" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B31</f>
-        <v>0.00200547719670786</v>
+        <v>0.00200547719670784</v>
       </c>
       <c r="N31" s="8" t="n">
         <f aca="false">C31-M31</f>
-        <v>0.0197235228032921</v>
+        <v>0.0197235228032922</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4546,7 +4560,7 @@
       </c>
       <c r="M32" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B32</f>
-        <v>0.00976820608140383</v>
+        <v>0.00976820608140385</v>
       </c>
       <c r="N32" s="8" t="n">
         <f aca="false">C32-M32</f>
@@ -4579,7 +4593,7 @@
       </c>
       <c r="M33" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B33</f>
-        <v>0.00245571938930323</v>
+        <v>0.00245571938930322</v>
       </c>
       <c r="N33" s="8" t="n">
         <f aca="false">C33-M33</f>
@@ -4645,7 +4659,7 @@
       </c>
       <c r="M35" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B35</f>
-        <v>0.00773305539627394</v>
+        <v>0.00773305539627395</v>
       </c>
       <c r="N35" s="8" t="n">
         <f aca="false">C35-M35</f>
@@ -4711,7 +4725,7 @@
       </c>
       <c r="M37" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B37</f>
-        <v>0.00956216301365726</v>
+        <v>0.00956216301365728</v>
       </c>
       <c r="N37" s="8" t="n">
         <f aca="false">C37-M37</f>
@@ -4744,7 +4758,7 @@
       </c>
       <c r="M38" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B38</f>
-        <v>0.00682504118265208</v>
+        <v>0.00682504118265209</v>
       </c>
       <c r="N38" s="8" t="n">
         <f aca="false">C38-M38</f>
@@ -4777,7 +4791,7 @@
       </c>
       <c r="M39" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B39</f>
-        <v>0.007497023764279</v>
+        <v>0.00749702376427901</v>
       </c>
       <c r="N39" s="8" t="n">
         <f aca="false">C39-M39</f>
@@ -4843,7 +4857,7 @@
       </c>
       <c r="M41" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B41</f>
-        <v>0.00720622181851899</v>
+        <v>0.007206221818519</v>
       </c>
       <c r="N41" s="8" t="n">
         <f aca="false">C41-M41</f>
@@ -4942,7 +4956,7 @@
       </c>
       <c r="M44" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B44</f>
-        <v>0.00403733576046029</v>
+        <v>0.00403733576046028</v>
       </c>
       <c r="N44" s="8" t="n">
         <f aca="false">C44-M44</f>
@@ -4975,7 +4989,7 @@
       </c>
       <c r="M45" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B45</f>
-        <v>0.00187414701835347</v>
+        <v>0.00187414701835346</v>
       </c>
       <c r="N45" s="8" t="n">
         <f aca="false">C45-M45</f>
@@ -5008,7 +5022,7 @@
       </c>
       <c r="M46" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B46</f>
-        <v>0.000867844509182743</v>
+        <v>0.000867844509182728</v>
       </c>
       <c r="N46" s="8" t="n">
         <f aca="false">C46-M46</f>
@@ -5140,7 +5154,7 @@
       </c>
       <c r="M50" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B50</f>
-        <v>0.00816846065160229</v>
+        <v>0.0081684606516023</v>
       </c>
       <c r="N50" s="8" t="n">
         <f aca="false">C50-M50</f>
@@ -5173,11 +5187,11 @@
       </c>
       <c r="M51" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B51</f>
-        <v>0.00806838331608505</v>
+        <v>0.00806838331608506</v>
       </c>
       <c r="N51" s="8" t="n">
         <f aca="false">C51-M51</f>
-        <v>0.020700616683915</v>
+        <v>0.0207006166839149</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5206,7 +5220,7 @@
       </c>
       <c r="M52" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B52</f>
-        <v>0.00741782973837808</v>
+        <v>0.00741782973837809</v>
       </c>
       <c r="N52" s="8" t="n">
         <f aca="false">C52-M52</f>
@@ -5272,7 +5286,7 @@
       </c>
       <c r="M54" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B54</f>
-        <v>0.00151164201319165</v>
+        <v>0.00151164201319164</v>
       </c>
       <c r="N54" s="8" t="n">
         <f aca="false">C54-M54</f>
@@ -5305,11 +5319,11 @@
       </c>
       <c r="M55" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B55</f>
-        <v>0.00794282471861964</v>
+        <v>0.00794282471861965</v>
       </c>
       <c r="N55" s="8" t="n">
         <f aca="false">C55-M55</f>
-        <v>-0.00666682471861964</v>
+        <v>-0.00666682471861965</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5338,7 +5352,7 @@
       </c>
       <c r="M56" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B56</f>
-        <v>0.00620510836200148</v>
+        <v>0.00620510836200149</v>
       </c>
       <c r="N56" s="8" t="n">
         <f aca="false">C56-M56</f>
@@ -5474,7 +5488,7 @@
       </c>
       <c r="N60" s="8" t="n">
         <f aca="false">C60-M60</f>
-        <v>0.000181122619152523</v>
+        <v>0.00018112261915252</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5536,11 +5550,11 @@
       </c>
       <c r="M62" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B62</f>
-        <v>0.00861994453666457</v>
+        <v>0.00861994453666458</v>
       </c>
       <c r="N62" s="8" t="n">
         <f aca="false">C62-M62</f>
-        <v>-0.00230994453666457</v>
+        <v>-0.00230994453666458</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5602,11 +5616,11 @@
       </c>
       <c r="M64" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B64</f>
-        <v>0.00770789134434444</v>
+        <v>0.00770789134434445</v>
       </c>
       <c r="N64" s="8" t="n">
         <f aca="false">C64-M64</f>
-        <v>-0.00047989134434444</v>
+        <v>-0.000479891344344448</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5672,7 +5686,7 @@
       </c>
       <c r="N66" s="8" t="n">
         <f aca="false">C66-M66</f>
-        <v>-0.049250586621586</v>
+        <v>-0.0492505866215861</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5734,7 +5748,7 @@
       </c>
       <c r="M68" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B68</f>
-        <v>0.00855399332255748</v>
+        <v>0.0085539933225575</v>
       </c>
       <c r="N68" s="8" t="n">
         <f aca="false">C68-M68</f>
@@ -5767,7 +5781,7 @@
       </c>
       <c r="M69" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B69</f>
-        <v>0.00348853445774387</v>
+        <v>0.00348853445774386</v>
       </c>
       <c r="N69" s="8" t="n">
         <f aca="false">C69-M69</f>
@@ -5800,11 +5814,11 @@
       </c>
       <c r="M70" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B70</f>
-        <v>0.00731643083495735</v>
+        <v>0.00731643083495736</v>
       </c>
       <c r="N70" s="8" t="n">
         <f aca="false">C70-M70</f>
-        <v>-0.0482424308349573</v>
+        <v>-0.0482424308349574</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5833,11 +5847,11 @@
       </c>
       <c r="M71" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B71</f>
-        <v>0.008245805776486</v>
+        <v>0.00824580577648601</v>
       </c>
       <c r="N71" s="8" t="n">
         <f aca="false">C71-M71</f>
-        <v>-0.009742805776486</v>
+        <v>-0.00974280577648601</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5899,7 +5913,7 @@
       </c>
       <c r="M73" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B73</f>
-        <v>0.00693078280868511</v>
+        <v>0.00693078280868512</v>
       </c>
       <c r="N73" s="8" t="n">
         <f aca="false">C73-M73</f>
@@ -5932,7 +5946,7 @@
       </c>
       <c r="M74" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B74</f>
-        <v>0.00313499160986238</v>
+        <v>0.00313499160986237</v>
       </c>
       <c r="N74" s="8" t="n">
         <f aca="false">C74-M74</f>
@@ -5965,7 +5979,7 @@
       </c>
       <c r="M75" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B75</f>
-        <v>0.00822940662129421</v>
+        <v>0.00822940662129422</v>
       </c>
       <c r="N75" s="8" t="n">
         <f aca="false">C75-M75</f>
@@ -5998,7 +6012,7 @@
       </c>
       <c r="M76" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B76</f>
-        <v>0.00585859232281019</v>
+        <v>0.0058585923228102</v>
       </c>
       <c r="N76" s="8" t="n">
         <f aca="false">C76-M76</f>
@@ -6031,11 +6045,11 @@
       </c>
       <c r="M77" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B77</f>
-        <v>0.00579533610619273</v>
+        <v>0.00579533610619274</v>
       </c>
       <c r="N77" s="8" t="n">
         <f aca="false">C77-M77</f>
-        <v>-0.00734133610619273</v>
+        <v>-0.00734133610619274</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6064,7 +6078,7 @@
       </c>
       <c r="M78" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B78</f>
-        <v>0.00681732498601138</v>
+        <v>0.00681732498601139</v>
       </c>
       <c r="N78" s="8" t="n">
         <f aca="false">C78-M78</f>
@@ -6097,7 +6111,7 @@
       </c>
       <c r="M79" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B79</f>
-        <v>0.00663778333712881</v>
+        <v>0.00663778333712882</v>
       </c>
       <c r="N79" s="8" t="n">
         <f aca="false">C79-M79</f>
@@ -6163,11 +6177,11 @@
       </c>
       <c r="M81" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B81</f>
-        <v>0.00786559155461235</v>
+        <v>0.00786559155461236</v>
       </c>
       <c r="N81" s="8" t="n">
         <f aca="false">C81-M81</f>
-        <v>-0.0150085915546123</v>
+        <v>-0.0150085915546124</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6229,7 +6243,7 @@
       </c>
       <c r="M83" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B83</f>
-        <v>0.00687332474677096</v>
+        <v>0.00687332474677097</v>
       </c>
       <c r="N83" s="8" t="n">
         <f aca="false">C83-M83</f>
@@ -6262,11 +6276,11 @@
       </c>
       <c r="M84" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B84</f>
-        <v>0.00703776741204038</v>
+        <v>0.00703776741204039</v>
       </c>
       <c r="N84" s="8" t="n">
         <f aca="false">C84-M84</f>
-        <v>0.00255123258795962</v>
+        <v>0.00255123258795961</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6361,7 +6375,7 @@
       </c>
       <c r="M87" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B87</f>
-        <v>0.00897735918692819</v>
+        <v>0.0089773591869282</v>
       </c>
       <c r="N87" s="8" t="n">
         <f aca="false">C87-M87</f>
@@ -6526,7 +6540,7 @@
       </c>
       <c r="M92" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B92</f>
-        <v>0.00665574915999072</v>
+        <v>0.00665574915999073</v>
       </c>
       <c r="N92" s="8" t="n">
         <f aca="false">C92-M92</f>
@@ -6559,7 +6573,7 @@
       </c>
       <c r="M93" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B93</f>
-        <v>0.00150292193425404</v>
+        <v>0.00150292193425403</v>
       </c>
       <c r="N93" s="8" t="n">
         <f aca="false">C93-M93</f>
@@ -6724,7 +6738,7 @@
       </c>
       <c r="M98" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B98</f>
-        <v>0.00217220900369559</v>
+        <v>0.00217220900369558</v>
       </c>
       <c r="N98" s="8" t="n">
         <f aca="false">C98-M98</f>
@@ -6790,11 +6804,11 @@
       </c>
       <c r="M100" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B100</f>
-        <v>0.00962186359771063</v>
+        <v>0.00962186359771065</v>
       </c>
       <c r="N100" s="8" t="n">
         <f aca="false">C100-M100</f>
-        <v>-0.0102678635977106</v>
+        <v>-0.0102678635977107</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6856,7 +6870,7 @@
       </c>
       <c r="M102" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B102</f>
-        <v>0.00646074519126224</v>
+        <v>0.00646074519126225</v>
       </c>
       <c r="N102" s="8" t="n">
         <f aca="false">C102-M102</f>
@@ -6922,11 +6936,11 @@
       </c>
       <c r="M104" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B104</f>
-        <v>0.00765568241149295</v>
+        <v>0.00765568241149296</v>
       </c>
       <c r="N104" s="8" t="n">
         <f aca="false">C104-M104</f>
-        <v>0.00391331758850705</v>
+        <v>0.00391331758850704</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6955,7 +6969,7 @@
       </c>
       <c r="M105" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B105</f>
-        <v>0.00540540702125768</v>
+        <v>0.00540540702125769</v>
       </c>
       <c r="N105" s="8" t="n">
         <f aca="false">C105-M105</f>
@@ -7054,7 +7068,7 @@
       </c>
       <c r="M108" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B108</f>
-        <v>0.00767638792385521</v>
+        <v>0.00767638792385522</v>
       </c>
       <c r="N108" s="8" t="n">
         <f aca="false">C108-M108</f>
@@ -7153,7 +7167,7 @@
       </c>
       <c r="M111" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B111</f>
-        <v>0.00782469190950674</v>
+        <v>0.00782469190950675</v>
       </c>
       <c r="N111" s="8" t="n">
         <f aca="false">C111-M111</f>
@@ -7219,7 +7233,7 @@
       </c>
       <c r="M113" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B113</f>
-        <v>0.0059501541600973</v>
+        <v>0.00595015416009731</v>
       </c>
       <c r="N113" s="8" t="n">
         <f aca="false">C113-M113</f>
@@ -7252,11 +7266,11 @@
       </c>
       <c r="M114" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B114</f>
-        <v>0.00618212381456252</v>
+        <v>0.00618212381456253</v>
       </c>
       <c r="N114" s="8" t="n">
         <f aca="false">C114-M114</f>
-        <v>-0.00816512381456252</v>
+        <v>-0.00816512381456253</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7384,7 +7398,7 @@
       </c>
       <c r="M118" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B118</f>
-        <v>0.00658521018071352</v>
+        <v>0.00658521018071353</v>
       </c>
       <c r="N118" s="8" t="n">
         <f aca="false">C118-M118</f>
@@ -7417,7 +7431,7 @@
       </c>
       <c r="M119" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B119</f>
-        <v>0.0067492103322333</v>
+        <v>0.00674921033223331</v>
       </c>
       <c r="N119" s="8" t="n">
         <f aca="false">C119-M119</f>
@@ -7450,7 +7464,7 @@
       </c>
       <c r="M120" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B120</f>
-        <v>0.00722615441974674</v>
+        <v>0.00722615441974675</v>
       </c>
       <c r="N120" s="8" t="n">
         <f aca="false">C120-M120</f>
@@ -7483,11 +7497,11 @@
       </c>
       <c r="M121" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B121</f>
-        <v>0.00597798909166793</v>
+        <v>0.00597798909166794</v>
       </c>
       <c r="N121" s="8" t="n">
         <f aca="false">C121-M121</f>
-        <v>0.00431401090833207</v>
+        <v>0.00431401090833206</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7516,7 +7530,7 @@
       </c>
       <c r="M122" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B122</f>
-        <v>0.00889049851128649</v>
+        <v>0.0088904985112865</v>
       </c>
       <c r="N122" s="8" t="n">
         <f aca="false">C122-M122</f>
@@ -7582,11 +7596,11 @@
       </c>
       <c r="M124" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B124</f>
-        <v>0.00364101921787425</v>
+        <v>0.00364101921787424</v>
       </c>
       <c r="N124" s="8" t="n">
         <f aca="false">C124-M124</f>
-        <v>-0.00211401921787425</v>
+        <v>-0.00211401921787424</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7648,7 +7662,7 @@
       </c>
       <c r="M126" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B126</f>
-        <v>0.00676633487713663</v>
+        <v>0.00676633487713664</v>
       </c>
       <c r="N126" s="8" t="n">
         <f aca="false">C126-M126</f>
@@ -7714,7 +7728,7 @@
       </c>
       <c r="M128" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B128</f>
-        <v>0.00758776841505602</v>
+        <v>0.00758776841505603</v>
       </c>
       <c r="N128" s="8" t="n">
         <f aca="false">C128-M128</f>
@@ -7747,7 +7761,7 @@
       </c>
       <c r="M129" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B129</f>
-        <v>0.00729398660947269</v>
+        <v>0.0072939866094727</v>
       </c>
       <c r="N129" s="8" t="n">
         <f aca="false">C129-M129</f>
@@ -7813,7 +7827,7 @@
       </c>
       <c r="M131" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B131</f>
-        <v>0.000870113154157406</v>
+        <v>0.000870113154157392</v>
       </c>
       <c r="N131" s="8" t="n">
         <f aca="false">C131-M131</f>
@@ -7846,11 +7860,11 @@
       </c>
       <c r="M132" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B132</f>
-        <v>0.00650753169616235</v>
+        <v>0.00650753169616236</v>
       </c>
       <c r="N132" s="8" t="n">
         <f aca="false">C132-M132</f>
-        <v>-0.00604953169616235</v>
+        <v>-0.00604953169616236</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7879,11 +7893,11 @@
       </c>
       <c r="M133" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B133</f>
-        <v>-0.000520028923063041</v>
+        <v>-0.000520028923063063</v>
       </c>
       <c r="N133" s="8" t="n">
         <f aca="false">C133-M133</f>
-        <v>0.048765028923063</v>
+        <v>0.0487650289230631</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7945,11 +7959,11 @@
       </c>
       <c r="M135" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B135</f>
-        <v>0.007252277096253</v>
+        <v>0.00725227709625301</v>
       </c>
       <c r="N135" s="8" t="n">
         <f aca="false">C135-M135</f>
-        <v>-0.006821277096253</v>
+        <v>-0.00682127709625301</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7978,7 +7992,7 @@
       </c>
       <c r="M136" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B136</f>
-        <v>0.00644407988408135</v>
+        <v>0.00644407988408136</v>
       </c>
       <c r="N136" s="8" t="n">
         <f aca="false">C136-M136</f>
@@ -8011,7 +8025,7 @@
       </c>
       <c r="M137" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B137</f>
-        <v>0.00776657054942773</v>
+        <v>0.00776657054942774</v>
       </c>
       <c r="N137" s="8" t="n">
         <f aca="false">C137-M137</f>
@@ -8044,11 +8058,11 @@
       </c>
       <c r="M138" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B138</f>
-        <v>0.0011647499737794</v>
+        <v>0.00116474997377939</v>
       </c>
       <c r="N138" s="8" t="n">
         <f aca="false">C138-M138</f>
-        <v>0.00517825002622061</v>
+        <v>0.00517825002622062</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8077,7 +8091,7 @@
       </c>
       <c r="M139" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B139</f>
-        <v>0.00968371366736449</v>
+        <v>0.00968371366736451</v>
       </c>
       <c r="N139" s="8" t="n">
         <f aca="false">C139-M139</f>
@@ -8110,11 +8124,11 @@
       </c>
       <c r="M140" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B140</f>
-        <v>0.00612003940539015</v>
+        <v>0.00612003940539016</v>
       </c>
       <c r="N140" s="8" t="n">
         <f aca="false">C140-M140</f>
-        <v>0.00425696059460985</v>
+        <v>0.00425696059460984</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8209,11 +8223,11 @@
       </c>
       <c r="M143" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B143</f>
-        <v>0.00660799539554286</v>
+        <v>0.00660799539554287</v>
       </c>
       <c r="N143" s="8" t="n">
         <f aca="false">C143-M143</f>
-        <v>0.00453000460445714</v>
+        <v>0.00453000460445713</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8242,7 +8256,7 @@
       </c>
       <c r="M144" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B144</f>
-        <v>0.00755675339422421</v>
+        <v>0.00755675339422422</v>
       </c>
       <c r="N144" s="8" t="n">
         <f aca="false">C144-M144</f>
@@ -8275,7 +8289,7 @@
       </c>
       <c r="M145" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B145</f>
-        <v>0.0071539111852582</v>
+        <v>0.00715391118525821</v>
       </c>
       <c r="N145" s="8" t="n">
         <f aca="false">C145-M145</f>
@@ -8341,11 +8355,11 @@
       </c>
       <c r="M147" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B147</f>
-        <v>3.11774311574651E-005</v>
+        <v>3.11774311574477E-005</v>
       </c>
       <c r="N147" s="8" t="n">
         <f aca="false">C147-M147</f>
-        <v>0.0275508225688425</v>
+        <v>0.0275508225688426</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8440,11 +8454,11 @@
       </c>
       <c r="M150" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B150</f>
-        <v>0.00834456819289343</v>
+        <v>0.00834456819289344</v>
       </c>
       <c r="N150" s="8" t="n">
         <f aca="false">C150-M150</f>
-        <v>-0.00326056819289343</v>
+        <v>-0.00326056819289344</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8506,7 +8520,7 @@
       </c>
       <c r="M152" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B152</f>
-        <v>0.00889959926660839</v>
+        <v>0.0088995992666084</v>
       </c>
       <c r="N152" s="8" t="n">
         <f aca="false">C152-M152</f>
@@ -8539,7 +8553,7 @@
       </c>
       <c r="M153" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B153</f>
-        <v>0.00988290614938589</v>
+        <v>0.00988290614938591</v>
       </c>
       <c r="N153" s="8" t="n">
         <f aca="false">C153-M153</f>
@@ -8572,7 +8586,7 @@
       </c>
       <c r="M154" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B154</f>
-        <v>0.00291202082208774</v>
+        <v>0.00291202082208773</v>
       </c>
       <c r="N154" s="8" t="n">
         <f aca="false">C154-M154</f>
@@ -8605,11 +8619,11 @@
       </c>
       <c r="M155" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B155</f>
-        <v>0.00363478724868136</v>
+        <v>0.00363478724868135</v>
       </c>
       <c r="N155" s="8" t="n">
         <f aca="false">C155-M155</f>
-        <v>-0.00776978724868136</v>
+        <v>-0.00776978724868135</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8638,11 +8652,11 @@
       </c>
       <c r="M156" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B156</f>
-        <v>0.0122676057487017</v>
+        <v>0.0122676057487018</v>
       </c>
       <c r="N156" s="8" t="n">
         <f aca="false">C156-M156</f>
-        <v>-0.0677306057487017</v>
+        <v>-0.0677306057487018</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8671,7 +8685,7 @@
       </c>
       <c r="M157" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B157</f>
-        <v>0.00776517976055786</v>
+        <v>0.00776517976055787</v>
       </c>
       <c r="N157" s="8" t="n">
         <f aca="false">C157-M157</f>
@@ -8704,7 +8718,7 @@
       </c>
       <c r="M158" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B158</f>
-        <v>0.00468795755434063</v>
+        <v>0.00468795755434064</v>
       </c>
       <c r="N158" s="8" t="n">
         <f aca="false">C158-M158</f>
@@ -8737,7 +8751,7 @@
       </c>
       <c r="M159" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B159</f>
-        <v>0.00708358461375467</v>
+        <v>0.00708358461375468</v>
       </c>
       <c r="N159" s="8" t="n">
         <f aca="false">C159-M159</f>
@@ -8770,7 +8784,7 @@
       </c>
       <c r="M160" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B160</f>
-        <v>0.00810859945825889</v>
+        <v>0.0081085994582589</v>
       </c>
       <c r="N160" s="8" t="n">
         <f aca="false">C160-M160</f>
@@ -8803,7 +8817,7 @@
       </c>
       <c r="M161" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B161</f>
-        <v>0.00871288820175694</v>
+        <v>0.00871288820175696</v>
       </c>
       <c r="N161" s="8" t="n">
         <f aca="false">C161-M161</f>
@@ -8836,7 +8850,7 @@
       </c>
       <c r="M162" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B162</f>
-        <v>0.00577122240447522</v>
+        <v>0.00577122240447523</v>
       </c>
       <c r="N162" s="8" t="n">
         <f aca="false">C162-M162</f>
@@ -8869,7 +8883,7 @@
       </c>
       <c r="M163" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B163</f>
-        <v>0.00680992207405762</v>
+        <v>0.00680992207405763</v>
       </c>
       <c r="N163" s="8" t="n">
         <f aca="false">C163-M163</f>
@@ -8902,7 +8916,7 @@
       </c>
       <c r="M164" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B164</f>
-        <v>0.00683448198997301</v>
+        <v>0.00683448198997302</v>
       </c>
       <c r="N164" s="8" t="n">
         <f aca="false">C164-M164</f>
@@ -8935,7 +8949,7 @@
       </c>
       <c r="M165" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B165</f>
-        <v>0.00725768399842872</v>
+        <v>0.00725768399842873</v>
       </c>
       <c r="N165" s="8" t="n">
         <f aca="false">C165-M165</f>
@@ -8968,7 +8982,7 @@
       </c>
       <c r="M166" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B166</f>
-        <v>0.00237749034045643</v>
+        <v>0.00237749034045642</v>
       </c>
       <c r="N166" s="8" t="n">
         <f aca="false">C166-M166</f>
@@ -9001,11 +9015,11 @@
       </c>
       <c r="M167" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B167</f>
-        <v>0.00977273219447915</v>
+        <v>0.00977273219447918</v>
       </c>
       <c r="N167" s="8" t="n">
         <f aca="false">C167-M167</f>
-        <v>0.0279812678055209</v>
+        <v>0.0279812678055208</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9067,11 +9081,11 @@
       </c>
       <c r="M169" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B169</f>
-        <v>0.00816464673780608</v>
+        <v>0.00816464673780609</v>
       </c>
       <c r="N169" s="8" t="n">
         <f aca="false">C169-M169</f>
-        <v>0.00425235326219393</v>
+        <v>0.00425235326219391</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9100,7 +9114,7 @@
       </c>
       <c r="M170" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B170</f>
-        <v>0.00204590113537178</v>
+        <v>0.00204590113537176</v>
       </c>
       <c r="N170" s="8" t="n">
         <f aca="false">C170-M170</f>
@@ -9133,7 +9147,7 @@
       </c>
       <c r="M171" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B171</f>
-        <v>0.00343285100679287</v>
+        <v>0.00343285100679286</v>
       </c>
       <c r="N171" s="8" t="n">
         <f aca="false">C171-M171</f>
@@ -9166,11 +9180,11 @@
       </c>
       <c r="M172" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B172</f>
-        <v>0.00767912246018036</v>
+        <v>0.00767912246018037</v>
       </c>
       <c r="N172" s="8" t="n">
         <f aca="false">C172-M172</f>
-        <v>0.00324887753981964</v>
+        <v>0.00324887753981963</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9199,11 +9213,11 @@
       </c>
       <c r="M173" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B173</f>
-        <v>-0.000202891892177959</v>
+        <v>-0.000202891892177976</v>
       </c>
       <c r="N173" s="8" t="n">
         <f aca="false">C173-M173</f>
-        <v>-0.00429310810782204</v>
+        <v>-0.00429310810782202</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9265,7 +9279,7 @@
       </c>
       <c r="M175" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B175</f>
-        <v>5.39707216330046E-005</v>
+        <v>5.39707216329908E-005</v>
       </c>
       <c r="N175" s="8" t="n">
         <f aca="false">C175-M175</f>
@@ -9331,7 +9345,7 @@
       </c>
       <c r="M177" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B177</f>
-        <v>0.00262011387208703</v>
+        <v>0.00262011387208702</v>
       </c>
       <c r="N177" s="8" t="n">
         <f aca="false">C177-M177</f>
@@ -9364,7 +9378,7 @@
       </c>
       <c r="M178" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B178</f>
-        <v>-0.000634224683780798</v>
+        <v>-0.000634224683780816</v>
       </c>
       <c r="N178" s="8" t="n">
         <f aca="false">C178-M178</f>
@@ -9397,11 +9411,11 @@
       </c>
       <c r="M179" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B179</f>
-        <v>0.0103170817091968</v>
+        <v>0.0103170817091969</v>
       </c>
       <c r="N179" s="8" t="n">
         <f aca="false">C179-M179</f>
-        <v>-0.0328830817091968</v>
+        <v>-0.0328830817091969</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9430,7 +9444,7 @@
       </c>
       <c r="M180" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B180</f>
-        <v>0.00868933645508725</v>
+        <v>0.00868933645508727</v>
       </c>
       <c r="N180" s="8" t="n">
         <f aca="false">C180-M180</f>
@@ -9463,11 +9477,11 @@
       </c>
       <c r="M181" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B181</f>
-        <v>0.00146416432551256</v>
+        <v>0.00146416432551255</v>
       </c>
       <c r="N181" s="8" t="n">
         <f aca="false">C181-M181</f>
-        <v>0.0251848356744874</v>
+        <v>0.0251848356744875</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9496,7 +9510,7 @@
       </c>
       <c r="M182" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B182</f>
-        <v>0.00909067146772297</v>
+        <v>0.00909067146772299</v>
       </c>
       <c r="N182" s="8" t="n">
         <f aca="false">C182-M182</f>
@@ -9628,7 +9642,7 @@
       </c>
       <c r="M186" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B186</f>
-        <v>0.00537449695462075</v>
+        <v>0.00537449695462076</v>
       </c>
       <c r="N186" s="8" t="n">
         <f aca="false">C186-M186</f>
@@ -9661,11 +9675,11 @@
       </c>
       <c r="M187" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B187</f>
-        <v>0.00926645109933193</v>
+        <v>0.00926645109933195</v>
       </c>
       <c r="N187" s="8" t="n">
         <f aca="false">C187-M187</f>
-        <v>-0.0415714510993319</v>
+        <v>-0.041571451099332</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9694,7 +9708,7 @@
       </c>
       <c r="M188" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B188</f>
-        <v>0.00708217370449488</v>
+        <v>0.00708217370449489</v>
       </c>
       <c r="N188" s="8" t="n">
         <f aca="false">C188-M188</f>
@@ -9727,7 +9741,7 @@
       </c>
       <c r="M189" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B189</f>
-        <v>0.00403391567472603</v>
+        <v>0.00403391567472602</v>
       </c>
       <c r="N189" s="8" t="n">
         <f aca="false">C189-M189</f>
@@ -9760,7 +9774,7 @@
       </c>
       <c r="M190" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B190</f>
-        <v>0.00203158137296767</v>
+        <v>0.00203158137296766</v>
       </c>
       <c r="N190" s="8" t="n">
         <f aca="false">C190-M190</f>
@@ -9830,7 +9844,7 @@
       </c>
       <c r="N192" s="8" t="n">
         <f aca="false">C192-M192</f>
-        <v>0.0049064051392532</v>
+        <v>0.00490640513925318</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9859,11 +9873,11 @@
       </c>
       <c r="M193" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B193</f>
-        <v>0.00793731351223745</v>
+        <v>0.00793731351223746</v>
       </c>
       <c r="N193" s="8" t="n">
         <f aca="false">C193-M193</f>
-        <v>-0.000190313512237451</v>
+        <v>-0.00019031351223746</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9892,7 +9906,7 @@
       </c>
       <c r="M194" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B194</f>
-        <v>0.00609599744963612</v>
+        <v>0.00609599744963613</v>
       </c>
       <c r="N194" s="8" t="n">
         <f aca="false">C194-M194</f>
@@ -9925,7 +9939,7 @@
       </c>
       <c r="M195" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B195</f>
-        <v>0.00845020916635227</v>
+        <v>0.00845020916635229</v>
       </c>
       <c r="N195" s="8" t="n">
         <f aca="false">C195-M195</f>
@@ -9958,11 +9972,11 @@
       </c>
       <c r="M196" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B196</f>
-        <v>0.00709670532195595</v>
+        <v>0.00709670532195596</v>
       </c>
       <c r="N196" s="8" t="n">
         <f aca="false">C196-M196</f>
-        <v>0.0742982946780441</v>
+        <v>0.074298294678044</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9991,7 +10005,7 @@
       </c>
       <c r="M197" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B197</f>
-        <v>0.00243933999317554</v>
+        <v>0.00243933999317553</v>
       </c>
       <c r="N197" s="8" t="n">
         <f aca="false">C197-M197</f>
@@ -10024,11 +10038,11 @@
       </c>
       <c r="M198" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B198</f>
-        <v>0.00819454288699641</v>
+        <v>0.00819454288699643</v>
       </c>
       <c r="N198" s="8" t="n">
         <f aca="false">C198-M198</f>
-        <v>-0.000455542886996413</v>
+        <v>-0.000455542886996427</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10057,7 +10071,7 @@
       </c>
       <c r="M199" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B199</f>
-        <v>0.00734441563178384</v>
+        <v>0.00734441563178385</v>
       </c>
       <c r="N199" s="8" t="n">
         <f aca="false">C199-M199</f>
@@ -10123,7 +10137,7 @@
       </c>
       <c r="M201" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B201</f>
-        <v>0.00656301635568523</v>
+        <v>0.00656301635568524</v>
       </c>
       <c r="N201" s="8" t="n">
         <f aca="false">C201-M201</f>
@@ -10156,7 +10170,7 @@
       </c>
       <c r="M202" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B202</f>
-        <v>0.00642884679313681</v>
+        <v>0.00642884679313682</v>
       </c>
       <c r="N202" s="8" t="n">
         <f aca="false">C202-M202</f>
@@ -10222,7 +10236,7 @@
       </c>
       <c r="M204" s="8" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B204</f>
-        <v>0.00879780699569768</v>
+        <v>0.00879780699569769</v>
       </c>
       <c r="N204" s="8" t="n">
         <f aca="false">C204-M204</f>
@@ -10468,8 +10482,8 @@
       <c r="A25" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="1" t="n">
-        <f aca="false">B3</f>
+      <c r="D25" s="13" t="n">
+        <f aca="false">AVERAGE('Excess returns'!B2:B205)</f>
         <v>0.0085301865477073</v>
       </c>
       <c r="F25" s="8" t="n">
@@ -10489,8 +10503,8 @@
       <c r="A26" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="1" t="n">
-        <f aca="false">B4</f>
+      <c r="D26" s="13" t="n">
+        <f aca="false">STDEV('Excess returns'!B2:B205)</f>
         <v>0.0460641309280882</v>
       </c>
       <c r="F26" s="8" t="n">
@@ -10510,7 +10524,7 @@
       <c r="A27" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="13" t="n">
+      <c r="B27" s="14" t="n">
         <f aca="false">C5</f>
         <v>0.120382598896978</v>
       </c>
@@ -10535,9 +10549,9 @@
       <c r="A28" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="11" t="n">
-        <f aca="false">B6</f>
-        <v>0.0598620726348209</v>
+      <c r="D28" s="15" t="n">
+        <f aca="false">CORREL('Excess returns'!B2:B205,'Excess returns'!C2:C205)</f>
+        <v>0.0598620726348211</v>
       </c>
       <c r="F28" s="12" t="n">
         <f aca="false">CORREL('Excess returns'!E2:E205,'Excess returns'!C2:C205)</f>
@@ -10564,7 +10578,7 @@
         <f aca="false">F27*F28</f>
         <v>0.0639891405855537</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="H29" s="14" t="n">
         <f aca="false">H27*H28</f>
         <v>0.120382598896978</v>
       </c>
@@ -10582,7 +10596,7 @@
         <v>35</v>
       </c>
       <c r="G30" s="7"/>
-      <c r="H30" s="14" t="s">
+      <c r="H30" s="16" t="s">
         <v>36</v>
       </c>
       <c r="J30" s="7" t="s">
@@ -10600,22 +10614,22 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="17" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="17" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15"/>
+      <c r="A37" s="17"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D38" s="9" t="s">
@@ -10637,7 +10651,7 @@
       </c>
       <c r="D39" s="12" t="n">
         <f aca="false">D28*$C$4/D26</f>
-        <v>0.063444009844686</v>
+        <v>0.0634440098446862</v>
       </c>
       <c r="F39" s="12" t="n">
         <f aca="false">F28*$C$4/F26</f>
@@ -10695,7 +10709,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="18" t="s">
         <v>45</v>
       </c>
       <c r="D42" s="8" t="n">
@@ -10724,7 +10738,7 @@
         <v>47</v>
       </c>
       <c r="G43" s="7"/>
-      <c r="H43" s="14" t="s">
+      <c r="H43" s="16" t="s">
         <v>48</v>
       </c>
       <c r="J43" s="7" t="s">
@@ -10750,7 +10764,7 @@
       </c>
       <c r="D48" s="12" t="n">
         <f aca="false">SQRT(C4^2 - D39^2*B4^2)</f>
-        <v>0.0487328957752134</v>
+        <v>0.0487328957752135</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10779,7 +10793,7 @@
         <f aca="false">SQRT(D27^2 + D50^2)</f>
         <v>0.215129592204537</v>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="E51" s="17" t="s">
         <v>56</v>
       </c>
     </row>
@@ -10799,7 +10813,7 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="15"/>
+      <c r="A56" s="17"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/Module 2/Week 8 - CAPM and investment styles/Homework 2 example.xlsx
+++ b/Module 2/Week 8 - CAPM and investment styles/Homework 2 example.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" state="visible" r:id="rId3"/>
@@ -341,7 +341,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -363,6 +363,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3510,6 +3514,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="8.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="18.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="17.71"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="6" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3522,22 +3529,22 @@
       <c r="C1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="10" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3553,7 +3560,7 @@
         <f aca="false">Data!C2-Data!D2</f>
         <v>0.102204</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="1" t="n">
         <f aca="false">0.2*C2+0.8*B2</f>
         <v>-0.0293635063263042</v>
       </c>
@@ -3568,11 +3575,11 @@
       <c r="K2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="8" t="n">
+      <c r="M2" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B2</f>
         <v>0.00138621198753916</v>
       </c>
-      <c r="N2" s="8" t="n">
+      <c r="N2" s="9" t="n">
         <f aca="false">C2-M2</f>
         <v>0.100817788012461</v>
       </c>
@@ -3589,7 +3596,7 @@
         <f aca="false">Data!C3-Data!D3</f>
         <v>0.047685</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="1" t="n">
         <f aca="false">0.2*C3+0.8*B3</f>
         <v>-0.0175146517083923</v>
       </c>
@@ -3601,11 +3608,11 @@
         <f aca="false">0.5*C3+0.5*B3</f>
         <v>0.00693521768225479</v>
       </c>
-      <c r="M3" s="8" t="n">
+      <c r="M3" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B3</f>
         <v>0.0031906115420036</v>
       </c>
-      <c r="N3" s="8" t="n">
+      <c r="N3" s="9" t="n">
         <f aca="false">C3-M3</f>
         <v>0.0444943884579964</v>
       </c>
@@ -3622,7 +3629,7 @@
         <f aca="false">Data!C4-Data!D4</f>
         <v>-0.034466</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="1" t="n">
         <f aca="false">0.2*C4+0.8*B4</f>
         <v>-0.0117771817801592</v>
       </c>
@@ -3634,11 +3641,11 @@
         <f aca="false">0.5*C4+0.5*B4</f>
         <v>-0.0202854886125995</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B4</f>
         <v>0.00494861887845431</v>
       </c>
-      <c r="N4" s="8" t="n">
+      <c r="N4" s="9" t="n">
         <f aca="false">C4-M4</f>
         <v>-0.0394146188784543</v>
       </c>
@@ -3655,7 +3662,7 @@
         <f aca="false">Data!C5-Data!D5</f>
         <v>-0.075953</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="1" t="n">
         <f aca="false">0.2*C5+0.8*B5</f>
         <v>0.0222030755646817</v>
       </c>
@@ -3667,11 +3674,11 @@
         <f aca="false">0.5*C5+0.5*B5</f>
         <v>-0.0146054527720739</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B5</f>
         <v>0.00830144901444976</v>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="N5" s="9" t="n">
         <f aca="false">C5-M5</f>
         <v>-0.0842544490144498</v>
       </c>
@@ -3688,7 +3695,7 @@
         <f aca="false">Data!C6-Data!D6</f>
         <v>0.011741</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="1" t="n">
         <f aca="false">0.2*C6+0.8*B6</f>
         <v>0.0112481655334483</v>
       </c>
@@ -3700,11 +3707,11 @@
         <f aca="false">0.5*C6+0.5*B6</f>
         <v>0.0114329784584052</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B6</f>
         <v>0.00604175498978326</v>
       </c>
-      <c r="N6" s="8" t="n">
+      <c r="N6" s="9" t="n">
         <f aca="false">C6-M6</f>
         <v>0.00569924501021674</v>
       </c>
@@ -3721,7 +3728,7 @@
         <f aca="false">Data!C7-Data!D7</f>
         <v>0.058846</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="1" t="n">
         <f aca="false">0.2*C7+0.8*B7</f>
         <v>-0.0570961711194138</v>
       </c>
@@ -3733,11 +3740,11 @@
         <f aca="false">0.5*C7+0.5*B7</f>
         <v>-0.0136178569496336</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="M7" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B7</f>
         <v>-0.000125425990441149</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N7" s="9" t="n">
         <f aca="false">C7-M7</f>
         <v>0.0589714259904412</v>
       </c>
@@ -3754,7 +3761,7 @@
         <f aca="false">Data!C8-Data!D8</f>
         <v>-0.023746</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="1" t="n">
         <f aca="false">0.2*C8+0.8*B8</f>
         <v>-0.0126028535687007</v>
       </c>
@@ -3766,11 +3773,11 @@
         <f aca="false">0.5*C8+0.5*B8</f>
         <v>-0.0167815334804379</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B8</f>
         <v>0.00471310902071968</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="N8" s="9" t="n">
         <f aca="false">C8-M8</f>
         <v>-0.0284591090207197</v>
       </c>
@@ -3787,7 +3794,7 @@
         <f aca="false">Data!C9-Data!D9</f>
         <v>-0.084085</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="1" t="n">
         <f aca="false">0.2*C9+0.8*B9</f>
         <v>-0.00628661061189545</v>
       </c>
@@ -3799,11 +3806,11 @@
         <f aca="false">0.5*C9+0.5*B9</f>
         <v>-0.0354610066324347</v>
       </c>
-      <c r="M9" s="8" t="n">
+      <c r="M9" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B9</f>
         <v>0.00617105577364053</v>
       </c>
-      <c r="N9" s="8" t="n">
+      <c r="N9" s="9" t="n">
         <f aca="false">C9-M9</f>
         <v>-0.0902560557736405</v>
       </c>
@@ -3820,7 +3827,7 @@
         <f aca="false">Data!C10-Data!D10</f>
         <v>0.070825</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="1" t="n">
         <f aca="false">0.2*C10+0.8*B10</f>
         <v>-0.0582835687393802</v>
       </c>
@@ -3832,11 +3839,11 @@
         <f aca="false">0.5*C10+0.5*B10</f>
         <v>-0.00986785546211265</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="M10" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B10</f>
         <v>-0.000409591521786904</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="N10" s="9" t="n">
         <f aca="false">C10-M10</f>
         <v>0.0712345915217869</v>
       </c>
@@ -3853,7 +3860,7 @@
         <f aca="false">Data!C11-Data!D11</f>
         <v>-0.188648</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="1" t="n">
         <f aca="false">0.2*C11+0.8*B11</f>
         <v>-0.172708800894104</v>
       </c>
@@ -3865,11 +3872,11 @@
         <f aca="false">0.5*C11+0.5*B11</f>
         <v>-0.178686000558815</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B11</f>
         <v>-0.0053685840743104</v>
       </c>
-      <c r="N11" s="8" t="n">
+      <c r="N11" s="9" t="n">
         <f aca="false">C11-M11</f>
         <v>-0.18327941592569</v>
       </c>
@@ -3886,7 +3893,7 @@
         <f aca="false">Data!C12-Data!D12</f>
         <v>0.116378</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="1" t="n">
         <f aca="false">0.2*C12+0.8*B12</f>
         <v>-0.0343631015894336</v>
       </c>
@@ -3898,11 +3905,11 @@
         <f aca="false">0.5*C12+0.5*B12</f>
         <v>0.022164811506604</v>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="M12" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B12</f>
         <v>0.000764905174787732</v>
       </c>
-      <c r="N12" s="8" t="n">
+      <c r="N12" s="9" t="n">
         <f aca="false">C12-M12</f>
         <v>0.115613094825212</v>
       </c>
@@ -3919,7 +3926,7 @@
         <f aca="false">Data!C13-Data!D13</f>
         <v>0.063307</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="1" t="n">
         <f aca="false">0.2*C13+0.8*B13</f>
         <v>0.0211982697395808</v>
       </c>
@@ -3931,11 +3938,11 @@
         <f aca="false">0.5*C13+0.5*B13</f>
         <v>0.036989043587238</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B13</f>
         <v>0.00601295967338239</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="N13" s="9" t="n">
         <f aca="false">C13-M13</f>
         <v>0.0572940403266176</v>
       </c>
@@ -3952,7 +3959,7 @@
         <f aca="false">Data!C14-Data!D14</f>
         <v>0.06185</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="1" t="n">
         <f aca="false">0.2*C14+0.8*B14</f>
         <v>-0.0549305175111326</v>
       </c>
@@ -3964,11 +3971,11 @@
         <f aca="false">0.5*C14+0.5*B14</f>
         <v>-0.0111378234444579</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B14</f>
         <v>-1.32525577954245E-006</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="N14" s="9" t="n">
         <f aca="false">C14-M14</f>
         <v>0.0618513252557795</v>
       </c>
@@ -3985,7 +3992,7 @@
         <f aca="false">Data!C15-Data!D15</f>
         <v>0.02739</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="1" t="n">
         <f aca="false">0.2*C15+0.8*B15</f>
         <v>-0.0798582417871222</v>
       </c>
@@ -3997,11 +4004,11 @@
         <f aca="false">0.5*C15+0.5*B15</f>
         <v>-0.0396401511169514</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B15</f>
         <v>-0.00143164859143197</v>
       </c>
-      <c r="N15" s="8" t="n">
+      <c r="N15" s="9" t="n">
         <f aca="false">C15-M15</f>
         <v>0.028821648591432</v>
       </c>
@@ -4018,7 +4025,7 @@
         <f aca="false">Data!C16-Data!D16</f>
         <v>-0.026955</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="1" t="n">
         <f aca="false">0.2*C16+0.8*B16</f>
         <v>0.064529353828283</v>
       </c>
@@ -4030,11 +4037,11 @@
         <f aca="false">0.5*C16+0.5*B16</f>
         <v>0.0302227211426769</v>
       </c>
-      <c r="M16" s="8" t="n">
+      <c r="M16" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B16</f>
         <v>0.0108809776344133</v>
       </c>
-      <c r="N16" s="8" t="n">
+      <c r="N16" s="9" t="n">
         <f aca="false">C16-M16</f>
         <v>-0.0378359776344134</v>
       </c>
@@ -4051,7 +4058,7 @@
         <f aca="false">Data!C17-Data!D17</f>
         <v>-0.032218</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="1" t="n">
         <f aca="false">0.2*C17+0.8*B17</f>
         <v>0.069946988235294</v>
       </c>
@@ -4063,11 +4070,11 @@
         <f aca="false">0.5*C17+0.5*B17</f>
         <v>0.0316351176470588</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B17</f>
         <v>0.0113940996536831</v>
       </c>
-      <c r="N17" s="8" t="n">
+      <c r="N17" s="9" t="n">
         <f aca="false">C17-M17</f>
         <v>-0.0436120996536831</v>
       </c>
@@ -4084,7 +4091,7 @@
         <f aca="false">Data!C18-Data!D18</f>
         <v>0.093363</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="1" t="n">
         <f aca="false">0.2*C18+0.8*B18</f>
         <v>0.0636141858811832</v>
       </c>
@@ -4096,11 +4103,11 @@
         <f aca="false">0.5*C18+0.5*B18</f>
         <v>0.0747699911757395</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B18</f>
         <v>0.00890003613498343</v>
       </c>
-      <c r="N18" s="8" t="n">
+      <c r="N18" s="9" t="n">
         <f aca="false">C18-M18</f>
         <v>0.0844629638650166</v>
       </c>
@@ -4117,7 +4124,7 @@
         <f aca="false">Data!C19-Data!D19</f>
         <v>-0.031993</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="1" t="n">
         <f aca="false">0.2*C19+0.8*B19</f>
         <v>-0.00471891871904122</v>
       </c>
@@ -4129,11 +4136,11 @@
         <f aca="false">0.5*C19+0.5*B19</f>
         <v>-0.0149466991994008</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B19</f>
         <v>0.00546915025828778</v>
       </c>
-      <c r="N19" s="8" t="n">
+      <c r="N19" s="9" t="n">
         <f aca="false">C19-M19</f>
         <v>-0.0374621502582878</v>
       </c>
@@ -4150,7 +4157,7 @@
         <f aca="false">Data!C20-Data!D20</f>
         <v>-0.004882</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="1" t="n">
         <f aca="false">0.2*C20+0.8*B20</f>
         <v>0.0595668294617564</v>
       </c>
@@ -4162,11 +4169,11 @@
         <f aca="false">0.5*C20+0.5*B20</f>
         <v>0.0353985184135978</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B20</f>
         <v>0.0101373246711324</v>
       </c>
-      <c r="N20" s="8" t="n">
+      <c r="N20" s="9" t="n">
         <f aca="false">C20-M20</f>
         <v>-0.0150193246711324</v>
       </c>
@@ -4183,7 +4190,7 @@
         <f aca="false">Data!C21-Data!D21</f>
         <v>0.015116</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E21" s="1" t="n">
         <f aca="false">0.2*C21+0.8*B21</f>
         <v>0.0317340711871845</v>
       </c>
@@ -4195,11 +4202,11 @@
         <f aca="false">0.5*C21+0.5*B21</f>
         <v>0.0255022944919903</v>
       </c>
-      <c r="M21" s="8" t="n">
+      <c r="M21" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B21</f>
         <v>0.00761285910644299</v>
       </c>
-      <c r="N21" s="8" t="n">
+      <c r="N21" s="9" t="n">
         <f aca="false">C21-M21</f>
         <v>0.00750314089355701</v>
       </c>
@@ -4216,7 +4223,7 @@
         <f aca="false">Data!C22-Data!D22</f>
         <v>0.053016</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="1" t="n">
         <f aca="false">0.2*C22+0.8*B22</f>
         <v>0.0402575167397658</v>
       </c>
@@ -4228,11 +4235,11 @@
         <f aca="false">0.5*C22+0.5*B22</f>
         <v>0.0450419479623536</v>
       </c>
-      <c r="M22" s="8" t="n">
+      <c r="M22" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B22</f>
         <v>0.00768767906760036</v>
       </c>
-      <c r="N22" s="8" t="n">
+      <c r="N22" s="9" t="n">
         <f aca="false">C22-M22</f>
         <v>0.0453283209323996</v>
       </c>
@@ -4249,7 +4256,7 @@
         <f aca="false">Data!C23-Data!D23</f>
         <v>0.043196</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="1" t="n">
         <f aca="false">0.2*C23+0.8*B23</f>
         <v>-0.00630179538224738</v>
       </c>
@@ -4261,11 +4268,11 @@
         <f aca="false">0.5*C23+0.5*B23</f>
         <v>0.0122598778860954</v>
       </c>
-      <c r="M23" s="8" t="n">
+      <c r="M23" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B23</f>
         <v>0.00415104729098054</v>
       </c>
-      <c r="N23" s="8" t="n">
+      <c r="N23" s="9" t="n">
         <f aca="false">C23-M23</f>
         <v>0.0390449527090195</v>
       </c>
@@ -4282,7 +4289,7 @@
         <f aca="false">Data!C24-Data!D24</f>
         <v>0.122068</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="1" t="n">
         <f aca="false">0.2*C24+0.8*B24</f>
         <v>0.0722646927533201</v>
       </c>
@@ -4294,11 +4301,11 @@
         <f aca="false">0.5*C24+0.5*B24</f>
         <v>0.090940932970825</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B24</f>
         <v>0.00913077461328222</v>
       </c>
-      <c r="N24" s="8" t="n">
+      <c r="N24" s="9" t="n">
         <f aca="false">C24-M24</f>
         <v>0.112937225386718</v>
       </c>
@@ -4315,7 +4322,7 @@
         <f aca="false">Data!C25-Data!D25</f>
         <v>-0.05812</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="1" t="n">
         <f aca="false">0.2*C25+0.8*B25</f>
         <v>0.00385999111940632</v>
       </c>
@@ -4327,11 +4334,11 @@
         <f aca="false">0.5*C25+0.5*B25</f>
         <v>-0.0193825055503711</v>
       </c>
-      <c r="M25" s="8" t="n">
+      <c r="M25" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B25</f>
         <v>0.00656390121989974</v>
       </c>
-      <c r="N25" s="8" t="n">
+      <c r="N25" s="9" t="n">
         <f aca="false">C25-M25</f>
         <v>-0.0646839012198997</v>
       </c>
@@ -4348,7 +4355,7 @@
         <f aca="false">Data!C26-Data!D26</f>
         <v>-0.019248</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="1" t="n">
         <f aca="false">0.2*C26+0.8*B26</f>
         <v>-0.0326798327846499</v>
       </c>
@@ -4360,11 +4367,11 @@
         <f aca="false">0.5*C26+0.5*B26</f>
         <v>-0.0276428954904062</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="M26" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B26</f>
         <v>0.00304956114786402</v>
       </c>
-      <c r="N26" s="8" t="n">
+      <c r="N26" s="9" t="n">
         <f aca="false">C26-M26</f>
         <v>-0.022297561147864</v>
       </c>
@@ -4381,7 +4388,7 @@
         <f aca="false">Data!C27-Data!D27</f>
         <v>0.027476</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="1" t="n">
         <f aca="false">0.2*C27+0.8*B27</f>
         <v>0.0302299681115489</v>
       </c>
@@ -4393,11 +4400,11 @@
         <f aca="false">0.5*C27+0.5*B27</f>
         <v>0.0291972300697181</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="M27" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B27</f>
         <v>0.00729753420310035</v>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="N27" s="9" t="n">
         <f aca="false">C27-M27</f>
         <v>0.0201784657968997</v>
       </c>
@@ -4414,7 +4421,7 @@
         <f aca="false">Data!C28-Data!D28</f>
         <v>-0.002797</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="1" t="n">
         <f aca="false">0.2*C28+0.8*B28</f>
         <v>0.0474690006693365</v>
       </c>
@@ -4426,11 +4433,11 @@
         <f aca="false">0.5*C28+0.5*B28</f>
         <v>0.0286192504183353</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B28</f>
         <v>0.00914483601974383</v>
       </c>
-      <c r="N28" s="8" t="n">
+      <c r="N28" s="9" t="n">
         <f aca="false">C28-M28</f>
         <v>-0.0119418360197438</v>
       </c>
@@ -4447,7 +4454,7 @@
         <f aca="false">Data!C29-Data!D29</f>
         <v>0.059161</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="1" t="n">
         <f aca="false">0.2*C29+0.8*B29</f>
         <v>0.0243763529750303</v>
       </c>
@@ -4459,11 +4466,11 @@
         <f aca="false">0.5*C29+0.5*B29</f>
         <v>0.0374205956093939</v>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="M29" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B29</f>
         <v>0.00633075731968276</v>
       </c>
-      <c r="N29" s="8" t="n">
+      <c r="N29" s="9" t="n">
         <f aca="false">C29-M29</f>
         <v>0.0528302426803172</v>
       </c>
@@ -4480,7 +4487,7 @@
         <f aca="false">Data!C30-Data!D30</f>
         <v>0.032872</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="1" t="n">
         <f aca="false">0.2*C30+0.8*B30</f>
         <v>-0.0575465394133236</v>
       </c>
@@ -4492,11 +4499,11 @@
         <f aca="false">0.5*C30+0.5*B30</f>
         <v>-0.0236395871333273</v>
       </c>
-      <c r="M30" s="8" t="n">
+      <c r="M30" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B30</f>
         <v>0.00025083122439464</v>
       </c>
-      <c r="N30" s="8" t="n">
+      <c r="N30" s="9" t="n">
         <f aca="false">C30-M30</f>
         <v>0.0326211687756054</v>
       </c>
@@ -4513,7 +4520,7 @@
         <f aca="false">Data!C31-Data!D31</f>
         <v>0.021729</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="1" t="n">
         <f aca="false">0.2*C31+0.8*B31</f>
         <v>-0.0376498547522984</v>
       </c>
@@ -4525,11 +4532,11 @@
         <f aca="false">0.5*C31+0.5*B31</f>
         <v>-0.0153827842201865</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="M31" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B31</f>
         <v>0.00200547719670784</v>
       </c>
-      <c r="N31" s="8" t="n">
+      <c r="N31" s="9" t="n">
         <f aca="false">C31-M31</f>
         <v>0.0197235228032922</v>
       </c>
@@ -4546,7 +4553,7 @@
         <f aca="false">Data!C32-Data!D32</f>
         <v>-0.058544</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" s="1" t="n">
         <f aca="false">0.2*C32+0.8*B32</f>
         <v>0.0441800125592666</v>
       </c>
@@ -4558,11 +4565,11 @@
         <f aca="false">0.5*C32+0.5*B32</f>
         <v>0.00565850784954165</v>
       </c>
-      <c r="M32" s="8" t="n">
+      <c r="M32" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B32</f>
         <v>0.00976820608140385</v>
       </c>
-      <c r="N32" s="8" t="n">
+      <c r="N32" s="9" t="n">
         <f aca="false">C32-M32</f>
         <v>-0.0683122060814038</v>
       </c>
@@ -4579,7 +4586,7 @@
         <f aca="false">Data!C33-Data!D33</f>
         <v>0.055979</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="1" t="n">
         <f aca="false">0.2*C33+0.8*B33</f>
         <v>-0.0251225062530773</v>
       </c>
@@ -4591,11 +4598,11 @@
         <f aca="false">0.5*C33+0.5*B33</f>
         <v>0.00529055859182669</v>
       </c>
-      <c r="M33" s="8" t="n">
+      <c r="M33" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B33</f>
         <v>0.00245571938930322</v>
       </c>
-      <c r="N33" s="8" t="n">
+      <c r="N33" s="9" t="n">
         <f aca="false">C33-M33</f>
         <v>0.0535232806106968</v>
       </c>
@@ -4612,7 +4619,7 @@
         <f aca="false">Data!C34-Data!D34</f>
         <v>0.062729</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="1" t="n">
         <f aca="false">0.2*C34+0.8*B34</f>
         <v>0.083816967326806</v>
       </c>
@@ -4624,11 +4631,11 @@
         <f aca="false">0.5*C34+0.5*B34</f>
         <v>0.0759089795792538</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B34</f>
         <v>0.0109881039155366</v>
       </c>
-      <c r="N34" s="8" t="n">
+      <c r="N34" s="9" t="n">
         <f aca="false">C34-M34</f>
         <v>0.0517408960844634</v>
       </c>
@@ -4645,7 +4652,7 @@
         <f aca="false">Data!C35-Data!D35</f>
         <v>0.019541</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E35" s="1" t="n">
         <f aca="false">0.2*C35+0.8*B35</f>
         <v>0.0341346915286503</v>
       </c>
@@ -4657,11 +4664,11 @@
         <f aca="false">0.5*C35+0.5*B35</f>
         <v>0.0286620572054065</v>
       </c>
-      <c r="M35" s="8" t="n">
+      <c r="M35" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B35</f>
         <v>0.00773305539627395</v>
       </c>
-      <c r="N35" s="8" t="n">
+      <c r="N35" s="9" t="n">
         <f aca="false">C35-M35</f>
         <v>0.0118079446037261</v>
       </c>
@@ -4678,7 +4685,7 @@
         <f aca="false">Data!C36-Data!D36</f>
         <v>0.028514</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E36" s="1" t="n">
         <f aca="false">0.2*C36+0.8*B36</f>
         <v>0.0056228</v>
       </c>
@@ -4690,11 +4697,11 @@
         <f aca="false">0.5*C36+0.5*B36</f>
         <v>0.014207</v>
       </c>
-      <c r="M36" s="8" t="n">
+      <c r="M36" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B36</f>
         <v>0.00532959871264696</v>
       </c>
-      <c r="N36" s="8" t="n">
+      <c r="N36" s="9" t="n">
         <f aca="false">C36-M36</f>
         <v>0.023184401287353</v>
       </c>
@@ -4711,7 +4718,7 @@
         <f aca="false">Data!C37-Data!D37</f>
         <v>0.025536</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="1" t="n">
         <f aca="false">0.2*C37+0.8*B37</f>
         <v>0.0583979035399789</v>
       </c>
@@ -4723,11 +4730,11 @@
         <f aca="false">0.5*C37+0.5*B37</f>
         <v>0.0460746897124868</v>
       </c>
-      <c r="M37" s="8" t="n">
+      <c r="M37" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B37</f>
         <v>0.00956216301365728</v>
       </c>
-      <c r="N37" s="8" t="n">
+      <c r="N37" s="9" t="n">
         <f aca="false">C37-M37</f>
         <v>0.0159738369863427</v>
       </c>
@@ -4744,7 +4751,7 @@
         <f aca="false">Data!C38-Data!D38</f>
         <v>-0.054523</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E38" s="1" t="n">
         <f aca="false">0.2*C38+0.8*B38</f>
         <v>0.00787224683128996</v>
       </c>
@@ -4756,11 +4763,11 @@
         <f aca="false">0.5*C38+0.5*B38</f>
         <v>-0.0155259707304438</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B38</f>
         <v>0.00682504118265209</v>
       </c>
-      <c r="N38" s="8" t="n">
+      <c r="N38" s="9" t="n">
         <f aca="false">C38-M38</f>
         <v>-0.0613480411826521</v>
       </c>
@@ -4777,7 +4784,7 @@
         <f aca="false">Data!C39-Data!D39</f>
         <v>0.05708</v>
       </c>
-      <c r="E39" s="5" t="n">
+      <c r="E39" s="1" t="n">
         <f aca="false">0.2*C39+0.8*B39</f>
         <v>0.0386662404048925</v>
       </c>
@@ -4789,11 +4796,11 @@
         <f aca="false">0.5*C39+0.5*B39</f>
         <v>0.0455714002530578</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M39" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B39</f>
         <v>0.00749702376427901</v>
       </c>
-      <c r="N39" s="8" t="n">
+      <c r="N39" s="9" t="n">
         <f aca="false">C39-M39</f>
         <v>0.049582976235721</v>
       </c>
@@ -4810,7 +4817,7 @@
         <f aca="false">Data!C40-Data!D40</f>
         <v>0.014974</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E40" s="1" t="n">
         <f aca="false">0.2*C40+0.8*B40</f>
         <v>0.00311974125741468</v>
       </c>
@@ -4822,11 +4829,11 @@
         <f aca="false">0.5*C40+0.5*B40</f>
         <v>0.00756508828588418</v>
       </c>
-      <c r="M40" s="8" t="n">
+      <c r="M40" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B40</f>
         <v>0.00534585158158821</v>
       </c>
-      <c r="N40" s="8" t="n">
+      <c r="N40" s="9" t="n">
         <f aca="false">C40-M40</f>
         <v>0.00962814841841179</v>
       </c>
@@ -4843,7 +4850,7 @@
         <f aca="false">Data!C41-Data!D41</f>
         <v>0.069881</v>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E41" s="1" t="n">
         <f aca="false">0.2*C41+0.8*B41</f>
         <v>0.0375595606288896</v>
       </c>
@@ -4855,11 +4862,11 @@
         <f aca="false">0.5*C41+0.5*B41</f>
         <v>0.049680100393056</v>
       </c>
-      <c r="M41" s="8" t="n">
+      <c r="M41" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B41</f>
         <v>0.007206221818519</v>
       </c>
-      <c r="N41" s="8" t="n">
+      <c r="N41" s="9" t="n">
         <f aca="false">C41-M41</f>
         <v>0.062674778181481</v>
       </c>
@@ -4876,7 +4883,7 @@
         <f aca="false">Data!C42-Data!D42</f>
         <v>0.003919</v>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E42" s="1" t="n">
         <f aca="false">0.2*C42+0.8*B42</f>
         <v>-0.00837941985364297</v>
       </c>
@@ -4888,11 +4895,11 @@
         <f aca="false">0.5*C42+0.5*B42</f>
         <v>-0.00376751240852686</v>
       </c>
-      <c r="M42" s="8" t="n">
+      <c r="M42" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B42</f>
         <v>0.00460925385037699</v>
       </c>
-      <c r="N42" s="8" t="n">
+      <c r="N42" s="9" t="n">
         <f aca="false">C42-M42</f>
         <v>-0.000690253850376994</v>
       </c>
@@ -4909,7 +4916,7 @@
         <f aca="false">Data!C43-Data!D43</f>
         <v>-0.018868</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E43" s="1" t="n">
         <f aca="false">0.2*C43+0.8*B43</f>
         <v>-0.017151834023525</v>
       </c>
@@ -4921,11 +4928,11 @@
         <f aca="false">0.5*C43+0.5*B43</f>
         <v>-0.0177953962647031</v>
       </c>
-      <c r="M43" s="8" t="n">
+      <c r="M43" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B43</f>
         <v>0.00427498209976514</v>
       </c>
-      <c r="N43" s="8" t="n">
+      <c r="N43" s="9" t="n">
         <f aca="false">C43-M43</f>
         <v>-0.0231429820997651</v>
       </c>
@@ -4942,7 +4949,7 @@
         <f aca="false">Data!C44-Data!D44</f>
         <v>0.070126</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E44" s="1" t="n">
         <f aca="false">0.2*C44+0.8*B44</f>
         <v>-0.00234964586929725</v>
       </c>
@@ -4954,11 +4961,11 @@
         <f aca="false">0.5*C44+0.5*B44</f>
         <v>0.0248287213316892</v>
       </c>
-      <c r="M44" s="8" t="n">
+      <c r="M44" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B44</f>
         <v>0.00403733576046028</v>
       </c>
-      <c r="N44" s="8" t="n">
+      <c r="N44" s="9" t="n">
         <f aca="false">C44-M44</f>
         <v>0.0660886642395397</v>
       </c>
@@ -4975,7 +4982,7 @@
         <f aca="false">Data!C45-Data!D45</f>
         <v>0.131426</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E45" s="1" t="n">
         <f aca="false">0.2*C45+0.8*B45</f>
         <v>-0.0173664683450822</v>
       </c>
@@ -4987,11 +4994,11 @@
         <f aca="false">0.5*C45+0.5*B45</f>
         <v>0.0384307072843236</v>
       </c>
-      <c r="M45" s="8" t="n">
+      <c r="M45" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B45</f>
         <v>0.00187414701835346</v>
       </c>
-      <c r="N45" s="8" t="n">
+      <c r="N45" s="9" t="n">
         <f aca="false">C45-M45</f>
         <v>0.129551852981647</v>
       </c>
@@ -5008,7 +5015,7 @@
         <f aca="false">Data!C46-Data!D46</f>
         <v>-0.107886</v>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="E46" s="1" t="n">
         <f aca="false">0.2*C46+0.8*B46</f>
         <v>-0.0779178835776844</v>
       </c>
@@ -5020,11 +5027,11 @@
         <f aca="false">0.5*C46+0.5*B46</f>
         <v>-0.0891559272360527</v>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B46</f>
         <v>0.000867844509182728</v>
       </c>
-      <c r="N46" s="8" t="n">
+      <c r="N46" s="9" t="n">
         <f aca="false">C46-M46</f>
         <v>-0.108753844509183</v>
       </c>
@@ -5041,7 +5048,7 @@
         <f aca="false">Data!C47-Data!D47</f>
         <v>0.054635</v>
       </c>
-      <c r="E47" s="5" t="n">
+      <c r="E47" s="1" t="n">
         <f aca="false">0.2*C47+0.8*B47</f>
         <v>0.0982374242656939</v>
       </c>
@@ -5053,11 +5060,11 @@
         <f aca="false">0.5*C47+0.5*B47</f>
         <v>0.0818865151660587</v>
       </c>
-      <c r="M47" s="8" t="n">
+      <c r="M47" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B47</f>
         <v>0.0122600973844519</v>
       </c>
-      <c r="N47" s="8" t="n">
+      <c r="N47" s="9" t="n">
         <f aca="false">C47-M47</f>
         <v>0.0423749026155481</v>
       </c>
@@ -5074,7 +5081,7 @@
         <f aca="false">Data!C48-Data!D48</f>
         <v>-0.008149</v>
       </c>
-      <c r="E48" s="5" t="n">
+      <c r="E48" s="1" t="n">
         <f aca="false">0.2*C48+0.8*B48</f>
         <v>-0.00349912064041541</v>
       </c>
@@ -5086,11 +5093,11 @@
         <f aca="false">0.5*C48+0.5*B48</f>
         <v>-0.00524282540025963</v>
       </c>
-      <c r="M48" s="8" t="n">
+      <c r="M48" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B48</f>
         <v>0.00518769661723969</v>
       </c>
-      <c r="N48" s="8" t="n">
+      <c r="N48" s="9" t="n">
         <f aca="false">C48-M48</f>
         <v>-0.0133366966172397</v>
       </c>
@@ -5107,7 +5114,7 @@
         <f aca="false">Data!C49-Data!D49</f>
         <v>-0.075998</v>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="E49" s="1" t="n">
         <f aca="false">0.2*C49+0.8*B49</f>
         <v>-0.0070588177708275</v>
       </c>
@@ -5119,11 +5126,11 @@
         <f aca="false">0.5*C49+0.5*B49</f>
         <v>-0.0329110111067672</v>
       </c>
-      <c r="M49" s="8" t="n">
+      <c r="M49" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B49</f>
         <v>0.00598154794849526</v>
       </c>
-      <c r="N49" s="8" t="n">
+      <c r="N49" s="9" t="n">
         <f aca="false">C49-M49</f>
         <v>-0.0819795479484953</v>
       </c>
@@ -5140,7 +5147,7 @@
         <f aca="false">Data!C50-Data!D50</f>
         <v>0.103842</v>
       </c>
-      <c r="E50" s="5" t="n">
+      <c r="E50" s="1" t="n">
         <f aca="false">0.2*C50+0.8*B50</f>
         <v>0.0564851530224524</v>
       </c>
@@ -5152,11 +5159,11 @@
         <f aca="false">0.5*C50+0.5*B50</f>
         <v>0.0742439706390328</v>
       </c>
-      <c r="M50" s="8" t="n">
+      <c r="M50" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B50</f>
         <v>0.0081684606516023</v>
       </c>
-      <c r="N50" s="8" t="n">
+      <c r="N50" s="9" t="n">
         <f aca="false">C50-M50</f>
         <v>0.0956735393483977</v>
       </c>
@@ -5173,7 +5180,7 @@
         <f aca="false">Data!C51-Data!D51</f>
         <v>0.028769</v>
       </c>
-      <c r="E51" s="5" t="n">
+      <c r="E51" s="1" t="n">
         <f aca="false">0.2*C51+0.8*B51</f>
         <v>0.0402086235099612</v>
       </c>
@@ -5185,11 +5192,11 @@
         <f aca="false">0.5*C51+0.5*B51</f>
         <v>0.0359187646937258</v>
       </c>
-      <c r="M51" s="8" t="n">
+      <c r="M51" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B51</f>
         <v>0.00806838331608506</v>
       </c>
-      <c r="N51" s="8" t="n">
+      <c r="N51" s="9" t="n">
         <f aca="false">C51-M51</f>
         <v>0.0207006166839149</v>
       </c>
@@ -5206,7 +5213,7 @@
         <f aca="false">Data!C52-Data!D52</f>
         <v>-0.071169</v>
       </c>
-      <c r="E52" s="5" t="n">
+      <c r="E52" s="1" t="n">
         <f aca="false">0.2*C52+0.8*B52</f>
         <v>0.01201783989279</v>
       </c>
@@ -5218,11 +5225,11 @@
         <f aca="false">0.5*C52+0.5*B52</f>
         <v>-0.0191772250670062</v>
       </c>
-      <c r="M52" s="8" t="n">
+      <c r="M52" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B52</f>
         <v>0.00741782973837809</v>
       </c>
-      <c r="N52" s="8" t="n">
+      <c r="N52" s="9" t="n">
         <f aca="false">C52-M52</f>
         <v>-0.0785868297383781</v>
       </c>
@@ -5239,7 +5246,7 @@
         <f aca="false">Data!C53-Data!D53</f>
         <v>0.001054</v>
       </c>
-      <c r="E53" s="5" t="n">
+      <c r="E53" s="1" t="n">
         <f aca="false">0.2*C53+0.8*B53</f>
         <v>-0.00490555074741879</v>
       </c>
@@ -5251,11 +5258,11 @@
         <f aca="false">0.5*C53+0.5*B53</f>
         <v>-0.00267071921713674</v>
       </c>
-      <c r="M53" s="8" t="n">
+      <c r="M53" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B53</f>
         <v>0.0049301908546463</v>
       </c>
-      <c r="N53" s="8" t="n">
+      <c r="N53" s="9" t="n">
         <f aca="false">C53-M53</f>
         <v>-0.0038761908546463</v>
       </c>
@@ -5272,7 +5279,7 @@
         <f aca="false">Data!C54-Data!D54</f>
         <v>-0.057243</v>
       </c>
-      <c r="E54" s="5" t="n">
+      <c r="E54" s="1" t="n">
         <f aca="false">0.2*C54+0.8*B54</f>
         <v>-0.0596712909654904</v>
       </c>
@@ -5284,11 +5291,11 @@
         <f aca="false">0.5*C54+0.5*B54</f>
         <v>-0.0587606818534315</v>
       </c>
-      <c r="M54" s="8" t="n">
+      <c r="M54" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B54</f>
         <v>0.00151164201319164</v>
       </c>
-      <c r="N54" s="8" t="n">
+      <c r="N54" s="9" t="n">
         <f aca="false">C54-M54</f>
         <v>-0.0587546420131916</v>
       </c>
@@ -5305,7 +5312,7 @@
         <f aca="false">Data!C55-Data!D55</f>
         <v>0.001276</v>
       </c>
-      <c r="E55" s="5" t="n">
+      <c r="E55" s="1" t="n">
         <f aca="false">0.2*C55+0.8*B55</f>
         <v>0.0331267869172832</v>
       </c>
@@ -5317,11 +5324,11 @@
         <f aca="false">0.5*C55+0.5*B55</f>
         <v>0.021182741823302</v>
       </c>
-      <c r="M55" s="8" t="n">
+      <c r="M55" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B55</f>
         <v>0.00794282471861965</v>
       </c>
-      <c r="N55" s="8" t="n">
+      <c r="N55" s="9" t="n">
         <f aca="false">C55-M55</f>
         <v>-0.00666682471861965</v>
       </c>
@@ -5338,7 +5345,7 @@
         <f aca="false">Data!C56-Data!D56</f>
         <v>0.033928</v>
       </c>
-      <c r="E56" s="5" t="n">
+      <c r="E56" s="1" t="n">
         <f aca="false">0.2*C56+0.8*B56</f>
         <v>0.0177453769812824</v>
       </c>
@@ -5350,11 +5357,11 @@
         <f aca="false">0.5*C56+0.5*B56</f>
         <v>0.0238138606133015</v>
       </c>
-      <c r="M56" s="8" t="n">
+      <c r="M56" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B56</f>
         <v>0.00620510836200149</v>
       </c>
-      <c r="N56" s="8" t="n">
+      <c r="N56" s="9" t="n">
         <f aca="false">C56-M56</f>
         <v>0.0277228916379985</v>
       </c>
@@ -5371,7 +5378,7 @@
         <f aca="false">Data!C57-Data!D57</f>
         <v>0.021468</v>
       </c>
-      <c r="E57" s="5" t="n">
+      <c r="E57" s="1" t="n">
         <f aca="false">0.2*C57+0.8*B57</f>
         <v>0.0221282696000629</v>
       </c>
@@ -5383,11 +5390,11 @@
         <f aca="false">0.5*C57+0.5*B57</f>
         <v>0.0218806685000393</v>
       </c>
-      <c r="M57" s="8" t="n">
+      <c r="M57" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B57</f>
         <v>0.00675032180573532</v>
       </c>
-      <c r="N57" s="8" t="n">
+      <c r="N57" s="9" t="n">
         <f aca="false">C57-M57</f>
         <v>0.0147176781942647</v>
       </c>
@@ -5404,7 +5411,7 @@
         <f aca="false">Data!C58-Data!D58</f>
         <v>0.074248</v>
       </c>
-      <c r="E58" s="5" t="n">
+      <c r="E58" s="1" t="n">
         <f aca="false">0.2*C58+0.8*B58</f>
         <v>0.0353818503664769</v>
       </c>
@@ -5416,11 +5423,11 @@
         <f aca="false">0.5*C58+0.5*B58</f>
         <v>0.0499566564790481</v>
       </c>
-      <c r="M58" s="8" t="n">
+      <c r="M58" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B58</f>
         <v>0.00696425348161183</v>
       </c>
-      <c r="N58" s="8" t="n">
+      <c r="N58" s="9" t="n">
         <f aca="false">C58-M58</f>
         <v>0.0672837465183882</v>
       </c>
@@ -5437,7 +5444,7 @@
         <f aca="false">Data!C59-Data!D59</f>
         <v>-0.035473</v>
       </c>
-      <c r="E59" s="5" t="n">
+      <c r="E59" s="1" t="n">
         <f aca="false">0.2*C59+0.8*B59</f>
         <v>-0.0220507574945419</v>
       </c>
@@ -5449,11 +5456,11 @@
         <f aca="false">0.5*C59+0.5*B59</f>
         <v>-0.0270840984340887</v>
       </c>
-      <c r="M59" s="8" t="n">
+      <c r="M59" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B59</f>
         <v>0.00414984485947844</v>
       </c>
-      <c r="N59" s="8" t="n">
+      <c r="N59" s="9" t="n">
         <f aca="false">C59-M59</f>
         <v>-0.0396228448594784</v>
       </c>
@@ -5470,7 +5477,7 @@
         <f aca="false">Data!C60-Data!D60</f>
         <v>0.005866</v>
       </c>
-      <c r="E60" s="5" t="n">
+      <c r="E60" s="1" t="n">
         <f aca="false">0.2*C60+0.8*B60</f>
         <v>0.00557310181037117</v>
       </c>
@@ -5482,11 +5489,11 @@
         <f aca="false">0.5*C60+0.5*B60</f>
         <v>0.00568293863148198</v>
       </c>
-      <c r="M60" s="8" t="n">
+      <c r="M60" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B60</f>
         <v>0.00568487738084748</v>
       </c>
-      <c r="N60" s="8" t="n">
+      <c r="N60" s="9" t="n">
         <f aca="false">C60-M60</f>
         <v>0.00018112261915252</v>
       </c>
@@ -5503,7 +5510,7 @@
         <f aca="false">Data!C61-Data!D61</f>
         <v>-0.037276</v>
       </c>
-      <c r="E61" s="5" t="n">
+      <c r="E61" s="1" t="n">
         <f aca="false">0.2*C61+0.8*B61</f>
         <v>-0.000316947525860148</v>
       </c>
@@ -5515,11 +5522,11 @@
         <f aca="false">0.5*C61+0.5*B61</f>
         <v>-0.0141765922036626</v>
       </c>
-      <c r="M61" s="8" t="n">
+      <c r="M61" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B61</f>
         <v>0.00590204231393541</v>
       </c>
-      <c r="N61" s="8" t="n">
+      <c r="N61" s="9" t="n">
         <f aca="false">C61-M61</f>
         <v>-0.0431780423139354</v>
       </c>
@@ -5536,7 +5543,7 @@
         <f aca="false">Data!C62-Data!D62</f>
         <v>0.00631</v>
       </c>
-      <c r="E62" s="5" t="n">
+      <c r="E62" s="1" t="n">
         <f aca="false">0.2*C62+0.8*B62</f>
         <v>0.0426717586968104</v>
       </c>
@@ -5548,11 +5555,11 @@
         <f aca="false">0.5*C62+0.5*B62</f>
         <v>0.0290360991855065</v>
       </c>
-      <c r="M62" s="8" t="n">
+      <c r="M62" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B62</f>
         <v>0.00861994453666458</v>
       </c>
-      <c r="N62" s="8" t="n">
+      <c r="N62" s="9" t="n">
         <f aca="false">C62-M62</f>
         <v>-0.00230994453666458</v>
       </c>
@@ -5569,7 +5576,7 @@
         <f aca="false">Data!C63-Data!D63</f>
         <v>-0.049866</v>
       </c>
-      <c r="E63" s="5" t="n">
+      <c r="E63" s="1" t="n">
         <f aca="false">0.2*C63+0.8*B63</f>
         <v>0.00073824242599704</v>
       </c>
@@ -5581,11 +5588,11 @@
         <f aca="false">0.5*C63+0.5*B63</f>
         <v>-0.0182383484837519</v>
       </c>
-      <c r="M63" s="8" t="n">
+      <c r="M63" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B63</f>
         <v>0.00618541418703861</v>
       </c>
-      <c r="N63" s="8" t="n">
+      <c r="N63" s="9" t="n">
         <f aca="false">C63-M63</f>
         <v>-0.0560514141870386</v>
       </c>
@@ -5602,7 +5609,7 @@
         <f aca="false">Data!C64-Data!D64</f>
         <v>0.007228</v>
       </c>
-      <c r="E64" s="5" t="n">
+      <c r="E64" s="1" t="n">
         <f aca="false">0.2*C64+0.8*B64</f>
         <v>0.0313547843219829</v>
       </c>
@@ -5614,11 +5621,11 @@
         <f aca="false">0.5*C64+0.5*B64</f>
         <v>0.0223072402012393</v>
       </c>
-      <c r="M64" s="8" t="n">
+      <c r="M64" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B64</f>
         <v>0.00770789134434445</v>
       </c>
-      <c r="N64" s="8" t="n">
+      <c r="N64" s="9" t="n">
         <f aca="false">C64-M64</f>
         <v>-0.000479891344344448</v>
       </c>
@@ -5635,7 +5642,7 @@
         <f aca="false">Data!C65-Data!D65</f>
         <v>-0.080967</v>
       </c>
-      <c r="E65" s="5" t="n">
+      <c r="E65" s="1" t="n">
         <f aca="false">0.2*C65+0.8*B65</f>
         <v>-0.000924746379918368</v>
       </c>
@@ -5647,11 +5654,11 @@
         <f aca="false">0.5*C65+0.5*B65</f>
         <v>-0.030940591487449</v>
       </c>
-      <c r="M65" s="8" t="n">
+      <c r="M65" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B65</f>
         <v>0.00654682387686588</v>
       </c>
-      <c r="N65" s="8" t="n">
+      <c r="N65" s="9" t="n">
         <f aca="false">C65-M65</f>
         <v>-0.0875138238768659</v>
       </c>
@@ -5668,7 +5675,7 @@
         <f aca="false">Data!C66-Data!D66</f>
         <v>-0.042438</v>
       </c>
-      <c r="E66" s="5" t="n">
+      <c r="E66" s="1" t="n">
         <f aca="false">0.2*C66+0.8*B66</f>
         <v>0.0101322005021374</v>
       </c>
@@ -5680,11 +5687,11 @@
         <f aca="false">0.5*C66+0.5*B66</f>
         <v>-0.00958162468616409</v>
       </c>
-      <c r="M66" s="8" t="n">
+      <c r="M66" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B66</f>
         <v>0.00681258662158605</v>
       </c>
-      <c r="N66" s="8" t="n">
+      <c r="N66" s="9" t="n">
         <f aca="false">C66-M66</f>
         <v>-0.0492505866215861</v>
       </c>
@@ -5701,7 +5708,7 @@
         <f aca="false">Data!C67-Data!D67</f>
         <v>-0.146782</v>
       </c>
-      <c r="E67" s="5" t="n">
+      <c r="E67" s="1" t="n">
         <f aca="false">0.2*C67+0.8*B67</f>
         <v>-0.0401608258321306</v>
       </c>
@@ -5713,11 +5720,11 @@
         <f aca="false">0.5*C67+0.5*B67</f>
         <v>-0.0801437661450816</v>
       </c>
-      <c r="M67" s="8" t="n">
+      <c r="M67" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B67</f>
         <v>0.00447909799005658</v>
       </c>
-      <c r="N67" s="8" t="n">
+      <c r="N67" s="9" t="n">
         <f aca="false">C67-M67</f>
         <v>-0.151261097990057</v>
       </c>
@@ -5734,7 +5741,7 @@
         <f aca="false">Data!C68-Data!D68</f>
         <v>0.106586</v>
       </c>
-      <c r="E68" s="5" t="n">
+      <c r="E68" s="1" t="n">
         <f aca="false">0.2*C68+0.8*B68</f>
         <v>0.0618953439956774</v>
       </c>
@@ -5746,11 +5753,11 @@
         <f aca="false">0.5*C68+0.5*B68</f>
         <v>0.0786543399972984</v>
       </c>
-      <c r="M68" s="8" t="n">
+      <c r="M68" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B68</f>
         <v>0.0085539933225575</v>
       </c>
-      <c r="N68" s="8" t="n">
+      <c r="N68" s="9" t="n">
         <f aca="false">C68-M68</f>
         <v>0.0980320066774425</v>
       </c>
@@ -5767,7 +5774,7 @@
         <f aca="false">Data!C69-Data!D69</f>
         <v>0.046001</v>
       </c>
-      <c r="E69" s="5" t="n">
+      <c r="E69" s="1" t="n">
         <f aca="false">0.2*C69+0.8*B69</f>
         <v>-0.0140947797518802</v>
       </c>
@@ -5779,11 +5786,11 @@
         <f aca="false">0.5*C69+0.5*B69</f>
         <v>0.00844113765507489</v>
       </c>
-      <c r="M69" s="8" t="n">
+      <c r="M69" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B69</f>
         <v>0.00348853445774386</v>
       </c>
-      <c r="N69" s="8" t="n">
+      <c r="N69" s="9" t="n">
         <f aca="false">C69-M69</f>
         <v>0.0425124655422561</v>
       </c>
@@ -5800,7 +5807,7 @@
         <f aca="false">Data!C70-Data!D70</f>
         <v>-0.040926</v>
       </c>
-      <c r="E70" s="5" t="n">
+      <c r="E70" s="1" t="n">
         <f aca="false">0.2*C70+0.8*B70</f>
         <v>0.0167878460123722</v>
       </c>
@@ -5812,11 +5819,11 @@
         <f aca="false">0.5*C70+0.5*B70</f>
         <v>-0.00485484624226739</v>
       </c>
-      <c r="M70" s="8" t="n">
+      <c r="M70" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B70</f>
         <v>0.00731643083495736</v>
       </c>
-      <c r="N70" s="8" t="n">
+      <c r="N70" s="9" t="n">
         <f aca="false">C70-M70</f>
         <v>-0.0482424308349574</v>
       </c>
@@ -5833,7 +5840,7 @@
         <f aca="false">Data!C71-Data!D71</f>
         <v>-0.001497</v>
       </c>
-      <c r="E71" s="5" t="n">
+      <c r="E71" s="1" t="n">
         <f aca="false">0.2*C71+0.8*B71</f>
         <v>0.036392639736808</v>
       </c>
@@ -5845,11 +5852,11 @@
         <f aca="false">0.5*C71+0.5*B71</f>
         <v>0.022184024835505</v>
       </c>
-      <c r="M71" s="8" t="n">
+      <c r="M71" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B71</f>
         <v>0.00824580577648601</v>
       </c>
-      <c r="N71" s="8" t="n">
+      <c r="N71" s="9" t="n">
         <f aca="false">C71-M71</f>
         <v>-0.00974280577648601</v>
       </c>
@@ -5866,7 +5873,7 @@
         <f aca="false">Data!C72-Data!D72</f>
         <v>-0.066354</v>
       </c>
-      <c r="E72" s="5" t="n">
+      <c r="E72" s="1" t="n">
         <f aca="false">0.2*C72+0.8*B72</f>
         <v>0.0109566717819035</v>
       </c>
@@ -5878,11 +5885,11 @@
         <f aca="false">0.5*C72+0.5*B72</f>
         <v>-0.0180348301363103</v>
       </c>
-      <c r="M72" s="8" t="n">
+      <c r="M72" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B72</f>
         <v>0.0072573030614351</v>
       </c>
-      <c r="N72" s="8" t="n">
+      <c r="N72" s="9" t="n">
         <f aca="false">C72-M72</f>
         <v>-0.0736113030614351</v>
       </c>
@@ -5899,7 +5906,7 @@
         <f aca="false">Data!C73-Data!D73</f>
         <v>-0.035134</v>
       </c>
-      <c r="E73" s="5" t="n">
+      <c r="E73" s="1" t="n">
         <f aca="false">0.2*C73+0.8*B73</f>
         <v>0.0130834004612626</v>
       </c>
@@ -5911,11 +5918,11 @@
         <f aca="false">0.5*C73+0.5*B73</f>
         <v>-0.00499812471171091</v>
       </c>
-      <c r="M73" s="8" t="n">
+      <c r="M73" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B73</f>
         <v>0.00693078280868512</v>
       </c>
-      <c r="N73" s="8" t="n">
+      <c r="N73" s="9" t="n">
         <f aca="false">C73-M73</f>
         <v>-0.0420647828086851</v>
       </c>
@@ -5932,7 +5939,7 @@
         <f aca="false">Data!C74-Data!D74</f>
         <v>0.037453</v>
       </c>
-      <c r="E74" s="5" t="n">
+      <c r="E74" s="1" t="n">
         <f aca="false">0.2*C74+0.8*B74</f>
         <v>-0.0202623936604838</v>
       </c>
@@ -5944,11 +5951,11 @@
         <f aca="false">0.5*C74+0.5*B74</f>
         <v>0.00138087896219765</v>
       </c>
-      <c r="M74" s="8" t="n">
+      <c r="M74" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B74</f>
         <v>0.00313499160986237</v>
       </c>
-      <c r="N74" s="8" t="n">
+      <c r="N74" s="9" t="n">
         <f aca="false">C74-M74</f>
         <v>0.0343180083901376</v>
       </c>
@@ -5965,7 +5972,7 @@
         <f aca="false">Data!C75-Data!D75</f>
         <v>0.065183</v>
       </c>
-      <c r="E75" s="5" t="n">
+      <c r="E75" s="1" t="n">
         <f aca="false">0.2*C75+0.8*B75</f>
         <v>0.0495218538765582</v>
       </c>
@@ -5977,11 +5984,11 @@
         <f aca="false">0.5*C75+0.5*B75</f>
         <v>0.0553947836728489</v>
       </c>
-      <c r="M75" s="8" t="n">
+      <c r="M75" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B75</f>
         <v>0.00822940662129422</v>
       </c>
-      <c r="N75" s="8" t="n">
+      <c r="N75" s="9" t="n">
         <f aca="false">C75-M75</f>
         <v>0.0569535933787058</v>
       </c>
@@ -5998,7 +6005,7 @@
         <f aca="false">Data!C76-Data!D76</f>
         <v>-0.025419</v>
       </c>
-      <c r="E76" s="5" t="n">
+      <c r="E76" s="1" t="n">
         <f aca="false">0.2*C76+0.8*B76</f>
         <v>0.001506567922308</v>
       </c>
@@ -6010,11 +6017,11 @@
         <f aca="false">0.5*C76+0.5*B76</f>
         <v>-0.0085905200485575</v>
       </c>
-      <c r="M76" s="8" t="n">
+      <c r="M76" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B76</f>
         <v>0.0058585923228102</v>
       </c>
-      <c r="N76" s="8" t="n">
+      <c r="N76" s="9" t="n">
         <f aca="false">C76-M76</f>
         <v>-0.0312775923228102</v>
       </c>
@@ -6031,7 +6038,7 @@
         <f aca="false">Data!C77-Data!D77</f>
         <v>-0.001546</v>
       </c>
-      <c r="E77" s="5" t="n">
+      <c r="E77" s="1" t="n">
         <f aca="false">0.2*C77+0.8*B77</f>
         <v>0.00548353590916998</v>
       </c>
@@ -6043,11 +6050,11 @@
         <f aca="false">0.5*C77+0.5*B77</f>
         <v>0.00284745994323124</v>
       </c>
-      <c r="M77" s="8" t="n">
+      <c r="M77" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B77</f>
         <v>0.00579533610619274</v>
       </c>
-      <c r="N77" s="8" t="n">
+      <c r="N77" s="9" t="n">
         <f aca="false">C77-M77</f>
         <v>-0.00734133610619274</v>
       </c>
@@ -6064,7 +6071,7 @@
         <f aca="false">Data!C78-Data!D78</f>
         <v>-0.029412</v>
       </c>
-      <c r="E78" s="5" t="n">
+      <c r="E78" s="1" t="n">
         <f aca="false">0.2*C78+0.8*B78</f>
         <v>0.0127971491143318</v>
       </c>
@@ -6076,11 +6083,11 @@
         <f aca="false">0.5*C78+0.5*B78</f>
         <v>-0.00303128180354262</v>
       </c>
-      <c r="M78" s="8" t="n">
+      <c r="M78" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B78</f>
         <v>0.00681732498601139</v>
       </c>
-      <c r="N78" s="8" t="n">
+      <c r="N78" s="9" t="n">
         <f aca="false">C78-M78</f>
         <v>-0.0362293249860114</v>
       </c>
@@ -6097,7 +6104,7 @@
         <f aca="false">Data!C79-Data!D79</f>
         <v>0.047049</v>
       </c>
-      <c r="E79" s="5" t="n">
+      <c r="E79" s="1" t="n">
         <f aca="false">0.2*C79+0.8*B79</f>
         <v>0.0258254108882064</v>
       </c>
@@ -6109,11 +6116,11 @@
         <f aca="false">0.5*C79+0.5*B79</f>
         <v>0.033784256805129</v>
       </c>
-      <c r="M79" s="8" t="n">
+      <c r="M79" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B79</f>
         <v>0.00663778333712882</v>
       </c>
-      <c r="N79" s="8" t="n">
+      <c r="N79" s="9" t="n">
         <f aca="false">C79-M79</f>
         <v>0.0404112166628712</v>
       </c>
@@ -6130,7 +6137,7 @@
         <f aca="false">Data!C80-Data!D80</f>
         <v>-0.013709</v>
       </c>
-      <c r="E80" s="5" t="n">
+      <c r="E80" s="1" t="n">
         <f aca="false">0.2*C80+0.8*B80</f>
         <v>-0.0138461521539568</v>
       </c>
@@ -6142,11 +6149,11 @@
         <f aca="false">0.5*C80+0.5*B80</f>
         <v>-0.013794720096223</v>
       </c>
-      <c r="M80" s="8" t="n">
+      <c r="M80" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B80</f>
         <v>0.0044553123294133</v>
       </c>
-      <c r="N80" s="8" t="n">
+      <c r="N80" s="9" t="n">
         <f aca="false">C80-M80</f>
         <v>-0.0181643123294133</v>
       </c>
@@ -6163,7 +6170,7 @@
         <f aca="false">Data!C81-Data!D81</f>
         <v>-0.007143</v>
       </c>
-      <c r="E81" s="5" t="n">
+      <c r="E81" s="1" t="n">
         <f aca="false">0.2*C81+0.8*B81</f>
         <v>0.0304691119784657</v>
       </c>
@@ -6175,11 +6182,11 @@
         <f aca="false">0.5*C81+0.5*B81</f>
         <v>0.0163645699865411</v>
       </c>
-      <c r="M81" s="8" t="n">
+      <c r="M81" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B81</f>
         <v>0.00786559155461236</v>
       </c>
-      <c r="N81" s="8" t="n">
+      <c r="N81" s="9" t="n">
         <f aca="false">C81-M81</f>
         <v>-0.0150085915546124</v>
       </c>
@@ -6196,7 +6203,7 @@
         <f aca="false">Data!C82-Data!D82</f>
         <v>-0.058915</v>
       </c>
-      <c r="E82" s="5" t="n">
+      <c r="E82" s="1" t="n">
         <f aca="false">0.2*C82+0.8*B82</f>
         <v>-0.0231266812524782</v>
       </c>
@@ -6208,11 +6215,11 @@
         <f aca="false">0.5*C82+0.5*B82</f>
         <v>-0.0365473007827989</v>
       </c>
-      <c r="M82" s="8" t="n">
+      <c r="M82" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B82</f>
         <v>0.00443633233230992</v>
       </c>
-      <c r="N82" s="8" t="n">
+      <c r="N82" s="9" t="n">
         <f aca="false">C82-M82</f>
         <v>-0.0633513323323099</v>
       </c>
@@ -6229,7 +6236,7 @@
         <f aca="false">Data!C83-Data!D83</f>
         <v>-0.030372</v>
       </c>
-      <c r="E83" s="5" t="n">
+      <c r="E83" s="1" t="n">
         <f aca="false">0.2*C83+0.8*B83</f>
         <v>0.0133112805318973</v>
       </c>
@@ -6241,11 +6248,11 @@
         <f aca="false">0.5*C83+0.5*B83</f>
         <v>-0.00306994966756421</v>
       </c>
-      <c r="M83" s="8" t="n">
+      <c r="M83" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B83</f>
         <v>0.00687332474677097</v>
       </c>
-      <c r="N83" s="8" t="n">
+      <c r="N83" s="9" t="n">
         <f aca="false">C83-M83</f>
         <v>-0.037245324746771</v>
       </c>
@@ -6262,7 +6269,7 @@
         <f aca="false">Data!C84-Data!D84</f>
         <v>0.009589</v>
       </c>
-      <c r="E84" s="5" t="n">
+      <c r="E84" s="1" t="n">
         <f aca="false">0.2*C84+0.8*B84</f>
         <v>0.0233770274678111</v>
       </c>
@@ -6274,11 +6281,11 @@
         <f aca="false">0.5*C84+0.5*B84</f>
         <v>0.0182065171673819</v>
       </c>
-      <c r="M84" s="8" t="n">
+      <c r="M84" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B84</f>
         <v>0.00703776741204039</v>
       </c>
-      <c r="N84" s="8" t="n">
+      <c r="N84" s="9" t="n">
         <f aca="false">C84-M84</f>
         <v>0.00255123258795961</v>
       </c>
@@ -6295,7 +6302,7 @@
         <f aca="false">Data!C85-Data!D85</f>
         <v>0.012453</v>
       </c>
-      <c r="E85" s="5" t="n">
+      <c r="E85" s="1" t="n">
         <f aca="false">0.2*C85+0.8*B85</f>
         <v>0.000375882081253688</v>
       </c>
@@ -6307,11 +6314,11 @@
         <f aca="false">0.5*C85+0.5*B85</f>
         <v>0.00490480130078356</v>
       </c>
-      <c r="M85" s="8" t="n">
+      <c r="M85" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B85</f>
         <v>0.00516823538306183</v>
       </c>
-      <c r="N85" s="8" t="n">
+      <c r="N85" s="9" t="n">
         <f aca="false">C85-M85</f>
         <v>0.00728476461693817</v>
       </c>
@@ -6328,7 +6335,7 @@
         <f aca="false">Data!C86-Data!D86</f>
         <v>0.053575</v>
       </c>
-      <c r="E86" s="5" t="n">
+      <c r="E86" s="1" t="n">
         <f aca="false">0.2*C86+0.8*B86</f>
         <v>-0.013425291747854</v>
       </c>
@@ -6340,11 +6347,11 @@
         <f aca="false">0.5*C86+0.5*B86</f>
         <v>0.0116998176575912</v>
       </c>
-      <c r="M86" s="8" t="n">
+      <c r="M86" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B86</f>
         <v>0.00342149697950087</v>
       </c>
-      <c r="N86" s="8" t="n">
+      <c r="N86" s="9" t="n">
         <f aca="false">C86-M86</f>
         <v>0.0501535030204991</v>
       </c>
@@ -6361,7 +6368,7 @@
         <f aca="false">Data!C87-Data!D87</f>
         <v>-0.0463</v>
       </c>
-      <c r="E87" s="5" t="n">
+      <c r="E87" s="1" t="n">
         <f aca="false">0.2*C87+0.8*B87</f>
         <v>0.0366565942658558</v>
       </c>
@@ -6373,11 +6380,11 @@
         <f aca="false">0.5*C87+0.5*B87</f>
         <v>0.00554787141615987</v>
       </c>
-      <c r="M87" s="8" t="n">
+      <c r="M87" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B87</f>
         <v>0.0089773591869282</v>
       </c>
-      <c r="N87" s="8" t="n">
+      <c r="N87" s="9" t="n">
         <f aca="false">C87-M87</f>
         <v>-0.0552773591869282</v>
       </c>
@@ -6394,7 +6401,7 @@
         <f aca="false">Data!C88-Data!D88</f>
         <v>-0.021369</v>
       </c>
-      <c r="E88" s="5" t="n">
+      <c r="E88" s="1" t="n">
         <f aca="false">0.2*C88+0.8*B88</f>
         <v>-0.0170231513360711</v>
       </c>
@@ -6406,11 +6413,11 @@
         <f aca="false">0.5*C88+0.5*B88</f>
         <v>-0.0186528445850444</v>
       </c>
-      <c r="M88" s="8" t="n">
+      <c r="M88" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B88</f>
         <v>0.00432485564903261</v>
       </c>
-      <c r="N88" s="8" t="n">
+      <c r="N88" s="9" t="n">
         <f aca="false">C88-M88</f>
         <v>-0.0256938556490326</v>
       </c>
@@ -6427,7 +6434,7 @@
         <f aca="false">Data!C89-Data!D89</f>
         <v>0.021242</v>
       </c>
-      <c r="E89" s="5" t="n">
+      <c r="E89" s="1" t="n">
         <f aca="false">0.2*C89+0.8*B89</f>
         <v>0.011841079985318</v>
       </c>
@@ -6439,11 +6446,11 @@
         <f aca="false">0.5*C89+0.5*B89</f>
         <v>0.0153664249908238</v>
       </c>
-      <c r="M89" s="8" t="n">
+      <c r="M89" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B89</f>
         <v>0.00593808069330151</v>
       </c>
-      <c r="N89" s="8" t="n">
+      <c r="N89" s="9" t="n">
         <f aca="false">C89-M89</f>
         <v>0.0153039193066985</v>
       </c>
@@ -6460,7 +6467,7 @@
         <f aca="false">Data!C90-Data!D90</f>
         <v>-0.011542</v>
       </c>
-      <c r="E90" s="5" t="n">
+      <c r="E90" s="1" t="n">
         <f aca="false">0.2*C90+0.8*B90</f>
         <v>0.00787236044047369</v>
       </c>
@@ -6472,11 +6479,11 @@
         <f aca="false">0.5*C90+0.5*B90</f>
         <v>0.000591975275296055</v>
       </c>
-      <c r="M90" s="8" t="n">
+      <c r="M90" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B90</f>
         <v>0.00614332844564618</v>
       </c>
-      <c r="N90" s="8" t="n">
+      <c r="N90" s="9" t="n">
         <f aca="false">C90-M90</f>
         <v>-0.0176853284456462</v>
       </c>
@@ -6493,7 +6500,7 @@
         <f aca="false">Data!C91-Data!D91</f>
         <v>-0.012937</v>
       </c>
-      <c r="E91" s="5" t="n">
+      <c r="E91" s="1" t="n">
         <f aca="false">0.2*C91+0.8*B91</f>
         <v>-0.0180507357459402</v>
       </c>
@@ -6505,11 +6512,11 @@
         <f aca="false">0.5*C91+0.5*B91</f>
         <v>-0.0161330848412126</v>
       </c>
-      <c r="M91" s="8" t="n">
+      <c r="M91" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B91</f>
         <v>0.00410962308201003</v>
       </c>
-      <c r="N91" s="8" t="n">
+      <c r="N91" s="9" t="n">
         <f aca="false">C91-M91</f>
         <v>-0.01704662308201</v>
       </c>
@@ -6526,7 +6533,7 @@
         <f aca="false">Data!C92-Data!D92</f>
         <v>-0.080809</v>
       </c>
-      <c r="E92" s="5" t="n">
+      <c r="E92" s="1" t="n">
         <f aca="false">0.2*C92+0.8*B92</f>
         <v>0.000480351712544617</v>
       </c>
@@ -6538,11 +6545,11 @@
         <f aca="false">0.5*C92+0.5*B92</f>
         <v>-0.0300031551796596</v>
       </c>
-      <c r="M92" s="8" t="n">
+      <c r="M92" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B92</f>
         <v>0.00665574915999073</v>
       </c>
-      <c r="N92" s="8" t="n">
+      <c r="N92" s="9" t="n">
         <f aca="false">C92-M92</f>
         <v>-0.0874647491599907</v>
       </c>
@@ -6559,7 +6566,7 @@
         <f aca="false">Data!C93-Data!D93</f>
         <v>0.042081</v>
       </c>
-      <c r="E93" s="5" t="n">
+      <c r="E93" s="1" t="n">
         <f aca="false">0.2*C93+0.8*B93</f>
         <v>-0.0399164471799094</v>
       </c>
@@ -6571,11 +6578,11 @@
         <f aca="false">0.5*C93+0.5*B93</f>
         <v>-0.00916740448744337</v>
       </c>
-      <c r="M93" s="8" t="n">
+      <c r="M93" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B93</f>
         <v>0.00150292193425403</v>
       </c>
-      <c r="N93" s="8" t="n">
+      <c r="N93" s="9" t="n">
         <f aca="false">C93-M93</f>
         <v>0.040578078065746</v>
       </c>
@@ -6592,7 +6599,7 @@
         <f aca="false">Data!C94-Data!D94</f>
         <v>-0.002665</v>
       </c>
-      <c r="E94" s="5" t="n">
+      <c r="E94" s="1" t="n">
         <f aca="false">0.2*C94+0.8*B94</f>
         <v>-0.0204532752219876</v>
       </c>
@@ -6604,11 +6611,11 @@
         <f aca="false">0.5*C94+0.5*B94</f>
         <v>-0.0137826720137423</v>
       </c>
-      <c r="M94" s="8" t="n">
+      <c r="M94" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B94</f>
         <v>0.00375616544201563</v>
       </c>
-      <c r="N94" s="8" t="n">
+      <c r="N94" s="9" t="n">
         <f aca="false">C94-M94</f>
         <v>-0.00642116544201563</v>
       </c>
@@ -6625,7 +6632,7 @@
         <f aca="false">Data!C95-Data!D95</f>
         <v>0.022494</v>
       </c>
-      <c r="E95" s="5" t="n">
+      <c r="E95" s="1" t="n">
         <f aca="false">0.2*C95+0.8*B95</f>
         <v>0.0718805319634189</v>
       </c>
@@ -6637,11 +6644,11 @@
         <f aca="false">0.5*C95+0.5*B95</f>
         <v>0.0533605824771368</v>
       </c>
-      <c r="M95" s="8" t="n">
+      <c r="M95" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B95</f>
         <v>0.0106796521961804</v>
       </c>
-      <c r="N95" s="8" t="n">
+      <c r="N95" s="9" t="n">
         <f aca="false">C95-M95</f>
         <v>0.0118143478038196</v>
       </c>
@@ -6658,7 +6665,7 @@
         <f aca="false">Data!C96-Data!D96</f>
         <v>-0.080244</v>
       </c>
-      <c r="E96" s="5" t="n">
+      <c r="E96" s="1" t="n">
         <f aca="false">0.2*C96+0.8*B96</f>
         <v>-0.013757849255441</v>
       </c>
@@ -6670,11 +6677,11 @@
         <f aca="false">0.5*C96+0.5*B96</f>
         <v>-0.0386901557846506</v>
       </c>
-      <c r="M96" s="8" t="n">
+      <c r="M96" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B96</f>
         <v>0.00551762699062079</v>
       </c>
-      <c r="N96" s="8" t="n">
+      <c r="N96" s="9" t="n">
         <f aca="false">C96-M96</f>
         <v>-0.0857616269906208</v>
       </c>
@@ -6691,7 +6698,7 @@
         <f aca="false">Data!C97-Data!D97</f>
         <v>0.006152</v>
       </c>
-      <c r="E97" s="5" t="n">
+      <c r="E97" s="1" t="n">
         <f aca="false">0.2*C97+0.8*B97</f>
         <v>-0.011590289264695</v>
       </c>
@@ -6703,11 +6710,11 @@
         <f aca="false">0.5*C97+0.5*B97</f>
         <v>-0.00493693079043437</v>
       </c>
-      <c r="M97" s="8" t="n">
+      <c r="M97" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B97</f>
         <v>0.00431919819372522</v>
       </c>
-      <c r="N97" s="8" t="n">
+      <c r="N97" s="9" t="n">
         <f aca="false">C97-M97</f>
         <v>0.00183280180627478</v>
       </c>
@@ -6724,7 +6731,7 @@
         <f aca="false">Data!C98-Data!D98</f>
         <v>0.047582</v>
       </c>
-      <c r="E98" s="5" t="n">
+      <c r="E98" s="1" t="n">
         <f aca="false">0.2*C98+0.8*B98</f>
         <v>-0.0303768427843803</v>
       </c>
@@ -6736,11 +6743,11 @@
         <f aca="false">0.5*C98+0.5*B98</f>
         <v>-0.00114227674023766</v>
       </c>
-      <c r="M98" s="8" t="n">
+      <c r="M98" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B98</f>
         <v>0.00217220900369558</v>
       </c>
-      <c r="N98" s="8" t="n">
+      <c r="N98" s="9" t="n">
         <f aca="false">C98-M98</f>
         <v>0.0454097909963044</v>
       </c>
@@ -6757,7 +6764,7 @@
         <f aca="false">Data!C99-Data!D99</f>
         <v>0.10875</v>
       </c>
-      <c r="E99" s="5" t="n">
+      <c r="E99" s="1" t="n">
         <f aca="false">0.2*C99+0.8*B99</f>
         <v>0.0204286376326075</v>
       </c>
@@ -6769,11 +6776,11 @@
         <f aca="false">0.5*C99+0.5*B99</f>
         <v>0.0535491485203797</v>
       </c>
-      <c r="M99" s="8" t="n">
+      <c r="M99" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B99</f>
         <v>0.00523115245482487</v>
       </c>
-      <c r="N99" s="8" t="n">
+      <c r="N99" s="9" t="n">
         <f aca="false">C99-M99</f>
         <v>0.103518847545175</v>
       </c>
@@ -6790,7 +6797,7 @@
         <f aca="false">Data!C100-Data!D100</f>
         <v>-0.000646</v>
       </c>
-      <c r="E100" s="5" t="n">
+      <c r="E100" s="1" t="n">
         <f aca="false">0.2*C100+0.8*B100</f>
         <v>0.0539143006497395</v>
       </c>
@@ -6802,11 +6809,11 @@
         <f aca="false">0.5*C100+0.5*B100</f>
         <v>0.0334541879060872</v>
       </c>
-      <c r="M100" s="8" t="n">
+      <c r="M100" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B100</f>
         <v>0.00962186359771065</v>
       </c>
-      <c r="N100" s="8" t="n">
+      <c r="N100" s="9" t="n">
         <f aca="false">C100-M100</f>
         <v>-0.0102678635977107</v>
       </c>
@@ -6823,7 +6830,7 @@
         <f aca="false">Data!C101-Data!D101</f>
         <v>0.033055</v>
       </c>
-      <c r="E101" s="5" t="n">
+      <c r="E101" s="1" t="n">
         <f aca="false">0.2*C101+0.8*B101</f>
         <v>0.00952063103321217</v>
       </c>
@@ -6835,11 +6842,11 @@
         <f aca="false">0.5*C101+0.5*B101</f>
         <v>0.0183460193957576</v>
       </c>
-      <c r="M101" s="8" t="n">
+      <c r="M101" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B101</f>
         <v>0.00556669143852582</v>
       </c>
-      <c r="N101" s="8" t="n">
+      <c r="N101" s="9" t="n">
         <f aca="false">C101-M101</f>
         <v>0.0274883085614742</v>
       </c>
@@ -6856,7 +6863,7 @@
         <f aca="false">Data!C102-Data!D102</f>
         <v>-0.050316</v>
       </c>
-      <c r="E102" s="5" t="n">
+      <c r="E102" s="1" t="n">
         <f aca="false">0.2*C102+0.8*B102</f>
         <v>0.00412004069218676</v>
       </c>
@@ -6868,11 +6875,11 @@
         <f aca="false">0.5*C102+0.5*B102</f>
         <v>-0.0162934745673833</v>
       </c>
-      <c r="M102" s="8" t="n">
+      <c r="M102" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B102</f>
         <v>0.00646074519126225</v>
       </c>
-      <c r="N102" s="8" t="n">
+      <c r="N102" s="9" t="n">
         <f aca="false">C102-M102</f>
         <v>-0.0567767451912622</v>
       </c>
@@ -6889,7 +6896,7 @@
         <f aca="false">Data!C103-Data!D103</f>
         <v>0.08778</v>
       </c>
-      <c r="E103" s="5" t="n">
+      <c r="E103" s="1" t="n">
         <f aca="false">0.2*C103+0.8*B103</f>
         <v>0.0193957227071896</v>
       </c>
@@ -6901,11 +6908,11 @@
         <f aca="false">0.5*C103+0.5*B103</f>
         <v>0.0450398266919935</v>
       </c>
-      <c r="M103" s="8" t="n">
+      <c r="M103" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B103</f>
         <v>0.00548184234556446</v>
       </c>
-      <c r="N103" s="8" t="n">
+      <c r="N103" s="9" t="n">
         <f aca="false">C103-M103</f>
         <v>0.0822981576544355</v>
       </c>
@@ -6922,7 +6929,7 @@
         <f aca="false">Data!C104-Data!D104</f>
         <v>0.011569</v>
       </c>
-      <c r="E104" s="5" t="n">
+      <c r="E104" s="1" t="n">
         <f aca="false">0.2*C104+0.8*B104</f>
         <v>0.031564653513709</v>
       </c>
@@ -6934,11 +6941,11 @@
         <f aca="false">0.5*C104+0.5*B104</f>
         <v>0.0240662834460681</v>
       </c>
-      <c r="M104" s="8" t="n">
+      <c r="M104" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B104</f>
         <v>0.00765568241149296</v>
       </c>
-      <c r="N104" s="8" t="n">
+      <c r="N104" s="9" t="n">
         <f aca="false">C104-M104</f>
         <v>0.00391331758850704</v>
       </c>
@@ -6955,7 +6962,7 @@
         <f aca="false">Data!C105-Data!D105</f>
         <v>-0.013746</v>
       </c>
-      <c r="E105" s="5" t="n">
+      <c r="E105" s="1" t="n">
         <f aca="false">0.2*C105+0.8*B105</f>
         <v>-0.00187329183724284</v>
       </c>
@@ -6967,11 +6974,11 @@
         <f aca="false">0.5*C105+0.5*B105</f>
         <v>-0.00632555739827678</v>
       </c>
-      <c r="M105" s="8" t="n">
+      <c r="M105" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B105</f>
         <v>0.00540540702125769</v>
       </c>
-      <c r="N105" s="8" t="n">
+      <c r="N105" s="9" t="n">
         <f aca="false">C105-M105</f>
         <v>-0.0191514070212577</v>
       </c>
@@ -6988,7 +6995,7 @@
         <f aca="false">Data!C106-Data!D106</f>
         <v>0.010032</v>
       </c>
-      <c r="E106" s="5" t="n">
+      <c r="E106" s="1" t="n">
         <f aca="false">0.2*C106+0.8*B106</f>
         <v>0.00191185182901974</v>
       </c>
@@ -7000,11 +7007,11 @@
         <f aca="false">0.5*C106+0.5*B106</f>
         <v>0.00495690739313733</v>
       </c>
-      <c r="M106" s="8" t="n">
+      <c r="M106" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B106</f>
         <v>0.00532844496976834</v>
       </c>
-      <c r="N106" s="8" t="n">
+      <c r="N106" s="9" t="n">
         <f aca="false">C106-M106</f>
         <v>0.00470355503023166</v>
       </c>
@@ -7021,7 +7028,7 @@
         <f aca="false">Data!C107-Data!D107</f>
         <v>-0.04064</v>
       </c>
-      <c r="E107" s="5" t="n">
+      <c r="E107" s="1" t="n">
         <f aca="false">0.2*C107+0.8*B107</f>
         <v>-0.0229526021677239</v>
       </c>
@@ -7033,11 +7040,11 @@
         <f aca="false">0.5*C107+0.5*B107</f>
         <v>-0.0295853763548275</v>
       </c>
-      <c r="M107" s="8" t="n">
+      <c r="M107" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B107</f>
         <v>0.00416027785629064</v>
       </c>
-      <c r="N107" s="8" t="n">
+      <c r="N107" s="9" t="n">
         <f aca="false">C107-M107</f>
         <v>-0.0448002778562906</v>
       </c>
@@ -7054,7 +7061,7 @@
         <f aca="false">Data!C108-Data!D108</f>
         <v>-0.068221</v>
       </c>
-      <c r="E108" s="5" t="n">
+      <c r="E108" s="1" t="n">
         <f aca="false">0.2*C108+0.8*B108</f>
         <v>0.0158677405718939</v>
       </c>
@@ -7066,11 +7073,11 @@
         <f aca="false">0.5*C108+0.5*B108</f>
         <v>-0.0156655371425663</v>
       </c>
-      <c r="M108" s="8" t="n">
+      <c r="M108" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B108</f>
         <v>0.00767638792385522</v>
       </c>
-      <c r="N108" s="8" t="n">
+      <c r="N108" s="9" t="n">
         <f aca="false">C108-M108</f>
         <v>-0.0758973879238552</v>
       </c>
@@ -7087,7 +7094,7 @@
         <f aca="false">Data!C109-Data!D109</f>
         <v>-0.024134</v>
       </c>
-      <c r="E109" s="5" t="n">
+      <c r="E109" s="1" t="n">
         <f aca="false">0.2*C109+0.8*B109</f>
         <v>0.0106341501312114</v>
       </c>
@@ -7099,11 +7106,11 @@
         <f aca="false">0.5*C109+0.5*B109</f>
         <v>-0.00240390616799288</v>
       </c>
-      <c r="M109" s="8" t="n">
+      <c r="M109" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B109</f>
         <v>0.0065620739540474</v>
       </c>
-      <c r="N109" s="8" t="n">
+      <c r="N109" s="9" t="n">
         <f aca="false">C109-M109</f>
         <v>-0.0306960739540474</v>
       </c>
@@ -7120,7 +7127,7 @@
         <f aca="false">Data!C110-Data!D110</f>
         <v>0.033851</v>
       </c>
-      <c r="E110" s="5" t="n">
+      <c r="E110" s="1" t="n">
         <f aca="false">0.2*C110+0.8*B110</f>
         <v>0.0215153111003535</v>
       </c>
@@ -7132,11 +7139,11 @@
         <f aca="false">0.5*C110+0.5*B110</f>
         <v>0.0261411944377209</v>
       </c>
-      <c r="M110" s="8" t="n">
+      <c r="M110" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B110</f>
         <v>0.0065053043308962</v>
       </c>
-      <c r="N110" s="8" t="n">
+      <c r="N110" s="9" t="n">
         <f aca="false">C110-M110</f>
         <v>0.0273456956691038</v>
       </c>
@@ -7153,7 +7160,7 @@
         <f aca="false">Data!C111-Data!D111</f>
         <v>0.043894</v>
       </c>
-      <c r="E111" s="5" t="n">
+      <c r="E111" s="1" t="n">
         <f aca="false">0.2*C111+0.8*B111</f>
         <v>0.0401607861256297</v>
       </c>
@@ -7165,11 +7172,11 @@
         <f aca="false">0.5*C111+0.5*B111</f>
         <v>0.0415607413285185</v>
       </c>
-      <c r="M111" s="8" t="n">
+      <c r="M111" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B111</f>
         <v>0.00782469190950675</v>
       </c>
-      <c r="N111" s="8" t="n">
+      <c r="N111" s="9" t="n">
         <f aca="false">C111-M111</f>
         <v>0.0360693080904933</v>
       </c>
@@ -7186,7 +7193,7 @@
         <f aca="false">Data!C112-Data!D112</f>
         <v>-0.008448</v>
       </c>
-      <c r="E112" s="5" t="n">
+      <c r="E112" s="1" t="n">
         <f aca="false">0.2*C112+0.8*B112</f>
         <v>-0.00112919976226487</v>
       </c>
@@ -7198,11 +7205,11 @@
         <f aca="false">0.5*C112+0.5*B112</f>
         <v>-0.00387374985141554</v>
       </c>
-      <c r="M112" s="8" t="n">
+      <c r="M112" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B112</f>
         <v>0.00538038566138122</v>
       </c>
-      <c r="N112" s="8" t="n">
+      <c r="N112" s="9" t="n">
         <f aca="false">C112-M112</f>
         <v>-0.0138283856613812</v>
       </c>
@@ -7219,7 +7226,7 @@
         <f aca="false">Data!C113-Data!D113</f>
         <v>0.018707</v>
       </c>
-      <c r="E113" s="5" t="n">
+      <c r="E113" s="1" t="n">
         <f aca="false">0.2*C113+0.8*B113</f>
         <v>0.0114863208897041</v>
       </c>
@@ -7231,11 +7238,11 @@
         <f aca="false">0.5*C113+0.5*B113</f>
         <v>0.0141940755560651</v>
       </c>
-      <c r="M113" s="8" t="n">
+      <c r="M113" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B113</f>
         <v>0.00595015416009731</v>
       </c>
-      <c r="N113" s="8" t="n">
+      <c r="N113" s="9" t="n">
         <f aca="false">C113-M113</f>
         <v>0.0127568458399027</v>
       </c>
@@ -7252,7 +7259,7 @@
         <f aca="false">Data!C114-Data!D114</f>
         <v>-0.001983</v>
       </c>
-      <c r="E114" s="5" t="n">
+      <c r="E114" s="1" t="n">
         <f aca="false">0.2*C114+0.8*B114</f>
         <v>0.0102733523312299</v>
       </c>
@@ -7264,11 +7271,11 @@
         <f aca="false">0.5*C114+0.5*B114</f>
         <v>0.00567722020701866</v>
       </c>
-      <c r="M114" s="8" t="n">
+      <c r="M114" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B114</f>
         <v>0.00618212381456253</v>
       </c>
-      <c r="N114" s="8" t="n">
+      <c r="N114" s="9" t="n">
         <f aca="false">C114-M114</f>
         <v>-0.00816512381456253</v>
       </c>
@@ -7285,7 +7292,7 @@
         <f aca="false">Data!C115-Data!D115</f>
         <v>-0.01686</v>
       </c>
-      <c r="E115" s="5" t="n">
+      <c r="E115" s="1" t="n">
         <f aca="false">0.2*C115+0.8*B115</f>
         <v>0.00104062546394897</v>
       </c>
@@ -7297,11 +7304,11 @@
         <f aca="false">0.5*C115+0.5*B115</f>
         <v>-0.00567210908503189</v>
       </c>
-      <c r="M115" s="8" t="n">
+      <c r="M115" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B115</f>
         <v>0.00568588643035104</v>
       </c>
-      <c r="N115" s="8" t="n">
+      <c r="N115" s="9" t="n">
         <f aca="false">C115-M115</f>
         <v>-0.022545886430351</v>
       </c>
@@ -7318,7 +7325,7 @@
         <f aca="false">Data!C116-Data!D116</f>
         <v>0.01788</v>
       </c>
-      <c r="E116" s="5" t="n">
+      <c r="E116" s="1" t="n">
         <f aca="false">0.2*C116+0.8*B116</f>
         <v>0.0193556648044692</v>
       </c>
@@ -7330,11 +7337,11 @@
         <f aca="false">0.5*C116+0.5*B116</f>
         <v>0.0188022905027933</v>
       </c>
-      <c r="M116" s="8" t="n">
+      <c r="M116" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B116</f>
         <v>0.00658734962513217</v>
       </c>
-      <c r="N116" s="8" t="n">
+      <c r="N116" s="9" t="n">
         <f aca="false">C116-M116</f>
         <v>0.0112926503748678</v>
       </c>
@@ -7351,7 +7358,7 @@
         <f aca="false">Data!C117-Data!D117</f>
         <v>0.030253</v>
       </c>
-      <c r="E117" s="5" t="n">
+      <c r="E117" s="1" t="n">
         <f aca="false">0.2*C117+0.8*B117</f>
         <v>0.00767818234057466</v>
       </c>
@@ -7363,11 +7370,11 @@
         <f aca="false">0.5*C117+0.5*B117</f>
         <v>0.0161437389628592</v>
       </c>
-      <c r="M117" s="8" t="n">
+      <c r="M117" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B117</f>
         <v>0.0054650185511795</v>
       </c>
-      <c r="N117" s="8" t="n">
+      <c r="N117" s="9" t="n">
         <f aca="false">C117-M117</f>
         <v>0.0247879814488205</v>
       </c>
@@ -7384,7 +7391,7 @@
         <f aca="false">Data!C118-Data!D118</f>
         <v>-0.015336</v>
       </c>
-      <c r="E118" s="5" t="n">
+      <c r="E118" s="1" t="n">
         <f aca="false">0.2*C118+0.8*B118</f>
         <v>0.0126854873870723</v>
       </c>
@@ -7396,11 +7403,11 @@
         <f aca="false">0.5*C118+0.5*B118</f>
         <v>0.0021774296169202</v>
       </c>
-      <c r="M118" s="8" t="n">
+      <c r="M118" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B118</f>
         <v>0.00658521018071353</v>
       </c>
-      <c r="N118" s="8" t="n">
+      <c r="N118" s="9" t="n">
         <f aca="false">C118-M118</f>
         <v>-0.0219212101807135</v>
       </c>
@@ -7417,7 +7424,7 @@
         <f aca="false">Data!C119-Data!D119</f>
         <v>-0.010652</v>
       </c>
-      <c r="E119" s="5" t="n">
+      <c r="E119" s="1" t="n">
         <f aca="false">0.2*C119+0.8*B119</f>
         <v>0.0156902544266243</v>
       </c>
@@ -7429,11 +7436,11 @@
         <f aca="false">0.5*C119+0.5*B119</f>
         <v>0.00581190901664019</v>
       </c>
-      <c r="M119" s="8" t="n">
+      <c r="M119" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B119</f>
         <v>0.00674921033223331</v>
       </c>
-      <c r="N119" s="8" t="n">
+      <c r="N119" s="9" t="n">
         <f aca="false">C119-M119</f>
         <v>-0.0174012103322333</v>
       </c>
@@ -7450,7 +7457,7 @@
         <f aca="false">Data!C120-Data!D120</f>
         <v>0.005281</v>
       </c>
-      <c r="E120" s="5" t="n">
+      <c r="E120" s="1" t="n">
         <f aca="false">0.2*C120+0.8*B120</f>
         <v>0.0248909016305261</v>
       </c>
@@ -7462,11 +7469,11 @@
         <f aca="false">0.5*C120+0.5*B120</f>
         <v>0.0175371885190788</v>
       </c>
-      <c r="M120" s="8" t="n">
+      <c r="M120" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B120</f>
         <v>0.00722615441974675</v>
       </c>
-      <c r="N120" s="8" t="n">
+      <c r="N120" s="9" t="n">
         <f aca="false">C120-M120</f>
         <v>-0.00194515441974675</v>
       </c>
@@ -7483,7 +7490,7 @@
         <f aca="false">Data!C121-Data!D121</f>
         <v>0.010292</v>
       </c>
-      <c r="E121" s="5" t="n">
+      <c r="E121" s="1" t="n">
         <f aca="false">0.2*C121+0.8*B121</f>
         <v>0.0101543066693075</v>
       </c>
@@ -7495,11 +7502,11 @@
         <f aca="false">0.5*C121+0.5*B121</f>
         <v>0.0102059416683172</v>
       </c>
-      <c r="M121" s="8" t="n">
+      <c r="M121" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B121</f>
         <v>0.00597798909166794</v>
       </c>
-      <c r="N121" s="8" t="n">
+      <c r="N121" s="9" t="n">
         <f aca="false">C121-M121</f>
         <v>0.00431401090833206</v>
       </c>
@@ -7516,7 +7523,7 @@
         <f aca="false">Data!C122-Data!D122</f>
         <v>0.035036</v>
       </c>
-      <c r="E122" s="5" t="n">
+      <c r="E122" s="1" t="n">
         <f aca="false">0.2*C122+0.8*B122</f>
         <v>0.0518285208005835</v>
       </c>
@@ -7528,11 +7535,11 @@
         <f aca="false">0.5*C122+0.5*B122</f>
         <v>0.0455313255003647</v>
       </c>
-      <c r="M122" s="8" t="n">
+      <c r="M122" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B122</f>
         <v>0.0088904985112865</v>
       </c>
-      <c r="N122" s="8" t="n">
+      <c r="N122" s="9" t="n">
         <f aca="false">C122-M122</f>
         <v>0.0261455014887135</v>
       </c>
@@ -7549,7 +7556,7 @@
         <f aca="false">Data!C123-Data!D123</f>
         <v>-0.018259</v>
       </c>
-      <c r="E123" s="5" t="n">
+      <c r="E123" s="1" t="n">
         <f aca="false">0.2*C123+0.8*B123</f>
         <v>-0.0341194130614748</v>
       </c>
@@ -7561,11 +7568,11 @@
         <f aca="false">0.5*C123+0.5*B123</f>
         <v>-0.0281717581634218</v>
       </c>
-      <c r="M123" s="8" t="n">
+      <c r="M123" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B123</f>
         <v>0.00291970868486106</v>
       </c>
-      <c r="N123" s="8" t="n">
+      <c r="N123" s="9" t="n">
         <f aca="false">C123-M123</f>
         <v>-0.0211787086848611</v>
       </c>
@@ -7582,7 +7589,7 @@
         <f aca="false">Data!C124-Data!D124</f>
         <v>0.001527</v>
       </c>
-      <c r="E124" s="5" t="n">
+      <c r="E124" s="1" t="n">
         <f aca="false">0.2*C124+0.8*B124</f>
         <v>-0.0210668165406182</v>
       </c>
@@ -7594,11 +7601,11 @@
         <f aca="false">0.5*C124+0.5*B124</f>
         <v>-0.0125941353378864</v>
       </c>
-      <c r="M124" s="8" t="n">
+      <c r="M124" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B124</f>
         <v>0.00364101921787424</v>
       </c>
-      <c r="N124" s="8" t="n">
+      <c r="N124" s="9" t="n">
         <f aca="false">C124-M124</f>
         <v>-0.00211401921787424</v>
       </c>
@@ -7615,7 +7622,7 @@
         <f aca="false">Data!C125-Data!D125</f>
         <v>-0.007178</v>
       </c>
-      <c r="E125" s="5" t="n">
+      <c r="E125" s="1" t="n">
         <f aca="false">0.2*C125+0.8*B125</f>
         <v>0.000430331668102282</v>
       </c>
@@ -7627,11 +7634,11 @@
         <f aca="false">0.5*C125+0.5*B125</f>
         <v>-0.00242279270743607</v>
       </c>
-      <c r="M125" s="8" t="n">
+      <c r="M125" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B125</f>
         <v>0.00548392084753217</v>
       </c>
-      <c r="N125" s="8" t="n">
+      <c r="N125" s="9" t="n">
         <f aca="false">C125-M125</f>
         <v>-0.0126619208475322</v>
       </c>
@@ -7648,7 +7655,7 @@
         <f aca="false">Data!C126-Data!D126</f>
         <v>-0.011087</v>
       </c>
-      <c r="E126" s="5" t="n">
+      <c r="E126" s="1" t="n">
         <f aca="false">0.2*C126+0.8*B126</f>
         <v>0.0158191871199739</v>
       </c>
@@ -7660,11 +7667,11 @@
         <f aca="false">0.5*C126+0.5*B126</f>
         <v>0.00572936694998368</v>
       </c>
-      <c r="M126" s="8" t="n">
+      <c r="M126" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B126</f>
         <v>0.00676633487713664</v>
       </c>
-      <c r="N126" s="8" t="n">
+      <c r="N126" s="9" t="n">
         <f aca="false">C126-M126</f>
         <v>-0.0178533348771366</v>
       </c>
@@ -7681,7 +7688,7 @@
         <f aca="false">Data!C127-Data!D127</f>
         <v>-0.042021</v>
       </c>
-      <c r="E127" s="5" t="n">
+      <c r="E127" s="1" t="n">
         <f aca="false">0.2*C127+0.8*B127</f>
         <v>-0.00468376681233853</v>
       </c>
@@ -7693,11 +7700,11 @@
         <f aca="false">0.5*C127+0.5*B127</f>
         <v>-0.0186852292577116</v>
       </c>
-      <c r="M127" s="8" t="n">
+      <c r="M127" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B127</f>
         <v>0.00563099211336204</v>
       </c>
-      <c r="N127" s="8" t="n">
+      <c r="N127" s="9" t="n">
         <f aca="false">C127-M127</f>
         <v>-0.047651992113362</v>
       </c>
@@ -7714,7 +7721,7 @@
         <f aca="false">Data!C128-Data!D128</f>
         <v>-0.026669</v>
       </c>
-      <c r="E128" s="5" t="n">
+      <c r="E128" s="1" t="n">
         <f aca="false">0.2*C128+0.8*B128</f>
         <v>0.023060689023467</v>
       </c>
@@ -7726,11 +7733,11 @@
         <f aca="false">0.5*C128+0.5*B128</f>
         <v>0.0044120556396669</v>
       </c>
-      <c r="M128" s="8" t="n">
+      <c r="M128" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B128</f>
         <v>0.00758776841505603</v>
       </c>
-      <c r="N128" s="8" t="n">
+      <c r="N128" s="9" t="n">
         <f aca="false">C128-M128</f>
         <v>-0.034256768415056</v>
       </c>
@@ -7747,7 +7754,7 @@
         <f aca="false">Data!C129-Data!D129</f>
         <v>-0.01173</v>
       </c>
-      <c r="E129" s="5" t="n">
+      <c r="E129" s="1" t="n">
         <f aca="false">0.2*C129+0.8*B129</f>
         <v>0.0223440345754897</v>
       </c>
@@ -7759,11 +7766,11 @@
         <f aca="false">0.5*C129+0.5*B129</f>
         <v>0.00956627160968107</v>
       </c>
-      <c r="M129" s="8" t="n">
+      <c r="M129" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B129</f>
         <v>0.0072939866094727</v>
       </c>
-      <c r="N129" s="8" t="n">
+      <c r="N129" s="9" t="n">
         <f aca="false">C129-M129</f>
         <v>-0.0190239866094727</v>
       </c>
@@ -7780,7 +7787,7 @@
         <f aca="false">Data!C130-Data!D130</f>
         <v>-0.020848</v>
       </c>
-      <c r="E130" s="5" t="n">
+      <c r="E130" s="1" t="n">
         <f aca="false">0.2*C130+0.8*B130</f>
         <v>-0.000934800574354315</v>
       </c>
@@ -7792,11 +7799,11 @@
         <f aca="false">0.5*C130+0.5*B130</f>
         <v>-0.00840225035897145</v>
       </c>
-      <c r="M130" s="8" t="n">
+      <c r="M130" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B130</f>
         <v>0.00559247892188924</v>
       </c>
-      <c r="N130" s="8" t="n">
+      <c r="N130" s="9" t="n">
         <f aca="false">C130-M130</f>
         <v>-0.0264404789218892</v>
       </c>
@@ -7813,7 +7820,7 @@
         <f aca="false">Data!C131-Data!D131</f>
         <v>0.026997</v>
       </c>
-      <c r="E131" s="5" t="n">
+      <c r="E131" s="1" t="n">
         <f aca="false">0.2*C131+0.8*B131</f>
         <v>-0.0509126770002601</v>
       </c>
@@ -7825,11 +7832,11 @@
         <f aca="false">0.5*C131+0.5*B131</f>
         <v>-0.0216965481251625</v>
       </c>
-      <c r="M131" s="8" t="n">
+      <c r="M131" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B131</f>
         <v>0.000870113154157392</v>
       </c>
-      <c r="N131" s="8" t="n">
+      <c r="N131" s="9" t="n">
         <f aca="false">C131-M131</f>
         <v>0.0261268868458426</v>
       </c>
@@ -7846,7 +7853,7 @@
         <f aca="false">Data!C132-Data!D132</f>
         <v>0.000458</v>
       </c>
-      <c r="E132" s="5" t="n">
+      <c r="E132" s="1" t="n">
         <f aca="false">0.2*C132+0.8*B132</f>
         <v>0.014864797159499</v>
       </c>
@@ -7858,11 +7865,11 @@
         <f aca="false">0.5*C132+0.5*B132</f>
         <v>0.00946224822468687</v>
       </c>
-      <c r="M132" s="8" t="n">
+      <c r="M132" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B132</f>
         <v>0.00650753169616236</v>
       </c>
-      <c r="N132" s="8" t="n">
+      <c r="N132" s="9" t="n">
         <f aca="false">C132-M132</f>
         <v>-0.00604953169616236</v>
       </c>
@@ -7879,7 +7886,7 @@
         <f aca="false">Data!C133-Data!D133</f>
         <v>0.048245</v>
       </c>
-      <c r="E133" s="5" t="n">
+      <c r="E133" s="1" t="n">
         <f aca="false">0.2*C133+0.8*B133</f>
         <v>-0.0641921339514028</v>
       </c>
@@ -7891,11 +7898,11 @@
         <f aca="false">0.5*C133+0.5*B133</f>
         <v>-0.0220282087196267</v>
       </c>
-      <c r="M133" s="8" t="n">
+      <c r="M133" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B133</f>
         <v>-0.000520028923063063</v>
       </c>
-      <c r="N133" s="8" t="n">
+      <c r="N133" s="9" t="n">
         <f aca="false">C133-M133</f>
         <v>0.0487650289230631</v>
       </c>
@@ -7912,7 +7919,7 @@
         <f aca="false">Data!C134-Data!D134</f>
         <v>0.029773</v>
       </c>
-      <c r="E134" s="5" t="n">
+      <c r="E134" s="1" t="n">
         <f aca="false">0.2*C134+0.8*B134</f>
         <v>0.0682911917732459</v>
       </c>
@@ -7924,11 +7931,11 @@
         <f aca="false">0.5*C134+0.5*B134</f>
         <v>0.0538468698582787</v>
       </c>
-      <c r="M134" s="8" t="n">
+      <c r="M134" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B134</f>
         <v>0.0102795472913139</v>
       </c>
-      <c r="N134" s="8" t="n">
+      <c r="N134" s="9" t="n">
         <f aca="false">C134-M134</f>
         <v>0.0194934527086861</v>
       </c>
@@ -7945,7 +7952,7 @@
         <f aca="false">Data!C135-Data!D135</f>
         <v>0.000431</v>
       </c>
-      <c r="E135" s="5" t="n">
+      <c r="E135" s="1" t="n">
         <f aca="false">0.2*C135+0.8*B135</f>
         <v>0.0242502966554648</v>
       </c>
@@ -7957,11 +7964,11 @@
         <f aca="false">0.5*C135+0.5*B135</f>
         <v>0.0153180604096655</v>
       </c>
-      <c r="M135" s="8" t="n">
+      <c r="M135" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B135</f>
         <v>0.00725227709625301</v>
       </c>
-      <c r="N135" s="8" t="n">
+      <c r="N135" s="9" t="n">
         <f aca="false">C135-M135</f>
         <v>-0.00682127709625301</v>
       </c>
@@ -7978,7 +7985,7 @@
         <f aca="false">Data!C136-Data!D136</f>
         <v>-0.027778</v>
       </c>
-      <c r="E136" s="5" t="n">
+      <c r="E136" s="1" t="n">
         <f aca="false">0.2*C136+0.8*B136</f>
         <v>0.00841749877686103</v>
       </c>
@@ -7990,11 +7997,11 @@
         <f aca="false">0.5*C136+0.5*B136</f>
         <v>-0.00515581326446186</v>
       </c>
-      <c r="M136" s="8" t="n">
+      <c r="M136" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B136</f>
         <v>0.00644407988408136</v>
       </c>
-      <c r="N136" s="8" t="n">
+      <c r="N136" s="9" t="n">
         <f aca="false">C136-M136</f>
         <v>-0.0342220798840814</v>
       </c>
@@ -8011,7 +8018,7 @@
         <f aca="false">Data!C137-Data!D137</f>
         <v>-0.006747</v>
       </c>
-      <c r="E137" s="5" t="n">
+      <c r="E137" s="1" t="n">
         <f aca="false">0.2*C137+0.8*B137</f>
         <v>0.0292997023092215</v>
       </c>
@@ -8023,11 +8030,11 @@
         <f aca="false">0.5*C137+0.5*B137</f>
         <v>0.0157821889432635</v>
       </c>
-      <c r="M137" s="8" t="n">
+      <c r="M137" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B137</f>
         <v>0.00776657054942774</v>
       </c>
-      <c r="N137" s="8" t="n">
+      <c r="N137" s="9" t="n">
         <f aca="false">C137-M137</f>
         <v>-0.0145135705494277</v>
       </c>
@@ -8044,7 +8051,7 @@
         <f aca="false">Data!C138-Data!D138</f>
         <v>0.006343</v>
       </c>
-      <c r="E138" s="5" t="n">
+      <c r="E138" s="1" t="n">
         <f aca="false">0.2*C138+0.8*B138</f>
         <v>-0.0513282412155955</v>
       </c>
@@ -8056,11 +8063,11 @@
         <f aca="false">0.5*C138+0.5*B138</f>
         <v>-0.0297015257597472</v>
       </c>
-      <c r="M138" s="8" t="n">
+      <c r="M138" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B138</f>
         <v>0.00116474997377939</v>
       </c>
-      <c r="N138" s="8" t="n">
+      <c r="N138" s="9" t="n">
         <f aca="false">C138-M138</f>
         <v>0.00517825002622062</v>
       </c>
@@ -8077,7 +8084,7 @@
         <f aca="false">Data!C139-Data!D139</f>
         <v>0.088632</v>
       </c>
-      <c r="E139" s="5" t="n">
+      <c r="E139" s="1" t="n">
         <f aca="false">0.2*C139+0.8*B139</f>
         <v>0.0725498017916159</v>
       </c>
@@ -8089,11 +8096,11 @@
         <f aca="false">0.5*C139+0.5*B139</f>
         <v>0.0785806261197599</v>
       </c>
-      <c r="M139" s="8" t="n">
+      <c r="M139" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B139</f>
         <v>0.00968371366736451</v>
       </c>
-      <c r="N139" s="8" t="n">
+      <c r="N139" s="9" t="n">
         <f aca="false">C139-M139</f>
         <v>0.0789482863326355</v>
       </c>
@@ -8110,7 +8117,7 @@
         <f aca="false">Data!C140-Data!D140</f>
         <v>0.010377</v>
       </c>
-      <c r="E140" s="5" t="n">
+      <c r="E140" s="1" t="n">
         <f aca="false">0.2*C140+0.8*B140</f>
         <v>0.0119624962750082</v>
       </c>
@@ -8122,11 +8129,11 @@
         <f aca="false">0.5*C140+0.5*B140</f>
         <v>0.0113679351718801</v>
       </c>
-      <c r="M140" s="8" t="n">
+      <c r="M140" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B140</f>
         <v>0.00612003940539016</v>
       </c>
-      <c r="N140" s="8" t="n">
+      <c r="N140" s="9" t="n">
         <f aca="false">C140-M140</f>
         <v>0.00425696059460984</v>
       </c>
@@ -8143,7 +8150,7 @@
         <f aca="false">Data!C141-Data!D141</f>
         <v>0.065507</v>
       </c>
-      <c r="E141" s="5" t="n">
+      <c r="E141" s="1" t="n">
         <f aca="false">0.2*C141+0.8*B141</f>
         <v>-0.000907457890148242</v>
       </c>
@@ -8155,11 +8162,11 @@
         <f aca="false">0.5*C141+0.5*B141</f>
         <v>0.0239979638186573</v>
       </c>
-      <c r="M141" s="8" t="n">
+      <c r="M141" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B141</f>
         <v>0.00422497046626221</v>
       </c>
-      <c r="N141" s="8" t="n">
+      <c r="N141" s="9" t="n">
         <f aca="false">C141-M141</f>
         <v>0.0612820295337378</v>
       </c>
@@ -8176,7 +8183,7 @@
         <f aca="false">Data!C142-Data!D142</f>
         <v>-0.027315</v>
       </c>
-      <c r="E142" s="5" t="n">
+      <c r="E142" s="1" t="n">
         <f aca="false">0.2*C142+0.8*B142</f>
         <v>0.0079677908681704</v>
       </c>
@@ -8188,11 +8195,11 @@
         <f aca="false">0.5*C142+0.5*B142</f>
         <v>-0.0052632557073935</v>
       </c>
-      <c r="M142" s="8" t="n">
+      <c r="M142" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B142</f>
         <v>0.00640107214870908</v>
       </c>
-      <c r="N142" s="8" t="n">
+      <c r="N142" s="9" t="n">
         <f aca="false">C142-M142</f>
         <v>-0.0337160721487091</v>
       </c>
@@ -8209,7 +8216,7 @@
         <f aca="false">Data!C143-Data!D143</f>
         <v>0.011138</v>
       </c>
-      <c r="E143" s="5" t="n">
+      <c r="E143" s="1" t="n">
         <f aca="false">0.2*C143+0.8*B143</f>
         <v>0.018267598543919</v>
       </c>
@@ -8221,11 +8228,11 @@
         <f aca="false">0.5*C143+0.5*B143</f>
         <v>0.0155939990899494</v>
       </c>
-      <c r="M143" s="8" t="n">
+      <c r="M143" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B143</f>
         <v>0.00660799539554287</v>
       </c>
-      <c r="N143" s="8" t="n">
+      <c r="N143" s="9" t="n">
         <f aca="false">C143-M143</f>
         <v>0.00453000460445713</v>
       </c>
@@ -8242,7 +8249,7 @@
         <f aca="false">Data!C144-Data!D144</f>
         <v>-0.034425</v>
       </c>
-      <c r="E144" s="5" t="n">
+      <c r="E144" s="1" t="n">
         <f aca="false">0.2*C144+0.8*B144</f>
         <v>0.0211184037700887</v>
       </c>
@@ -8254,11 +8261,11 @@
         <f aca="false">0.5*C144+0.5*B144</f>
         <v>0.000289627356305458</v>
       </c>
-      <c r="M144" s="8" t="n">
+      <c r="M144" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B144</f>
         <v>0.00755675339422422</v>
       </c>
-      <c r="N144" s="8" t="n">
+      <c r="N144" s="9" t="n">
         <f aca="false">C144-M144</f>
         <v>-0.0419817533942242</v>
       </c>
@@ -8275,7 +8282,7 @@
         <f aca="false">Data!C145-Data!D145</f>
         <v>0.044365</v>
       </c>
-      <c r="E145" s="5" t="n">
+      <c r="E145" s="1" t="n">
         <f aca="false">0.2*C145+0.8*B145</f>
         <v>0.0317967474248838</v>
       </c>
@@ -8287,11 +8294,11 @@
         <f aca="false">0.5*C145+0.5*B145</f>
         <v>0.0365098421405524</v>
       </c>
-      <c r="M145" s="8" t="n">
+      <c r="M145" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B145</f>
         <v>0.00715391118525821</v>
       </c>
-      <c r="N145" s="8" t="n">
+      <c r="N145" s="9" t="n">
         <f aca="false">C145-M145</f>
         <v>0.0372110888147418</v>
       </c>
@@ -8308,7 +8315,7 @@
         <f aca="false">Data!C146-Data!D146</f>
         <v>0.036684</v>
       </c>
-      <c r="E146" s="5" t="n">
+      <c r="E146" s="1" t="n">
         <f aca="false">0.2*C146+0.8*B146</f>
         <v>0.00589433152669695</v>
       </c>
@@ -8320,11 +8327,11 @@
         <f aca="false">0.5*C146+0.5*B146</f>
         <v>0.0174404572041856</v>
       </c>
-      <c r="M146" s="8" t="n">
+      <c r="M146" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B146</f>
         <v>0.00522154813360532</v>
       </c>
-      <c r="N146" s="8" t="n">
+      <c r="N146" s="9" t="n">
         <f aca="false">C146-M146</f>
         <v>0.0314624518663947</v>
       </c>
@@ -8341,7 +8348,7 @@
         <f aca="false">Data!C147-Data!D147</f>
         <v>0.027582</v>
       </c>
-      <c r="E147" s="5" t="n">
+      <c r="E147" s="1" t="n">
         <f aca="false">0.2*C147+0.8*B147</f>
         <v>-0.0613742734673333</v>
       </c>
@@ -8353,11 +8360,11 @@
         <f aca="false">0.5*C147+0.5*B147</f>
         <v>-0.0280156709170833</v>
       </c>
-      <c r="M147" s="8" t="n">
+      <c r="M147" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B147</f>
         <v>3.11774311574477E-005</v>
       </c>
-      <c r="N147" s="8" t="n">
+      <c r="N147" s="9" t="n">
         <f aca="false">C147-M147</f>
         <v>0.0275508225688426</v>
       </c>
@@ -8374,7 +8381,7 @@
         <f aca="false">Data!C148-Data!D148</f>
         <v>-0.014543</v>
       </c>
-      <c r="E148" s="5" t="n">
+      <c r="E148" s="1" t="n">
         <f aca="false">0.2*C148+0.8*B148</f>
         <v>-0.102845339118891</v>
       </c>
@@ -8386,11 +8393,11 @@
         <f aca="false">0.5*C148+0.5*B148</f>
         <v>-0.0697319619493067</v>
       </c>
-      <c r="M148" s="8" t="n">
+      <c r="M148" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B148</f>
         <v>-0.00258954121199947</v>
       </c>
-      <c r="N148" s="8" t="n">
+      <c r="N148" s="9" t="n">
         <f aca="false">C148-M148</f>
         <v>-0.0119534587880005</v>
       </c>
@@ -8407,7 +8414,7 @@
         <f aca="false">Data!C149-Data!D149</f>
         <v>0.069859</v>
       </c>
-      <c r="E149" s="5" t="n">
+      <c r="E149" s="1" t="n">
         <f aca="false">0.2*C149+0.8*B149</f>
         <v>0.116482593477805</v>
       </c>
@@ -8419,11 +8426,11 @@
         <f aca="false">0.5*C149+0.5*B149</f>
         <v>0.0989987459236283</v>
       </c>
-      <c r="M149" s="8" t="n">
+      <c r="M149" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B149</f>
         <v>0.013465562851872</v>
       </c>
-      <c r="N149" s="8" t="n">
+      <c r="N149" s="9" t="n">
         <f aca="false">C149-M149</f>
         <v>0.056393437148128</v>
       </c>
@@ -8440,7 +8447,7 @@
         <f aca="false">Data!C150-Data!D150</f>
         <v>0.005084</v>
       </c>
-      <c r="E150" s="5" t="n">
+      <c r="E150" s="1" t="n">
         <f aca="false">0.2*C150+0.8*B150</f>
         <v>0.0389541887196255</v>
       </c>
@@ -8452,11 +8459,11 @@
         <f aca="false">0.5*C150+0.5*B150</f>
         <v>0.026252867949766</v>
       </c>
-      <c r="M150" s="8" t="n">
+      <c r="M150" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B150</f>
         <v>0.00834456819289344</v>
       </c>
-      <c r="N150" s="8" t="n">
+      <c r="N150" s="9" t="n">
         <f aca="false">C150-M150</f>
         <v>-0.00326056819289344</v>
       </c>
@@ -8473,7 +8480,7 @@
         <f aca="false">Data!C151-Data!D151</f>
         <v>0.026006</v>
       </c>
-      <c r="E151" s="5" t="n">
+      <c r="E151" s="1" t="n">
         <f aca="false">0.2*C151+0.8*B151</f>
         <v>0.020971725937636</v>
       </c>
@@ -8485,11 +8492,11 @@
         <f aca="false">0.5*C151+0.5*B151</f>
         <v>0.0228595787110225</v>
       </c>
-      <c r="M151" s="8" t="n">
+      <c r="M151" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B151</f>
         <v>0.0065866248671855</v>
       </c>
-      <c r="N151" s="8" t="n">
+      <c r="N151" s="9" t="n">
         <f aca="false">C151-M151</f>
         <v>0.0194193751328145</v>
       </c>
@@ -8506,7 +8513,7 @@
         <f aca="false">Data!C152-Data!D152</f>
         <v>0.115109</v>
       </c>
-      <c r="E152" s="5" t="n">
+      <c r="E152" s="1" t="n">
         <f aca="false">0.2*C152+0.8*B152</f>
         <v>0.067957877170418</v>
       </c>
@@ -8518,11 +8525,11 @@
         <f aca="false">0.5*C152+0.5*B152</f>
         <v>0.0856395482315113</v>
       </c>
-      <c r="M152" s="8" t="n">
+      <c r="M152" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B152</f>
         <v>0.0088995992666084</v>
       </c>
-      <c r="N152" s="8" t="n">
+      <c r="N152" s="9" t="n">
         <f aca="false">C152-M152</f>
         <v>0.106209400733392</v>
       </c>
@@ -8539,7 +8546,7 @@
         <f aca="false">Data!C153-Data!D153</f>
         <v>-0.009646</v>
       </c>
-      <c r="E153" s="5" t="n">
+      <c r="E153" s="1" t="n">
         <f aca="false">0.2*C153+0.8*B153</f>
         <v>0.0554059280524122</v>
       </c>
@@ -8551,11 +8558,11 @@
         <f aca="false">0.5*C153+0.5*B153</f>
         <v>0.0310114550327576</v>
       </c>
-      <c r="M153" s="8" t="n">
+      <c r="M153" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B153</f>
         <v>0.00988290614938591</v>
       </c>
-      <c r="N153" s="8" t="n">
+      <c r="N153" s="9" t="n">
         <f aca="false">C153-M153</f>
         <v>-0.0195289061493859</v>
       </c>
@@ -8572,7 +8579,7 @@
         <f aca="false">Data!C154-Data!D154</f>
         <v>-0.037143</v>
       </c>
-      <c r="E154" s="5" t="n">
+      <c r="E154" s="1" t="n">
         <f aca="false">0.2*C154+0.8*B154</f>
         <v>-0.0379931535013007</v>
       </c>
@@ -8584,11 +8591,11 @@
         <f aca="false">0.5*C154+0.5*B154</f>
         <v>-0.0376743459383129</v>
       </c>
-      <c r="M154" s="8" t="n">
+      <c r="M154" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B154</f>
         <v>0.00291202082208773</v>
       </c>
-      <c r="N154" s="8" t="n">
+      <c r="N154" s="9" t="n">
         <f aca="false">C154-M154</f>
         <v>-0.0400550208220877</v>
       </c>
@@ -8605,7 +8612,7 @@
         <f aca="false">Data!C155-Data!D155</f>
         <v>-0.004135</v>
       </c>
-      <c r="E155" s="5" t="n">
+      <c r="E155" s="1" t="n">
         <f aca="false">0.2*C155+0.8*B155</f>
         <v>-0.022277798827055</v>
       </c>
@@ -8617,11 +8624,11 @@
         <f aca="false">0.5*C155+0.5*B155</f>
         <v>-0.0154742492669094</v>
       </c>
-      <c r="M155" s="8" t="n">
+      <c r="M155" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B155</f>
         <v>0.00363478724868135</v>
       </c>
-      <c r="N155" s="8" t="n">
+      <c r="N155" s="9" t="n">
         <f aca="false">C155-M155</f>
         <v>-0.00776978724868135</v>
       </c>
@@ -8638,7 +8645,7 @@
         <f aca="false">Data!C156-Data!D156</f>
         <v>-0.055463</v>
       </c>
-      <c r="E156" s="5" t="n">
+      <c r="E156" s="1" t="n">
         <f aca="false">0.2*C156+0.8*B156</f>
         <v>0.0763125013110846</v>
       </c>
@@ -8650,11 +8657,11 @@
         <f aca="false">0.5*C156+0.5*B156</f>
         <v>0.0268966883194278</v>
       </c>
-      <c r="M156" s="8" t="n">
+      <c r="M156" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B156</f>
         <v>0.0122676057487018</v>
       </c>
-      <c r="N156" s="8" t="n">
+      <c r="N156" s="9" t="n">
         <f aca="false">C156-M156</f>
         <v>-0.0677306057487018</v>
       </c>
@@ -8671,7 +8678,7 @@
         <f aca="false">Data!C157-Data!D157</f>
         <v>0.067142</v>
       </c>
-      <c r="E157" s="5" t="n">
+      <c r="E157" s="1" t="n">
         <f aca="false">0.2*C157+0.8*B157</f>
         <v>0.0440599650965104</v>
       </c>
@@ -8683,11 +8690,11 @@
         <f aca="false">0.5*C157+0.5*B157</f>
         <v>0.052715728185319</v>
       </c>
-      <c r="M157" s="8" t="n">
+      <c r="M157" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B157</f>
         <v>0.00776517976055787</v>
       </c>
-      <c r="N157" s="8" t="n">
+      <c r="N157" s="9" t="n">
         <f aca="false">C157-M157</f>
         <v>0.0593768202394421</v>
       </c>
@@ -8704,7 +8711,7 @@
         <f aca="false">Data!C158-Data!D158</f>
         <v>-0.020306</v>
       </c>
-      <c r="E158" s="5" t="n">
+      <c r="E158" s="1" t="n">
         <f aca="false">0.2*C158+0.8*B158</f>
         <v>-0.0122320020773226</v>
       </c>
@@ -8716,11 +8723,11 @@
         <f aca="false">0.5*C158+0.5*B158</f>
         <v>-0.0152597512983266</v>
       </c>
-      <c r="M158" s="8" t="n">
+      <c r="M158" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B158</f>
         <v>0.00468795755434064</v>
       </c>
-      <c r="N158" s="8" t="n">
+      <c r="N158" s="9" t="n">
         <f aca="false">C158-M158</f>
         <v>-0.0249939575543406</v>
       </c>
@@ -8737,7 +8744,7 @@
         <f aca="false">Data!C159-Data!D159</f>
         <v>-0.047282</v>
       </c>
-      <c r="E159" s="5" t="n">
+      <c r="E159" s="1" t="n">
         <f aca="false">0.2*C159+0.8*B159</f>
         <v>0.0125805614644667</v>
       </c>
@@ -8749,11 +8756,11 @@
         <f aca="false">0.5*C159+0.5*B159</f>
         <v>-0.00986789908470828</v>
       </c>
-      <c r="M159" s="8" t="n">
+      <c r="M159" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B159</f>
         <v>0.00708358461375468</v>
       </c>
-      <c r="N159" s="8" t="n">
+      <c r="N159" s="9" t="n">
         <f aca="false">C159-M159</f>
         <v>-0.0543655846137547</v>
       </c>
@@ -8770,7 +8777,7 @@
         <f aca="false">Data!C160-Data!D160</f>
         <v>-0.045182</v>
       </c>
-      <c r="E160" s="5" t="n">
+      <c r="E160" s="1" t="n">
         <f aca="false">0.2*C160+0.8*B160</f>
         <v>0.0259255307028677</v>
       </c>
@@ -8782,11 +8789,11 @@
         <f aca="false">0.5*C160+0.5*B160</f>
         <v>-0.000739793310707702</v>
       </c>
-      <c r="M160" s="8" t="n">
+      <c r="M160" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B160</f>
         <v>0.0081085994582589</v>
       </c>
-      <c r="N160" s="8" t="n">
+      <c r="N160" s="9" t="n">
         <f aca="false">C160-M160</f>
         <v>-0.0532905994582589</v>
       </c>
@@ -8803,7 +8810,7 @@
         <f aca="false">Data!C161-Data!D161</f>
         <v>0.049515</v>
       </c>
-      <c r="E161" s="5" t="n">
+      <c r="E161" s="1" t="n">
         <f aca="false">0.2*C161+0.8*B161</f>
         <v>0.052484735881984</v>
       </c>
@@ -8815,11 +8822,11 @@
         <f aca="false">0.5*C161+0.5*B161</f>
         <v>0.05137108492624</v>
       </c>
-      <c r="M161" s="8" t="n">
+      <c r="M161" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B161</f>
         <v>0.00871288820175696</v>
       </c>
-      <c r="N161" s="8" t="n">
+      <c r="N161" s="9" t="n">
         <f aca="false">C161-M161</f>
         <v>0.0408021117982431</v>
       </c>
@@ -8836,7 +8843,7 @@
         <f aca="false">Data!C162-Data!D162</f>
         <v>0.069906</v>
       </c>
-      <c r="E162" s="5" t="n">
+      <c r="E162" s="1" t="n">
         <f aca="false">0.2*C162+0.8*B162</f>
         <v>0.0194698731391585</v>
       </c>
@@ -8848,11 +8855,11 @@
         <f aca="false">0.5*C162+0.5*B162</f>
         <v>0.0383834207119741</v>
       </c>
-      <c r="M162" s="8" t="n">
+      <c r="M162" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B162</f>
         <v>0.00577122240447523</v>
       </c>
-      <c r="N162" s="8" t="n">
+      <c r="N162" s="9" t="n">
         <f aca="false">C162-M162</f>
         <v>0.0641347775955248</v>
       </c>
@@ -8869,7 +8876,7 @@
         <f aca="false">Data!C163-Data!D163</f>
         <v>-0.071151</v>
       </c>
-      <c r="E163" s="5" t="n">
+      <c r="E163" s="1" t="n">
         <f aca="false">0.2*C163+0.8*B163</f>
         <v>0.00435600177425187</v>
       </c>
@@ -8881,11 +8888,11 @@
         <f aca="false">0.5*C163+0.5*B163</f>
         <v>-0.0239591238910926</v>
       </c>
-      <c r="M163" s="8" t="n">
+      <c r="M163" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B163</f>
         <v>0.00680992207405763</v>
       </c>
-      <c r="N163" s="8" t="n">
+      <c r="N163" s="9" t="n">
         <f aca="false">C163-M163</f>
         <v>-0.0779609220740576</v>
       </c>
@@ -8902,7 +8909,7 @@
         <f aca="false">Data!C164-Data!D164</f>
         <v>0.040078</v>
       </c>
-      <c r="E164" s="5" t="n">
+      <c r="E164" s="1" t="n">
         <f aca="false">0.2*C164+0.8*B164</f>
         <v>0.0269114911015881</v>
       </c>
@@ -8914,11 +8921,11 @@
         <f aca="false">0.5*C164+0.5*B164</f>
         <v>0.0318489319384926</v>
       </c>
-      <c r="M164" s="8" t="n">
+      <c r="M164" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B164</f>
         <v>0.00683448198997302</v>
       </c>
-      <c r="N164" s="8" t="n">
+      <c r="N164" s="9" t="n">
         <f aca="false">C164-M164</f>
         <v>0.033243518010027</v>
       </c>
@@ -8935,7 +8942,7 @@
         <f aca="false">Data!C165-Data!D165</f>
         <v>-0.00763</v>
       </c>
-      <c r="E165" s="5" t="n">
+      <c r="E165" s="1" t="n">
         <f aca="false">0.2*C165+0.8*B165</f>
         <v>0.0227062752234836</v>
       </c>
@@ -8947,11 +8954,11 @@
         <f aca="false">0.5*C165+0.5*B165</f>
         <v>0.0113301720146772</v>
       </c>
-      <c r="M165" s="8" t="n">
+      <c r="M165" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B165</f>
         <v>0.00725768399842873</v>
       </c>
-      <c r="N165" s="8" t="n">
+      <c r="N165" s="9" t="n">
         <f aca="false">C165-M165</f>
         <v>-0.0148876839984287</v>
       </c>
@@ -8968,7 +8975,7 @@
         <f aca="false">Data!C166-Data!D166</f>
         <v>-0.045941</v>
       </c>
-      <c r="E166" s="5" t="n">
+      <c r="E166" s="1" t="n">
         <f aca="false">0.2*C166+0.8*B166</f>
         <v>-0.046492938845069</v>
       </c>
@@ -8980,11 +8987,11 @@
         <f aca="false">0.5*C166+0.5*B166</f>
         <v>-0.0462859617781681</v>
       </c>
-      <c r="M166" s="8" t="n">
+      <c r="M166" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B166</f>
         <v>0.00237749034045642</v>
       </c>
-      <c r="N166" s="8" t="n">
+      <c r="N166" s="9" t="n">
         <f aca="false">C166-M166</f>
         <v>-0.0483184903404564</v>
       </c>
@@ -9001,7 +9008,7 @@
         <f aca="false">Data!C167-Data!D167</f>
         <v>0.037754</v>
       </c>
-      <c r="E167" s="5" t="n">
+      <c r="E167" s="1" t="n">
         <f aca="false">0.2*C167+0.8*B167</f>
         <v>0.0634966847788367</v>
       </c>
@@ -9013,11 +9020,11 @@
         <f aca="false">0.5*C167+0.5*B167</f>
         <v>0.0538431779867729</v>
       </c>
-      <c r="M167" s="8" t="n">
+      <c r="M167" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B167</f>
         <v>0.00977273219447918</v>
       </c>
-      <c r="N167" s="8" t="n">
+      <c r="N167" s="9" t="n">
         <f aca="false">C167-M167</f>
         <v>0.0279812678055208</v>
       </c>
@@ -9034,7 +9041,7 @@
         <f aca="false">Data!C168-Data!D168</f>
         <v>0.000724</v>
       </c>
-      <c r="E168" s="5" t="n">
+      <c r="E168" s="1" t="n">
         <f aca="false">0.2*C168+0.8*B168</f>
         <v>-0.00549588816395604</v>
       </c>
@@ -9046,11 +9053,11 @@
         <f aca="false">0.5*C168+0.5*B168</f>
         <v>-0.00316343010247253</v>
       </c>
-      <c r="M168" s="8" t="n">
+      <c r="M168" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B168</f>
         <v>0.00488860826937539</v>
       </c>
-      <c r="N168" s="8" t="n">
+      <c r="N168" s="9" t="n">
         <f aca="false">C168-M168</f>
         <v>-0.00416460826937539</v>
       </c>
@@ -9067,7 +9074,7 @@
         <f aca="false">Data!C169-Data!D169</f>
         <v>0.012417</v>
       </c>
-      <c r="E169" s="5" t="n">
+      <c r="E169" s="1" t="n">
         <f aca="false">0.2*C169+0.8*B169</f>
         <v>0.0381520613106511</v>
       </c>
@@ -9079,11 +9086,11 @@
         <f aca="false">0.5*C169+0.5*B169</f>
         <v>0.0285014133191569</v>
       </c>
-      <c r="M169" s="8" t="n">
+      <c r="M169" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B169</f>
         <v>0.00816464673780609</v>
       </c>
-      <c r="N169" s="8" t="n">
+      <c r="N169" s="9" t="n">
         <f aca="false">C169-M169</f>
         <v>0.00425235326219391</v>
       </c>
@@ -9100,7 +9107,7 @@
         <f aca="false">Data!C170-Data!D170</f>
         <v>-0.016208</v>
       </c>
-      <c r="E170" s="5" t="n">
+      <c r="E170" s="1" t="n">
         <f aca="false">0.2*C170+0.8*B170</f>
         <v>-0.0447275273405175</v>
       </c>
@@ -9112,11 +9119,11 @@
         <f aca="false">0.5*C170+0.5*B170</f>
         <v>-0.0340327045878234</v>
       </c>
-      <c r="M170" s="8" t="n">
+      <c r="M170" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B170</f>
         <v>0.00204590113537176</v>
       </c>
-      <c r="N170" s="8" t="n">
+      <c r="N170" s="9" t="n">
         <f aca="false">C170-M170</f>
         <v>-0.0182539011353718</v>
       </c>
@@ -9133,7 +9140,7 @@
         <f aca="false">Data!C171-Data!D171</f>
         <v>0.06294</v>
       </c>
-      <c r="E171" s="5" t="n">
+      <c r="E171" s="1" t="n">
         <f aca="false">0.2*C171+0.8*B171</f>
         <v>-0.0114091226471646</v>
       </c>
@@ -9145,11 +9152,11 @@
         <f aca="false">0.5*C171+0.5*B171</f>
         <v>0.0164717983455222</v>
       </c>
-      <c r="M171" s="8" t="n">
+      <c r="M171" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B171</f>
         <v>0.00343285100679286</v>
       </c>
-      <c r="N171" s="8" t="n">
+      <c r="N171" s="9" t="n">
         <f aca="false">C171-M171</f>
         <v>0.0595071489932071</v>
       </c>
@@ -9166,7 +9173,7 @@
         <f aca="false">Data!C172-Data!D172</f>
         <v>0.010928</v>
       </c>
-      <c r="E172" s="5" t="n">
+      <c r="E172" s="1" t="n">
         <f aca="false">0.2*C172+0.8*B172</f>
         <v>0.0317320218265542</v>
       </c>
@@ -9178,11 +9185,11 @@
         <f aca="false">0.5*C172+0.5*B172</f>
         <v>0.0239305136415964</v>
       </c>
-      <c r="M172" s="8" t="n">
+      <c r="M172" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B172</f>
         <v>0.00767912246018037</v>
       </c>
-      <c r="N172" s="8" t="n">
+      <c r="N172" s="9" t="n">
         <f aca="false">C172-M172</f>
         <v>0.00324887753981963</v>
       </c>
@@ -9199,7 +9206,7 @@
         <f aca="false">Data!C173-Data!D173</f>
         <v>-0.004496</v>
       </c>
-      <c r="E173" s="5" t="n">
+      <c r="E173" s="1" t="n">
         <f aca="false">0.2*C173+0.8*B173</f>
         <v>-0.0707413807747489</v>
       </c>
@@ -9211,11 +9218,11 @@
         <f aca="false">0.5*C173+0.5*B173</f>
         <v>-0.0458993629842181</v>
       </c>
-      <c r="M173" s="8" t="n">
+      <c r="M173" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B173</f>
         <v>-0.000202891892177976</v>
       </c>
-      <c r="N173" s="8" t="n">
+      <c r="N173" s="9" t="n">
         <f aca="false">C173-M173</f>
         <v>-0.00429310810782202</v>
       </c>
@@ -9232,7 +9239,7 @@
         <f aca="false">Data!C174-Data!D174</f>
         <v>-0.032172</v>
       </c>
-      <c r="E174" s="5" t="n">
+      <c r="E174" s="1" t="n">
         <f aca="false">0.2*C174+0.8*B174</f>
         <v>-0.00531203787366722</v>
       </c>
@@ -9244,11 +9251,11 @@
         <f aca="false">0.5*C174+0.5*B174</f>
         <v>-0.015384523671042</v>
       </c>
-      <c r="M174" s="8" t="n">
+      <c r="M174" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B174</f>
         <v>0.00542495205587188</v>
       </c>
-      <c r="N174" s="8" t="n">
+      <c r="N174" s="9" t="n">
         <f aca="false">C174-M174</f>
         <v>-0.0375969520558719</v>
       </c>
@@ -9265,7 +9272,7 @@
         <f aca="false">Data!C175-Data!D175</f>
         <v>-0.022602</v>
       </c>
-      <c r="E175" s="5" t="n">
+      <c r="E175" s="1" t="n">
         <f aca="false">0.2*C175+0.8*B175</f>
         <v>-0.0711236604802747</v>
       </c>
@@ -9277,11 +9284,11 @@
         <f aca="false">0.5*C175+0.5*B175</f>
         <v>-0.0529280378001717</v>
       </c>
-      <c r="M175" s="8" t="n">
+      <c r="M175" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B175</f>
         <v>5.39707216329908E-005</v>
       </c>
-      <c r="N175" s="8" t="n">
+      <c r="N175" s="9" t="n">
         <f aca="false">C175-M175</f>
         <v>-0.022655970721633</v>
       </c>
@@ -9298,7 +9305,7 @@
         <f aca="false">Data!C176-Data!D176</f>
         <v>-0.030961</v>
       </c>
-      <c r="E176" s="5" t="n">
+      <c r="E176" s="1" t="n">
         <f aca="false">0.2*C176+0.8*B176</f>
         <v>0.0668441779978249</v>
       </c>
@@ -9310,11 +9317,11 @@
         <f aca="false">0.5*C176+0.5*B176</f>
         <v>0.0301672362486406</v>
       </c>
-      <c r="M176" s="8" t="n">
+      <c r="M176" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B176</f>
         <v>0.0111280939695242</v>
       </c>
-      <c r="N176" s="8" t="n">
+      <c r="N176" s="9" t="n">
         <f aca="false">C176-M176</f>
         <v>-0.0420890939695242</v>
       </c>
@@ -9331,7 +9338,7 @@
         <f aca="false">Data!C177-Data!D177</f>
         <v>-0.028337</v>
       </c>
-      <c r="E177" s="5" t="n">
+      <c r="E177" s="1" t="n">
         <f aca="false">0.2*C177+0.8*B177</f>
         <v>-0.0399127668763103</v>
       </c>
@@ -9343,11 +9350,11 @@
         <f aca="false">0.5*C177+0.5*B177</f>
         <v>-0.035571854297694</v>
       </c>
-      <c r="M177" s="8" t="n">
+      <c r="M177" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B177</f>
         <v>0.00262011387208702</v>
       </c>
-      <c r="N177" s="8" t="n">
+      <c r="N177" s="9" t="n">
         <f aca="false">C177-M177</f>
         <v>-0.030957113872087</v>
       </c>
@@ -9364,7 +9371,7 @@
         <f aca="false">Data!C178-Data!D178</f>
         <v>-0.025055</v>
       </c>
-      <c r="E178" s="5" t="n">
+      <c r="E178" s="1" t="n">
         <f aca="false">0.2*C178+0.8*B178</f>
         <v>-0.0802920903601772</v>
       </c>
@@ -9376,11 +9383,11 @@
         <f aca="false">0.5*C178+0.5*B178</f>
         <v>-0.0595781814751108</v>
       </c>
-      <c r="M178" s="8" t="n">
+      <c r="M178" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B178</f>
         <v>-0.000634224683780816</v>
       </c>
-      <c r="N178" s="8" t="n">
+      <c r="N178" s="9" t="n">
         <f aca="false">C178-M178</f>
         <v>-0.0244207753162192</v>
       </c>
@@ -9397,7 +9404,7 @@
         <f aca="false">Data!C179-Data!D179</f>
         <v>-0.022566</v>
       </c>
-      <c r="E179" s="5" t="n">
+      <c r="E179" s="1" t="n">
         <f aca="false">0.2*C179+0.8*B179</f>
         <v>0.0582966836471336</v>
       </c>
@@ -9409,11 +9416,11 @@
         <f aca="false">0.5*C179+0.5*B179</f>
         <v>0.0279731772794585</v>
       </c>
-      <c r="M179" s="8" t="n">
+      <c r="M179" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B179</f>
         <v>0.0103170817091969</v>
       </c>
-      <c r="N179" s="8" t="n">
+      <c r="N179" s="9" t="n">
         <f aca="false">C179-M179</f>
         <v>-0.0328830817091969</v>
       </c>
@@ -9430,7 +9437,7 @@
         <f aca="false">Data!C180-Data!D180</f>
         <v>0.07081</v>
       </c>
-      <c r="E180" s="5" t="n">
+      <c r="E180" s="1" t="n">
         <f aca="false">0.2*C180+0.8*B180</f>
         <v>0.0564467591085758</v>
       </c>
@@ -9442,11 +9449,11 @@
         <f aca="false">0.5*C180+0.5*B180</f>
         <v>0.0618329744428599</v>
       </c>
-      <c r="M180" s="8" t="n">
+      <c r="M180" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B180</f>
         <v>0.00868933645508727</v>
       </c>
-      <c r="N180" s="8" t="n">
+      <c r="N180" s="9" t="n">
         <f aca="false">C180-M180</f>
         <v>0.0621206635449127</v>
       </c>
@@ -9463,7 +9470,7 @@
         <f aca="false">Data!C181-Data!D181</f>
         <v>0.026649</v>
       </c>
-      <c r="E181" s="5" t="n">
+      <c r="E181" s="1" t="n">
         <f aca="false">0.2*C181+0.8*B181</f>
         <v>-0.0434915629320993</v>
       </c>
@@ -9475,11 +9482,11 @@
         <f aca="false">0.5*C181+0.5*B181</f>
         <v>-0.0171888518325621</v>
       </c>
-      <c r="M181" s="8" t="n">
+      <c r="M181" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B181</f>
         <v>0.00146416432551255</v>
       </c>
-      <c r="N181" s="8" t="n">
+      <c r="N181" s="9" t="n">
         <f aca="false">C181-M181</f>
         <v>0.0251848356744875</v>
       </c>
@@ -9496,7 +9503,7 @@
         <f aca="false">Data!C182-Data!D182</f>
         <v>0.047732</v>
       </c>
-      <c r="E182" s="5" t="n">
+      <c r="E182" s="1" t="n">
         <f aca="false">0.2*C182+0.8*B182</f>
         <v>0.0568918103961374</v>
       </c>
@@ -9508,11 +9515,11 @@
         <f aca="false">0.5*C182+0.5*B182</f>
         <v>0.0534568814975858</v>
       </c>
-      <c r="M182" s="8" t="n">
+      <c r="M182" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B182</f>
         <v>0.00909067146772299</v>
       </c>
-      <c r="N182" s="8" t="n">
+      <c r="N182" s="9" t="n">
         <f aca="false">C182-M182</f>
         <v>0.038641328532277</v>
       </c>
@@ -9529,7 +9536,7 @@
         <f aca="false">Data!C183-Data!D183</f>
         <v>-0.053264</v>
       </c>
-      <c r="E183" s="5" t="n">
+      <c r="E183" s="1" t="n">
         <f aca="false">0.2*C183+0.8*B183</f>
         <v>-0.0329705362701598</v>
       </c>
@@ -9541,11 +9548,11 @@
         <f aca="false">0.5*C183+0.5*B183</f>
         <v>-0.0405805851688499</v>
       </c>
-      <c r="M183" s="8" t="n">
+      <c r="M183" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B183</f>
         <v>0.00356603476408752</v>
       </c>
-      <c r="N183" s="8" t="n">
+      <c r="N183" s="9" t="n">
         <f aca="false">C183-M183</f>
         <v>-0.0568300347640875</v>
       </c>
@@ -9562,7 +9569,7 @@
         <f aca="false">Data!C184-Data!D184</f>
         <v>0.089539</v>
       </c>
-      <c r="E184" s="5" t="n">
+      <c r="E184" s="1" t="n">
         <f aca="false">0.2*C184+0.8*B184</f>
         <v>0.0442863021485218</v>
       </c>
@@ -9574,11 +9581,11 @@
         <f aca="false">0.5*C184+0.5*B184</f>
         <v>0.0612560638428261</v>
       </c>
-      <c r="M184" s="8" t="n">
+      <c r="M184" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B184</f>
         <v>0.00742789055113004</v>
       </c>
-      <c r="N184" s="8" t="n">
+      <c r="N184" s="9" t="n">
         <f aca="false">C184-M184</f>
         <v>0.08211110944887</v>
       </c>
@@ -9595,7 +9602,7 @@
         <f aca="false">Data!C185-Data!D185</f>
         <v>-0.001529</v>
       </c>
-      <c r="E185" s="5" t="n">
+      <c r="E185" s="1" t="n">
         <f aca="false">0.2*C185+0.8*B185</f>
         <v>0.00930155367815784</v>
       </c>
@@ -9607,11 +9614,11 @@
         <f aca="false">0.5*C185+0.5*B185</f>
         <v>0.00524009604884865</v>
       </c>
-      <c r="M185" s="8" t="n">
+      <c r="M185" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B185</f>
         <v>0.00609785441530446</v>
       </c>
-      <c r="N185" s="8" t="n">
+      <c r="N185" s="9" t="n">
         <f aca="false">C185-M185</f>
         <v>-0.00762685441530446</v>
       </c>
@@ -9628,7 +9635,7 @@
         <f aca="false">Data!C186-Data!D186</f>
         <v>-0.015553</v>
       </c>
-      <c r="E186" s="5" t="n">
+      <c r="E186" s="1" t="n">
         <f aca="false">0.2*C186+0.8*B186</f>
         <v>-0.00262445366613859</v>
       </c>
@@ -9640,11 +9647,11 @@
         <f aca="false">0.5*C186+0.5*B186</f>
         <v>-0.00747265854133662</v>
       </c>
-      <c r="M186" s="8" t="n">
+      <c r="M186" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B186</f>
         <v>0.00537449695462076</v>
       </c>
-      <c r="N186" s="8" t="n">
+      <c r="N186" s="9" t="n">
         <f aca="false">C186-M186</f>
         <v>-0.0209274969546208</v>
       </c>
@@ -9661,7 +9668,7 @@
         <f aca="false">Data!C187-Data!D187</f>
         <v>-0.032305</v>
       </c>
-      <c r="E187" s="5" t="n">
+      <c r="E187" s="1" t="n">
         <f aca="false">0.2*C187+0.8*B187</f>
         <v>0.043100911301919</v>
       </c>
@@ -9673,11 +9680,11 @@
         <f aca="false">0.5*C187+0.5*B187</f>
         <v>0.0148236945636994</v>
       </c>
-      <c r="M187" s="8" t="n">
+      <c r="M187" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B187</f>
         <v>0.00926645109933195</v>
       </c>
-      <c r="N187" s="8" t="n">
+      <c r="N187" s="9" t="n">
         <f aca="false">C187-M187</f>
         <v>-0.041571451099332</v>
       </c>
@@ -9694,7 +9701,7 @@
         <f aca="false">Data!C188-Data!D188</f>
         <v>0.022817</v>
       </c>
-      <c r="E188" s="5" t="n">
+      <c r="E188" s="1" t="n">
         <f aca="false">0.2*C188+0.8*B188</f>
         <v>0.0265825705428243</v>
       </c>
@@ -9706,11 +9713,11 @@
         <f aca="false">0.5*C188+0.5*B188</f>
         <v>0.0251704815892652</v>
       </c>
-      <c r="M188" s="8" t="n">
+      <c r="M188" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B188</f>
         <v>0.00708217370449489</v>
       </c>
-      <c r="N188" s="8" t="n">
+      <c r="N188" s="9" t="n">
         <f aca="false">C188-M188</f>
         <v>0.0157348262955051</v>
       </c>
@@ -9727,7 +9734,7 @@
         <f aca="false">Data!C189-Data!D189</f>
         <v>-0.010304</v>
       </c>
-      <c r="E189" s="5" t="n">
+      <c r="E189" s="1" t="n">
         <f aca="false">0.2*C189+0.8*B189</f>
         <v>-0.018478771589032</v>
       </c>
@@ -9739,11 +9746,11 @@
         <f aca="false">0.5*C189+0.5*B189</f>
         <v>-0.015413232243145</v>
       </c>
-      <c r="M189" s="8" t="n">
+      <c r="M189" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B189</f>
         <v>0.00403391567472602</v>
       </c>
-      <c r="N189" s="8" t="n">
+      <c r="N189" s="9" t="n">
         <f aca="false">C189-M189</f>
         <v>-0.014337915674726</v>
       </c>
@@ -9760,7 +9767,7 @@
         <f aca="false">Data!C190-Data!D190</f>
         <v>-0.041642</v>
       </c>
-      <c r="E190" s="5" t="n">
+      <c r="E190" s="1" t="n">
         <f aca="false">0.2*C190+0.8*B190</f>
         <v>-0.0499948930070214</v>
       </c>
@@ -9772,11 +9779,11 @@
         <f aca="false">0.5*C190+0.5*B190</f>
         <v>-0.0468625581293884</v>
       </c>
-      <c r="M190" s="8" t="n">
+      <c r="M190" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B190</f>
         <v>0.00203158137296766</v>
       </c>
-      <c r="N190" s="8" t="n">
+      <c r="N190" s="9" t="n">
         <f aca="false">C190-M190</f>
         <v>-0.0436735813729677</v>
       </c>
@@ -9793,7 +9800,7 @@
         <f aca="false">Data!C191-Data!D191</f>
         <v>0.062622</v>
       </c>
-      <c r="E191" s="5" t="n">
+      <c r="E191" s="1" t="n">
         <f aca="false">0.2*C191+0.8*B191</f>
         <v>-0.0081587935703996</v>
       </c>
@@ -9805,11 +9812,11 @@
         <f aca="false">0.5*C191+0.5*B191</f>
         <v>0.0183840040185003</v>
       </c>
-      <c r="M191" s="8" t="n">
+      <c r="M191" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B191</f>
         <v>0.00369566219300645</v>
       </c>
-      <c r="N191" s="8" t="n">
+      <c r="N191" s="9" t="n">
         <f aca="false">C191-M191</f>
         <v>0.0589263378069936</v>
       </c>
@@ -9826,7 +9833,7 @@
         <f aca="false">Data!C192-Data!D192</f>
         <v>0.015749</v>
       </c>
-      <c r="E192" s="5" t="n">
+      <c r="E192" s="1" t="n">
         <f aca="false">0.2*C192+0.8*B192</f>
         <v>0.0725861645752647</v>
       </c>
@@ -9838,11 +9845,11 @@
         <f aca="false">0.5*C192+0.5*B192</f>
         <v>0.0512722278595404</v>
       </c>
-      <c r="M192" s="8" t="n">
+      <c r="M192" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B192</f>
         <v>0.0108425948607468</v>
       </c>
-      <c r="N192" s="8" t="n">
+      <c r="N192" s="9" t="n">
         <f aca="false">C192-M192</f>
         <v>0.00490640513925318</v>
       </c>
@@ -9859,7 +9866,7 @@
         <f aca="false">Data!C193-Data!D193</f>
         <v>0.007747</v>
       </c>
-      <c r="E193" s="5" t="n">
+      <c r="E193" s="1" t="n">
         <f aca="false">0.2*C193+0.8*B193</f>
         <v>0.0343514931208391</v>
       </c>
@@ -9871,11 +9878,11 @@
         <f aca="false">0.5*C193+0.5*B193</f>
         <v>0.0243748082005244</v>
       </c>
-      <c r="M193" s="8" t="n">
+      <c r="M193" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B193</f>
         <v>0.00793731351223746</v>
       </c>
-      <c r="N193" s="8" t="n">
+      <c r="N193" s="9" t="n">
         <f aca="false">C193-M193</f>
         <v>-0.00019031351223746</v>
       </c>
@@ -9892,7 +9899,7 @@
         <f aca="false">Data!C194-Data!D194</f>
         <v>-0.016579</v>
       </c>
-      <c r="E194" s="5" t="n">
+      <c r="E194" s="1" t="n">
         <f aca="false">0.2*C194+0.8*B194</f>
         <v>0.00626813818884206</v>
       </c>
@@ -9904,11 +9911,11 @@
         <f aca="false">0.5*C194+0.5*B194</f>
         <v>-0.00229953863197372</v>
       </c>
-      <c r="M194" s="8" t="n">
+      <c r="M194" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B194</f>
         <v>0.00609599744963613</v>
       </c>
-      <c r="N194" s="8" t="n">
+      <c r="N194" s="9" t="n">
         <f aca="false">C194-M194</f>
         <v>-0.0226749974496361</v>
       </c>
@@ -9925,7 +9932,7 @@
         <f aca="false">Data!C195-Data!D195</f>
         <v>-0.006703</v>
       </c>
-      <c r="E195" s="5" t="n">
+      <c r="E195" s="1" t="n">
         <f aca="false">0.2*C195+0.8*B195</f>
         <v>0.0379288731665886</v>
       </c>
@@ -9937,11 +9944,11 @@
         <f aca="false">0.5*C195+0.5*B195</f>
         <v>0.0211919207291179</v>
       </c>
-      <c r="M195" s="8" t="n">
+      <c r="M195" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B195</f>
         <v>0.00845020916635229</v>
       </c>
-      <c r="N195" s="8" t="n">
+      <c r="N195" s="9" t="n">
         <f aca="false">C195-M195</f>
         <v>-0.0151532091663523</v>
       </c>
@@ -9958,7 +9965,7 @@
         <f aca="false">Data!C196-Data!D196</f>
         <v>0.081395</v>
       </c>
-      <c r="E196" s="5" t="n">
+      <c r="E196" s="1" t="n">
         <f aca="false">0.2*C196+0.8*B196</f>
         <v>0.0384814076048781</v>
       </c>
@@ -9970,11 +9977,11 @@
         <f aca="false">0.5*C196+0.5*B196</f>
         <v>0.0545740047530488</v>
       </c>
-      <c r="M196" s="8" t="n">
+      <c r="M196" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B196</f>
         <v>0.00709670532195596</v>
       </c>
-      <c r="N196" s="8" t="n">
+      <c r="N196" s="9" t="n">
         <f aca="false">C196-M196</f>
         <v>0.074298294678044</v>
       </c>
@@ -9991,7 +9998,7 @@
         <f aca="false">Data!C197-Data!D197</f>
         <v>0.044145</v>
       </c>
-      <c r="E197" s="5" t="n">
+      <c r="E197" s="1" t="n">
         <f aca="false">0.2*C197+0.8*B197</f>
         <v>-0.0276958429605494</v>
       </c>
@@ -10003,11 +10010,11 @@
         <f aca="false">0.5*C197+0.5*B197</f>
         <v>-0.000755526850343392</v>
       </c>
-      <c r="M197" s="8" t="n">
+      <c r="M197" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B197</f>
         <v>0.00243933999317553</v>
       </c>
-      <c r="N197" s="8" t="n">
+      <c r="N197" s="9" t="n">
         <f aca="false">C197-M197</f>
         <v>0.0417056600068245</v>
       </c>
@@ -10024,7 +10031,7 @@
         <f aca="false">Data!C198-Data!D198</f>
         <v>0.007739</v>
       </c>
-      <c r="E198" s="5" t="n">
+      <c r="E198" s="1" t="n">
         <f aca="false">0.2*C198+0.8*B198</f>
         <v>0.0375934381034298</v>
       </c>
@@ -10036,11 +10043,11 @@
         <f aca="false">0.5*C198+0.5*B198</f>
         <v>0.0263980238146436</v>
       </c>
-      <c r="M198" s="8" t="n">
+      <c r="M198" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B198</f>
         <v>0.00819454288699643</v>
       </c>
-      <c r="N198" s="8" t="n">
+      <c r="N198" s="9" t="n">
         <f aca="false">C198-M198</f>
         <v>-0.000455542886996427</v>
       </c>
@@ -10057,7 +10064,7 @@
         <f aca="false">Data!C199-Data!D199</f>
         <v>-0.01063</v>
       </c>
-      <c r="E199" s="5" t="n">
+      <c r="E199" s="1" t="n">
         <f aca="false">0.2*C199+0.8*B199</f>
         <v>0.023199921524434</v>
       </c>
@@ -10069,11 +10076,11 @@
         <f aca="false">0.5*C199+0.5*B199</f>
         <v>0.0105137009527712</v>
       </c>
-      <c r="M199" s="8" t="n">
+      <c r="M199" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B199</f>
         <v>0.00734441563178385</v>
       </c>
-      <c r="N199" s="8" t="n">
+      <c r="N199" s="9" t="n">
         <f aca="false">C199-M199</f>
         <v>-0.0179744156317838</v>
       </c>
@@ -10090,7 +10097,7 @@
         <f aca="false">Data!C200-Data!D200</f>
         <v>0.035026</v>
       </c>
-      <c r="E200" s="5" t="n">
+      <c r="E200" s="1" t="n">
         <f aca="false">0.2*C200+0.8*B200</f>
         <v>0.0130429890245112</v>
       </c>
@@ -10102,11 +10109,11 @@
         <f aca="false">0.5*C200+0.5*B200</f>
         <v>0.0212866181403195</v>
       </c>
-      <c r="M200" s="8" t="n">
+      <c r="M200" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B200</f>
         <v>0.00581477004652046</v>
       </c>
-      <c r="N200" s="8" t="n">
+      <c r="N200" s="9" t="n">
         <f aca="false">C200-M200</f>
         <v>0.0292112299534795</v>
       </c>
@@ -10123,7 +10130,7 @@
         <f aca="false">Data!C201-Data!D201</f>
         <v>0.03841</v>
       </c>
-      <c r="E201" s="5" t="n">
+      <c r="E201" s="1" t="n">
         <f aca="false">0.2*C201+0.8*B201</f>
         <v>0.0231548333856292</v>
       </c>
@@ -10135,11 +10142,11 @@
         <f aca="false">0.5*C201+0.5*B201</f>
         <v>0.0288755208660182</v>
       </c>
-      <c r="M201" s="8" t="n">
+      <c r="M201" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B201</f>
         <v>0.00656301635568524</v>
       </c>
-      <c r="N201" s="8" t="n">
+      <c r="N201" s="9" t="n">
         <f aca="false">C201-M201</f>
         <v>0.0318469836443148</v>
       </c>
@@ -10156,7 +10163,7 @@
         <f aca="false">Data!C202-Data!D202</f>
         <v>0.045918</v>
       </c>
-      <c r="E202" s="5" t="n">
+      <c r="E202" s="1" t="n">
         <f aca="false">0.2*C202+0.8*B202</f>
         <v>0.0229646164544249</v>
       </c>
@@ -10168,11 +10175,11 @@
         <f aca="false">0.5*C202+0.5*B202</f>
         <v>0.0315721352840155</v>
       </c>
-      <c r="M202" s="8" t="n">
+      <c r="M202" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B202</f>
         <v>0.00642884679313682</v>
       </c>
-      <c r="N202" s="8" t="n">
+      <c r="N202" s="9" t="n">
         <f aca="false">C202-M202</f>
         <v>0.0394891532068632</v>
       </c>
@@ -10189,7 +10196,7 @@
         <f aca="false">Data!C203-Data!D203</f>
         <v>0.044871</v>
       </c>
-      <c r="E203" s="5" t="n">
+      <c r="E203" s="1" t="n">
         <f aca="false">0.2*C203+0.8*B203</f>
         <v>-0.00147186242948482</v>
       </c>
@@ -10201,11 +10208,11 @@
         <f aca="false">0.5*C203+0.5*B203</f>
         <v>0.015906710981572</v>
       </c>
-      <c r="M203" s="8" t="n">
+      <c r="M203" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B203</f>
         <v>0.00450751800411338</v>
       </c>
-      <c r="N203" s="8" t="n">
+      <c r="N203" s="9" t="n">
         <f aca="false">C203-M203</f>
         <v>0.0403634819958866</v>
       </c>
@@ -10222,7 +10229,7 @@
         <f aca="false">Data!C204-Data!D204</f>
         <v>-0.045412</v>
       </c>
-      <c r="E204" s="5" t="n">
+      <c r="E204" s="1" t="n">
         <f aca="false">0.2*C204+0.8*B204</f>
         <v>0.0345701231055359</v>
       </c>
@@ -10234,11 +10241,11 @@
         <f aca="false">0.5*C204+0.5*B204</f>
         <v>0.00457682694095996</v>
       </c>
-      <c r="M204" s="8" t="n">
+      <c r="M204" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B204</f>
         <v>0.00879780699569769</v>
       </c>
-      <c r="N204" s="8" t="n">
+      <c r="N204" s="9" t="n">
         <f aca="false">C204-M204</f>
         <v>-0.0542098069956977</v>
       </c>
@@ -10255,7 +10262,7 @@
         <f aca="false">Data!C205-Data!D205</f>
         <v>-0.023762</v>
       </c>
-      <c r="E205" s="5" t="n">
+      <c r="E205" s="1" t="n">
         <f aca="false">0.2*C205+0.8*B205</f>
         <v>-0.0268774108537389</v>
       </c>
@@ -10267,11 +10274,11 @@
         <f aca="false">0.5*C205+0.5*B205</f>
         <v>-0.0257091317835868</v>
       </c>
-      <c r="M205" s="8" t="n">
+      <c r="M205" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B205</f>
         <v>0.00358131885560843</v>
       </c>
-      <c r="N205" s="8" t="n">
+      <c r="N205" s="9" t="n">
         <f aca="false">C205-M205</f>
         <v>-0.0273433188556084</v>
       </c>
@@ -10295,24 +10302,24 @@
   <dimension ref="A1:J1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="29.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="29.03"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="1" t="n">
@@ -10325,7 +10332,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="1" t="n">
@@ -10338,86 +10345,86 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="12" t="n">
         <f aca="false">B3/B4</f>
         <v>0.18518066825192</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <f aca="false">C3/C4</f>
         <v>0.120382598896978</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
         <f aca="false">CORREL('Excess returns'!B2:B205,'Excess returns'!C2:C205)</f>
         <v>0.0598620726348209</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="11" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10"/>
+      <c r="A9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="12" t="n">
         <f aca="false">B4^2</f>
         <v>0.00212190415816005</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="12" t="n">
         <f aca="false">B6*B4*C4</f>
         <v>0.000134622108299787</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="13" t="n">
         <f aca="false">B6*B4*C4</f>
         <v>0.000134622108299787</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="12" t="n">
         <f aca="false">C4^2</f>
         <v>0.0023834360970021</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="12" t="n">
         <f aca="false" t="array" ref="B14:C14">TRANSPOSE( MMULT( MINVERSE( B11:C12 ), TRANSPOSE( B3:C3 ) ))</f>
         <v>3.87751536012175</v>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="12" t="n">
         <v>2.24681209910872</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="1" t="n">
@@ -10430,390 +10437,390 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="13" t="n">
         <f aca="false" t="array" ref="B17:B17">MMULT(B15:C15,TRANSPOSE(B3:C3)) / SQRT( MMULT( B15:C15, MMULT( B11:C12, TRANSPOSE(B15:C15) ) ) )</f>
         <v>0.215129592204537</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="8" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7"/>
+      <c r="A23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="J24" s="9" t="s">
+      <c r="J24" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="14" t="n">
         <f aca="false">AVERAGE('Excess returns'!B2:B205)</f>
         <v>0.0085301865477073</v>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="9" t="n">
         <f aca="false">AVERAGE('Excess returns'!E2:E205)</f>
         <v>0.00799957570875407</v>
       </c>
-      <c r="H25" s="8" t="n">
+      <c r="H25" s="9" t="n">
         <f aca="false">AVERAGE('Excess returns'!G2:G205)</f>
         <v>0.00755686918280913</v>
       </c>
-      <c r="J25" s="8" t="n">
+      <c r="J25" s="9" t="n">
         <f aca="false">AVERAGE('Excess returns'!I2:I205)</f>
         <v>0.00720365945032424</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="14" t="n">
         <f aca="false">STDEV('Excess returns'!B2:B205)</f>
         <v>0.0460641309280882</v>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="F26" s="9" t="n">
         <f aca="false">STDEV('Excess returns'!E2:E205)</f>
         <v>0.0386837844549684</v>
       </c>
-      <c r="H26" s="8" t="n">
+      <c r="H26" s="9" t="n">
         <f aca="false">STDEV('Excess returns'!G2:G205)</f>
         <v>0.0351270557684335</v>
       </c>
-      <c r="J26" s="8" t="n">
+      <c r="J26" s="9" t="n">
         <f aca="false">STDEV('Excess returns'!I2:I205)</f>
         <v>0.0345491840416012</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="14" t="n">
+      <c r="B27" s="15" t="n">
         <f aca="false">C5</f>
         <v>0.120382598896978</v>
       </c>
-      <c r="D27" s="11" t="n">
+      <c r="D27" s="12" t="n">
         <f aca="false">D25/D26</f>
         <v>0.18518066825192</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="12" t="n">
         <f aca="false">F25/F26</f>
         <v>0.206794030663322</v>
       </c>
-      <c r="H27" s="11" t="n">
+      <c r="H27" s="12" t="n">
         <f aca="false">H25/H26</f>
         <v>0.215129592204537</v>
       </c>
-      <c r="J27" s="11" t="n">
+      <c r="J27" s="12" t="n">
         <f aca="false">J25/J26</f>
         <v>0.208504474133172</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="16" t="n">
         <f aca="false">CORREL('Excess returns'!B2:B205,'Excess returns'!C2:C205)</f>
         <v>0.0598620726348211</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="F28" s="13" t="n">
         <f aca="false">CORREL('Excess returns'!E2:E205,'Excess returns'!C2:C205)</f>
         <v>0.309434176510314</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="H28" s="13" t="n">
         <f aca="false">CORREL('Excess returns'!G2:G205,'Excess returns'!$C2:$C205)</f>
         <v>0.559581774238304</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="J28" s="13" t="n">
         <f aca="false">CORREL('Excess returns'!I2:I205,'Excess returns'!$C2:$C205)</f>
         <v>0.746442257783727</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="12" t="n">
         <f aca="false">D27*D28</f>
         <v>0.0110852986134611</v>
       </c>
-      <c r="F29" s="11" t="n">
+      <c r="F29" s="12" t="n">
         <f aca="false">F27*F28</f>
         <v>0.0639891405855537</v>
       </c>
-      <c r="H29" s="14" t="n">
+      <c r="H29" s="15" t="n">
         <f aca="false">H27*H28</f>
         <v>0.120382598896978</v>
       </c>
-      <c r="J29" s="11" t="n">
+      <c r="J29" s="12" t="n">
         <f aca="false">J27*J28</f>
         <v>0.155636550429974</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7" t="s">
+      <c r="E30" s="8"/>
+      <c r="F30" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G30" s="7"/>
-      <c r="H30" s="16" t="s">
+      <c r="G30" s="8"/>
+      <c r="H30" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J30" s="7" t="s">
+      <c r="J30" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="11" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="18" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="18" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17"/>
+      <c r="A37" s="18"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F38" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H38" s="9" t="s">
+      <c r="H38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="J38" s="9" t="s">
+      <c r="J38" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="D39" s="13" t="n">
         <f aca="false">D28*$C$4/D26</f>
         <v>0.0634440098446862</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="F39" s="13" t="n">
         <f aca="false">F28*$C$4/F26</f>
         <v>0.390518021725858</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="H39" s="13" t="n">
         <f aca="false">H28*$C$4/H26</f>
         <v>0.777720536212386</v>
       </c>
-      <c r="J39" s="12" t="n">
+      <c r="J39" s="13" t="n">
         <f aca="false">J28*$C$4/J26</f>
         <v>1.05477585335202</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="D40" s="12" t="n">
         <f aca="false">SLOPE('Excess returns'!C2:C205,'Excess returns'!B2:B205)</f>
         <v>0.063444009844686</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="F40" s="13" t="n">
         <f aca="false">SLOPE('Excess returns'!$C2:$C205,'Excess returns'!E2:E205)</f>
         <v>0.390518021725858</v>
       </c>
-      <c r="H40" s="12" t="n">
+      <c r="H40" s="13" t="n">
         <f aca="false">SLOPE('Excess returns'!$C2:$C205,'Excess returns'!G2:G205)</f>
         <v>0.777720536212385</v>
       </c>
-      <c r="J40" s="12" t="n">
+      <c r="J40" s="13" t="n">
         <f aca="false">SLOPE('Excess returns'!$C2:$C205,'Excess returns'!I2:I205)</f>
         <v>1.05477585335202</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="8" t="n">
+      <c r="D41" s="9" t="n">
         <f aca="false">$C$3-D39*D25</f>
         <v>0.00533594311363143</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="9" t="n">
         <f aca="false">$C$3-F39*F25</f>
         <v>0.00275315387251231</v>
       </c>
-      <c r="H41" s="8" t="n">
+      <c r="H41" s="9" t="n">
         <f aca="false">$C$3-H39*H25</f>
         <v>0</v>
       </c>
-      <c r="J41" s="8" t="n">
+      <c r="J41" s="9" t="n">
         <f aca="false">$C$3-J39*J25</f>
         <v>-0.0017211136910319</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="D42" s="8" t="n">
+      <c r="D42" s="9" t="n">
         <f aca="false">INTERCEPT('Excess returns'!C2:C205,'Excess returns'!B2:B205)</f>
         <v>0.00533594311363143</v>
       </c>
-      <c r="F42" s="8" t="n">
+      <c r="F42" s="9" t="n">
         <f aca="false">INTERCEPT('Excess returns'!$C2:$C205,'Excess returns'!E2:E205)</f>
         <v>0.00275315387251231</v>
       </c>
-      <c r="H42" s="8" t="n">
+      <c r="H42" s="9" t="n">
         <f aca="false">INTERCEPT('Excess returns'!$C2:$C205,'Excess returns'!G2:G205)</f>
         <v>6.93889390390723E-018</v>
       </c>
-      <c r="J42" s="8" t="n">
+      <c r="J42" s="9" t="n">
         <f aca="false">INTERCEPT('Excess returns'!$C2:$C205,'Excess returns'!I2:I205)</f>
         <v>-0.0017211136910319</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7" t="s">
+      <c r="E43" s="8"/>
+      <c r="F43" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="7"/>
-      <c r="H43" s="16" t="s">
+      <c r="G43" s="8"/>
+      <c r="H43" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="J43" s="7" t="s">
+      <c r="J43" s="8" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7"/>
+      <c r="A47" s="8"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9" t="s">
+      <c r="A48" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D48" s="12" t="n">
+      <c r="D48" s="13" t="n">
         <f aca="false">SQRT(C4^2 - D39^2*B4^2)</f>
         <v>0.0487328957752135</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D49" s="12" t="n">
+      <c r="D49" s="13" t="n">
         <f aca="false">STDEV('Excess returns'!N2:N205)</f>
         <v>0.0487328957752135</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D50" s="11" t="n">
+      <c r="D50" s="12" t="n">
         <f aca="false">D42/D49</f>
         <v>0.109493659852354</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="9" t="s">
+      <c r="A51" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D51" s="11" t="n">
+      <c r="D51" s="12" t="n">
         <f aca="false">SQRT(D27^2 + D50^2)</f>
         <v>0.215129592204537</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" s="18" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="8" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="8" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="8" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="17"/>
+      <c r="A56" s="18"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/Module 2/Week 8 - CAPM and investment styles/Homework 2 example.xlsx
+++ b/Module 2/Week 8 - CAPM and investment styles/Homework 2 example.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" state="visible" r:id="rId3"/>
@@ -341,7 +341,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -395,6 +395,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3709,11 +3713,11 @@
       </c>
       <c r="M6" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B6</f>
-        <v>0.00604175498978326</v>
+        <v>0.00604175498978325</v>
       </c>
       <c r="N6" s="9" t="n">
         <f aca="false">C6-M6</f>
-        <v>0.00569924501021674</v>
+        <v>0.00569924501021675</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3742,7 +3746,7 @@
       </c>
       <c r="M7" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B7</f>
-        <v>-0.000125425990441149</v>
+        <v>-0.000125425990441148</v>
       </c>
       <c r="N7" s="9" t="n">
         <f aca="false">C7-M7</f>
@@ -3775,7 +3779,7 @@
       </c>
       <c r="M8" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B8</f>
-        <v>0.00471310902071968</v>
+        <v>0.00471310902071967</v>
       </c>
       <c r="N8" s="9" t="n">
         <f aca="false">C8-M8</f>
@@ -3841,7 +3845,7 @@
       </c>
       <c r="M10" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B10</f>
-        <v>-0.000409591521786904</v>
+        <v>-0.000409591521786903</v>
       </c>
       <c r="N10" s="9" t="n">
         <f aca="false">C10-M10</f>
@@ -3907,7 +3911,7 @@
       </c>
       <c r="M12" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B12</f>
-        <v>0.000764905174787732</v>
+        <v>0.000764905174787733</v>
       </c>
       <c r="N12" s="9" t="n">
         <f aca="false">C12-M12</f>
@@ -3973,7 +3977,7 @@
       </c>
       <c r="M14" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B14</f>
-        <v>-1.32525577954245E-006</v>
+        <v>-1.32525577954158E-006</v>
       </c>
       <c r="N14" s="9" t="n">
         <f aca="false">C14-M14</f>
@@ -4043,7 +4047,7 @@
       </c>
       <c r="N16" s="9" t="n">
         <f aca="false">C16-M16</f>
-        <v>-0.0378359776344134</v>
+        <v>-0.0378359776344133</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4270,7 +4274,7 @@
       </c>
       <c r="M23" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B23</f>
-        <v>0.00415104729098054</v>
+        <v>0.00415104729098053</v>
       </c>
       <c r="N23" s="9" t="n">
         <f aca="false">C23-M23</f>
@@ -4303,7 +4307,7 @@
       </c>
       <c r="M24" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B24</f>
-        <v>0.00913077461328222</v>
+        <v>0.00913077461328221</v>
       </c>
       <c r="N24" s="9" t="n">
         <f aca="false">C24-M24</f>
@@ -4336,7 +4340,7 @@
       </c>
       <c r="M25" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B25</f>
-        <v>0.00656390121989974</v>
+        <v>0.00656390121989973</v>
       </c>
       <c r="N25" s="9" t="n">
         <f aca="false">C25-M25</f>
@@ -4435,7 +4439,7 @@
       </c>
       <c r="M28" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B28</f>
-        <v>0.00914483601974383</v>
+        <v>0.00914483601974382</v>
       </c>
       <c r="N28" s="9" t="n">
         <f aca="false">C28-M28</f>
@@ -4501,7 +4505,7 @@
       </c>
       <c r="M30" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B30</f>
-        <v>0.00025083122439464</v>
+        <v>0.000250831224394641</v>
       </c>
       <c r="N30" s="9" t="n">
         <f aca="false">C30-M30</f>
@@ -4567,7 +4571,7 @@
       </c>
       <c r="M32" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B32</f>
-        <v>0.00976820608140385</v>
+        <v>0.00976820608140384</v>
       </c>
       <c r="N32" s="9" t="n">
         <f aca="false">C32-M32</f>
@@ -4666,7 +4670,7 @@
       </c>
       <c r="M35" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B35</f>
-        <v>0.00773305539627395</v>
+        <v>0.00773305539627394</v>
       </c>
       <c r="N35" s="9" t="n">
         <f aca="false">C35-M35</f>
@@ -4732,7 +4736,7 @@
       </c>
       <c r="M37" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B37</f>
-        <v>0.00956216301365728</v>
+        <v>0.00956216301365727</v>
       </c>
       <c r="N37" s="9" t="n">
         <f aca="false">C37-M37</f>
@@ -4765,7 +4769,7 @@
       </c>
       <c r="M38" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B38</f>
-        <v>0.00682504118265209</v>
+        <v>0.00682504118265208</v>
       </c>
       <c r="N38" s="9" t="n">
         <f aca="false">C38-M38</f>
@@ -4798,7 +4802,7 @@
       </c>
       <c r="M39" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B39</f>
-        <v>0.00749702376427901</v>
+        <v>0.007497023764279</v>
       </c>
       <c r="N39" s="9" t="n">
         <f aca="false">C39-M39</f>
@@ -4864,7 +4868,7 @@
       </c>
       <c r="M41" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B41</f>
-        <v>0.007206221818519</v>
+        <v>0.00720622181851899</v>
       </c>
       <c r="N41" s="9" t="n">
         <f aca="false">C41-M41</f>
@@ -4901,7 +4905,7 @@
       </c>
       <c r="N42" s="9" t="n">
         <f aca="false">C42-M42</f>
-        <v>-0.000690253850376994</v>
+        <v>-0.00069025385037699</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4930,7 +4934,7 @@
       </c>
       <c r="M43" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B43</f>
-        <v>0.00427498209976514</v>
+        <v>0.00427498209976513</v>
       </c>
       <c r="N43" s="9" t="n">
         <f aca="false">C43-M43</f>
@@ -5161,7 +5165,7 @@
       </c>
       <c r="M50" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B50</f>
-        <v>0.0081684606516023</v>
+        <v>0.00816846065160229</v>
       </c>
       <c r="N50" s="9" t="n">
         <f aca="false">C50-M50</f>
@@ -5194,7 +5198,7 @@
       </c>
       <c r="M51" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B51</f>
-        <v>0.00806838331608506</v>
+        <v>0.00806838331608505</v>
       </c>
       <c r="N51" s="9" t="n">
         <f aca="false">C51-M51</f>
@@ -5227,7 +5231,7 @@
       </c>
       <c r="M52" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B52</f>
-        <v>0.00741782973837809</v>
+        <v>0.00741782973837808</v>
       </c>
       <c r="N52" s="9" t="n">
         <f aca="false">C52-M52</f>
@@ -5260,11 +5264,11 @@
       </c>
       <c r="M53" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B53</f>
-        <v>0.0049301908546463</v>
+        <v>0.00493019085464629</v>
       </c>
       <c r="N53" s="9" t="n">
         <f aca="false">C53-M53</f>
-        <v>-0.0038761908546463</v>
+        <v>-0.00387619085464629</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5326,11 +5330,11 @@
       </c>
       <c r="M55" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B55</f>
-        <v>0.00794282471861965</v>
+        <v>0.00794282471861964</v>
       </c>
       <c r="N55" s="9" t="n">
         <f aca="false">C55-M55</f>
-        <v>-0.00666682471861965</v>
+        <v>-0.00666682471861964</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5359,7 +5363,7 @@
       </c>
       <c r="M56" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B56</f>
-        <v>0.00620510836200149</v>
+        <v>0.00620510836200148</v>
       </c>
       <c r="N56" s="9" t="n">
         <f aca="false">C56-M56</f>
@@ -5495,7 +5499,7 @@
       </c>
       <c r="N60" s="9" t="n">
         <f aca="false">C60-M60</f>
-        <v>0.00018112261915252</v>
+        <v>0.000181122619152524</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5557,11 +5561,11 @@
       </c>
       <c r="M62" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B62</f>
-        <v>0.00861994453666458</v>
+        <v>0.00861994453666457</v>
       </c>
       <c r="N62" s="9" t="n">
         <f aca="false">C62-M62</f>
-        <v>-0.00230994453666458</v>
+        <v>-0.00230994453666457</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5623,11 +5627,11 @@
       </c>
       <c r="M64" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B64</f>
-        <v>0.00770789134434445</v>
+        <v>0.00770789134434444</v>
       </c>
       <c r="N64" s="9" t="n">
         <f aca="false">C64-M64</f>
-        <v>-0.000479891344344448</v>
+        <v>-0.000479891344344443</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5656,7 +5660,7 @@
       </c>
       <c r="M65" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B65</f>
-        <v>0.00654682387686588</v>
+        <v>0.00654682387686587</v>
       </c>
       <c r="N65" s="9" t="n">
         <f aca="false">C65-M65</f>
@@ -5693,7 +5697,7 @@
       </c>
       <c r="N66" s="9" t="n">
         <f aca="false">C66-M66</f>
-        <v>-0.0492505866215861</v>
+        <v>-0.049250586621586</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5755,7 +5759,7 @@
       </c>
       <c r="M68" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B68</f>
-        <v>0.0085539933225575</v>
+        <v>0.00855399332255749</v>
       </c>
       <c r="N68" s="9" t="n">
         <f aca="false">C68-M68</f>
@@ -5821,7 +5825,7 @@
       </c>
       <c r="M70" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B70</f>
-        <v>0.00731643083495736</v>
+        <v>0.00731643083495735</v>
       </c>
       <c r="N70" s="9" t="n">
         <f aca="false">C70-M70</f>
@@ -5854,11 +5858,11 @@
       </c>
       <c r="M71" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B71</f>
-        <v>0.00824580577648601</v>
+        <v>0.008245805776486</v>
       </c>
       <c r="N71" s="9" t="n">
         <f aca="false">C71-M71</f>
-        <v>-0.00974280577648601</v>
+        <v>-0.009742805776486</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6019,7 +6023,7 @@
       </c>
       <c r="M76" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B76</f>
-        <v>0.0058585923228102</v>
+        <v>0.00585859232281019</v>
       </c>
       <c r="N76" s="9" t="n">
         <f aca="false">C76-M76</f>
@@ -6052,11 +6056,11 @@
       </c>
       <c r="M77" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B77</f>
-        <v>0.00579533610619274</v>
+        <v>0.00579533610619273</v>
       </c>
       <c r="N77" s="9" t="n">
         <f aca="false">C77-M77</f>
-        <v>-0.00734133610619274</v>
+        <v>-0.00734133610619273</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6118,7 +6122,7 @@
       </c>
       <c r="M79" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B79</f>
-        <v>0.00663778333712882</v>
+        <v>0.00663778333712881</v>
       </c>
       <c r="N79" s="9" t="n">
         <f aca="false">C79-M79</f>
@@ -6184,7 +6188,7 @@
       </c>
       <c r="M81" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B81</f>
-        <v>0.00786559155461236</v>
+        <v>0.00786559155461235</v>
       </c>
       <c r="N81" s="9" t="n">
         <f aca="false">C81-M81</f>
@@ -6287,7 +6291,7 @@
       </c>
       <c r="N84" s="9" t="n">
         <f aca="false">C84-M84</f>
-        <v>0.00255123258795961</v>
+        <v>0.00255123258795962</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6382,7 +6386,7 @@
       </c>
       <c r="M87" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B87</f>
-        <v>0.0089773591869282</v>
+        <v>0.00897735918692819</v>
       </c>
       <c r="N87" s="9" t="n">
         <f aca="false">C87-M87</f>
@@ -6514,7 +6518,7 @@
       </c>
       <c r="M91" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B91</f>
-        <v>0.00410962308201003</v>
+        <v>0.00410962308201002</v>
       </c>
       <c r="N91" s="9" t="n">
         <f aca="false">C91-M91</f>
@@ -6712,11 +6716,11 @@
       </c>
       <c r="M97" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B97</f>
-        <v>0.00431919819372522</v>
+        <v>0.00431919819372521</v>
       </c>
       <c r="N97" s="9" t="n">
         <f aca="false">C97-M97</f>
-        <v>0.00183280180627478</v>
+        <v>0.00183280180627479</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6815,7 +6819,7 @@
       </c>
       <c r="N100" s="9" t="n">
         <f aca="false">C100-M100</f>
-        <v>-0.0102678635977107</v>
+        <v>-0.0102678635977106</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6877,7 +6881,7 @@
       </c>
       <c r="M102" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B102</f>
-        <v>0.00646074519126225</v>
+        <v>0.00646074519126224</v>
       </c>
       <c r="N102" s="9" t="n">
         <f aca="false">C102-M102</f>
@@ -6947,7 +6951,7 @@
       </c>
       <c r="N104" s="9" t="n">
         <f aca="false">C104-M104</f>
-        <v>0.00391331758850704</v>
+        <v>0.00391331758850705</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6976,7 +6980,7 @@
       </c>
       <c r="M105" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B105</f>
-        <v>0.00540540702125769</v>
+        <v>0.00540540702125768</v>
       </c>
       <c r="N105" s="9" t="n">
         <f aca="false">C105-M105</f>
@@ -7042,7 +7046,7 @@
       </c>
       <c r="M107" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B107</f>
-        <v>0.00416027785629064</v>
+        <v>0.00416027785629063</v>
       </c>
       <c r="N107" s="9" t="n">
         <f aca="false">C107-M107</f>
@@ -7075,7 +7079,7 @@
       </c>
       <c r="M108" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B108</f>
-        <v>0.00767638792385522</v>
+        <v>0.00767638792385521</v>
       </c>
       <c r="N108" s="9" t="n">
         <f aca="false">C108-M108</f>
@@ -7108,7 +7112,7 @@
       </c>
       <c r="M109" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B109</f>
-        <v>0.0065620739540474</v>
+        <v>0.00656207395404739</v>
       </c>
       <c r="N109" s="9" t="n">
         <f aca="false">C109-M109</f>
@@ -7174,7 +7178,7 @@
       </c>
       <c r="M111" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B111</f>
-        <v>0.00782469190950675</v>
+        <v>0.00782469190950674</v>
       </c>
       <c r="N111" s="9" t="n">
         <f aca="false">C111-M111</f>
@@ -7240,7 +7244,7 @@
       </c>
       <c r="M113" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B113</f>
-        <v>0.00595015416009731</v>
+        <v>0.0059501541600973</v>
       </c>
       <c r="N113" s="9" t="n">
         <f aca="false">C113-M113</f>
@@ -7273,11 +7277,11 @@
       </c>
       <c r="M114" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B114</f>
-        <v>0.00618212381456253</v>
+        <v>0.00618212381456252</v>
       </c>
       <c r="N114" s="9" t="n">
         <f aca="false">C114-M114</f>
-        <v>-0.00816512381456253</v>
+        <v>-0.00816512381456252</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7339,7 +7343,7 @@
       </c>
       <c r="M116" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B116</f>
-        <v>0.00658734962513217</v>
+        <v>0.00658734962513216</v>
       </c>
       <c r="N116" s="9" t="n">
         <f aca="false">C116-M116</f>
@@ -7405,7 +7409,7 @@
       </c>
       <c r="M118" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B118</f>
-        <v>0.00658521018071353</v>
+        <v>0.00658521018071352</v>
       </c>
       <c r="N118" s="9" t="n">
         <f aca="false">C118-M118</f>
@@ -7438,7 +7442,7 @@
       </c>
       <c r="M119" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B119</f>
-        <v>0.00674921033223331</v>
+        <v>0.0067492103322333</v>
       </c>
       <c r="N119" s="9" t="n">
         <f aca="false">C119-M119</f>
@@ -7504,11 +7508,11 @@
       </c>
       <c r="M121" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B121</f>
-        <v>0.00597798909166794</v>
+        <v>0.00597798909166793</v>
       </c>
       <c r="N121" s="9" t="n">
         <f aca="false">C121-M121</f>
-        <v>0.00431401090833206</v>
+        <v>0.00431401090833207</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7537,7 +7541,7 @@
       </c>
       <c r="M122" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B122</f>
-        <v>0.0088904985112865</v>
+        <v>0.00889049851128649</v>
       </c>
       <c r="N122" s="9" t="n">
         <f aca="false">C122-M122</f>
@@ -7570,7 +7574,7 @@
       </c>
       <c r="M123" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B123</f>
-        <v>0.00291970868486106</v>
+        <v>0.00291970868486105</v>
       </c>
       <c r="N123" s="9" t="n">
         <f aca="false">C123-M123</f>
@@ -7669,7 +7673,7 @@
       </c>
       <c r="M126" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B126</f>
-        <v>0.00676633487713664</v>
+        <v>0.00676633487713663</v>
       </c>
       <c r="N126" s="9" t="n">
         <f aca="false">C126-M126</f>
@@ -7735,7 +7739,7 @@
       </c>
       <c r="M128" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B128</f>
-        <v>0.00758776841505603</v>
+        <v>0.00758776841505602</v>
       </c>
       <c r="N128" s="9" t="n">
         <f aca="false">C128-M128</f>
@@ -7768,7 +7772,7 @@
       </c>
       <c r="M129" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B129</f>
-        <v>0.0072939866094727</v>
+        <v>0.00729398660947269</v>
       </c>
       <c r="N129" s="9" t="n">
         <f aca="false">C129-M129</f>
@@ -7834,7 +7838,7 @@
       </c>
       <c r="M131" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B131</f>
-        <v>0.000870113154157392</v>
+        <v>0.000870113154157393</v>
       </c>
       <c r="N131" s="9" t="n">
         <f aca="false">C131-M131</f>
@@ -7867,11 +7871,11 @@
       </c>
       <c r="M132" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B132</f>
-        <v>0.00650753169616236</v>
+        <v>0.00650753169616235</v>
       </c>
       <c r="N132" s="9" t="n">
         <f aca="false">C132-M132</f>
-        <v>-0.00604953169616236</v>
+        <v>-0.00604953169616235</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7900,7 +7904,7 @@
       </c>
       <c r="M133" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B133</f>
-        <v>-0.000520028923063063</v>
+        <v>-0.000520028923063062</v>
       </c>
       <c r="N133" s="9" t="n">
         <f aca="false">C133-M133</f>
@@ -7966,11 +7970,11 @@
       </c>
       <c r="M135" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B135</f>
-        <v>0.00725227709625301</v>
+        <v>0.007252277096253</v>
       </c>
       <c r="N135" s="9" t="n">
         <f aca="false">C135-M135</f>
-        <v>-0.00682127709625301</v>
+        <v>-0.006821277096253</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8032,7 +8036,7 @@
       </c>
       <c r="M137" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B137</f>
-        <v>0.00776657054942774</v>
+        <v>0.00776657054942773</v>
       </c>
       <c r="N137" s="9" t="n">
         <f aca="false">C137-M137</f>
@@ -8098,7 +8102,7 @@
       </c>
       <c r="M139" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B139</f>
-        <v>0.00968371366736451</v>
+        <v>0.0096837136673645</v>
       </c>
       <c r="N139" s="9" t="n">
         <f aca="false">C139-M139</f>
@@ -8131,11 +8135,11 @@
       </c>
       <c r="M140" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B140</f>
-        <v>0.00612003940539016</v>
+        <v>0.00612003940539015</v>
       </c>
       <c r="N140" s="9" t="n">
         <f aca="false">C140-M140</f>
-        <v>0.00425696059460984</v>
+        <v>0.00425696059460985</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8230,11 +8234,11 @@
       </c>
       <c r="M143" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B143</f>
-        <v>0.00660799539554287</v>
+        <v>0.00660799539554286</v>
       </c>
       <c r="N143" s="9" t="n">
         <f aca="false">C143-M143</f>
-        <v>0.00453000460445713</v>
+        <v>0.00453000460445714</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8263,7 +8267,7 @@
       </c>
       <c r="M144" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B144</f>
-        <v>0.00755675339422422</v>
+        <v>0.00755675339422421</v>
       </c>
       <c r="N144" s="9" t="n">
         <f aca="false">C144-M144</f>
@@ -8329,7 +8333,7 @@
       </c>
       <c r="M146" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B146</f>
-        <v>0.00522154813360532</v>
+        <v>0.00522154813360531</v>
       </c>
       <c r="N146" s="9" t="n">
         <f aca="false">C146-M146</f>
@@ -8362,7 +8366,7 @@
       </c>
       <c r="M147" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B147</f>
-        <v>3.11774311574477E-005</v>
+        <v>3.11774311574494E-005</v>
       </c>
       <c r="N147" s="9" t="n">
         <f aca="false">C147-M147</f>
@@ -8461,11 +8465,11 @@
       </c>
       <c r="M150" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B150</f>
-        <v>0.00834456819289344</v>
+        <v>0.00834456819289343</v>
       </c>
       <c r="N150" s="9" t="n">
         <f aca="false">C150-M150</f>
-        <v>-0.00326056819289344</v>
+        <v>-0.00326056819289343</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8560,7 +8564,7 @@
       </c>
       <c r="M153" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B153</f>
-        <v>0.00988290614938591</v>
+        <v>0.0098829061493859</v>
       </c>
       <c r="N153" s="9" t="n">
         <f aca="false">C153-M153</f>
@@ -8659,11 +8663,11 @@
       </c>
       <c r="M156" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B156</f>
-        <v>0.0122676057487018</v>
+        <v>0.0122676057487017</v>
       </c>
       <c r="N156" s="9" t="n">
         <f aca="false">C156-M156</f>
-        <v>-0.0677306057487018</v>
+        <v>-0.0677306057487017</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8692,7 +8696,7 @@
       </c>
       <c r="M157" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B157</f>
-        <v>0.00776517976055787</v>
+        <v>0.00776517976055786</v>
       </c>
       <c r="N157" s="9" t="n">
         <f aca="false">C157-M157</f>
@@ -8725,7 +8729,7 @@
       </c>
       <c r="M158" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B158</f>
-        <v>0.00468795755434064</v>
+        <v>0.00468795755434063</v>
       </c>
       <c r="N158" s="9" t="n">
         <f aca="false">C158-M158</f>
@@ -8758,7 +8762,7 @@
       </c>
       <c r="M159" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B159</f>
-        <v>0.00708358461375468</v>
+        <v>0.00708358461375467</v>
       </c>
       <c r="N159" s="9" t="n">
         <f aca="false">C159-M159</f>
@@ -8791,7 +8795,7 @@
       </c>
       <c r="M160" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B160</f>
-        <v>0.0081085994582589</v>
+        <v>0.00810859945825889</v>
       </c>
       <c r="N160" s="9" t="n">
         <f aca="false">C160-M160</f>
@@ -8824,7 +8828,7 @@
       </c>
       <c r="M161" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B161</f>
-        <v>0.00871288820175696</v>
+        <v>0.00871288820175695</v>
       </c>
       <c r="N161" s="9" t="n">
         <f aca="false">C161-M161</f>
@@ -8857,7 +8861,7 @@
       </c>
       <c r="M162" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B162</f>
-        <v>0.00577122240447523</v>
+        <v>0.00577122240447522</v>
       </c>
       <c r="N162" s="9" t="n">
         <f aca="false">C162-M162</f>
@@ -8890,7 +8894,7 @@
       </c>
       <c r="M163" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B163</f>
-        <v>0.00680992207405763</v>
+        <v>0.00680992207405762</v>
       </c>
       <c r="N163" s="9" t="n">
         <f aca="false">C163-M163</f>
@@ -8956,7 +8960,7 @@
       </c>
       <c r="M165" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B165</f>
-        <v>0.00725768399842873</v>
+        <v>0.00725768399842872</v>
       </c>
       <c r="N165" s="9" t="n">
         <f aca="false">C165-M165</f>
@@ -9022,7 +9026,7 @@
       </c>
       <c r="M167" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B167</f>
-        <v>0.00977273219447918</v>
+        <v>0.00977273219447917</v>
       </c>
       <c r="N167" s="9" t="n">
         <f aca="false">C167-M167</f>
@@ -9088,11 +9092,11 @@
       </c>
       <c r="M169" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B169</f>
-        <v>0.00816464673780609</v>
+        <v>0.00816464673780608</v>
       </c>
       <c r="N169" s="9" t="n">
         <f aca="false">C169-M169</f>
-        <v>0.00425235326219391</v>
+        <v>0.00425235326219392</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9187,11 +9191,11 @@
       </c>
       <c r="M172" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B172</f>
-        <v>0.00767912246018037</v>
+        <v>0.00767912246018036</v>
       </c>
       <c r="N172" s="9" t="n">
         <f aca="false">C172-M172</f>
-        <v>0.00324887753981963</v>
+        <v>0.00324887753981964</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9220,11 +9224,11 @@
       </c>
       <c r="M173" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B173</f>
-        <v>-0.000202891892177976</v>
+        <v>-0.000202891892177974</v>
       </c>
       <c r="N173" s="9" t="n">
         <f aca="false">C173-M173</f>
-        <v>-0.00429310810782202</v>
+        <v>-0.00429310810782203</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9286,7 +9290,7 @@
       </c>
       <c r="M175" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B175</f>
-        <v>5.39707216329908E-005</v>
+        <v>5.39707216329925E-005</v>
       </c>
       <c r="N175" s="9" t="n">
         <f aca="false">C175-M175</f>
@@ -9385,7 +9389,7 @@
       </c>
       <c r="M178" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B178</f>
-        <v>-0.000634224683780816</v>
+        <v>-0.000634224683780814</v>
       </c>
       <c r="N178" s="9" t="n">
         <f aca="false">C178-M178</f>
@@ -9418,7 +9422,7 @@
       </c>
       <c r="M179" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B179</f>
-        <v>0.0103170817091969</v>
+        <v>0.0103170817091968</v>
       </c>
       <c r="N179" s="9" t="n">
         <f aca="false">C179-M179</f>
@@ -9451,7 +9455,7 @@
       </c>
       <c r="M180" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B180</f>
-        <v>0.00868933645508727</v>
+        <v>0.00868933645508726</v>
       </c>
       <c r="N180" s="9" t="n">
         <f aca="false">C180-M180</f>
@@ -9517,7 +9521,7 @@
       </c>
       <c r="M182" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B182</f>
-        <v>0.00909067146772299</v>
+        <v>0.00909067146772298</v>
       </c>
       <c r="N182" s="9" t="n">
         <f aca="false">C182-M182</f>
@@ -9649,7 +9653,7 @@
       </c>
       <c r="M186" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B186</f>
-        <v>0.00537449695462076</v>
+        <v>0.00537449695462075</v>
       </c>
       <c r="N186" s="9" t="n">
         <f aca="false">C186-M186</f>
@@ -9682,11 +9686,11 @@
       </c>
       <c r="M187" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B187</f>
-        <v>0.00926645109933195</v>
+        <v>0.00926645109933194</v>
       </c>
       <c r="N187" s="9" t="n">
         <f aca="false">C187-M187</f>
-        <v>-0.041571451099332</v>
+        <v>-0.0415714510993319</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9851,7 +9855,7 @@
       </c>
       <c r="N192" s="9" t="n">
         <f aca="false">C192-M192</f>
-        <v>0.00490640513925318</v>
+        <v>0.00490640513925319</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9884,7 +9888,7 @@
       </c>
       <c r="N193" s="9" t="n">
         <f aca="false">C193-M193</f>
-        <v>-0.00019031351223746</v>
+        <v>-0.000190313512237455</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9946,7 +9950,7 @@
       </c>
       <c r="M195" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B195</f>
-        <v>0.00845020916635229</v>
+        <v>0.00845020916635228</v>
       </c>
       <c r="N195" s="9" t="n">
         <f aca="false">C195-M195</f>
@@ -9979,11 +9983,11 @@
       </c>
       <c r="M196" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B196</f>
-        <v>0.00709670532195596</v>
+        <v>0.00709670532195595</v>
       </c>
       <c r="N196" s="9" t="n">
         <f aca="false">C196-M196</f>
-        <v>0.074298294678044</v>
+        <v>0.0742982946780441</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10045,11 +10049,11 @@
       </c>
       <c r="M198" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B198</f>
-        <v>0.00819454288699643</v>
+        <v>0.00819454288699642</v>
       </c>
       <c r="N198" s="9" t="n">
         <f aca="false">C198-M198</f>
-        <v>-0.000455542886996427</v>
+        <v>-0.000455542886996421</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10078,7 +10082,7 @@
       </c>
       <c r="M199" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B199</f>
-        <v>0.00734441563178385</v>
+        <v>0.00734441563178384</v>
       </c>
       <c r="N199" s="9" t="n">
         <f aca="false">C199-M199</f>
@@ -10144,7 +10148,7 @@
       </c>
       <c r="M201" s="9" t="n">
         <f aca="false">'Optimal portfolio from homework'!D$41+'Optimal portfolio from homework'!D$39*B201</f>
-        <v>0.00656301635568524</v>
+        <v>0.00656301635568523</v>
       </c>
       <c r="N201" s="9" t="n">
         <f aca="false">C201-M201</f>
@@ -10489,7 +10493,11 @@
       <c r="A25" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="B25" s="14" t="n">
+        <f aca="false">AVERAGE('Excess returns'!C2:C205)</f>
+        <v>0.00587713235294118</v>
+      </c>
+      <c r="D25" s="15" t="n">
         <f aca="false">AVERAGE('Excess returns'!B2:B205)</f>
         <v>0.0085301865477073</v>
       </c>
@@ -10510,7 +10518,11 @@
       <c r="A26" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="B26" s="14" t="n">
+        <f aca="false">STDEV('Excess returns'!C2:C205)</f>
+        <v>0.0488204475297196</v>
+      </c>
+      <c r="D26" s="15" t="n">
         <f aca="false">STDEV('Excess returns'!B2:B205)</f>
         <v>0.0460641309280882</v>
       </c>
@@ -10531,8 +10543,8 @@
       <c r="A27" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="15" t="n">
-        <f aca="false">C5</f>
+      <c r="B27" s="16" t="n">
+        <f aca="false">B25/B26</f>
         <v>0.120382598896978</v>
       </c>
       <c r="D27" s="12" t="n">
@@ -10556,7 +10568,7 @@
       <c r="A28" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="17" t="n">
         <f aca="false">CORREL('Excess returns'!B2:B205,'Excess returns'!C2:C205)</f>
         <v>0.0598620726348211</v>
       </c>
@@ -10585,7 +10597,7 @@
         <f aca="false">F27*F28</f>
         <v>0.0639891405855537</v>
       </c>
-      <c r="H29" s="15" t="n">
+      <c r="H29" s="16" t="n">
         <f aca="false">H27*H28</f>
         <v>0.120382598896978</v>
       </c>
@@ -10603,7 +10615,7 @@
         <v>35</v>
       </c>
       <c r="G30" s="8"/>
-      <c r="H30" s="17" t="s">
+      <c r="H30" s="18" t="s">
         <v>36</v>
       </c>
       <c r="J30" s="8" t="s">
@@ -10621,22 +10633,22 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="19" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="19" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="19" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="18"/>
+      <c r="A37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D38" s="10" t="s">
@@ -10657,19 +10669,19 @@
         <v>42</v>
       </c>
       <c r="D39" s="13" t="n">
-        <f aca="false">D28*$C$4/D26</f>
+        <f aca="false">D28*$B$26/D26</f>
         <v>0.0634440098446862</v>
       </c>
       <c r="F39" s="13" t="n">
-        <f aca="false">F28*$C$4/F26</f>
+        <f aca="false">F28*$B$26/F26</f>
         <v>0.390518021725858</v>
       </c>
       <c r="H39" s="13" t="n">
-        <f aca="false">H28*$C$4/H26</f>
-        <v>0.777720536212386</v>
+        <f aca="false">H28*$B$26/H26</f>
+        <v>0.777720536212385</v>
       </c>
       <c r="J39" s="13" t="n">
-        <f aca="false">J28*$C$4/J26</f>
+        <f aca="false">J28*$B$26/J26</f>
         <v>1.05477585335202</v>
       </c>
     </row>
@@ -10699,24 +10711,24 @@
         <v>44</v>
       </c>
       <c r="D41" s="9" t="n">
-        <f aca="false">$C$3-D39*D25</f>
+        <f aca="false">$B$25-D39*D25</f>
         <v>0.00533594311363143</v>
       </c>
       <c r="F41" s="9" t="n">
-        <f aca="false">$C$3-F39*F25</f>
+        <f aca="false">$B$25-F39*F25</f>
         <v>0.00275315387251231</v>
       </c>
       <c r="H41" s="9" t="n">
-        <f aca="false">$C$3-H39*H25</f>
+        <f aca="false">$B$25-H39*H25</f>
         <v>0</v>
       </c>
       <c r="J41" s="9" t="n">
-        <f aca="false">$C$3-J39*J25</f>
-        <v>-0.0017211136910319</v>
+        <f aca="false">$B$25-J39*J25</f>
+        <v>-0.00172111369103191</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="19" t="s">
+      <c r="A42" s="20" t="s">
         <v>45</v>
       </c>
       <c r="D42" s="9" t="n">
@@ -10745,7 +10757,7 @@
         <v>47</v>
       </c>
       <c r="G43" s="8"/>
-      <c r="H43" s="17" t="s">
+      <c r="H43" s="18" t="s">
         <v>48</v>
       </c>
       <c r="J43" s="8" t="s">
@@ -10800,7 +10812,7 @@
         <f aca="false">SQRT(D27^2 + D50^2)</f>
         <v>0.215129592204537</v>
       </c>
-      <c r="E51" s="18" t="s">
+      <c r="E51" s="19" t="s">
         <v>56</v>
       </c>
     </row>
@@ -10820,7 +10832,7 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="18"/>
+      <c r="A56" s="19"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
